--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>0.11</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0.91</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -951,7 +951,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>0.09</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0.87</v>
+        <v>86.84</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1184,10 +1184,10 @@
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="H12" s="1">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="I12" s="2">
         <v>6.8</v>
@@ -1219,10 +1219,10 @@
         <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H13" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
@@ -1254,10 +1254,10 @@
         <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I14" s="2">
         <v>7</v>
@@ -1289,10 +1289,10 @@
         <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H15" s="1">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I15" s="2">
         <v>7.9</v>
@@ -1324,10 +1324,10 @@
         <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H16" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="2">
         <v>8.1</v>
@@ -1359,10 +1359,10 @@
         <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>0.31</v>
+        <v>31.43</v>
       </c>
       <c r="I17" s="2">
         <v>6.9</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0.58</v>
+        <v>57.5</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="K18" s="1">
-        <v>0.43</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0.68</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -1441,7 +1441,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="1">
-        <v>0.32</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1499,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0.78</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>0.22</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0.78</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>0.22</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1569,10 +1569,10 @@
         <v>10</v>
       </c>
       <c r="G23" s="1">
-        <v>0.74</v>
+        <v>74.36</v>
       </c>
       <c r="H23" s="1">
-        <v>0.26</v>
+        <v>25.64</v>
       </c>
       <c r="I23" s="2">
         <v>7.5</v>
@@ -1604,10 +1604,10 @@
         <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>0.77</v>
+        <v>77.14</v>
       </c>
       <c r="H24" s="1">
-        <v>0.23</v>
+        <v>22.86</v>
       </c>
       <c r="I24" s="2">
         <v>7.3</v>
@@ -1639,10 +1639,10 @@
         <v>19</v>
       </c>
       <c r="G25" s="1">
-        <v>0.42</v>
+        <v>42.42</v>
       </c>
       <c r="H25" s="1">
-        <v>0.58</v>
+        <v>57.58</v>
       </c>
       <c r="I25" s="2">
         <v>6.2</v>
@@ -1674,10 +1674,10 @@
         <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H26" s="1">
-        <v>0.38</v>
+        <v>38.1</v>
       </c>
       <c r="I26" s="2">
         <v>7.2</v>
@@ -1709,10 +1709,10 @@
         <v>12</v>
       </c>
       <c r="G27" s="1">
-        <v>0.68</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>0.32</v>
+        <v>32.43</v>
       </c>
       <c r="I27" s="2">
         <v>7.7</v>
@@ -1744,10 +1744,10 @@
         <v>11</v>
       </c>
       <c r="G28" s="1">
-        <v>0.5600000000000001</v>
+        <v>56</v>
       </c>
       <c r="H28" s="1">
-        <v>0.44</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2">
         <v>6.4</v>
@@ -1779,10 +1779,10 @@
         <v>10</v>
       </c>
       <c r="G29" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H29" s="1">
-        <v>0.31</v>
+        <v>31.25</v>
       </c>
       <c r="I29" s="2">
         <v>6.8</v>
@@ -1814,10 +1814,10 @@
         <v>18</v>
       </c>
       <c r="G30" s="1">
-        <v>0.49</v>
+        <v>48.57</v>
       </c>
       <c r="H30" s="1">
-        <v>0.51</v>
+        <v>51.43</v>
       </c>
       <c r="I30" s="2">
         <v>6.5</v>
@@ -1849,10 +1849,10 @@
         <v>7</v>
       </c>
       <c r="G31" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H31" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="I31" s="2">
         <v>7.2</v>
@@ -1884,10 +1884,10 @@
         <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H32" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
       <c r="I32" s="2">
         <v>6.2</v>
@@ -1919,10 +1919,10 @@
         <v>15</v>
       </c>
       <c r="G33" s="1">
-        <v>0.58</v>
+        <v>58.33</v>
       </c>
       <c r="H33" s="1">
-        <v>0.42</v>
+        <v>41.67</v>
       </c>
       <c r="I33" s="2">
         <v>6.8</v>
@@ -1954,10 +1954,10 @@
         <v>7</v>
       </c>
       <c r="G34" s="1">
-        <v>0.82</v>
+        <v>82.05</v>
       </c>
       <c r="H34" s="1">
-        <v>0.18</v>
+        <v>17.95</v>
       </c>
       <c r="I34" s="2">
         <v>8.4</v>
@@ -1989,10 +1989,10 @@
         <v>11</v>
       </c>
       <c r="G35" s="1">
-        <v>0.54</v>
+        <v>54.17</v>
       </c>
       <c r="H35" s="1">
-        <v>0.46</v>
+        <v>45.83</v>
       </c>
       <c r="I35" s="2">
         <v>6.8</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -2199,10 +2199,10 @@
         <v>4</v>
       </c>
       <c r="G41" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H41" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I41" s="2">
         <v>7.7</v>
@@ -2234,10 +2234,10 @@
         <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>0.84</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>0.16</v>
+        <v>15.79</v>
       </c>
       <c r="I42" s="2">
         <v>7.8</v>
@@ -2269,10 +2269,10 @@
         <v>7</v>
       </c>
       <c r="G43" s="1">
-        <v>0.78</v>
+        <v>78.13</v>
       </c>
       <c r="H43" s="1">
-        <v>0.22</v>
+        <v>21.88</v>
       </c>
       <c r="I43" s="2">
         <v>7.1</v>
@@ -2304,10 +2304,10 @@
         <v>7</v>
       </c>
       <c r="G44" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H44" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I44" s="2">
         <v>7.1</v>
@@ -2339,10 +2339,10 @@
         <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>0.92</v>
+        <v>92.31</v>
       </c>
       <c r="H45" s="1">
-        <v>0.08</v>
+        <v>7.69</v>
       </c>
       <c r="I45" s="2">
         <v>6.7</v>
@@ -2374,10 +2374,10 @@
         <v>2</v>
       </c>
       <c r="G46" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H46" s="1">
-        <v>0.09</v>
+        <v>9.09</v>
       </c>
       <c r="I46" s="2">
         <v>6.7</v>
@@ -2386,7 +2386,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2409,10 +2409,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>0.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H47" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
       <c r="I47" s="2">
         <v>8.4</v>
@@ -2421,7 +2421,7 @@
         <v>3</v>
       </c>
       <c r="K47" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2444,10 +2444,10 @@
         <v>6</v>
       </c>
       <c r="G48" s="1">
-        <v>0.61</v>
+        <v>60.53</v>
       </c>
       <c r="H48" s="1">
-        <v>0.16</v>
+        <v>15.79</v>
       </c>
       <c r="I48" s="2">
         <v>7.8</v>
@@ -2456,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="K48" s="1">
-        <v>0.24</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2479,10 +2479,10 @@
         <v>3</v>
       </c>
       <c r="G49" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H49" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
       <c r="I49" s="2">
         <v>7.6</v>
@@ -2491,7 +2491,7 @@
         <v>3</v>
       </c>
       <c r="K49" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2514,10 +2514,10 @@
         <v>3</v>
       </c>
       <c r="G50" s="1">
-        <v>0.7</v>
+        <v>69.7</v>
       </c>
       <c r="H50" s="1">
-        <v>0.09</v>
+        <v>9.09</v>
       </c>
       <c r="I50" s="2">
         <v>7.7</v>
@@ -2526,7 +2526,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2549,10 +2549,10 @@
         <v>6</v>
       </c>
       <c r="G51" s="1">
-        <v>0.73</v>
+        <v>73.08</v>
       </c>
       <c r="H51" s="1">
-        <v>0.23</v>
+        <v>23.08</v>
       </c>
       <c r="I51" s="2">
         <v>6.5</v>
@@ -2561,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="1">
-        <v>0.04</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2619,10 +2619,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H53" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I53" s="2">
         <v>8.9</v>
@@ -2631,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2654,10 +2654,10 @@
         <v>4</v>
       </c>
       <c r="G54" s="1">
-        <v>0.8100000000000001</v>
+        <v>81.25</v>
       </c>
       <c r="H54" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I54" s="2">
         <v>7.5</v>
@@ -2666,7 +2666,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1">
-        <v>0.06</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2689,10 +2689,10 @@
         <v>5</v>
       </c>
       <c r="G55" s="1">
-        <v>0.66</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H55" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
       <c r="I55" s="2">
         <v>8</v>
@@ -2701,7 +2701,7 @@
         <v>8</v>
       </c>
       <c r="K55" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2724,10 +2724,10 @@
         <v>4</v>
       </c>
       <c r="G56" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H56" s="1">
-        <v>0.11</v>
+        <v>11.11</v>
       </c>
       <c r="I56" s="2">
         <v>7.8</v>
@@ -2736,7 +2736,7 @@
         <v>5</v>
       </c>
       <c r="K56" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2759,10 +2759,10 @@
         <v>10</v>
       </c>
       <c r="G57" s="1">
-        <v>0.68</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H57" s="1">
-        <v>0.32</v>
+        <v>32.26</v>
       </c>
       <c r="I57" s="2">
         <v>7.1</v>
@@ -2794,10 +2794,10 @@
         <v>9</v>
       </c>
       <c r="G58" s="1">
-        <v>0.71</v>
+        <v>70.97</v>
       </c>
       <c r="H58" s="1">
-        <v>0.29</v>
+        <v>29.03</v>
       </c>
       <c r="I58" s="2">
         <v>7.1</v>
@@ -2829,10 +2829,10 @@
         <v>8</v>
       </c>
       <c r="G59" s="1">
-        <v>0.76</v>
+        <v>76.47</v>
       </c>
       <c r="H59" s="1">
-        <v>0.24</v>
+        <v>23.53</v>
       </c>
       <c r="I59" s="2">
         <v>7.3</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>0.74</v>
+        <v>74.19</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>8</v>
       </c>
       <c r="K61" s="1">
-        <v>0.26</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -2946,7 +2946,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>7</v>
       </c>
       <c r="K63" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>0.86</v>
+        <v>86.05</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -3016,7 +3016,7 @@
         <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>0.14</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="1">
-        <v>0.04</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0.73</v>
+        <v>72.5</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>11</v>
       </c>
       <c r="K66" s="1">
-        <v>0.28</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0.8</v>
+        <v>79.55</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>9</v>
       </c>
       <c r="K67" s="1">
-        <v>0.2</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0.91</v>
+        <v>90.7</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0.83</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>5</v>
       </c>
       <c r="K69" s="1">
-        <v>0.17</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0.76</v>
+        <v>76.19</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3249,10 +3249,10 @@
         <v>5</v>
       </c>
       <c r="G71" s="1">
-        <v>0.86</v>
+        <v>86.11</v>
       </c>
       <c r="H71" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I71" s="2">
         <v>6.7</v>
@@ -3284,10 +3284,10 @@
         <v>11</v>
       </c>
       <c r="G72" s="1">
-        <v>0.72</v>
+        <v>72.09</v>
       </c>
       <c r="H72" s="1">
-        <v>0.26</v>
+        <v>25.58</v>
       </c>
       <c r="I72" s="2">
         <v>6.3</v>
@@ -3296,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3319,10 +3319,10 @@
         <v>5</v>
       </c>
       <c r="G73" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H73" s="1">
-        <v>0.12</v>
+        <v>11.63</v>
       </c>
       <c r="I73" s="2">
         <v>6.6</v>
@@ -3354,10 +3354,10 @@
         <v>2</v>
       </c>
       <c r="G74" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H74" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I74" s="2">
         <v>6.5</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>0.79</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>6</v>
       </c>
       <c r="K75" s="1">
-        <v>0.21</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3424,10 +3424,10 @@
         <v>9</v>
       </c>
       <c r="G76" s="1">
-        <v>0.64</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H76" s="1">
-        <v>0.32</v>
+        <v>32.14</v>
       </c>
       <c r="I76" s="2">
         <v>7.8</v>
@@ -3436,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="1">
-        <v>0.04</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3459,10 +3459,10 @@
         <v>7</v>
       </c>
       <c r="G77" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H77" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
       <c r="I77" s="2">
         <v>6.8</v>
@@ -3471,7 +3471,7 @@
         <v>4</v>
       </c>
       <c r="K77" s="1">
-        <v>0.12</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3494,10 +3494,10 @@
         <v>4</v>
       </c>
       <c r="G78" s="1">
-        <v>0.77</v>
+        <v>77.42</v>
       </c>
       <c r="H78" s="1">
-        <v>0.13</v>
+        <v>12.9</v>
       </c>
       <c r="I78" s="2">
         <v>7.7</v>
@@ -3506,7 +3506,7 @@
         <v>3</v>
       </c>
       <c r="K78" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3529,10 +3529,10 @@
         <v>10</v>
       </c>
       <c r="G79" s="1">
-        <v>0.48</v>
+        <v>47.62</v>
       </c>
       <c r="H79" s="1">
-        <v>0.48</v>
+        <v>47.62</v>
       </c>
       <c r="I79" s="2">
         <v>7.2</v>
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3564,10 +3564,10 @@
         <v>6</v>
       </c>
       <c r="G80" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H80" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
       <c r="I80" s="2">
         <v>8</v>
@@ -3599,10 +3599,10 @@
         <v>6</v>
       </c>
       <c r="G81" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H81" s="1">
-        <v>0.29</v>
+        <v>28.57</v>
       </c>
       <c r="I81" s="2">
         <v>6.9</v>
@@ -3611,7 +3611,7 @@
         <v>3</v>
       </c>
       <c r="K81" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3634,10 +3634,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="1">
-        <v>0.97</v>
+        <v>96.77</v>
       </c>
       <c r="H82" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
       <c r="I82" s="2">
         <v>8.5</v>
@@ -3669,10 +3669,10 @@
         <v>5</v>
       </c>
       <c r="G83" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H83" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I83" s="2">
         <v>8</v>
@@ -3704,10 +3704,10 @@
         <v>7</v>
       </c>
       <c r="G84" s="1">
-        <v>0.6899999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="H84" s="1">
-        <v>0.27</v>
+        <v>26.92</v>
       </c>
       <c r="I84" s="2">
         <v>6.2</v>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="1">
-        <v>0.04</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -3774,10 +3774,10 @@
         <v>8</v>
       </c>
       <c r="G86" s="1">
-        <v>0.63</v>
+        <v>62.5</v>
       </c>
       <c r="H86" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I86" s="2">
         <v>6.9</v>
@@ -3786,7 +3786,7 @@
         <v>4</v>
       </c>
       <c r="K86" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3809,10 +3809,10 @@
         <v>2</v>
       </c>
       <c r="G87" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H87" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
       <c r="I87" s="2">
         <v>7.6</v>
@@ -3844,10 +3844,10 @@
         <v>6</v>
       </c>
       <c r="G88" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H88" s="1">
-        <v>0.17</v>
+        <v>16.67</v>
       </c>
       <c r="I88" s="2">
         <v>7.2</v>
@@ -3856,7 +3856,7 @@
         <v>3</v>
       </c>
       <c r="K88" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>0.65</v>
+        <v>64.52</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>11</v>
       </c>
       <c r="K89" s="1">
-        <v>0.35</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>9</v>
       </c>
       <c r="K90" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0.74</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         <v>9</v>
       </c>
       <c r="K91" s="1">
-        <v>0.26</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0.61</v>
+        <v>60.61</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>13</v>
       </c>
       <c r="K92" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4019,10 +4019,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H93" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I93" s="2">
         <v>6.9</v>
@@ -4054,10 +4054,10 @@
         <v>6</v>
       </c>
       <c r="G94" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H94" s="1">
-        <v>0.19</v>
+        <v>19.35</v>
       </c>
       <c r="I94" s="2">
         <v>6.8</v>
@@ -4089,10 +4089,10 @@
         <v>3</v>
       </c>
       <c r="G95" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H95" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I95" s="2">
         <v>7.2</v>
@@ -4124,10 +4124,10 @@
         <v>4</v>
       </c>
       <c r="G96" s="1">
-        <v>0.91</v>
+        <v>90.7</v>
       </c>
       <c r="H96" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I96" s="2">
         <v>7</v>
@@ -4159,10 +4159,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>0.98</v>
+        <v>97.67</v>
       </c>
       <c r="H97" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
       <c r="I97" s="2">
         <v>7.1</v>
@@ -4194,10 +4194,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="H98" s="1">
-        <v>0.04</v>
+        <v>4.17</v>
       </c>
       <c r="I98" s="2">
         <v>7.3</v>
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>0.68</v>
+        <v>68.42</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -4241,7 +4241,7 @@
         <v>12</v>
       </c>
       <c r="K99" s="1">
-        <v>0.32</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>6</v>
       </c>
       <c r="K100" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>0.91</v>
+        <v>91.3</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -4311,7 +4311,7 @@
         <v>2</v>
       </c>
       <c r="K101" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>0.82</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -4381,7 +4381,7 @@
         <v>6</v>
       </c>
       <c r="K103" s="1">
-        <v>0.18</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4404,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>0.7</v>
+        <v>69.7</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>10</v>
       </c>
       <c r="K104" s="1">
-        <v>0.3</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4439,10 +4439,10 @@
         <v>9</v>
       </c>
       <c r="G105" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H105" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
       <c r="I105" s="2">
         <v>6.7</v>
@@ -4474,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>0.6899999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -4486,7 +4486,7 @@
         <v>11</v>
       </c>
       <c r="K106" s="1">
-        <v>0.31</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4509,10 +4509,10 @@
         <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>0.91</v>
+        <v>91.3</v>
       </c>
       <c r="H107" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I107" s="2">
         <v>8.6</v>
@@ -4544,10 +4544,10 @@
         <v>2</v>
       </c>
       <c r="G108" s="1">
-        <v>0.87</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I108" s="2">
         <v>8.699999999999999</v>
@@ -4556,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4579,10 +4579,10 @@
         <v>10</v>
       </c>
       <c r="G109" s="1">
-        <v>0.74</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H109" s="1">
-        <v>0.26</v>
+        <v>26.32</v>
       </c>
       <c r="I109" s="2">
         <v>7</v>
@@ -4614,10 +4614,10 @@
         <v>13</v>
       </c>
       <c r="G110" s="1">
-        <v>0.61</v>
+        <v>60.61</v>
       </c>
       <c r="H110" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
       <c r="I110" s="2">
         <v>5.8</v>
@@ -4649,10 +4649,10 @@
         <v>14</v>
       </c>
       <c r="G111" s="1">
-        <v>0.58</v>
+        <v>57.58</v>
       </c>
       <c r="H111" s="1">
-        <v>0.42</v>
+        <v>42.42</v>
       </c>
       <c r="I111" s="2">
         <v>6.4</v>
@@ -4684,10 +4684,10 @@
         <v>2</v>
       </c>
       <c r="G112" s="1">
-        <v>0.55</v>
+        <v>54.55</v>
       </c>
       <c r="H112" s="1">
-        <v>0.05</v>
+        <v>4.55</v>
       </c>
       <c r="I112" s="2">
         <v>8.300000000000001</v>
@@ -4696,7 +4696,7 @@
         <v>18</v>
       </c>
       <c r="K112" s="1">
-        <v>0.41</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4719,10 +4719,10 @@
         <v>2</v>
       </c>
       <c r="G113" s="1">
-        <v>0.58</v>
+        <v>58.14</v>
       </c>
       <c r="H113" s="1">
-        <v>0.05</v>
+        <v>4.65</v>
       </c>
       <c r="I113" s="2">
         <v>8</v>
@@ -4731,7 +4731,7 @@
         <v>16</v>
       </c>
       <c r="K113" s="1">
-        <v>0.37</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -4754,10 +4754,10 @@
         <v>1</v>
       </c>
       <c r="G114" s="1">
-        <v>0.52</v>
+        <v>52.38</v>
       </c>
       <c r="H114" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
       <c r="I114" s="2">
         <v>8.300000000000001</v>
@@ -4766,7 +4766,7 @@
         <v>9</v>
       </c>
       <c r="K114" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -4789,10 +4789,10 @@
         <v>5</v>
       </c>
       <c r="G115" s="1">
-        <v>0.86</v>
+        <v>86.11</v>
       </c>
       <c r="H115" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I115" s="2">
         <v>8.1</v>
@@ -4824,10 +4824,10 @@
         <v>6</v>
       </c>
       <c r="G116" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H116" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
       <c r="I116" s="2">
         <v>7.5</v>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -4871,7 +4871,7 @@
         <v>5</v>
       </c>
       <c r="K117" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -4894,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>2</v>
       </c>
       <c r="K118" s="1">
-        <v>0.06</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -4941,7 +4941,7 @@
         <v>4</v>
       </c>
       <c r="K119" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         <v>4</v>
       </c>
       <c r="K120" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>0.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -5011,7 +5011,7 @@
         <v>4</v>
       </c>
       <c r="K121" s="1">
-        <v>0.13</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5034,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>0.89</v>
+        <v>88.89</v>
       </c>
       <c r="H122" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
       <c r="I122" s="2">
         <v>8.199999999999999</v>
@@ -5046,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="K122" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H123" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
       <c r="I123" s="2">
         <v>8.1</v>
@@ -5081,7 +5081,7 @@
         <v>4</v>
       </c>
       <c r="K123" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5104,10 +5104,10 @@
         <v>2</v>
       </c>
       <c r="G124" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H124" s="1">
-        <v>0.05</v>
+        <v>4.65</v>
       </c>
       <c r="I124" s="2">
         <v>7.6</v>
@@ -5116,7 +5116,7 @@
         <v>3</v>
       </c>
       <c r="K124" s="1">
-        <v>0.07000000000000001</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
@@ -5174,10 +5174,10 @@
         <v>1</v>
       </c>
       <c r="G126" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H126" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
       <c r="I126" s="2">
         <v>7.8</v>
@@ -5186,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="K126" s="1">
-        <v>0.16</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5209,10 +5209,10 @@
         <v>2</v>
       </c>
       <c r="G127" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H127" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I127" s="2">
         <v>7.6</v>
@@ -5221,7 +5221,7 @@
         <v>7</v>
       </c>
       <c r="K127" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5244,10 +5244,10 @@
         <v>3</v>
       </c>
       <c r="G128" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H128" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
       <c r="I128" s="2">
         <v>8.199999999999999</v>
@@ -5256,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="K128" s="1">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5279,10 +5279,10 @@
         <v>2</v>
       </c>
       <c r="G129" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H129" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I129" s="2">
         <v>7.4</v>
@@ -5291,7 +5291,7 @@
         <v>5</v>
       </c>
       <c r="K129" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5314,10 +5314,10 @@
         <v>7</v>
       </c>
       <c r="G130" s="1">
-        <v>0.79</v>
+        <v>79.41</v>
       </c>
       <c r="H130" s="1">
-        <v>0.21</v>
+        <v>20.59</v>
       </c>
       <c r="I130" s="2">
         <v>7.1</v>
@@ -5349,10 +5349,10 @@
         <v>11</v>
       </c>
       <c r="G131" s="1">
-        <v>0.65</v>
+        <v>64.52</v>
       </c>
       <c r="H131" s="1">
-        <v>0.35</v>
+        <v>35.48</v>
       </c>
       <c r="I131" s="2">
         <v>6.4</v>
@@ -5384,10 +5384,10 @@
         <v>8</v>
       </c>
       <c r="G132" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H132" s="1">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I132" s="2">
         <v>7.7</v>
@@ -5419,10 +5419,10 @@
         <v>17</v>
       </c>
       <c r="G133" s="1">
-        <v>0.6</v>
+        <v>60.47</v>
       </c>
       <c r="H133" s="1">
-        <v>0.4</v>
+        <v>39.53</v>
       </c>
       <c r="I133" s="2">
         <v>6.4</v>
@@ -5454,10 +5454,10 @@
         <v>9</v>
       </c>
       <c r="G134" s="1">
-        <v>0.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H134" s="1">
-        <v>0.21</v>
+        <v>20.93</v>
       </c>
       <c r="I134" s="2">
         <v>6.8</v>
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="G135" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H135" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I135" s="2">
         <v>7.3</v>
@@ -5524,10 +5524,10 @@
         <v>3</v>
       </c>
       <c r="G136" s="1">
-        <v>0.89</v>
+        <v>88.89</v>
       </c>
       <c r="H136" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I136" s="2">
         <v>7.8</v>
@@ -5536,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="K136" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
@@ -5571,7 +5571,7 @@
         <v>2</v>
       </c>
       <c r="K137" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -5594,10 +5594,10 @@
         <v>10</v>
       </c>
       <c r="G138" s="1">
-        <v>0.74</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H138" s="1">
-        <v>0.26</v>
+        <v>26.32</v>
       </c>
       <c r="I138" s="2">
         <v>6.7</v>
@@ -5629,10 +5629,10 @@
         <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H139" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I139" s="2">
         <v>7.4</v>
@@ -5664,10 +5664,10 @@
         <v>7</v>
       </c>
       <c r="G140" s="1">
-        <v>0.73</v>
+        <v>73.08</v>
       </c>
       <c r="H140" s="1">
-        <v>0.27</v>
+        <v>26.92</v>
       </c>
       <c r="I140" s="2">
         <v>6.3</v>
@@ -5699,10 +5699,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H141" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
       <c r="I141" s="2">
         <v>7.1</v>
@@ -5734,10 +5734,10 @@
         <v>11</v>
       </c>
       <c r="G142" s="1">
-        <v>0.66</v>
+        <v>65.63</v>
       </c>
       <c r="H142" s="1">
-        <v>0.34</v>
+        <v>34.38</v>
       </c>
       <c r="I142" s="2">
         <v>6.7</v>
@@ -5769,10 +5769,10 @@
         <v>2</v>
       </c>
       <c r="G143" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H143" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
       <c r="I143" s="2">
         <v>7.8</v>
@@ -5804,10 +5804,10 @@
         <v>9</v>
       </c>
       <c r="G144" s="1">
-        <v>0.78</v>
+        <v>77.5</v>
       </c>
       <c r="H144" s="1">
-        <v>0.23</v>
+        <v>22.5</v>
       </c>
       <c r="I144" s="2">
         <v>7.3</v>
@@ -5839,10 +5839,10 @@
         <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>0.95</v>
+        <v>95.45</v>
       </c>
       <c r="H145" s="1">
-        <v>0.05</v>
+        <v>4.55</v>
       </c>
       <c r="I145" s="2">
         <v>8.1</v>
@@ -5874,10 +5874,10 @@
         <v>3</v>
       </c>
       <c r="G146" s="1">
-        <v>0.93</v>
+        <v>93.02</v>
       </c>
       <c r="H146" s="1">
-        <v>0.07000000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="I146" s="2">
         <v>8.199999999999999</v>
@@ -5909,10 +5909,10 @@
         <v>3</v>
       </c>
       <c r="G147" s="1">
-        <v>0.86</v>
+        <v>86.36</v>
       </c>
       <c r="H147" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
       <c r="I147" s="2">
         <v>7.9</v>
@@ -5944,10 +5944,10 @@
         <v>6</v>
       </c>
       <c r="G148" s="1">
-        <v>0.84</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H148" s="1">
-        <v>0.16</v>
+        <v>15.79</v>
       </c>
       <c r="I148" s="2">
         <v>7.7</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>7</v>
       </c>
       <c r="K149" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6014,10 +6014,10 @@
         <v>8</v>
       </c>
       <c r="G150" s="1">
-        <v>0.35</v>
+        <v>34.78</v>
       </c>
       <c r="H150" s="1">
-        <v>0.35</v>
+        <v>34.78</v>
       </c>
       <c r="I150" s="2">
         <v>6.2</v>
@@ -6026,7 +6026,7 @@
         <v>7</v>
       </c>
       <c r="K150" s="1">
-        <v>0.3</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6049,10 +6049,10 @@
         <v>15</v>
       </c>
       <c r="G151" s="1">
-        <v>0.48</v>
+        <v>48.39</v>
       </c>
       <c r="H151" s="1">
-        <v>0.48</v>
+        <v>48.39</v>
       </c>
       <c r="I151" s="2">
         <v>6.2</v>
@@ -6061,7 +6061,7 @@
         <v>1</v>
       </c>
       <c r="K151" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6084,10 +6084,10 @@
         <v>6</v>
       </c>
       <c r="G152" s="1">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
       <c r="H152" s="1">
-        <v>0.16</v>
+        <v>15.79</v>
       </c>
       <c r="I152" s="2">
         <v>7</v>
@@ -6096,7 +6096,7 @@
         <v>16</v>
       </c>
       <c r="K152" s="1">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -6119,10 +6119,10 @@
         <v>10</v>
       </c>
       <c r="G153" s="1">
-        <v>0.62</v>
+        <v>62.16</v>
       </c>
       <c r="H153" s="1">
-        <v>0.27</v>
+        <v>27.03</v>
       </c>
       <c r="I153" s="2">
         <v>6.9</v>
@@ -6131,7 +6131,7 @@
         <v>4</v>
       </c>
       <c r="K153" s="1">
-        <v>0.11</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6154,10 +6154,10 @@
         <v>7</v>
       </c>
       <c r="G154" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
       <c r="H154" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
       <c r="I154" s="2">
         <v>6.4</v>
@@ -6166,7 +6166,7 @@
         <v>13</v>
       </c>
       <c r="K154" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6189,10 +6189,10 @@
         <v>13</v>
       </c>
       <c r="G155" s="1">
-        <v>0.64</v>
+        <v>63.89</v>
       </c>
       <c r="H155" s="1">
-        <v>0.36</v>
+        <v>36.11</v>
       </c>
       <c r="I155" s="2">
         <v>6.1</v>
@@ -6224,10 +6224,10 @@
         <v>5</v>
       </c>
       <c r="G156" s="1">
-        <v>0.87</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H156" s="1">
-        <v>0.13</v>
+        <v>12.82</v>
       </c>
       <c r="I156" s="2">
         <v>7.7</v>
@@ -6259,10 +6259,10 @@
         <v>3</v>
       </c>
       <c r="G157" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H157" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I157" s="2">
         <v>7.8</v>
@@ -6294,10 +6294,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="H158" s="1">
-        <v>0.36</v>
+        <v>36.36</v>
       </c>
       <c r="I158" s="2">
         <v>6.2</v>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
@@ -6399,10 +6399,10 @@
         <v>3</v>
       </c>
       <c r="G161" s="1">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="H161" s="1">
-        <v>0.12</v>
+        <v>12</v>
       </c>
       <c r="I161" s="2">
         <v>6.5</v>
@@ -6434,10 +6434,10 @@
         <v>3</v>
       </c>
       <c r="G162" s="1">
-        <v>0.86</v>
+        <v>86.36</v>
       </c>
       <c r="H162" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
       <c r="I162" s="2">
         <v>6.2</v>
@@ -6469,10 +6469,10 @@
         <v>4</v>
       </c>
       <c r="G163" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H163" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I163" s="2">
         <v>6.3</v>
@@ -6504,10 +6504,10 @@
         <v>15</v>
       </c>
       <c r="G164" s="1">
-        <v>0.58</v>
+        <v>58.33</v>
       </c>
       <c r="H164" s="1">
-        <v>0.42</v>
+        <v>41.67</v>
       </c>
       <c r="I164" s="2">
         <v>6</v>
@@ -6539,10 +6539,10 @@
         <v>10</v>
       </c>
       <c r="G165" s="1">
-        <v>0.74</v>
+        <v>74.36</v>
       </c>
       <c r="H165" s="1">
-        <v>0.26</v>
+        <v>25.64</v>
       </c>
       <c r="I165" s="2">
         <v>6.9</v>
@@ -6574,10 +6574,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H166" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="I166" s="2">
         <v>6.6</v>
@@ -6609,10 +6609,10 @@
         <v>10</v>
       </c>
       <c r="G167" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H167" s="1">
-        <v>0.31</v>
+        <v>31.25</v>
       </c>
       <c r="I167" s="2">
         <v>6.3</v>
@@ -6644,10 +6644,10 @@
         <v>9</v>
       </c>
       <c r="G168" s="1">
-        <v>0.71</v>
+        <v>70.97</v>
       </c>
       <c r="H168" s="1">
-        <v>0.29</v>
+        <v>29.03</v>
       </c>
       <c r="I168" s="2">
         <v>6.6</v>
@@ -6679,10 +6679,10 @@
         <v>7</v>
       </c>
       <c r="G169" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="H169" s="1">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="I169" s="2">
         <v>7.5</v>
@@ -6714,10 +6714,10 @@
         <v>7</v>
       </c>
       <c r="G170" s="1">
-        <v>0.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
       <c r="I170" s="2">
         <v>7.5</v>
@@ -6726,7 +6726,7 @@
         <v>2</v>
       </c>
       <c r="K170" s="1">
-        <v>0.05</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6749,10 +6749,10 @@
         <v>5</v>
       </c>
       <c r="G171" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H171" s="1">
-        <v>0.12</v>
+        <v>11.63</v>
       </c>
       <c r="I171" s="2">
         <v>7.1</v>
@@ -6784,10 +6784,10 @@
         <v>3</v>
       </c>
       <c r="G172" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H172" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I172" s="2">
         <v>7.1</v>
@@ -6819,10 +6819,10 @@
         <v>3</v>
       </c>
       <c r="G173" s="1">
-        <v>0.88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>0.12</v>
+        <v>11.54</v>
       </c>
       <c r="I173" s="2">
         <v>6.7</v>
@@ -6854,10 +6854,10 @@
         <v>9</v>
       </c>
       <c r="G174" s="1">
-        <v>0.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H174" s="1">
-        <v>0.21</v>
+        <v>20.93</v>
       </c>
       <c r="I174" s="2">
         <v>6.7</v>
@@ -6889,10 +6889,10 @@
         <v>6</v>
       </c>
       <c r="G175" s="1">
-        <v>0.79</v>
+        <v>79.31</v>
       </c>
       <c r="H175" s="1">
-        <v>0.21</v>
+        <v>20.69</v>
       </c>
       <c r="I175" s="2">
         <v>7</v>
@@ -6924,10 +6924,10 @@
         <v>10</v>
       </c>
       <c r="G176" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H176" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I176" s="2">
         <v>7.4</v>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0.58</v>
+        <v>57.58</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>14</v>
       </c>
       <c r="K177" s="1">
-        <v>0.42</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -6994,10 +6994,10 @@
         <v>2</v>
       </c>
       <c r="G178" s="1">
-        <v>0.9</v>
+        <v>90.48</v>
       </c>
       <c r="H178" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I178" s="2">
         <v>8</v>
@@ -7029,10 +7029,10 @@
         <v>7</v>
       </c>
       <c r="G179" s="1">
-        <v>0.82</v>
+        <v>81.58</v>
       </c>
       <c r="H179" s="1">
-        <v>0.18</v>
+        <v>18.42</v>
       </c>
       <c r="I179" s="2">
         <v>7.8</v>
@@ -7064,10 +7064,10 @@
         <v>17</v>
       </c>
       <c r="G180" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H180" s="1">
-        <v>0.47</v>
+        <v>47.22</v>
       </c>
       <c r="I180" s="2">
         <v>6.7</v>
@@ -7076,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7099,10 +7099,10 @@
         <v>17</v>
       </c>
       <c r="G181" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H181" s="1">
-        <v>0.47</v>
+        <v>47.22</v>
       </c>
       <c r="I181" s="2">
         <v>6.7</v>
@@ -7111,7 +7111,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7134,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="G182" s="1">
-        <v>0.87</v>
+        <v>86.84</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -7146,7 +7146,7 @@
         <v>5</v>
       </c>
       <c r="K182" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="K183" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -7216,7 +7216,7 @@
         <v>5</v>
       </c>
       <c r="K184" s="1">
-        <v>0.23</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7239,10 +7239,10 @@
         <v>10</v>
       </c>
       <c r="G185" s="1">
-        <v>0.71</v>
+        <v>70.59</v>
       </c>
       <c r="H185" s="1">
-        <v>0.29</v>
+        <v>29.41</v>
       </c>
       <c r="I185" s="2">
         <v>7.6</v>
@@ -7274,10 +7274,10 @@
         <v>10</v>
       </c>
       <c r="G186" s="1">
-        <v>0.68</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H186" s="1">
-        <v>0.32</v>
+        <v>32.26</v>
       </c>
       <c r="I186" s="2">
         <v>7.3</v>
@@ -7309,10 +7309,10 @@
         <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H187" s="1">
-        <v>0.24</v>
+        <v>24</v>
       </c>
       <c r="I187" s="2">
         <v>7</v>
@@ -7321,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="K187" s="1">
-        <v>0.04</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7344,10 +7344,10 @@
         <v>10</v>
       </c>
       <c r="G188" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>0.29</v>
+        <v>28.57</v>
       </c>
       <c r="I188" s="2">
         <v>7.1</v>
@@ -7356,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7379,10 +7379,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="H189" s="1">
-        <v>0.36</v>
+        <v>36.36</v>
       </c>
       <c r="I189" s="2">
         <v>6.6</v>
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="G190" s="1">
-        <v>0.83</v>
+        <v>82.5</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -7426,7 +7426,7 @@
         <v>7</v>
       </c>
       <c r="K190" s="1">
-        <v>0.18</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -7461,7 +7461,7 @@
         <v>10</v>
       </c>
       <c r="K191" s="1">
-        <v>0.23</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -7484,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="K192" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -7519,10 +7519,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H193" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
       <c r="I193" s="2">
         <v>6.7</v>
@@ -7531,7 +7531,7 @@
         <v>7</v>
       </c>
       <c r="K193" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -7554,10 +7554,10 @@
         <v>7</v>
       </c>
       <c r="G194" s="1">
-        <v>0.79</v>
+        <v>79.41</v>
       </c>
       <c r="H194" s="1">
-        <v>0.21</v>
+        <v>20.59</v>
       </c>
       <c r="I194" s="2">
         <v>8.1</v>
@@ -7589,10 +7589,10 @@
         <v>11</v>
       </c>
       <c r="G195" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H195" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="I195" s="2">
         <v>7.2</v>
@@ -7624,10 +7624,10 @@
         <v>4</v>
       </c>
       <c r="G196" s="1">
-        <v>0.83</v>
+        <v>82.61</v>
       </c>
       <c r="H196" s="1">
-        <v>0.17</v>
+        <v>17.39</v>
       </c>
       <c r="I196" s="2">
         <v>7.4</v>
@@ -7659,10 +7659,10 @@
         <v>7</v>
       </c>
       <c r="G197" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H197" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="I197" s="2">
         <v>8.5</v>
@@ -7694,10 +7694,10 @@
         <v>3</v>
       </c>
       <c r="G198" s="1">
-        <v>0.91</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H198" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
       <c r="I198" s="2">
         <v>8.9</v>
@@ -7729,10 +7729,10 @@
         <v>3</v>
       </c>
       <c r="G199" s="1">
-        <v>0.91</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H199" s="1">
-        <v>0.09</v>
+        <v>8.82</v>
       </c>
       <c r="I199" s="2">
         <v>8.699999999999999</v>
@@ -7764,10 +7764,10 @@
         <v>6</v>
       </c>
       <c r="G200" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H200" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I200" s="2">
         <v>7.2</v>
@@ -7799,10 +7799,10 @@
         <v>13</v>
       </c>
       <c r="G201" s="1">
-        <v>0.63</v>
+        <v>62.86</v>
       </c>
       <c r="H201" s="1">
-        <v>0.37</v>
+        <v>37.14</v>
       </c>
       <c r="I201" s="2">
         <v>6.6</v>
@@ -7834,10 +7834,10 @@
         <v>1</v>
       </c>
       <c r="G202" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H202" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I202" s="2">
         <v>9</v>
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -7933,7 +7933,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>0.11</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -7968,7 +7968,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -7991,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -8026,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0.91</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -8038,7 +8038,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>0.09</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8061,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0.87</v>
+        <v>86.84</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -8073,7 +8073,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8096,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -8131,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -8166,7 +8166,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -8201,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -8236,7 +8236,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -8271,10 +8271,10 @@
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="H12" s="1">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>
@@ -8306,10 +8306,10 @@
         <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H13" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
@@ -8341,10 +8341,10 @@
         <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I14" s="2">
         <v>6.7</v>
@@ -8376,10 +8376,10 @@
         <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H15" s="1">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I15" s="2">
         <v>7.4</v>
@@ -8411,10 +8411,10 @@
         <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H16" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="2">
         <v>7.8</v>
@@ -8446,10 +8446,10 @@
         <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>0.31</v>
+        <v>31.43</v>
       </c>
       <c r="I17" s="2">
         <v>7.4</v>
@@ -8484,13 +8484,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0.58</v>
+        <v>57.5</v>
       </c>
       <c r="J18">
         <v>17</v>
       </c>
       <c r="K18" s="1">
-        <v>0.43</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -8516,13 +8516,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0.68</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="J19">
         <v>14</v>
       </c>
       <c r="K19" s="1">
-        <v>0.32</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -8548,13 +8548,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="J20">
         <v>7</v>
       </c>
       <c r="K20" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8580,13 +8580,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0.78</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="J21">
         <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>0.22</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8612,13 +8612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>0.78</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="J22">
         <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>0.22</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -8641,10 +8641,10 @@
         <v>12</v>
       </c>
       <c r="G23" s="1">
-        <v>0.6899999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="H23" s="1">
-        <v>0.31</v>
+        <v>30.77</v>
       </c>
       <c r="I23" s="2">
         <v>7.9</v>
@@ -8676,10 +8676,10 @@
         <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
       <c r="I24" s="2">
         <v>7.6</v>
@@ -8711,10 +8711,10 @@
         <v>22</v>
       </c>
       <c r="G25" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="H25" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="I25" s="2">
         <v>5.9</v>
@@ -8746,10 +8746,10 @@
         <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H26" s="1">
-        <v>0.38</v>
+        <v>38.1</v>
       </c>
       <c r="I26" s="2">
         <v>6.3</v>
@@ -8781,10 +8781,10 @@
         <v>7</v>
       </c>
       <c r="G27" s="1">
-        <v>0.8100000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="H27" s="1">
-        <v>0.19</v>
+        <v>18.92</v>
       </c>
       <c r="I27" s="2">
         <v>8.300000000000001</v>
@@ -8816,10 +8816,10 @@
         <v>7</v>
       </c>
       <c r="G28" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H28" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I28" s="2">
         <v>7.6</v>
@@ -8851,10 +8851,10 @@
         <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H29" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I29" s="2">
         <v>8.5</v>
@@ -8886,10 +8886,10 @@
         <v>11</v>
       </c>
       <c r="G30" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>0.31</v>
+        <v>31.43</v>
       </c>
       <c r="I30" s="2">
         <v>7.9</v>
@@ -8921,10 +8921,10 @@
         <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>0.91</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
       <c r="I31" s="2">
         <v>8.699999999999999</v>
@@ -8959,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -8988,10 +8988,10 @@
         <v>16</v>
       </c>
       <c r="G33" s="1">
-        <v>0.5600000000000001</v>
+        <v>55.56</v>
       </c>
       <c r="H33" s="1">
-        <v>0.44</v>
+        <v>44.44</v>
       </c>
       <c r="I33" s="2">
         <v>6.9</v>
@@ -9023,10 +9023,10 @@
         <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H34" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I34" s="2">
         <v>8</v>
@@ -9058,10 +9058,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="1">
-        <v>0.46</v>
+        <v>45.83</v>
       </c>
       <c r="H35" s="1">
-        <v>0.54</v>
+        <v>54.17</v>
       </c>
       <c r="I35" s="2">
         <v>6.6</v>
@@ -9093,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -9128,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -9198,7 +9198,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -9233,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -9268,10 +9268,10 @@
         <v>5</v>
       </c>
       <c r="G41" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H41" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
       <c r="I41" s="2">
         <v>7.5</v>
@@ -9303,10 +9303,10 @@
         <v>7</v>
       </c>
       <c r="G42" s="1">
-        <v>0.82</v>
+        <v>81.58</v>
       </c>
       <c r="H42" s="1">
-        <v>0.18</v>
+        <v>18.42</v>
       </c>
       <c r="I42" s="2">
         <v>7.5</v>
@@ -9338,10 +9338,10 @@
         <v>7</v>
       </c>
       <c r="G43" s="1">
-        <v>0.78</v>
+        <v>78.13</v>
       </c>
       <c r="H43" s="1">
-        <v>0.22</v>
+        <v>21.88</v>
       </c>
       <c r="I43" s="2">
         <v>6.8</v>
@@ -9373,10 +9373,10 @@
         <v>8</v>
       </c>
       <c r="G44" s="1">
-        <v>0.68</v>
+        <v>68</v>
       </c>
       <c r="H44" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
       <c r="I44" s="2">
         <v>8</v>
@@ -9408,10 +9408,10 @@
         <v>3</v>
       </c>
       <c r="G45" s="1">
-        <v>0.88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H45" s="1">
-        <v>0.12</v>
+        <v>11.54</v>
       </c>
       <c r="I45" s="2">
         <v>8.5</v>
@@ -9443,10 +9443,10 @@
         <v>6</v>
       </c>
       <c r="G46" s="1">
-        <v>0.59</v>
+        <v>59.09</v>
       </c>
       <c r="H46" s="1">
-        <v>0.27</v>
+        <v>27.27</v>
       </c>
       <c r="I46" s="2">
         <v>6.4</v>
@@ -9455,7 +9455,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -9478,10 +9478,10 @@
         <v>6</v>
       </c>
       <c r="G47" s="1">
-        <v>0.71</v>
+        <v>70.97</v>
       </c>
       <c r="H47" s="1">
-        <v>0.19</v>
+        <v>19.35</v>
       </c>
       <c r="I47" s="2">
         <v>7.8</v>
@@ -9490,7 +9490,7 @@
         <v>3</v>
       </c>
       <c r="K47" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -9513,10 +9513,10 @@
         <v>13</v>
       </c>
       <c r="G48" s="1">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
       <c r="H48" s="1">
-        <v>0.34</v>
+        <v>34.21</v>
       </c>
       <c r="I48" s="2">
         <v>6.9</v>
@@ -9525,7 +9525,7 @@
         <v>9</v>
       </c>
       <c r="K48" s="1">
-        <v>0.24</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -9548,10 +9548,10 @@
         <v>6</v>
       </c>
       <c r="G49" s="1">
-        <v>0.74</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H49" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
       <c r="I49" s="2">
         <v>7.8</v>
@@ -9560,7 +9560,7 @@
         <v>3</v>
       </c>
       <c r="K49" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -9583,10 +9583,10 @@
         <v>8</v>
       </c>
       <c r="G50" s="1">
-        <v>0.55</v>
+        <v>54.55</v>
       </c>
       <c r="H50" s="1">
-        <v>0.24</v>
+        <v>24.24</v>
       </c>
       <c r="I50" s="2">
         <v>7.4</v>
@@ -9595,7 +9595,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -9618,10 +9618,10 @@
         <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.77</v>
       </c>
       <c r="H51" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I51" s="2">
         <v>6.7</v>
@@ -9630,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="1">
-        <v>0.04</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -9665,7 +9665,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -9688,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -9700,7 +9700,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -9723,10 +9723,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>0.91</v>
+        <v>90.63</v>
       </c>
       <c r="H54" s="1">
-        <v>0.03</v>
+        <v>3.13</v>
       </c>
       <c r="I54" s="2">
         <v>7.2</v>
@@ -9735,7 +9735,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1">
-        <v>0.06</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -9758,10 +9758,10 @@
         <v>7</v>
       </c>
       <c r="G55" s="1">
-        <v>0.61</v>
+        <v>60.53</v>
       </c>
       <c r="H55" s="1">
-        <v>0.18</v>
+        <v>18.42</v>
       </c>
       <c r="I55" s="2">
         <v>7.8</v>
@@ -9770,7 +9770,7 @@
         <v>8</v>
       </c>
       <c r="K55" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -9793,10 +9793,10 @@
         <v>3</v>
       </c>
       <c r="G56" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H56" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I56" s="2">
         <v>7.8</v>
@@ -9805,7 +9805,7 @@
         <v>5</v>
       </c>
       <c r="K56" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -9828,10 +9828,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="1">
-        <v>0.61</v>
+        <v>61.29</v>
       </c>
       <c r="H57" s="1">
-        <v>0.39</v>
+        <v>38.71</v>
       </c>
       <c r="I57" s="2">
         <v>8.4</v>
@@ -9863,10 +9863,10 @@
         <v>10</v>
       </c>
       <c r="G58" s="1">
-        <v>0.68</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H58" s="1">
-        <v>0.32</v>
+        <v>32.26</v>
       </c>
       <c r="I58" s="2">
         <v>8.1</v>
@@ -9898,10 +9898,10 @@
         <v>8</v>
       </c>
       <c r="G59" s="1">
-        <v>0.76</v>
+        <v>76.47</v>
       </c>
       <c r="H59" s="1">
-        <v>0.24</v>
+        <v>23.53</v>
       </c>
       <c r="I59" s="2">
         <v>8.199999999999999</v>
@@ -9933,10 +9933,10 @@
         <v>3</v>
       </c>
       <c r="G60" s="1">
-        <v>0.85</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H60" s="1">
-        <v>0.09</v>
+        <v>8.82</v>
       </c>
       <c r="I60" s="2">
         <v>8.4</v>
@@ -9945,7 +9945,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -9968,10 +9968,10 @@
         <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>0.65</v>
+        <v>64.52</v>
       </c>
       <c r="H61" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
       <c r="I61" s="2">
         <v>8.1</v>
@@ -9980,7 +9980,7 @@
         <v>8</v>
       </c>
       <c r="K61" s="1">
-        <v>0.26</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -10003,10 +10003,10 @@
         <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H62" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I62" s="2">
         <v>8.6</v>
@@ -10015,7 +10015,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -10038,10 +10038,10 @@
         <v>5</v>
       </c>
       <c r="G63" s="1">
-        <v>0.72</v>
+        <v>72.09</v>
       </c>
       <c r="H63" s="1">
-        <v>0.12</v>
+        <v>11.63</v>
       </c>
       <c r="I63" s="2">
         <v>8.699999999999999</v>
@@ -10050,7 +10050,7 @@
         <v>7</v>
       </c>
       <c r="K63" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -10073,10 +10073,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H64" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
       <c r="I64" s="2">
         <v>8</v>
@@ -10085,7 +10085,7 @@
         <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>0.14</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -10108,10 +10108,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H65" s="1">
-        <v>0.04</v>
+        <v>4.17</v>
       </c>
       <c r="I65" s="2">
         <v>8.9</v>
@@ -10120,7 +10120,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="1">
-        <v>0.04</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -10143,7 +10143,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0.73</v>
+        <v>72.5</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -10155,7 +10155,7 @@
         <v>11</v>
       </c>
       <c r="K66" s="1">
-        <v>0.28</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -10178,10 +10178,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H67" s="1">
-        <v>0.02</v>
+        <v>2.27</v>
       </c>
       <c r="I67" s="2">
         <v>7.1</v>
@@ -10190,7 +10190,7 @@
         <v>9</v>
       </c>
       <c r="K67" s="1">
-        <v>0.2</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -10213,10 +10213,10 @@
         <v>5</v>
       </c>
       <c r="G68" s="1">
-        <v>0.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H68" s="1">
-        <v>0.12</v>
+        <v>11.63</v>
       </c>
       <c r="I68" s="2">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -10248,10 +10248,10 @@
         <v>5</v>
       </c>
       <c r="G69" s="1">
-        <v>0.66</v>
+        <v>65.52</v>
       </c>
       <c r="H69" s="1">
-        <v>0.17</v>
+        <v>17.24</v>
       </c>
       <c r="I69" s="2">
         <v>7.6</v>
@@ -10260,7 +10260,7 @@
         <v>5</v>
       </c>
       <c r="K69" s="1">
-        <v>0.17</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10283,10 +10283,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="1">
-        <v>0.71</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H70" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
       <c r="I70" s="2">
         <v>7.9</v>
@@ -10295,7 +10295,7 @@
         <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -10318,10 +10318,10 @@
         <v>9</v>
       </c>
       <c r="G71" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H71" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I71" s="2">
         <v>7.3</v>
@@ -10353,10 +10353,10 @@
         <v>15</v>
       </c>
       <c r="G72" s="1">
-        <v>0.63</v>
+        <v>62.79</v>
       </c>
       <c r="H72" s="1">
-        <v>0.35</v>
+        <v>34.88</v>
       </c>
       <c r="I72" s="2">
         <v>6.9</v>
@@ -10365,7 +10365,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -10388,10 +10388,10 @@
         <v>13</v>
       </c>
       <c r="G73" s="1">
-        <v>0.7</v>
+        <v>69.77</v>
       </c>
       <c r="H73" s="1">
-        <v>0.3</v>
+        <v>30.23</v>
       </c>
       <c r="I73" s="2">
         <v>7.1</v>
@@ -10423,10 +10423,10 @@
         <v>5</v>
       </c>
       <c r="G74" s="1">
-        <v>0.79</v>
+        <v>79.17</v>
       </c>
       <c r="H74" s="1">
-        <v>0.21</v>
+        <v>20.83</v>
       </c>
       <c r="I74" s="2">
         <v>7.4</v>
@@ -10458,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>0.79</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -10470,7 +10470,7 @@
         <v>6</v>
       </c>
       <c r="K75" s="1">
-        <v>0.21</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -10493,10 +10493,10 @@
         <v>13</v>
       </c>
       <c r="G76" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H76" s="1">
-        <v>0.46</v>
+        <v>46.43</v>
       </c>
       <c r="I76" s="2">
         <v>9.199999999999999</v>
@@ -10505,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="1">
-        <v>0.04</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -10528,10 +10528,10 @@
         <v>18</v>
       </c>
       <c r="G77" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="H77" s="1">
-        <v>0.55</v>
+        <v>54.55</v>
       </c>
       <c r="I77" s="2">
         <v>7.9</v>
@@ -10540,7 +10540,7 @@
         <v>4</v>
       </c>
       <c r="K77" s="1">
-        <v>0.12</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -10563,10 +10563,10 @@
         <v>11</v>
       </c>
       <c r="G78" s="1">
-        <v>0.55</v>
+        <v>54.84</v>
       </c>
       <c r="H78" s="1">
-        <v>0.35</v>
+        <v>35.48</v>
       </c>
       <c r="I78" s="2">
         <v>8.800000000000001</v>
@@ -10575,7 +10575,7 @@
         <v>3</v>
       </c>
       <c r="K78" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -10598,10 +10598,10 @@
         <v>10</v>
       </c>
       <c r="G79" s="1">
-        <v>0.48</v>
+        <v>47.62</v>
       </c>
       <c r="H79" s="1">
-        <v>0.48</v>
+        <v>47.62</v>
       </c>
       <c r="I79" s="2">
         <v>9.199999999999999</v>
@@ -10610,7 +10610,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -10636,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -10665,10 +10665,10 @@
         <v>8</v>
       </c>
       <c r="G81" s="1">
-        <v>0.48</v>
+        <v>47.62</v>
       </c>
       <c r="H81" s="1">
-        <v>0.38</v>
+        <v>38.1</v>
       </c>
       <c r="I81" s="2">
         <v>8.1</v>
@@ -10677,7 +10677,7 @@
         <v>3</v>
       </c>
       <c r="K81" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -10703,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -10767,13 +10767,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>0.96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="J84">
         <v>1</v>
       </c>
       <c r="K84" s="1">
-        <v>0.04</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -10799,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -10831,13 +10831,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="J86">
         <v>4</v>
       </c>
       <c r="K86" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -10863,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -10895,13 +10895,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="J88">
         <v>3</v>
       </c>
       <c r="K88" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -10924,10 +10924,10 @@
         <v>7</v>
       </c>
       <c r="G89" s="1">
-        <v>0.42</v>
+        <v>41.94</v>
       </c>
       <c r="H89" s="1">
-        <v>0.23</v>
+        <v>22.58</v>
       </c>
       <c r="I89" s="2">
         <v>9.199999999999999</v>
@@ -10936,7 +10936,7 @@
         <v>11</v>
       </c>
       <c r="K89" s="1">
-        <v>0.35</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -10959,10 +10959,10 @@
         <v>3</v>
       </c>
       <c r="G90" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
       <c r="H90" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I90" s="2">
         <v>9.1</v>
@@ -10971,7 +10971,7 @@
         <v>9</v>
       </c>
       <c r="K90" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -10994,10 +10994,10 @@
         <v>3</v>
       </c>
       <c r="G91" s="1">
-        <v>0.66</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="H91" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
       <c r="I91" s="2">
         <v>8.9</v>
@@ -11006,7 +11006,7 @@
         <v>9</v>
       </c>
       <c r="K91" s="1">
-        <v>0.26</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -11029,10 +11029,10 @@
         <v>4</v>
       </c>
       <c r="G92" s="1">
-        <v>0.48</v>
+        <v>48.48</v>
       </c>
       <c r="H92" s="1">
-        <v>0.12</v>
+        <v>12.12</v>
       </c>
       <c r="I92" s="2">
         <v>8.300000000000001</v>
@@ -11041,7 +11041,7 @@
         <v>13</v>
       </c>
       <c r="K92" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -11064,10 +11064,10 @@
         <v>6</v>
       </c>
       <c r="G93" s="1">
-        <v>0.82</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H93" s="1">
-        <v>0.18</v>
+        <v>17.65</v>
       </c>
       <c r="I93" s="2">
         <v>7.4</v>
@@ -11099,10 +11099,10 @@
         <v>11</v>
       </c>
       <c r="G94" s="1">
-        <v>0.65</v>
+        <v>64.52</v>
       </c>
       <c r="H94" s="1">
-        <v>0.35</v>
+        <v>35.48</v>
       </c>
       <c r="I94" s="2">
         <v>7.6</v>
@@ -11134,10 +11134,10 @@
         <v>7</v>
       </c>
       <c r="G95" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="H95" s="1">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="I95" s="2">
         <v>8.1</v>
@@ -11169,10 +11169,10 @@
         <v>8</v>
       </c>
       <c r="G96" s="1">
-        <v>0.8100000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H96" s="1">
-        <v>0.19</v>
+        <v>18.6</v>
       </c>
       <c r="I96" s="2">
         <v>7.8</v>
@@ -11204,10 +11204,10 @@
         <v>7</v>
       </c>
       <c r="G97" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H97" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
       <c r="I97" s="2">
         <v>7.4</v>
@@ -11239,10 +11239,10 @@
         <v>4</v>
       </c>
       <c r="G98" s="1">
-        <v>0.83</v>
+        <v>83.33</v>
       </c>
       <c r="H98" s="1">
-        <v>0.17</v>
+        <v>16.67</v>
       </c>
       <c r="I98" s="2">
         <v>8.1</v>
@@ -11277,13 +11277,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>0.68</v>
+        <v>68.42</v>
       </c>
       <c r="J99">
         <v>12</v>
       </c>
       <c r="K99" s="1">
-        <v>0.32</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -11309,13 +11309,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="J100">
         <v>6</v>
       </c>
       <c r="K100" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -11341,13 +11341,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>0.91</v>
+        <v>91.3</v>
       </c>
       <c r="J101">
         <v>2</v>
       </c>
       <c r="K101" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -11373,13 +11373,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="J102">
         <v>16</v>
       </c>
       <c r="K102" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -11405,13 +11405,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>0.82</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="J103">
         <v>6</v>
       </c>
       <c r="K103" s="1">
-        <v>0.18</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -11437,13 +11437,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>0.7</v>
+        <v>69.7</v>
       </c>
       <c r="J104">
         <v>10</v>
       </c>
       <c r="K104" s="1">
-        <v>0.3</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -11466,10 +11466,10 @@
         <v>5</v>
       </c>
       <c r="G105" s="1">
-        <v>0.76</v>
+        <v>76.19</v>
       </c>
       <c r="H105" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
       <c r="I105" s="2">
         <v>8.300000000000001</v>
@@ -11504,13 +11504,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="1">
-        <v>0.6899999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="J106">
         <v>11</v>
       </c>
       <c r="K106" s="1">
-        <v>0.31</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11536,7 +11536,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -11568,13 +11568,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J108">
         <v>1</v>
       </c>
       <c r="K108" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -11597,10 +11597,10 @@
         <v>8</v>
       </c>
       <c r="G109" s="1">
-        <v>0.79</v>
+        <v>78.95</v>
       </c>
       <c r="H109" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
       <c r="I109" s="2">
         <v>8.1</v>
@@ -11632,10 +11632,10 @@
         <v>8</v>
       </c>
       <c r="G110" s="1">
-        <v>0.76</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H110" s="1">
-        <v>0.24</v>
+        <v>24.24</v>
       </c>
       <c r="I110" s="2">
         <v>8.1</v>
@@ -11667,10 +11667,10 @@
         <v>10</v>
       </c>
       <c r="G111" s="1">
-        <v>0.7</v>
+        <v>69.7</v>
       </c>
       <c r="H111" s="1">
-        <v>0.3</v>
+        <v>30.3</v>
       </c>
       <c r="I111" s="2">
         <v>7.7</v>
@@ -11702,10 +11702,10 @@
         <v>11</v>
       </c>
       <c r="G112" s="1">
-        <v>0.34</v>
+        <v>34.09</v>
       </c>
       <c r="H112" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I112" s="2">
         <v>8.9</v>
@@ -11714,7 +11714,7 @@
         <v>18</v>
       </c>
       <c r="K112" s="1">
-        <v>0.41</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -11737,10 +11737,10 @@
         <v>11</v>
       </c>
       <c r="G113" s="1">
-        <v>0.37</v>
+        <v>37.21</v>
       </c>
       <c r="H113" s="1">
-        <v>0.26</v>
+        <v>25.58</v>
       </c>
       <c r="I113" s="2">
         <v>9.1</v>
@@ -11749,7 +11749,7 @@
         <v>16</v>
       </c>
       <c r="K113" s="1">
-        <v>0.37</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -11772,10 +11772,10 @@
         <v>2</v>
       </c>
       <c r="G114" s="1">
-        <v>0.48</v>
+        <v>47.62</v>
       </c>
       <c r="H114" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I114" s="2">
         <v>9.5</v>
@@ -11784,7 +11784,7 @@
         <v>9</v>
       </c>
       <c r="K114" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -11807,10 +11807,10 @@
         <v>5</v>
       </c>
       <c r="G115" s="1">
-        <v>0.86</v>
+        <v>86.11</v>
       </c>
       <c r="H115" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I115" s="2">
         <v>7.9</v>
@@ -11842,10 +11842,10 @@
         <v>8</v>
       </c>
       <c r="G116" s="1">
-        <v>0.77</v>
+        <v>77.14</v>
       </c>
       <c r="H116" s="1">
-        <v>0.23</v>
+        <v>22.86</v>
       </c>
       <c r="I116" s="2">
         <v>7.8</v>
@@ -11877,10 +11877,10 @@
         <v>3</v>
       </c>
       <c r="G117" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H117" s="1">
-        <v>0.09</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I117" s="2">
         <v>8.5</v>
@@ -11889,7 +11889,7 @@
         <v>5</v>
       </c>
       <c r="K117" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -11912,10 +11912,10 @@
         <v>4</v>
       </c>
       <c r="G118" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H118" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
       <c r="I118" s="2">
         <v>8.1</v>
@@ -11924,7 +11924,7 @@
         <v>2</v>
       </c>
       <c r="K118" s="1">
-        <v>0.06</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -11947,10 +11947,10 @@
         <v>9</v>
       </c>
       <c r="G119" s="1">
-        <v>0.63</v>
+        <v>62.86</v>
       </c>
       <c r="H119" s="1">
-        <v>0.26</v>
+        <v>25.71</v>
       </c>
       <c r="I119" s="2">
         <v>9.199999999999999</v>
@@ -11959,7 +11959,7 @@
         <v>4</v>
       </c>
       <c r="K119" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -11982,10 +11982,10 @@
         <v>5</v>
       </c>
       <c r="G120" s="1">
-        <v>0.74</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H120" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I120" s="2">
         <v>9.199999999999999</v>
@@ -11994,7 +11994,7 @@
         <v>4</v>
       </c>
       <c r="K120" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -12017,10 +12017,10 @@
         <v>2</v>
       </c>
       <c r="G121" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H121" s="1">
-        <v>0.06</v>
+        <v>6.45</v>
       </c>
       <c r="I121" s="2">
         <v>6.8</v>
@@ -12029,7 +12029,7 @@
         <v>4</v>
       </c>
       <c r="K121" s="1">
-        <v>0.13</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -12052,10 +12052,10 @@
         <v>5</v>
       </c>
       <c r="G122" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H122" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I122" s="2">
         <v>8.4</v>
@@ -12064,7 +12064,7 @@
         <v>3</v>
       </c>
       <c r="K122" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -12087,10 +12087,10 @@
         <v>4</v>
       </c>
       <c r="G123" s="1">
-        <v>0.8100000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H123" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I123" s="2">
         <v>7.7</v>
@@ -12099,7 +12099,7 @@
         <v>4</v>
       </c>
       <c r="K123" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -12122,10 +12122,10 @@
         <v>6</v>
       </c>
       <c r="G124" s="1">
-        <v>0.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H124" s="1">
-        <v>0.14</v>
+        <v>13.95</v>
       </c>
       <c r="I124" s="2">
         <v>7.6</v>
@@ -12134,7 +12134,7 @@
         <v>3</v>
       </c>
       <c r="K124" s="1">
-        <v>0.07000000000000001</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -12157,7 +12157,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
@@ -12192,10 +12192,10 @@
         <v>2</v>
       </c>
       <c r="G126" s="1">
-        <v>0.77</v>
+        <v>77.42</v>
       </c>
       <c r="H126" s="1">
-        <v>0.06</v>
+        <v>6.45</v>
       </c>
       <c r="I126" s="2">
         <v>8.5</v>
@@ -12204,7 +12204,7 @@
         <v>5</v>
       </c>
       <c r="K126" s="1">
-        <v>0.16</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -12227,10 +12227,10 @@
         <v>2</v>
       </c>
       <c r="G127" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H127" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I127" s="2">
         <v>8.6</v>
@@ -12239,7 +12239,7 @@
         <v>7</v>
       </c>
       <c r="K127" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -12262,10 +12262,10 @@
         <v>7</v>
       </c>
       <c r="G128" s="1">
-        <v>0.77</v>
+        <v>77.14</v>
       </c>
       <c r="H128" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="I128" s="2">
         <v>8.6</v>
@@ -12274,7 +12274,7 @@
         <v>1</v>
       </c>
       <c r="K128" s="1">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -12297,10 +12297,10 @@
         <v>4</v>
       </c>
       <c r="G129" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H129" s="1">
-        <v>0.19</v>
+        <v>19.05</v>
       </c>
       <c r="I129" s="2">
         <v>7.8</v>
@@ -12309,7 +12309,7 @@
         <v>5</v>
       </c>
       <c r="K129" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -12332,10 +12332,10 @@
         <v>7</v>
       </c>
       <c r="G130" s="1">
-        <v>0.79</v>
+        <v>79.41</v>
       </c>
       <c r="H130" s="1">
-        <v>0.21</v>
+        <v>20.59</v>
       </c>
       <c r="I130" s="2">
         <v>7.5</v>
@@ -12367,10 +12367,10 @@
         <v>13</v>
       </c>
       <c r="G131" s="1">
-        <v>0.58</v>
+        <v>58.06</v>
       </c>
       <c r="H131" s="1">
-        <v>0.42</v>
+        <v>41.94</v>
       </c>
       <c r="I131" s="2">
         <v>6.7</v>
@@ -12402,10 +12402,10 @@
         <v>10</v>
       </c>
       <c r="G132" s="1">
-        <v>0.72</v>
+        <v>72.22</v>
       </c>
       <c r="H132" s="1">
-        <v>0.28</v>
+        <v>27.78</v>
       </c>
       <c r="I132" s="2">
         <v>7.5</v>
@@ -12437,10 +12437,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="1">
-        <v>0.72</v>
+        <v>72.09</v>
       </c>
       <c r="H133" s="1">
-        <v>0.28</v>
+        <v>27.91</v>
       </c>
       <c r="I133" s="2">
         <v>7.3</v>
@@ -12472,10 +12472,10 @@
         <v>10</v>
       </c>
       <c r="G134" s="1">
-        <v>0.77</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H134" s="1">
-        <v>0.23</v>
+        <v>23.26</v>
       </c>
       <c r="I134" s="2">
         <v>7</v>
@@ -12507,10 +12507,10 @@
         <v>4</v>
       </c>
       <c r="G135" s="1">
-        <v>0.83</v>
+        <v>83.33</v>
       </c>
       <c r="H135" s="1">
-        <v>0.17</v>
+        <v>16.67</v>
       </c>
       <c r="I135" s="2">
         <v>7.3</v>
@@ -12542,10 +12542,10 @@
         <v>8</v>
       </c>
       <c r="G136" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H136" s="1">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I136" s="2">
         <v>6.9</v>
@@ -12554,7 +12554,7 @@
         <v>1</v>
       </c>
       <c r="K136" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -12577,10 +12577,10 @@
         <v>3</v>
       </c>
       <c r="G137" s="1">
-        <v>0.85</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H137" s="1">
-        <v>0.09</v>
+        <v>8.82</v>
       </c>
       <c r="I137" s="2">
         <v>7.3</v>
@@ -12589,7 +12589,7 @@
         <v>2</v>
       </c>
       <c r="K137" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -12612,10 +12612,10 @@
         <v>10</v>
       </c>
       <c r="G138" s="1">
-        <v>0.74</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H138" s="1">
-        <v>0.26</v>
+        <v>26.32</v>
       </c>
       <c r="I138" s="2">
         <v>7.2</v>
@@ -12647,10 +12647,10 @@
         <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H139" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I139" s="2">
         <v>7.9</v>
@@ -12682,10 +12682,10 @@
         <v>7</v>
       </c>
       <c r="G140" s="1">
-        <v>0.73</v>
+        <v>73.08</v>
       </c>
       <c r="H140" s="1">
-        <v>0.27</v>
+        <v>26.92</v>
       </c>
       <c r="I140" s="2">
         <v>6.8</v>
@@ -12717,10 +12717,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H141" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
       <c r="I141" s="2">
         <v>7.5</v>
@@ -12752,10 +12752,10 @@
         <v>10</v>
       </c>
       <c r="G142" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H142" s="1">
-        <v>0.31</v>
+        <v>31.25</v>
       </c>
       <c r="I142" s="2">
         <v>7.3</v>
@@ -12787,10 +12787,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H143" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I143" s="2">
         <v>8</v>
@@ -12822,10 +12822,10 @@
         <v>9</v>
       </c>
       <c r="G144" s="1">
-        <v>0.78</v>
+        <v>77.5</v>
       </c>
       <c r="H144" s="1">
-        <v>0.23</v>
+        <v>22.5</v>
       </c>
       <c r="I144" s="2">
         <v>7.4</v>
@@ -12857,10 +12857,10 @@
         <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>0.95</v>
+        <v>95.45</v>
       </c>
       <c r="H145" s="1">
-        <v>0.05</v>
+        <v>4.55</v>
       </c>
       <c r="I145" s="2">
         <v>7.8</v>
@@ -12892,10 +12892,10 @@
         <v>3</v>
       </c>
       <c r="G146" s="1">
-        <v>0.93</v>
+        <v>93.02</v>
       </c>
       <c r="H146" s="1">
-        <v>0.07000000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="I146" s="2">
         <v>8.699999999999999</v>
@@ -12927,10 +12927,10 @@
         <v>4</v>
       </c>
       <c r="G147" s="1">
-        <v>0.82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H147" s="1">
-        <v>0.18</v>
+        <v>18.18</v>
       </c>
       <c r="I147" s="2">
         <v>8</v>
@@ -12962,10 +12962,10 @@
         <v>8</v>
       </c>
       <c r="G148" s="1">
-        <v>0.79</v>
+        <v>78.95</v>
       </c>
       <c r="H148" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
       <c r="I148" s="2">
         <v>7.6</v>
@@ -13000,13 +13000,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="J149">
         <v>7</v>
       </c>
       <c r="K149" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -13032,13 +13032,13 @@
         <v>0</v>
       </c>
       <c r="H150" s="1">
-        <v>0.7</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="J150">
         <v>7</v>
       </c>
       <c r="K150" s="1">
-        <v>0.3</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -13064,13 +13064,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="1">
-        <v>0.97</v>
+        <v>96.77</v>
       </c>
       <c r="J151">
         <v>1</v>
       </c>
       <c r="K151" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -13096,13 +13096,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="1">
-        <v>0.58</v>
+        <v>57.89</v>
       </c>
       <c r="J152">
         <v>16</v>
       </c>
       <c r="K152" s="1">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -13128,13 +13128,13 @@
         <v>0</v>
       </c>
       <c r="H153" s="1">
-        <v>0.89</v>
+        <v>89.19</v>
       </c>
       <c r="J153">
         <v>4</v>
       </c>
       <c r="K153" s="1">
-        <v>0.11</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -13160,13 +13160,13 @@
         <v>0</v>
       </c>
       <c r="H154" s="1">
-        <v>0.61</v>
+        <v>60.61</v>
       </c>
       <c r="J154">
         <v>13</v>
       </c>
       <c r="K154" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -13189,10 +13189,10 @@
         <v>22</v>
       </c>
       <c r="G155" s="1">
-        <v>0.39</v>
+        <v>38.89</v>
       </c>
       <c r="H155" s="1">
-        <v>0.61</v>
+        <v>61.11</v>
       </c>
       <c r="I155" s="2">
         <v>7.9</v>
@@ -13224,10 +13224,10 @@
         <v>14</v>
       </c>
       <c r="G156" s="1">
-        <v>0.64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H156" s="1">
-        <v>0.36</v>
+        <v>35.9</v>
       </c>
       <c r="I156" s="2">
         <v>8.300000000000001</v>
@@ -13259,10 +13259,10 @@
         <v>14</v>
       </c>
       <c r="G157" s="1">
-        <v>0.61</v>
+        <v>61.11</v>
       </c>
       <c r="H157" s="1">
-        <v>0.39</v>
+        <v>38.89</v>
       </c>
       <c r="I157" s="2">
         <v>8.5</v>
@@ -13294,10 +13294,10 @@
         <v>22</v>
       </c>
       <c r="G158" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="H158" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="I158" s="2">
         <v>8.1</v>
@@ -13329,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -13364,7 +13364,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
@@ -13399,10 +13399,10 @@
         <v>5</v>
       </c>
       <c r="G161" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H161" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="I161" s="2">
         <v>7.7</v>
@@ -13434,10 +13434,10 @@
         <v>6</v>
       </c>
       <c r="G162" s="1">
-        <v>0.73</v>
+        <v>72.73</v>
       </c>
       <c r="H162" s="1">
-        <v>0.27</v>
+        <v>27.27</v>
       </c>
       <c r="I162" s="2">
         <v>7.2</v>
@@ -13469,10 +13469,10 @@
         <v>4</v>
       </c>
       <c r="G163" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H163" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I163" s="2">
         <v>7</v>
@@ -13504,10 +13504,10 @@
         <v>24</v>
       </c>
       <c r="G164" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="H164" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="I164" s="2">
         <v>6.7</v>
@@ -13539,10 +13539,10 @@
         <v>16</v>
       </c>
       <c r="G165" s="1">
-        <v>0.59</v>
+        <v>58.97</v>
       </c>
       <c r="H165" s="1">
-        <v>0.41</v>
+        <v>41.03</v>
       </c>
       <c r="I165" s="2">
         <v>6.8</v>
@@ -13574,10 +13574,10 @@
         <v>22</v>
       </c>
       <c r="G166" s="1">
-        <v>0.39</v>
+        <v>38.89</v>
       </c>
       <c r="H166" s="1">
-        <v>0.61</v>
+        <v>61.11</v>
       </c>
       <c r="I166" s="2">
         <v>7.4</v>
@@ -13609,10 +13609,10 @@
         <v>11</v>
       </c>
       <c r="G167" s="1">
-        <v>0.66</v>
+        <v>65.63</v>
       </c>
       <c r="H167" s="1">
-        <v>0.34</v>
+        <v>34.38</v>
       </c>
       <c r="I167" s="2">
         <v>6.7</v>
@@ -13647,7 +13647,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -13679,7 +13679,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -13711,13 +13711,13 @@
         <v>0</v>
       </c>
       <c r="H170" s="1">
-        <v>0.95</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="J170">
         <v>2</v>
       </c>
       <c r="K170" s="1">
-        <v>0.05</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -13743,7 +13743,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -13775,7 +13775,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -13807,7 +13807,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -13836,10 +13836,10 @@
         <v>19</v>
       </c>
       <c r="G174" s="1">
-        <v>0.5600000000000001</v>
+        <v>55.81</v>
       </c>
       <c r="H174" s="1">
-        <v>0.44</v>
+        <v>44.19</v>
       </c>
       <c r="I174" s="2">
         <v>7</v>
@@ -13871,10 +13871,10 @@
         <v>11</v>
       </c>
       <c r="G175" s="1">
-        <v>0.62</v>
+        <v>62.07</v>
       </c>
       <c r="H175" s="1">
-        <v>0.38</v>
+        <v>37.93</v>
       </c>
       <c r="I175" s="2">
         <v>7.5</v>
@@ -13906,10 +13906,10 @@
         <v>10</v>
       </c>
       <c r="G176" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H176" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I176" s="2">
         <v>7.6</v>
@@ -13944,13 +13944,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="1">
-        <v>0.58</v>
+        <v>57.58</v>
       </c>
       <c r="J177">
         <v>14</v>
       </c>
       <c r="K177" s="1">
-        <v>0.42</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -13973,10 +13973,10 @@
         <v>2</v>
       </c>
       <c r="G178" s="1">
-        <v>0.9</v>
+        <v>90.48</v>
       </c>
       <c r="H178" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I178" s="2">
         <v>7.8</v>
@@ -14008,10 +14008,10 @@
         <v>7</v>
       </c>
       <c r="G179" s="1">
-        <v>0.82</v>
+        <v>81.58</v>
       </c>
       <c r="H179" s="1">
-        <v>0.18</v>
+        <v>18.42</v>
       </c>
       <c r="I179" s="2">
         <v>8.199999999999999</v>
@@ -14046,13 +14046,13 @@
         <v>0</v>
       </c>
       <c r="H180" s="1">
-        <v>0.97</v>
+        <v>97.22</v>
       </c>
       <c r="J180">
         <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -14078,13 +14078,13 @@
         <v>0</v>
       </c>
       <c r="H181" s="1">
-        <v>0.97</v>
+        <v>97.22</v>
       </c>
       <c r="J181">
         <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -14107,10 +14107,10 @@
         <v>1</v>
       </c>
       <c r="G182" s="1">
-        <v>0.84</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H182" s="1">
-        <v>0.03</v>
+        <v>2.63</v>
       </c>
       <c r="I182" s="2">
         <v>8.699999999999999</v>
@@ -14119,7 +14119,7 @@
         <v>5</v>
       </c>
       <c r="K182" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -14142,7 +14142,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -14154,7 +14154,7 @@
         <v>5</v>
       </c>
       <c r="K183" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -14177,10 +14177,10 @@
         <v>3</v>
       </c>
       <c r="G184" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="H184" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
       <c r="I184" s="2">
         <v>7.1</v>
@@ -14189,7 +14189,7 @@
         <v>5</v>
       </c>
       <c r="K184" s="1">
-        <v>0.23</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -14215,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="H185" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -14247,7 +14247,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -14279,13 +14279,13 @@
         <v>0</v>
       </c>
       <c r="H187" s="1">
-        <v>0.96</v>
+        <v>96</v>
       </c>
       <c r="J187">
         <v>1</v>
       </c>
       <c r="K187" s="1">
-        <v>0.04</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -14311,13 +14311,13 @@
         <v>0</v>
       </c>
       <c r="H188" s="1">
-        <v>0.97</v>
+        <v>97.14</v>
       </c>
       <c r="J188">
         <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="G190" s="1">
-        <v>0.83</v>
+        <v>82.5</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -14384,7 +14384,7 @@
         <v>7</v>
       </c>
       <c r="K190" s="1">
-        <v>0.18</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -14407,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -14419,7 +14419,7 @@
         <v>10</v>
       </c>
       <c r="K191" s="1">
-        <v>0.23</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -14442,10 +14442,10 @@
         <v>1</v>
       </c>
       <c r="G192" s="1">
-        <v>0.8100000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H192" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
       <c r="I192" s="2">
         <v>6.7</v>
@@ -14454,7 +14454,7 @@
         <v>7</v>
       </c>
       <c r="K192" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -14477,10 +14477,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H193" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
       <c r="I193" s="2">
         <v>6.7</v>
@@ -14489,7 +14489,7 @@
         <v>7</v>
       </c>
       <c r="K193" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -14512,10 +14512,10 @@
         <v>15</v>
       </c>
       <c r="G194" s="1">
-        <v>0.5600000000000001</v>
+        <v>55.88</v>
       </c>
       <c r="H194" s="1">
-        <v>0.44</v>
+        <v>44.12</v>
       </c>
       <c r="I194" s="2">
         <v>8.6</v>
@@ -14547,10 +14547,10 @@
         <v>21</v>
       </c>
       <c r="G195" s="1">
-        <v>0.36</v>
+        <v>36.36</v>
       </c>
       <c r="H195" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="I195" s="2">
         <v>9</v>
@@ -14582,10 +14582,10 @@
         <v>11</v>
       </c>
       <c r="G196" s="1">
-        <v>0.52</v>
+        <v>52.17</v>
       </c>
       <c r="H196" s="1">
-        <v>0.48</v>
+        <v>47.83</v>
       </c>
       <c r="I196" s="2">
         <v>9.300000000000001</v>
@@ -14617,10 +14617,10 @@
         <v>7</v>
       </c>
       <c r="G197" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H197" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="I197" s="2">
         <v>8.800000000000001</v>
@@ -14652,10 +14652,10 @@
         <v>4</v>
       </c>
       <c r="G198" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H198" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
       <c r="I198" s="2">
         <v>8.699999999999999</v>
@@ -14687,10 +14687,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H199" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I199" s="2">
         <v>9.4</v>
@@ -14722,10 +14722,10 @@
         <v>10</v>
       </c>
       <c r="G200" s="1">
-        <v>0.74</v>
+        <v>74.36</v>
       </c>
       <c r="H200" s="1">
-        <v>0.26</v>
+        <v>25.64</v>
       </c>
       <c r="I200" s="2">
         <v>7</v>
@@ -14757,10 +14757,10 @@
         <v>15</v>
       </c>
       <c r="G201" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H201" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
       <c r="I201" s="2">
         <v>7.2</v>
@@ -14792,10 +14792,10 @@
         <v>1</v>
       </c>
       <c r="G202" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H202" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I202" s="2">
         <v>8.1</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -14891,7 +14891,7 @@
         <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>0.11</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -14914,7 +14914,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -14926,7 +14926,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -14949,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -14984,7 +14984,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0.91</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -14996,7 +14996,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>0.09</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -15019,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0.87</v>
+        <v>86.84</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -15031,7 +15031,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -15054,7 +15054,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -15089,7 +15089,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -15124,7 +15124,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -15194,7 +15194,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -15229,10 +15229,10 @@
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="H12" s="1">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="I12" s="2">
         <v>7.2</v>
@@ -15264,10 +15264,10 @@
         <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H13" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I13" s="2">
         <v>8.1</v>
@@ -15299,10 +15299,10 @@
         <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I14" s="2">
         <v>6.9</v>
@@ -15334,10 +15334,10 @@
         <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H15" s="1">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I15" s="2">
         <v>7.8</v>
@@ -15369,10 +15369,10 @@
         <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H16" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="2">
         <v>8</v>
@@ -15404,10 +15404,10 @@
         <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>0.31</v>
+        <v>31.43</v>
       </c>
       <c r="I17" s="2">
         <v>7.3</v>
@@ -15439,7 +15439,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0.58</v>
+        <v>57.5</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -15451,7 +15451,7 @@
         <v>17</v>
       </c>
       <c r="K18" s="1">
-        <v>0.43</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15474,7 +15474,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0.68</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -15486,7 +15486,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="1">
-        <v>0.32</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -15509,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -15544,7 +15544,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0.78</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -15556,7 +15556,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>0.22</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15579,7 +15579,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0.78</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -15591,7 +15591,7 @@
         <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>0.22</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -15614,10 +15614,10 @@
         <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>0.79</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>0.21</v>
+        <v>20.51</v>
       </c>
       <c r="I23" s="2">
         <v>7.7</v>
@@ -15649,10 +15649,10 @@
         <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
       <c r="I24" s="2">
         <v>7.6</v>
@@ -15684,10 +15684,10 @@
         <v>22</v>
       </c>
       <c r="G25" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="H25" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="I25" s="2">
         <v>6.1</v>
@@ -15719,10 +15719,10 @@
         <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H26" s="1">
-        <v>0.38</v>
+        <v>38.1</v>
       </c>
       <c r="I26" s="2">
         <v>6.9</v>
@@ -15754,10 +15754,10 @@
         <v>7</v>
       </c>
       <c r="G27" s="1">
-        <v>0.8100000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="H27" s="1">
-        <v>0.19</v>
+        <v>18.92</v>
       </c>
       <c r="I27" s="2">
         <v>8.1</v>
@@ -15789,10 +15789,10 @@
         <v>7</v>
       </c>
       <c r="G28" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H28" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I28" s="2">
         <v>7.1</v>
@@ -15824,10 +15824,10 @@
         <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H29" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I29" s="2">
         <v>7.8</v>
@@ -15859,10 +15859,10 @@
         <v>11</v>
       </c>
       <c r="G30" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>0.31</v>
+        <v>31.43</v>
       </c>
       <c r="I30" s="2">
         <v>7.5</v>
@@ -15894,10 +15894,10 @@
         <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>0.91</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
       <c r="I31" s="2">
         <v>8.199999999999999</v>
@@ -15929,10 +15929,10 @@
         <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H32" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
       <c r="I32" s="2">
         <v>6.2</v>
@@ -15964,10 +15964,10 @@
         <v>16</v>
       </c>
       <c r="G33" s="1">
-        <v>0.5600000000000001</v>
+        <v>55.56</v>
       </c>
       <c r="H33" s="1">
-        <v>0.44</v>
+        <v>44.44</v>
       </c>
       <c r="I33" s="2">
         <v>6.9</v>
@@ -15999,10 +15999,10 @@
         <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H34" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I34" s="2">
         <v>8.300000000000001</v>
@@ -16034,10 +16034,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="1">
-        <v>0.46</v>
+        <v>45.83</v>
       </c>
       <c r="H35" s="1">
-        <v>0.54</v>
+        <v>54.17</v>
       </c>
       <c r="I35" s="2">
         <v>6.8</v>
@@ -16069,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -16139,7 +16139,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -16209,7 +16209,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -16244,10 +16244,10 @@
         <v>5</v>
       </c>
       <c r="G41" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H41" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
       <c r="I41" s="2">
         <v>7.7</v>
@@ -16279,10 +16279,10 @@
         <v>7</v>
       </c>
       <c r="G42" s="1">
-        <v>0.82</v>
+        <v>81.58</v>
       </c>
       <c r="H42" s="1">
-        <v>0.18</v>
+        <v>18.42</v>
       </c>
       <c r="I42" s="2">
         <v>7.7</v>
@@ -16314,10 +16314,10 @@
         <v>7</v>
       </c>
       <c r="G43" s="1">
-        <v>0.78</v>
+        <v>78.13</v>
       </c>
       <c r="H43" s="1">
-        <v>0.22</v>
+        <v>21.88</v>
       </c>
       <c r="I43" s="2">
         <v>7.1</v>
@@ -16349,10 +16349,10 @@
         <v>7</v>
       </c>
       <c r="G44" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H44" s="1">
-        <v>0.28</v>
+        <v>28</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>
@@ -16384,10 +16384,10 @@
         <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>0.92</v>
+        <v>92.31</v>
       </c>
       <c r="H45" s="1">
-        <v>0.08</v>
+        <v>7.69</v>
       </c>
       <c r="I45" s="2">
         <v>7.5</v>
@@ -16419,10 +16419,10 @@
         <v>4</v>
       </c>
       <c r="G46" s="1">
-        <v>0.68</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H46" s="1">
-        <v>0.18</v>
+        <v>18.18</v>
       </c>
       <c r="I46" s="2">
         <v>6.7</v>
@@ -16431,7 +16431,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -16454,10 +16454,10 @@
         <v>2</v>
       </c>
       <c r="G47" s="1">
-        <v>0.84</v>
+        <v>83.87</v>
       </c>
       <c r="H47" s="1">
-        <v>0.06</v>
+        <v>6.45</v>
       </c>
       <c r="I47" s="2">
         <v>8.300000000000001</v>
@@ -16466,7 +16466,7 @@
         <v>3</v>
       </c>
       <c r="K47" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -16489,10 +16489,10 @@
         <v>10</v>
       </c>
       <c r="G48" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H48" s="1">
-        <v>0.26</v>
+        <v>26.32</v>
       </c>
       <c r="I48" s="2">
         <v>7.6</v>
@@ -16501,7 +16501,7 @@
         <v>9</v>
       </c>
       <c r="K48" s="1">
-        <v>0.24</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -16524,10 +16524,10 @@
         <v>5</v>
       </c>
       <c r="G49" s="1">
-        <v>0.77</v>
+        <v>77.14</v>
       </c>
       <c r="H49" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I49" s="2">
         <v>7.8</v>
@@ -16536,7 +16536,7 @@
         <v>3</v>
       </c>
       <c r="K49" s="1">
-        <v>0.09</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -16559,10 +16559,10 @@
         <v>5</v>
       </c>
       <c r="G50" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="H50" s="1">
-        <v>0.15</v>
+        <v>15.15</v>
       </c>
       <c r="I50" s="2">
         <v>7.6</v>
@@ -16571,7 +16571,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -16594,10 +16594,10 @@
         <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.77</v>
       </c>
       <c r="H51" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I51" s="2">
         <v>6.7</v>
@@ -16606,7 +16606,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="1">
-        <v>0.04</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -16629,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -16641,7 +16641,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -16664,7 +16664,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -16676,7 +16676,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -16699,10 +16699,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>0.91</v>
+        <v>90.63</v>
       </c>
       <c r="H54" s="1">
-        <v>0.03</v>
+        <v>3.13</v>
       </c>
       <c r="I54" s="2">
         <v>7.5</v>
@@ -16711,7 +16711,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="1">
-        <v>0.06</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -16734,10 +16734,10 @@
         <v>6</v>
       </c>
       <c r="G55" s="1">
-        <v>0.63</v>
+        <v>63.16</v>
       </c>
       <c r="H55" s="1">
-        <v>0.16</v>
+        <v>15.79</v>
       </c>
       <c r="I55" s="2">
         <v>7.9</v>
@@ -16746,7 +16746,7 @@
         <v>8</v>
       </c>
       <c r="K55" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -16769,10 +16769,10 @@
         <v>3</v>
       </c>
       <c r="G56" s="1">
-        <v>0.78</v>
+        <v>77.78</v>
       </c>
       <c r="H56" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I56" s="2">
         <v>7.9</v>
@@ -16781,7 +16781,7 @@
         <v>5</v>
       </c>
       <c r="K56" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -16804,10 +16804,10 @@
         <v>8</v>
       </c>
       <c r="G57" s="1">
-        <v>0.74</v>
+        <v>74.19</v>
       </c>
       <c r="H57" s="1">
-        <v>0.26</v>
+        <v>25.81</v>
       </c>
       <c r="I57" s="2">
         <v>7.4</v>
@@ -16839,10 +16839,10 @@
         <v>8</v>
       </c>
       <c r="G58" s="1">
-        <v>0.74</v>
+        <v>74.19</v>
       </c>
       <c r="H58" s="1">
-        <v>0.26</v>
+        <v>25.81</v>
       </c>
       <c r="I58" s="2">
         <v>7.2</v>
@@ -16874,10 +16874,10 @@
         <v>7</v>
       </c>
       <c r="G59" s="1">
-        <v>0.79</v>
+        <v>79.41</v>
       </c>
       <c r="H59" s="1">
-        <v>0.21</v>
+        <v>20.59</v>
       </c>
       <c r="I59" s="2">
         <v>7.5</v>
@@ -16909,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -16921,7 +16921,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -16944,7 +16944,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>0.74</v>
+        <v>74.19</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -16956,7 +16956,7 @@
         <v>8</v>
       </c>
       <c r="K61" s="1">
-        <v>0.26</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -16979,7 +16979,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -16991,7 +16991,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -17014,7 +17014,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -17026,7 +17026,7 @@
         <v>7</v>
       </c>
       <c r="K63" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -17049,7 +17049,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>0.86</v>
+        <v>86.05</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -17061,7 +17061,7 @@
         <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>0.14</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -17084,7 +17084,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -17096,7 +17096,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="1">
-        <v>0.04</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -17119,7 +17119,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0.73</v>
+        <v>72.5</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>11</v>
       </c>
       <c r="K66" s="1">
-        <v>0.28</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -17154,7 +17154,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0.8</v>
+        <v>79.55</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -17166,7 +17166,7 @@
         <v>9</v>
       </c>
       <c r="K67" s="1">
-        <v>0.2</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -17189,7 +17189,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0.91</v>
+        <v>90.7</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -17224,7 +17224,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0.83</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -17236,7 +17236,7 @@
         <v>5</v>
       </c>
       <c r="K69" s="1">
-        <v>0.17</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -17259,7 +17259,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0.76</v>
+        <v>76.19</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -17271,7 +17271,7 @@
         <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -17294,10 +17294,10 @@
         <v>5</v>
       </c>
       <c r="G71" s="1">
-        <v>0.86</v>
+        <v>86.11</v>
       </c>
       <c r="H71" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I71" s="2">
         <v>7</v>
@@ -17329,10 +17329,10 @@
         <v>11</v>
       </c>
       <c r="G72" s="1">
-        <v>0.72</v>
+        <v>72.09</v>
       </c>
       <c r="H72" s="1">
-        <v>0.26</v>
+        <v>25.58</v>
       </c>
       <c r="I72" s="2">
         <v>6.4</v>
@@ -17341,7 +17341,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -17364,10 +17364,10 @@
         <v>5</v>
       </c>
       <c r="G73" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H73" s="1">
-        <v>0.12</v>
+        <v>11.63</v>
       </c>
       <c r="I73" s="2">
         <v>6.8</v>
@@ -17399,10 +17399,10 @@
         <v>2</v>
       </c>
       <c r="G74" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H74" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I74" s="2">
         <v>7</v>
@@ -17434,7 +17434,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>0.79</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -17446,7 +17446,7 @@
         <v>6</v>
       </c>
       <c r="K75" s="1">
-        <v>0.21</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -17469,10 +17469,10 @@
         <v>8</v>
       </c>
       <c r="G76" s="1">
-        <v>0.68</v>
+        <v>67.86</v>
       </c>
       <c r="H76" s="1">
-        <v>0.29</v>
+        <v>28.57</v>
       </c>
       <c r="I76" s="2">
         <v>8</v>
@@ -17481,7 +17481,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="1">
-        <v>0.04</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -17504,10 +17504,10 @@
         <v>7</v>
       </c>
       <c r="G77" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H77" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
       <c r="I77" s="2">
         <v>6.9</v>
@@ -17516,7 +17516,7 @@
         <v>4</v>
       </c>
       <c r="K77" s="1">
-        <v>0.12</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -17539,10 +17539,10 @@
         <v>4</v>
       </c>
       <c r="G78" s="1">
-        <v>0.77</v>
+        <v>77.42</v>
       </c>
       <c r="H78" s="1">
-        <v>0.13</v>
+        <v>12.9</v>
       </c>
       <c r="I78" s="2">
         <v>8</v>
@@ -17551,7 +17551,7 @@
         <v>3</v>
       </c>
       <c r="K78" s="1">
-        <v>0.1</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -17574,10 +17574,10 @@
         <v>8</v>
       </c>
       <c r="G79" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H79" s="1">
-        <v>0.38</v>
+        <v>38.1</v>
       </c>
       <c r="I79" s="2">
         <v>7.4</v>
@@ -17586,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -17609,10 +17609,10 @@
         <v>6</v>
       </c>
       <c r="G80" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H80" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
       <c r="I80" s="2">
         <v>8</v>
@@ -17644,10 +17644,10 @@
         <v>5</v>
       </c>
       <c r="G81" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H81" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
       <c r="I81" s="2">
         <v>7.2</v>
@@ -17656,7 +17656,7 @@
         <v>3</v>
       </c>
       <c r="K81" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -17679,10 +17679,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="1">
-        <v>0.97</v>
+        <v>96.77</v>
       </c>
       <c r="H82" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
       <c r="I82" s="2">
         <v>8.5</v>
@@ -17714,10 +17714,10 @@
         <v>5</v>
       </c>
       <c r="G83" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H83" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I83" s="2">
         <v>8</v>
@@ -17749,10 +17749,10 @@
         <v>7</v>
       </c>
       <c r="G84" s="1">
-        <v>0.6899999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="H84" s="1">
-        <v>0.27</v>
+        <v>26.92</v>
       </c>
       <c r="I84" s="2">
         <v>6.2</v>
@@ -17761,7 +17761,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="1">
-        <v>0.04</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -17784,7 +17784,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -17819,10 +17819,10 @@
         <v>8</v>
       </c>
       <c r="G86" s="1">
-        <v>0.63</v>
+        <v>62.5</v>
       </c>
       <c r="H86" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I86" s="2">
         <v>6.9</v>
@@ -17831,7 +17831,7 @@
         <v>4</v>
       </c>
       <c r="K86" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -17854,10 +17854,10 @@
         <v>2</v>
       </c>
       <c r="G87" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H87" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
       <c r="I87" s="2">
         <v>7.6</v>
@@ -17889,10 +17889,10 @@
         <v>6</v>
       </c>
       <c r="G88" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H88" s="1">
-        <v>0.17</v>
+        <v>16.67</v>
       </c>
       <c r="I88" s="2">
         <v>7.2</v>
@@ -17901,7 +17901,7 @@
         <v>3</v>
       </c>
       <c r="K88" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -17924,7 +17924,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>0.65</v>
+        <v>64.52</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -17936,7 +17936,7 @@
         <v>11</v>
       </c>
       <c r="K89" s="1">
-        <v>0.35</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -17959,7 +17959,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="K90" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -17994,7 +17994,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0.74</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -18006,7 +18006,7 @@
         <v>9</v>
       </c>
       <c r="K91" s="1">
-        <v>0.26</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -18029,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0.61</v>
+        <v>60.61</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -18041,7 +18041,7 @@
         <v>13</v>
       </c>
       <c r="K92" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -18064,10 +18064,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H93" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I93" s="2">
         <v>7.2</v>
@@ -18099,10 +18099,10 @@
         <v>6</v>
       </c>
       <c r="G94" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H94" s="1">
-        <v>0.19</v>
+        <v>19.35</v>
       </c>
       <c r="I94" s="2">
         <v>7.1</v>
@@ -18134,10 +18134,10 @@
         <v>3</v>
       </c>
       <c r="G95" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H95" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I95" s="2">
         <v>7.7</v>
@@ -18169,10 +18169,10 @@
         <v>4</v>
       </c>
       <c r="G96" s="1">
-        <v>0.91</v>
+        <v>90.7</v>
       </c>
       <c r="H96" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I96" s="2">
         <v>7.3</v>
@@ -18204,10 +18204,10 @@
         <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>0.98</v>
+        <v>97.67</v>
       </c>
       <c r="H97" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
       <c r="I97" s="2">
         <v>7.3</v>
@@ -18239,10 +18239,10 @@
         <v>1</v>
       </c>
       <c r="G98" s="1">
-        <v>0.96</v>
+        <v>95.83</v>
       </c>
       <c r="H98" s="1">
-        <v>0.04</v>
+        <v>4.17</v>
       </c>
       <c r="I98" s="2">
         <v>7.8</v>
@@ -18274,7 +18274,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>0.68</v>
+        <v>68.42</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -18286,7 +18286,7 @@
         <v>12</v>
       </c>
       <c r="K99" s="1">
-        <v>0.32</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -18309,7 +18309,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>0.83</v>
+        <v>82.86</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -18321,7 +18321,7 @@
         <v>6</v>
       </c>
       <c r="K100" s="1">
-        <v>0.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -18344,7 +18344,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>0.91</v>
+        <v>91.3</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>2</v>
       </c>
       <c r="K101" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -18379,7 +18379,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -18391,7 +18391,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -18414,7 +18414,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>0.82</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -18426,7 +18426,7 @@
         <v>6</v>
       </c>
       <c r="K103" s="1">
-        <v>0.18</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -18449,7 +18449,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>0.7</v>
+        <v>69.7</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -18461,7 +18461,7 @@
         <v>10</v>
       </c>
       <c r="K104" s="1">
-        <v>0.3</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -18484,10 +18484,10 @@
         <v>5</v>
       </c>
       <c r="G105" s="1">
-        <v>0.76</v>
+        <v>76.19</v>
       </c>
       <c r="H105" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
       <c r="I105" s="2">
         <v>7.7</v>
@@ -18519,7 +18519,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>0.6899999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -18531,7 +18531,7 @@
         <v>11</v>
       </c>
       <c r="K106" s="1">
-        <v>0.31</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18554,10 +18554,10 @@
         <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>0.91</v>
+        <v>91.3</v>
       </c>
       <c r="H107" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I107" s="2">
         <v>8.6</v>
@@ -18589,10 +18589,10 @@
         <v>2</v>
       </c>
       <c r="G108" s="1">
-        <v>0.87</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>0.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I108" s="2">
         <v>8.699999999999999</v>
@@ -18601,7 +18601,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -18624,10 +18624,10 @@
         <v>8</v>
       </c>
       <c r="G109" s="1">
-        <v>0.79</v>
+        <v>78.95</v>
       </c>
       <c r="H109" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
       <c r="I109" s="2">
         <v>7.6</v>
@@ -18659,10 +18659,10 @@
         <v>8</v>
       </c>
       <c r="G110" s="1">
-        <v>0.76</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H110" s="1">
-        <v>0.24</v>
+        <v>24.24</v>
       </c>
       <c r="I110" s="2">
         <v>6.9</v>
@@ -18694,10 +18694,10 @@
         <v>10</v>
       </c>
       <c r="G111" s="1">
-        <v>0.7</v>
+        <v>69.7</v>
       </c>
       <c r="H111" s="1">
-        <v>0.3</v>
+        <v>30.3</v>
       </c>
       <c r="I111" s="2">
         <v>7.1</v>
@@ -18729,7 +18729,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>0.59</v>
+        <v>59.09</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -18741,7 +18741,7 @@
         <v>18</v>
       </c>
       <c r="K112" s="1">
-        <v>0.41</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -18764,7 +18764,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="1">
-        <v>0.63</v>
+        <v>62.79</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -18776,7 +18776,7 @@
         <v>16</v>
       </c>
       <c r="K113" s="1">
-        <v>0.37</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -18799,7 +18799,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="1">
-        <v>0.57</v>
+        <v>57.14</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -18811,7 +18811,7 @@
         <v>9</v>
       </c>
       <c r="K114" s="1">
-        <v>0.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -18834,10 +18834,10 @@
         <v>5</v>
       </c>
       <c r="G115" s="1">
-        <v>0.86</v>
+        <v>86.11</v>
       </c>
       <c r="H115" s="1">
-        <v>0.14</v>
+        <v>13.89</v>
       </c>
       <c r="I115" s="2">
         <v>8</v>
@@ -18869,10 +18869,10 @@
         <v>8</v>
       </c>
       <c r="G116" s="1">
-        <v>0.77</v>
+        <v>77.14</v>
       </c>
       <c r="H116" s="1">
-        <v>0.23</v>
+        <v>22.86</v>
       </c>
       <c r="I116" s="2">
         <v>7.7</v>
@@ -18904,7 +18904,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -18916,7 +18916,7 @@
         <v>5</v>
       </c>
       <c r="K117" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -18939,7 +18939,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -18951,7 +18951,7 @@
         <v>2</v>
       </c>
       <c r="K118" s="1">
-        <v>0.06</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -18974,7 +18974,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -18986,7 +18986,7 @@
         <v>4</v>
       </c>
       <c r="K119" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -19009,7 +19009,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -19021,7 +19021,7 @@
         <v>4</v>
       </c>
       <c r="K120" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -19044,7 +19044,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>0.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -19056,7 +19056,7 @@
         <v>4</v>
       </c>
       <c r="K121" s="1">
-        <v>0.13</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -19079,10 +19079,10 @@
         <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>0.89</v>
+        <v>88.89</v>
       </c>
       <c r="H122" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
       <c r="I122" s="2">
         <v>8.4</v>
@@ -19091,7 +19091,7 @@
         <v>3</v>
       </c>
       <c r="K122" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -19114,10 +19114,10 @@
         <v>1</v>
       </c>
       <c r="G123" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H123" s="1">
-        <v>0.02</v>
+        <v>2.33</v>
       </c>
       <c r="I123" s="2">
         <v>8.1</v>
@@ -19126,7 +19126,7 @@
         <v>4</v>
       </c>
       <c r="K123" s="1">
-        <v>0.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -19149,10 +19149,10 @@
         <v>2</v>
       </c>
       <c r="G124" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H124" s="1">
-        <v>0.05</v>
+        <v>4.65</v>
       </c>
       <c r="I124" s="2">
         <v>7.7</v>
@@ -19161,7 +19161,7 @@
         <v>3</v>
       </c>
       <c r="K124" s="1">
-        <v>0.07000000000000001</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -19184,7 +19184,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="1">
-        <v>0.84</v>
+        <v>83.87</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
@@ -19231,7 +19231,7 @@
         <v>5</v>
       </c>
       <c r="K126" s="1">
-        <v>0.16</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -19254,7 +19254,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
@@ -19266,7 +19266,7 @@
         <v>7</v>
       </c>
       <c r="K127" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -19289,10 +19289,10 @@
         <v>2</v>
       </c>
       <c r="G128" s="1">
-        <v>0.91</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>0.06</v>
+        <v>5.71</v>
       </c>
       <c r="I128" s="2">
         <v>8.5</v>
@@ -19301,7 +19301,7 @@
         <v>1</v>
       </c>
       <c r="K128" s="1">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -19324,7 +19324,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="1">
-        <v>0.76</v>
+        <v>76.19</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -19336,7 +19336,7 @@
         <v>5</v>
       </c>
       <c r="K129" s="1">
-        <v>0.24</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -19359,10 +19359,10 @@
         <v>7</v>
       </c>
       <c r="G130" s="1">
-        <v>0.79</v>
+        <v>79.41</v>
       </c>
       <c r="H130" s="1">
-        <v>0.21</v>
+        <v>20.59</v>
       </c>
       <c r="I130" s="2">
         <v>7.4</v>
@@ -19394,10 +19394,10 @@
         <v>13</v>
       </c>
       <c r="G131" s="1">
-        <v>0.58</v>
+        <v>58.06</v>
       </c>
       <c r="H131" s="1">
-        <v>0.42</v>
+        <v>41.94</v>
       </c>
       <c r="I131" s="2">
         <v>6.6</v>
@@ -19429,10 +19429,10 @@
         <v>10</v>
       </c>
       <c r="G132" s="1">
-        <v>0.72</v>
+        <v>72.22</v>
       </c>
       <c r="H132" s="1">
-        <v>0.28</v>
+        <v>27.78</v>
       </c>
       <c r="I132" s="2">
         <v>7.8</v>
@@ -19464,10 +19464,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="1">
-        <v>0.72</v>
+        <v>72.09</v>
       </c>
       <c r="H133" s="1">
-        <v>0.28</v>
+        <v>27.91</v>
       </c>
       <c r="I133" s="2">
         <v>7</v>
@@ -19499,10 +19499,10 @@
         <v>10</v>
       </c>
       <c r="G134" s="1">
-        <v>0.77</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H134" s="1">
-        <v>0.23</v>
+        <v>23.26</v>
       </c>
       <c r="I134" s="2">
         <v>7.1</v>
@@ -19534,10 +19534,10 @@
         <v>4</v>
       </c>
       <c r="G135" s="1">
-        <v>0.83</v>
+        <v>83.33</v>
       </c>
       <c r="H135" s="1">
-        <v>0.17</v>
+        <v>16.67</v>
       </c>
       <c r="I135" s="2">
         <v>7.4</v>
@@ -19569,10 +19569,10 @@
         <v>8</v>
       </c>
       <c r="G136" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H136" s="1">
-        <v>0.22</v>
+        <v>22.22</v>
       </c>
       <c r="I136" s="2">
         <v>7.5</v>
@@ -19581,7 +19581,7 @@
         <v>1</v>
       </c>
       <c r="K136" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -19604,7 +19604,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="1">
-        <v>0.9399999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
@@ -19616,7 +19616,7 @@
         <v>2</v>
       </c>
       <c r="K137" s="1">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -19639,10 +19639,10 @@
         <v>10</v>
       </c>
       <c r="G138" s="1">
-        <v>0.74</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H138" s="1">
-        <v>0.26</v>
+        <v>26.32</v>
       </c>
       <c r="I138" s="2">
         <v>7.1</v>
@@ -19674,10 +19674,10 @@
         <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>0.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H139" s="1">
-        <v>0.14</v>
+        <v>14.29</v>
       </c>
       <c r="I139" s="2">
         <v>7.8</v>
@@ -19709,10 +19709,10 @@
         <v>7</v>
       </c>
       <c r="G140" s="1">
-        <v>0.73</v>
+        <v>73.08</v>
       </c>
       <c r="H140" s="1">
-        <v>0.27</v>
+        <v>26.92</v>
       </c>
       <c r="I140" s="2">
         <v>6.5</v>
@@ -19744,10 +19744,10 @@
         <v>1</v>
       </c>
       <c r="G141" s="1">
-        <v>0.96</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H141" s="1">
-        <v>0.04</v>
+        <v>4.35</v>
       </c>
       <c r="I141" s="2">
         <v>7.6</v>
@@ -19779,10 +19779,10 @@
         <v>10</v>
       </c>
       <c r="G142" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H142" s="1">
-        <v>0.31</v>
+        <v>31.25</v>
       </c>
       <c r="I142" s="2">
         <v>6.9</v>
@@ -19814,10 +19814,10 @@
         <v>1</v>
       </c>
       <c r="G143" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H143" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I143" s="2">
         <v>8</v>
@@ -19849,10 +19849,10 @@
         <v>9</v>
       </c>
       <c r="G144" s="1">
-        <v>0.78</v>
+        <v>77.5</v>
       </c>
       <c r="H144" s="1">
-        <v>0.23</v>
+        <v>22.5</v>
       </c>
       <c r="I144" s="2">
         <v>7.5</v>
@@ -19884,10 +19884,10 @@
         <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>0.95</v>
+        <v>95.45</v>
       </c>
       <c r="H145" s="1">
-        <v>0.05</v>
+        <v>4.55</v>
       </c>
       <c r="I145" s="2">
         <v>8.1</v>
@@ -19919,10 +19919,10 @@
         <v>3</v>
       </c>
       <c r="G146" s="1">
-        <v>0.93</v>
+        <v>93.02</v>
       </c>
       <c r="H146" s="1">
-        <v>0.07000000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="I146" s="2">
         <v>8.699999999999999</v>
@@ -19954,10 +19954,10 @@
         <v>4</v>
       </c>
       <c r="G147" s="1">
-        <v>0.82</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H147" s="1">
-        <v>0.18</v>
+        <v>18.18</v>
       </c>
       <c r="I147" s="2">
         <v>8.199999999999999</v>
@@ -19989,10 +19989,10 @@
         <v>8</v>
       </c>
       <c r="G148" s="1">
-        <v>0.79</v>
+        <v>78.95</v>
       </c>
       <c r="H148" s="1">
-        <v>0.21</v>
+        <v>21.05</v>
       </c>
       <c r="I148" s="2">
         <v>7.9</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
@@ -20036,7 +20036,7 @@
         <v>7</v>
       </c>
       <c r="K149" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -20059,10 +20059,10 @@
         <v>8</v>
       </c>
       <c r="G150" s="1">
-        <v>0.35</v>
+        <v>34.78</v>
       </c>
       <c r="H150" s="1">
-        <v>0.35</v>
+        <v>34.78</v>
       </c>
       <c r="I150" s="2">
         <v>6.2</v>
@@ -20071,7 +20071,7 @@
         <v>7</v>
       </c>
       <c r="K150" s="1">
-        <v>0.3</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -20094,10 +20094,10 @@
         <v>15</v>
       </c>
       <c r="G151" s="1">
-        <v>0.48</v>
+        <v>48.39</v>
       </c>
       <c r="H151" s="1">
-        <v>0.48</v>
+        <v>48.39</v>
       </c>
       <c r="I151" s="2">
         <v>6.2</v>
@@ -20106,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="K151" s="1">
-        <v>0.03</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -20129,10 +20129,10 @@
         <v>6</v>
       </c>
       <c r="G152" s="1">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
       <c r="H152" s="1">
-        <v>0.16</v>
+        <v>15.79</v>
       </c>
       <c r="I152" s="2">
         <v>7</v>
@@ -20141,7 +20141,7 @@
         <v>16</v>
       </c>
       <c r="K152" s="1">
-        <v>0.42</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -20164,10 +20164,10 @@
         <v>10</v>
       </c>
       <c r="G153" s="1">
-        <v>0.62</v>
+        <v>62.16</v>
       </c>
       <c r="H153" s="1">
-        <v>0.27</v>
+        <v>27.03</v>
       </c>
       <c r="I153" s="2">
         <v>6.9</v>
@@ -20176,7 +20176,7 @@
         <v>4</v>
       </c>
       <c r="K153" s="1">
-        <v>0.11</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -20199,10 +20199,10 @@
         <v>7</v>
       </c>
       <c r="G154" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
       <c r="H154" s="1">
-        <v>0.21</v>
+        <v>21.21</v>
       </c>
       <c r="I154" s="2">
         <v>6.4</v>
@@ -20211,7 +20211,7 @@
         <v>13</v>
       </c>
       <c r="K154" s="1">
-        <v>0.39</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -20234,10 +20234,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H155" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="I155" s="2">
         <v>6.4</v>
@@ -20269,10 +20269,10 @@
         <v>4</v>
       </c>
       <c r="G156" s="1">
-        <v>0.9</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H156" s="1">
-        <v>0.1</v>
+        <v>10.26</v>
       </c>
       <c r="I156" s="2">
         <v>7.8</v>
@@ -20304,10 +20304,10 @@
         <v>3</v>
       </c>
       <c r="G157" s="1">
-        <v>0.92</v>
+        <v>91.67</v>
       </c>
       <c r="H157" s="1">
-        <v>0.08</v>
+        <v>8.33</v>
       </c>
       <c r="I157" s="2">
         <v>8</v>
@@ -20339,10 +20339,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="H158" s="1">
-        <v>0.36</v>
+        <v>36.36</v>
       </c>
       <c r="I158" s="2">
         <v>6.5</v>
@@ -20374,7 +20374,7 @@
         <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -20409,7 +20409,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
@@ -20444,10 +20444,10 @@
         <v>3</v>
       </c>
       <c r="G161" s="1">
-        <v>0.88</v>
+        <v>88</v>
       </c>
       <c r="H161" s="1">
-        <v>0.12</v>
+        <v>12</v>
       </c>
       <c r="I161" s="2">
         <v>7</v>
@@ -20479,10 +20479,10 @@
         <v>3</v>
       </c>
       <c r="G162" s="1">
-        <v>0.86</v>
+        <v>86.36</v>
       </c>
       <c r="H162" s="1">
-        <v>0.14</v>
+        <v>13.64</v>
       </c>
       <c r="I162" s="2">
         <v>6.6</v>
@@ -20514,10 +20514,10 @@
         <v>4</v>
       </c>
       <c r="G163" s="1">
-        <v>0.85</v>
+        <v>84.62</v>
       </c>
       <c r="H163" s="1">
-        <v>0.15</v>
+        <v>15.38</v>
       </c>
       <c r="I163" s="2">
         <v>6.7</v>
@@ -20549,10 +20549,10 @@
         <v>15</v>
       </c>
       <c r="G164" s="1">
-        <v>0.58</v>
+        <v>58.33</v>
       </c>
       <c r="H164" s="1">
-        <v>0.42</v>
+        <v>41.67</v>
       </c>
       <c r="I164" s="2">
         <v>6</v>
@@ -20584,10 +20584,10 @@
         <v>10</v>
       </c>
       <c r="G165" s="1">
-        <v>0.74</v>
+        <v>74.36</v>
       </c>
       <c r="H165" s="1">
-        <v>0.26</v>
+        <v>25.64</v>
       </c>
       <c r="I165" s="2">
         <v>6.8</v>
@@ -20619,10 +20619,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="1">
-        <v>0.67</v>
+        <v>66.67</v>
       </c>
       <c r="H166" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
       <c r="I166" s="2">
         <v>6.6</v>
@@ -20654,10 +20654,10 @@
         <v>10</v>
       </c>
       <c r="G167" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H167" s="1">
-        <v>0.31</v>
+        <v>31.25</v>
       </c>
       <c r="I167" s="2">
         <v>6.4</v>
@@ -20689,10 +20689,10 @@
         <v>9</v>
       </c>
       <c r="G168" s="1">
-        <v>0.71</v>
+        <v>70.97</v>
       </c>
       <c r="H168" s="1">
-        <v>0.29</v>
+        <v>29.03</v>
       </c>
       <c r="I168" s="2">
         <v>6.6</v>
@@ -20724,10 +20724,10 @@
         <v>7</v>
       </c>
       <c r="G169" s="1">
-        <v>0.8100000000000001</v>
+        <v>80.56</v>
       </c>
       <c r="H169" s="1">
-        <v>0.19</v>
+        <v>19.44</v>
       </c>
       <c r="I169" s="2">
         <v>7.5</v>
@@ -20759,10 +20759,10 @@
         <v>7</v>
       </c>
       <c r="G170" s="1">
-        <v>0.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
       <c r="I170" s="2">
         <v>7.5</v>
@@ -20771,7 +20771,7 @@
         <v>2</v>
       </c>
       <c r="K170" s="1">
-        <v>0.05</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -20794,10 +20794,10 @@
         <v>5</v>
       </c>
       <c r="G171" s="1">
-        <v>0.88</v>
+        <v>88.37</v>
       </c>
       <c r="H171" s="1">
-        <v>0.12</v>
+        <v>11.63</v>
       </c>
       <c r="I171" s="2">
         <v>7.1</v>
@@ -20829,10 +20829,10 @@
         <v>3</v>
       </c>
       <c r="G172" s="1">
-        <v>0.88</v>
+        <v>87.5</v>
       </c>
       <c r="H172" s="1">
-        <v>0.13</v>
+        <v>12.5</v>
       </c>
       <c r="I172" s="2">
         <v>7.1</v>
@@ -20864,10 +20864,10 @@
         <v>3</v>
       </c>
       <c r="G173" s="1">
-        <v>0.88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>0.12</v>
+        <v>11.54</v>
       </c>
       <c r="I173" s="2">
         <v>6.7</v>
@@ -20899,10 +20899,10 @@
         <v>7</v>
       </c>
       <c r="G174" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H174" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
       <c r="I174" s="2">
         <v>6.8</v>
@@ -20934,10 +20934,10 @@
         <v>6</v>
       </c>
       <c r="G175" s="1">
-        <v>0.79</v>
+        <v>79.31</v>
       </c>
       <c r="H175" s="1">
-        <v>0.21</v>
+        <v>20.69</v>
       </c>
       <c r="I175" s="2">
         <v>7.1</v>
@@ -20969,10 +20969,10 @@
         <v>10</v>
       </c>
       <c r="G176" s="1">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="H176" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="I176" s="2">
         <v>7.4</v>
@@ -21004,7 +21004,7 @@
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0.58</v>
+        <v>57.58</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
@@ -21016,7 +21016,7 @@
         <v>14</v>
       </c>
       <c r="K177" s="1">
-        <v>0.42</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -21039,10 +21039,10 @@
         <v>2</v>
       </c>
       <c r="G178" s="1">
-        <v>0.9</v>
+        <v>90.48</v>
       </c>
       <c r="H178" s="1">
-        <v>0.1</v>
+        <v>9.52</v>
       </c>
       <c r="I178" s="2">
         <v>8</v>
@@ -21074,10 +21074,10 @@
         <v>7</v>
       </c>
       <c r="G179" s="1">
-        <v>0.82</v>
+        <v>81.58</v>
       </c>
       <c r="H179" s="1">
-        <v>0.18</v>
+        <v>18.42</v>
       </c>
       <c r="I179" s="2">
         <v>7.8</v>
@@ -21109,10 +21109,10 @@
         <v>17</v>
       </c>
       <c r="G180" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H180" s="1">
-        <v>0.47</v>
+        <v>47.22</v>
       </c>
       <c r="I180" s="2">
         <v>6.7</v>
@@ -21121,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -21144,10 +21144,10 @@
         <v>17</v>
       </c>
       <c r="G181" s="1">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="H181" s="1">
-        <v>0.47</v>
+        <v>47.22</v>
       </c>
       <c r="I181" s="2">
         <v>6.7</v>
@@ -21156,7 +21156,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -21179,7 +21179,7 @@
         <v>0</v>
       </c>
       <c r="G182" s="1">
-        <v>0.87</v>
+        <v>86.84</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>5</v>
       </c>
       <c r="K182" s="1">
-        <v>0.13</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -21214,7 +21214,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>0.84</v>
+        <v>84.38</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -21226,7 +21226,7 @@
         <v>5</v>
       </c>
       <c r="K183" s="1">
-        <v>0.16</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -21249,7 +21249,7 @@
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -21261,7 +21261,7 @@
         <v>5</v>
       </c>
       <c r="K184" s="1">
-        <v>0.23</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -21284,10 +21284,10 @@
         <v>10</v>
       </c>
       <c r="G185" s="1">
-        <v>0.71</v>
+        <v>70.59</v>
       </c>
       <c r="H185" s="1">
-        <v>0.29</v>
+        <v>29.41</v>
       </c>
       <c r="I185" s="2">
         <v>7.6</v>
@@ -21319,10 +21319,10 @@
         <v>10</v>
       </c>
       <c r="G186" s="1">
-        <v>0.68</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H186" s="1">
-        <v>0.32</v>
+        <v>32.26</v>
       </c>
       <c r="I186" s="2">
         <v>7.3</v>
@@ -21354,10 +21354,10 @@
         <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>0.72</v>
+        <v>72</v>
       </c>
       <c r="H187" s="1">
-        <v>0.24</v>
+        <v>24</v>
       </c>
       <c r="I187" s="2">
         <v>7</v>
@@ -21366,7 +21366,7 @@
         <v>1</v>
       </c>
       <c r="K187" s="1">
-        <v>0.04</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -21389,10 +21389,10 @@
         <v>10</v>
       </c>
       <c r="G188" s="1">
-        <v>0.6899999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>0.29</v>
+        <v>28.57</v>
       </c>
       <c r="I188" s="2">
         <v>7.1</v>
@@ -21401,7 +21401,7 @@
         <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>0.03</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -21424,10 +21424,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="1">
-        <v>0.64</v>
+        <v>63.64</v>
       </c>
       <c r="H189" s="1">
-        <v>0.36</v>
+        <v>36.36</v>
       </c>
       <c r="I189" s="2">
         <v>6.6</v>
@@ -21459,7 +21459,7 @@
         <v>0</v>
       </c>
       <c r="G190" s="1">
-        <v>0.83</v>
+        <v>82.5</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -21471,7 +21471,7 @@
         <v>7</v>
       </c>
       <c r="K190" s="1">
-        <v>0.18</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -21494,7 +21494,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>0.77</v>
+        <v>77.27</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -21506,7 +21506,7 @@
         <v>10</v>
       </c>
       <c r="K191" s="1">
-        <v>0.23</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -21529,7 +21529,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="1">
-        <v>0.84</v>
+        <v>83.72</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -21541,7 +21541,7 @@
         <v>7</v>
       </c>
       <c r="K192" s="1">
-        <v>0.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -21564,10 +21564,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="1">
-        <v>0.62</v>
+        <v>61.9</v>
       </c>
       <c r="H193" s="1">
-        <v>0.05</v>
+        <v>4.76</v>
       </c>
       <c r="I193" s="2">
         <v>6.9</v>
@@ -21576,7 +21576,7 @@
         <v>7</v>
       </c>
       <c r="K193" s="1">
-        <v>0.33</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -21599,10 +21599,10 @@
         <v>7</v>
       </c>
       <c r="G194" s="1">
-        <v>0.79</v>
+        <v>79.41</v>
       </c>
       <c r="H194" s="1">
-        <v>0.21</v>
+        <v>20.59</v>
       </c>
       <c r="I194" s="2">
         <v>8.1</v>
@@ -21634,10 +21634,10 @@
         <v>9</v>
       </c>
       <c r="G195" s="1">
-        <v>0.73</v>
+        <v>72.73</v>
       </c>
       <c r="H195" s="1">
-        <v>0.27</v>
+        <v>27.27</v>
       </c>
       <c r="I195" s="2">
         <v>7.5</v>
@@ -21669,10 +21669,10 @@
         <v>4</v>
       </c>
       <c r="G196" s="1">
-        <v>0.83</v>
+        <v>82.61</v>
       </c>
       <c r="H196" s="1">
-        <v>0.17</v>
+        <v>17.39</v>
       </c>
       <c r="I196" s="2">
         <v>7.8</v>
@@ -21704,10 +21704,10 @@
         <v>7</v>
       </c>
       <c r="G197" s="1">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="H197" s="1">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="I197" s="2">
         <v>8.800000000000001</v>
@@ -21739,10 +21739,10 @@
         <v>4</v>
       </c>
       <c r="G198" s="1">
-        <v>0.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H198" s="1">
-        <v>0.11</v>
+        <v>11.43</v>
       </c>
       <c r="I198" s="2">
         <v>8.800000000000001</v>
@@ -21774,10 +21774,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H199" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I199" s="2">
         <v>9.199999999999999</v>
@@ -21809,10 +21809,10 @@
         <v>10</v>
       </c>
       <c r="G200" s="1">
-        <v>0.74</v>
+        <v>74.36</v>
       </c>
       <c r="H200" s="1">
-        <v>0.26</v>
+        <v>25.64</v>
       </c>
       <c r="I200" s="2">
         <v>7.2</v>
@@ -21844,10 +21844,10 @@
         <v>14</v>
       </c>
       <c r="G201" s="1">
-        <v>0.6</v>
+        <v>60</v>
       </c>
       <c r="H201" s="1">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="I201" s="2">
         <v>7</v>
@@ -21879,10 +21879,10 @@
         <v>1</v>
       </c>
       <c r="G202" s="1">
-        <v>0.97</v>
+        <v>97.06</v>
       </c>
       <c r="H202" s="1">
-        <v>0.03</v>
+        <v>2.94</v>
       </c>
       <c r="I202" s="2">
         <v>8.699999999999999</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1388,25 +1388,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K18" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1423,25 +1423,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1458,25 +1458,25 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1493,25 +1493,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K21" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1528,25 +1528,25 @@
         <v>23</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>78.26000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4223,25 +4223,25 @@
         <v>38</v>
       </c>
       <c r="E99">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
       </c>
       <c r="I99" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J99">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K99" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4258,25 +4258,25 @@
         <v>35</v>
       </c>
       <c r="E100">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
       </c>
       <c r="I100" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J100">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K100" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4328,25 +4328,25 @@
         <v>32</v>
       </c>
       <c r="E102">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
       </c>
       <c r="I102" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J102">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K102" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4363,25 +4363,25 @@
         <v>34</v>
       </c>
       <c r="E103">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="J103">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K103" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4398,25 +4398,25 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
       <c r="I104" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="J104">
         <v>9</v>
       </c>
-      <c r="J104">
-        <v>10</v>
-      </c>
       <c r="K104" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4468,25 +4468,25 @@
         <v>36</v>
       </c>
       <c r="E106">
+        <v>26</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1">
+        <v>72.22</v>
+      </c>
+      <c r="H106" s="1">
+        <v>2.78</v>
+      </c>
+      <c r="I106" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J106">
+        <v>9</v>
+      </c>
+      <c r="K106" s="1">
         <v>25</v>
-      </c>
-      <c r="F106">
-        <v>0</v>
-      </c>
-      <c r="G106" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="H106" s="1">
-        <v>0</v>
-      </c>
-      <c r="I106" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J106">
-        <v>11</v>
-      </c>
-      <c r="K106" s="1">
-        <v>30.56</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -5238,13 +5238,13 @@
         <v>35</v>
       </c>
       <c r="E128">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F128">
         <v>3</v>
       </c>
       <c r="G128" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H128" s="1">
         <v>8.57</v>
@@ -5253,10 +5253,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -6011,22 +6011,22 @@
         <v>8</v>
       </c>
       <c r="F150">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G150" s="1">
         <v>34.78</v>
       </c>
       <c r="H150" s="1">
-        <v>34.78</v>
+        <v>65.22</v>
       </c>
       <c r="I150" s="2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J150">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6046,22 +6046,22 @@
         <v>15</v>
       </c>
       <c r="F151">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G151" s="1">
         <v>48.39</v>
       </c>
       <c r="H151" s="1">
-        <v>48.39</v>
+        <v>51.61</v>
       </c>
       <c r="I151" s="2">
         <v>6.2</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6081,22 +6081,22 @@
         <v>16</v>
       </c>
       <c r="F152">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G152" s="1">
         <v>42.11</v>
       </c>
       <c r="H152" s="1">
-        <v>15.79</v>
+        <v>57.89</v>
       </c>
       <c r="I152" s="2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J152">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -6116,22 +6116,22 @@
         <v>23</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G153" s="1">
         <v>62.16</v>
       </c>
       <c r="H153" s="1">
-        <v>27.03</v>
+        <v>37.84</v>
       </c>
       <c r="I153" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J153">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6151,22 +6151,22 @@
         <v>13</v>
       </c>
       <c r="F154">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G154" s="1">
         <v>39.39</v>
       </c>
       <c r="H154" s="1">
-        <v>21.21</v>
+        <v>60.61</v>
       </c>
       <c r="I154" s="2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6708,25 +6708,25 @@
         <v>43</v>
       </c>
       <c r="E170">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F170">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G170" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H170" s="1">
-        <v>16.28</v>
+        <v>18.6</v>
       </c>
       <c r="I170" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J170">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6953,25 +6953,25 @@
         <v>33</v>
       </c>
       <c r="E177">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G177" s="1">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="I177" s="2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J177">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -7303,13 +7303,13 @@
         <v>25</v>
       </c>
       <c r="E187">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F187">
         <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H187" s="1">
         <v>24</v>
@@ -7318,10 +7318,10 @@
         <v>7</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7338,13 +7338,13 @@
         <v>35</v>
       </c>
       <c r="E188">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F188">
         <v>10</v>
       </c>
       <c r="G188" s="1">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H188" s="1">
         <v>28.57</v>
@@ -7353,10 +7353,10 @@
         <v>7.1</v>
       </c>
       <c r="J188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -8475,22 +8475,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H18" s="1">
-        <v>57.5</v>
+        <v>27.5</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.1</v>
       </c>
       <c r="J18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K18" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -8507,22 +8510,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>56.82</v>
       </c>
       <c r="H19" s="1">
-        <v>68.18000000000001</v>
+        <v>20.45</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -8539,22 +8545,25 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="H20" s="1">
-        <v>66.67</v>
+        <v>19.05</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.9</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8571,22 +8580,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>78.26000000000001</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I21" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K21" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8603,22 +8615,25 @@
         <v>23</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>78.26000000000001</v>
+        <v>21.74</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8.5</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -10487,19 +10502,19 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F76">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G76" s="1">
-        <v>50</v>
+        <v>53.57</v>
       </c>
       <c r="H76" s="1">
-        <v>46.43</v>
+        <v>42.86</v>
       </c>
       <c r="I76" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -10592,19 +10607,19 @@
         <v>21</v>
       </c>
       <c r="E79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F79">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G79" s="1">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H79" s="1">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
       <c r="I79" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -10627,16 +10642,19 @@
         <v>35</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F80">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H80" s="1">
-        <v>100</v>
+        <v>17.14</v>
+      </c>
+      <c r="I80" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -11268,22 +11286,25 @@
         <v>38</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F99">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="H99" s="1">
-        <v>68.42</v>
+        <v>10.53</v>
+      </c>
+      <c r="I99" s="2">
+        <v>9.9</v>
       </c>
       <c r="J99">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K99" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -11300,22 +11321,25 @@
         <v>35</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F100">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H100" s="1">
-        <v>82.86</v>
+        <v>5.71</v>
+      </c>
+      <c r="I100" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J100">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K100" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -11332,16 +11356,19 @@
         <v>23</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F101">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>73.91</v>
       </c>
       <c r="H101" s="1">
-        <v>91.3</v>
+        <v>17.39</v>
+      </c>
+      <c r="I101" s="2">
+        <v>9.6</v>
       </c>
       <c r="J101">
         <v>2</v>
@@ -11364,22 +11391,25 @@
         <v>32</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F102">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H102" s="1">
-        <v>50</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I102" s="2">
+        <v>9.4</v>
       </c>
       <c r="J102">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K102" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -11396,22 +11426,25 @@
         <v>34</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F103">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H103" s="1">
-        <v>82.34999999999999</v>
+        <v>2.94</v>
+      </c>
+      <c r="I103" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J103">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K103" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -11428,22 +11461,25 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F104">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H104" s="1">
-        <v>69.7</v>
+        <v>12.12</v>
+      </c>
+      <c r="I104" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J104">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K104" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -11495,22 +11531,25 @@
         <v>36</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F106">
+        <v>4</v>
+      </c>
+      <c r="G106" s="1">
+        <v>63.89</v>
+      </c>
+      <c r="H106" s="1">
+        <v>11.11</v>
+      </c>
+      <c r="I106" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J106">
+        <v>9</v>
+      </c>
+      <c r="K106" s="1">
         <v>25</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0</v>
-      </c>
-      <c r="H106" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="J106">
-        <v>11</v>
-      </c>
-      <c r="K106" s="1">
-        <v>30.56</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11527,16 +11566,19 @@
         <v>23</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F107">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>82.61</v>
       </c>
       <c r="H107" s="1">
-        <v>100</v>
+        <v>17.39</v>
+      </c>
+      <c r="I107" s="2">
+        <v>8.6</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -11559,16 +11601,19 @@
         <v>23</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F108">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>95.65000000000001</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I108" s="2">
+        <v>9</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -11941,16 +11986,16 @@
         <v>35</v>
       </c>
       <c r="E119">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F119">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G119" s="1">
-        <v>62.86</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H119" s="1">
-        <v>25.71</v>
+        <v>17.14</v>
       </c>
       <c r="I119" s="2">
         <v>9.199999999999999</v>
@@ -11976,19 +12021,19 @@
         <v>35</v>
       </c>
       <c r="E120">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G120" s="1">
-        <v>74.29000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="H120" s="1">
-        <v>14.29</v>
+        <v>11.43</v>
       </c>
       <c r="I120" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J120">
         <v>4</v>
@@ -12221,19 +12266,19 @@
         <v>21</v>
       </c>
       <c r="E127">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G127" s="1">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H127" s="1">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="I127" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J127">
         <v>7</v>
@@ -12256,25 +12301,25 @@
         <v>35</v>
       </c>
       <c r="E128">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F128">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G128" s="1">
-        <v>77.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H128" s="1">
-        <v>20</v>
+        <v>14.29</v>
       </c>
       <c r="I128" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -12291,16 +12336,16 @@
         <v>21</v>
       </c>
       <c r="E129">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G129" s="1">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H129" s="1">
-        <v>19.05</v>
+        <v>14.29</v>
       </c>
       <c r="I129" s="2">
         <v>7.8</v>
@@ -13023,22 +13068,25 @@
         <v>23</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F150">
         <v>16</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="H150" s="1">
         <v>69.56999999999999</v>
       </c>
+      <c r="I150" s="2">
+        <v>5.3</v>
+      </c>
       <c r="J150">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -13055,22 +13103,25 @@
         <v>31</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F151">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="H151" s="1">
-        <v>96.77</v>
+        <v>61.29</v>
+      </c>
+      <c r="I151" s="2">
+        <v>6.1</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -13087,22 +13138,25 @@
         <v>38</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F152">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>31.58</v>
       </c>
       <c r="H152" s="1">
-        <v>57.89</v>
+        <v>68.42</v>
+      </c>
+      <c r="I152" s="2">
+        <v>5.8</v>
       </c>
       <c r="J152">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -13119,22 +13173,25 @@
         <v>37</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F153">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>56.76</v>
       </c>
       <c r="H153" s="1">
-        <v>89.19</v>
+        <v>43.24</v>
+      </c>
+      <c r="I153" s="2">
+        <v>6.6</v>
       </c>
       <c r="J153">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -13151,22 +13208,25 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F154">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>21.21</v>
       </c>
       <c r="H154" s="1">
-        <v>60.61</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="I154" s="2">
+        <v>5.2</v>
       </c>
       <c r="J154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -13638,16 +13698,19 @@
         <v>31</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F168">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G168" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H168" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I168" s="2">
+        <v>6.5</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -13670,16 +13733,19 @@
         <v>36</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F169">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G169" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H169" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I169" s="2">
+        <v>7.5</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -13702,22 +13768,25 @@
         <v>43</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F170">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>95.34999999999999</v>
+        <v>20.93</v>
+      </c>
+      <c r="I170" s="2">
+        <v>7</v>
       </c>
       <c r="J170">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -13734,16 +13803,19 @@
         <v>43</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F171">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G171" s="1">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H171" s="1">
-        <v>100</v>
+        <v>18.6</v>
+      </c>
+      <c r="I171" s="2">
+        <v>6.9</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -13766,16 +13838,19 @@
         <v>24</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F172">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H172" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I172" s="2">
+        <v>7</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -13798,16 +13873,19 @@
         <v>26</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F173">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G173" s="1">
-        <v>0</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>100</v>
+        <v>11.54</v>
+      </c>
+      <c r="I173" s="2">
+        <v>7.1</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -13935,22 +14013,25 @@
         <v>33</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F177">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="H177" s="1">
-        <v>57.58</v>
+        <v>42.42</v>
+      </c>
+      <c r="I177" s="2">
+        <v>6.3</v>
       </c>
       <c r="J177">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -14206,16 +14287,19 @@
         <v>34</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F185">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H185" s="1">
-        <v>100</v>
+        <v>17.65</v>
+      </c>
+      <c r="I185" s="2">
+        <v>7.6</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -14238,16 +14322,19 @@
         <v>31</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F186">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G186" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H186" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I186" s="2">
+        <v>7.8</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -14270,22 +14357,25 @@
         <v>25</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F187">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H187" s="1">
-        <v>96</v>
+        <v>36</v>
+      </c>
+      <c r="I187" s="2">
+        <v>7.2</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -14302,22 +14392,25 @@
         <v>35</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F188">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H188" s="1">
-        <v>97.14</v>
+        <v>28.57</v>
+      </c>
+      <c r="I188" s="2">
+        <v>7.2</v>
       </c>
       <c r="J188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -14334,16 +14427,19 @@
         <v>33</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F189">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="H189" s="1">
-        <v>100</v>
+        <v>42.42</v>
+      </c>
+      <c r="I189" s="2">
+        <v>6.6</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -15433,25 +15529,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K18" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15468,25 +15564,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -15503,25 +15599,25 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -15538,25 +15634,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K21" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15573,25 +15669,25 @@
         <v>23</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>78.26000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -17580,7 +17676,7 @@
         <v>38.1</v>
       </c>
       <c r="I79" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -17603,19 +17699,19 @@
         <v>35</v>
       </c>
       <c r="E80">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G80" s="1">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H80" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I80" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -18268,25 +18364,25 @@
         <v>38</v>
       </c>
       <c r="E99">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
       </c>
       <c r="I99" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J99">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K99" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -18303,25 +18399,25 @@
         <v>35</v>
       </c>
       <c r="E100">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
       </c>
       <c r="I100" s="2">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J100">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K100" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -18350,7 +18446,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J101">
         <v>2</v>
@@ -18373,13 +18469,13 @@
         <v>32</v>
       </c>
       <c r="E102">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -18388,10 +18484,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J102">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K102" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -18408,25 +18504,25 @@
         <v>34</v>
       </c>
       <c r="E103">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K103" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -18443,13 +18539,13 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -18458,10 +18554,10 @@
         <v>9</v>
       </c>
       <c r="J104">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K104" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -18513,25 +18609,25 @@
         <v>36</v>
       </c>
       <c r="E106">
+        <v>26</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1">
+        <v>72.22</v>
+      </c>
+      <c r="H106" s="1">
+        <v>2.78</v>
+      </c>
+      <c r="I106" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J106">
+        <v>9</v>
+      </c>
+      <c r="K106" s="1">
         <v>25</v>
-      </c>
-      <c r="F106">
-        <v>0</v>
-      </c>
-      <c r="G106" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="H106" s="1">
-        <v>0</v>
-      </c>
-      <c r="I106" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J106">
-        <v>11</v>
-      </c>
-      <c r="K106" s="1">
-        <v>30.56</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18595,7 +18691,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I108" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -18980,7 +19076,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="2">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J119">
         <v>4</v>
@@ -19015,7 +19111,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="2">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J120">
         <v>4</v>
@@ -19260,7 +19356,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J127">
         <v>7</v>
@@ -19283,13 +19379,13 @@
         <v>35</v>
       </c>
       <c r="E128">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F128">
         <v>2</v>
       </c>
       <c r="G128" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H128" s="1">
         <v>5.71</v>
@@ -19298,10 +19394,10 @@
         <v>8.5</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -19330,7 +19426,7 @@
         <v>0</v>
       </c>
       <c r="I129" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J129">
         <v>5</v>
@@ -20053,25 +20149,25 @@
         <v>23</v>
       </c>
       <c r="E150">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F150">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G150" s="1">
-        <v>34.78</v>
+        <v>30.43</v>
       </c>
       <c r="H150" s="1">
-        <v>34.78</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="I150" s="2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J150">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -20088,25 +20184,25 @@
         <v>31</v>
       </c>
       <c r="E151">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F151">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G151" s="1">
-        <v>48.39</v>
+        <v>38.71</v>
       </c>
       <c r="H151" s="1">
-        <v>48.39</v>
+        <v>61.29</v>
       </c>
       <c r="I151" s="2">
         <v>6.2</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -20123,25 +20219,25 @@
         <v>38</v>
       </c>
       <c r="E152">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F152">
+        <v>26</v>
+      </c>
+      <c r="G152" s="1">
+        <v>31.58</v>
+      </c>
+      <c r="H152" s="1">
+        <v>68.42</v>
+      </c>
+      <c r="I152" s="2">
         <v>6</v>
       </c>
-      <c r="G152" s="1">
-        <v>42.11</v>
-      </c>
-      <c r="H152" s="1">
-        <v>15.79</v>
-      </c>
-      <c r="I152" s="2">
-        <v>7</v>
-      </c>
       <c r="J152">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -20158,25 +20254,25 @@
         <v>37</v>
       </c>
       <c r="E153">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G153" s="1">
-        <v>62.16</v>
+        <v>56.76</v>
       </c>
       <c r="H153" s="1">
-        <v>27.03</v>
+        <v>43.24</v>
       </c>
       <c r="I153" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J153">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -20193,25 +20289,25 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F154">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G154" s="1">
-        <v>39.39</v>
+        <v>21.21</v>
       </c>
       <c r="H154" s="1">
-        <v>21.21</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="I154" s="2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="J154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -20683,16 +20779,16 @@
         <v>31</v>
       </c>
       <c r="E168">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F168">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G168" s="1">
-        <v>70.97</v>
+        <v>64.52</v>
       </c>
       <c r="H168" s="1">
-        <v>29.03</v>
+        <v>35.48</v>
       </c>
       <c r="I168" s="2">
         <v>6.6</v>
@@ -20718,19 +20814,19 @@
         <v>36</v>
       </c>
       <c r="E169">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F169">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G169" s="1">
-        <v>80.56</v>
+        <v>69.44</v>
       </c>
       <c r="H169" s="1">
-        <v>19.44</v>
+        <v>30.56</v>
       </c>
       <c r="I169" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -20756,22 +20852,22 @@
         <v>34</v>
       </c>
       <c r="F170">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G170" s="1">
         <v>79.06999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>16.28</v>
+        <v>20.93</v>
       </c>
       <c r="I170" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J170">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -20788,19 +20884,19 @@
         <v>43</v>
       </c>
       <c r="E171">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F171">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G171" s="1">
-        <v>88.37</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H171" s="1">
-        <v>11.63</v>
+        <v>18.6</v>
       </c>
       <c r="I171" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -20823,16 +20919,16 @@
         <v>24</v>
       </c>
       <c r="E172">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G172" s="1">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="H172" s="1">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="I172" s="2">
         <v>7.1</v>
@@ -20870,7 +20966,7 @@
         <v>11.54</v>
       </c>
       <c r="I173" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -21001,22 +21097,22 @@
         <v>19</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G177" s="1">
         <v>57.58</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>42.42</v>
       </c>
       <c r="I177" s="2">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="J177">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -21278,19 +21374,19 @@
         <v>34</v>
       </c>
       <c r="E185">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F185">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G185" s="1">
-        <v>70.59</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H185" s="1">
-        <v>29.41</v>
+        <v>17.65</v>
       </c>
       <c r="I185" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -21313,19 +21409,19 @@
         <v>31</v>
       </c>
       <c r="E186">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F186">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G186" s="1">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="H186" s="1">
-        <v>32.26</v>
+        <v>25.81</v>
       </c>
       <c r="I186" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -21348,25 +21444,25 @@
         <v>25</v>
       </c>
       <c r="E187">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F187">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G187" s="1">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H187" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I187" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -21383,25 +21479,25 @@
         <v>35</v>
       </c>
       <c r="E188">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F188">
         <v>10</v>
       </c>
       <c r="G188" s="1">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H188" s="1">
         <v>28.57</v>
       </c>
       <c r="I188" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -21418,19 +21514,19 @@
         <v>33</v>
       </c>
       <c r="E189">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F189">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G189" s="1">
-        <v>63.64</v>
+        <v>57.58</v>
       </c>
       <c r="H189" s="1">
-        <v>36.36</v>
+        <v>42.42</v>
       </c>
       <c r="I189" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J189">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -2683,13 +2683,13 @@
         <v>38</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F55">
         <v>5</v>
       </c>
       <c r="G55" s="1">
-        <v>65.79000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H55" s="1">
         <v>13.16</v>
@@ -2698,10 +2698,10 @@
         <v>8</v>
       </c>
       <c r="J55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="1">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3701,22 +3701,22 @@
         <v>18</v>
       </c>
       <c r="F84">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G84" s="1">
         <v>69.23</v>
       </c>
       <c r="H84" s="1">
-        <v>26.92</v>
+        <v>30.77</v>
       </c>
       <c r="I84" s="2">
         <v>6.2</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3771,22 +3771,22 @@
         <v>20</v>
       </c>
       <c r="F86">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G86" s="1">
         <v>62.5</v>
       </c>
       <c r="H86" s="1">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="I86" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J86">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3841,22 +3841,22 @@
         <v>27</v>
       </c>
       <c r="F88">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G88" s="1">
         <v>75</v>
       </c>
       <c r="H88" s="1">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="I88" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J88">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -4468,25 +4468,25 @@
         <v>36</v>
       </c>
       <c r="E106">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="H106" s="1">
-        <v>2.78</v>
+        <v>22.22</v>
       </c>
       <c r="I106" s="2">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J106">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4541,22 +4541,22 @@
         <v>20</v>
       </c>
       <c r="F108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G108" s="1">
         <v>86.95999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>8.699999999999999</v>
+        <v>13.04</v>
       </c>
       <c r="I108" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4748,25 +4748,25 @@
         <v>21</v>
       </c>
       <c r="E114">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114" s="1">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H114" s="1">
         <v>4.76</v>
       </c>
       <c r="I114" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J114">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K114" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -4853,13 +4853,13 @@
         <v>32</v>
       </c>
       <c r="E117">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F117">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -4868,10 +4868,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J117">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K117" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -4923,13 +4923,13 @@
         <v>35</v>
       </c>
       <c r="E119">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F119">
         <v>0</v>
       </c>
       <c r="G119" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>10</v>
       </c>
       <c r="J119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K119" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -5168,25 +5168,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G126" s="1">
-        <v>80.65000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="H126" s="1">
-        <v>3.23</v>
+        <v>16.13</v>
       </c>
       <c r="I126" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J126">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5206,22 +5206,22 @@
         <v>12</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G127" s="1">
         <v>57.14</v>
       </c>
       <c r="H127" s="1">
-        <v>9.52</v>
+        <v>42.86</v>
       </c>
       <c r="I127" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5273,25 +5273,25 @@
         <v>21</v>
       </c>
       <c r="E129">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F129">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G129" s="1">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H129" s="1">
-        <v>9.52</v>
+        <v>28.57</v>
       </c>
       <c r="I129" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5973,25 +5973,25 @@
         <v>35</v>
       </c>
       <c r="E149">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G149" s="1">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="I149" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J149">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K149" s="1">
-        <v>20</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -7061,22 +7061,22 @@
         <v>18</v>
       </c>
       <c r="F180">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G180" s="1">
         <v>50</v>
       </c>
       <c r="H180" s="1">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="I180" s="2">
         <v>6.7</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7096,22 +7096,22 @@
         <v>18</v>
       </c>
       <c r="F181">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G181" s="1">
         <v>50</v>
       </c>
       <c r="H181" s="1">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="I181" s="2">
         <v>6.7</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -8965,16 +8965,19 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I32" s="2">
+        <v>7.1</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -9770,22 +9773,22 @@
         <v>23</v>
       </c>
       <c r="F55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G55" s="1">
         <v>60.53</v>
       </c>
       <c r="H55" s="1">
-        <v>18.42</v>
+        <v>21.05</v>
       </c>
       <c r="I55" s="2">
         <v>7.8</v>
       </c>
       <c r="J55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="1">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -10712,16 +10715,19 @@
         <v>31</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F82">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="H82" s="1">
-        <v>100</v>
+        <v>3.23</v>
+      </c>
+      <c r="I82" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -10744,16 +10750,19 @@
         <v>35</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F83">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H83" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I83" s="2">
+        <v>7.7</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -10776,22 +10785,25 @@
         <v>26</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F84">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="H84" s="1">
-        <v>96.15000000000001</v>
+        <v>46.15</v>
+      </c>
+      <c r="I84" s="2">
+        <v>6.4</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -10808,16 +10820,19 @@
         <v>23</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F85">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>82.61</v>
       </c>
       <c r="H85" s="1">
-        <v>100</v>
+        <v>17.39</v>
+      </c>
+      <c r="I85" s="2">
+        <v>7.2</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -10840,22 +10855,25 @@
         <v>32</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F86">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G86" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H86" s="1">
-        <v>87.5</v>
+        <v>46.88</v>
+      </c>
+      <c r="I86" s="2">
+        <v>6.9</v>
       </c>
       <c r="J86">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -10872,16 +10890,19 @@
         <v>34</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F87">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H87" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I87" s="2">
+        <v>7.4</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -10904,22 +10925,25 @@
         <v>36</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F88">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="H88" s="1">
-        <v>91.67</v>
+        <v>36.11</v>
+      </c>
+      <c r="I88" s="2">
+        <v>7.2</v>
       </c>
       <c r="J88">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -11076,19 +11100,19 @@
         <v>34</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F93">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G93" s="1">
-        <v>82.34999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H93" s="1">
-        <v>17.65</v>
+        <v>8.82</v>
       </c>
       <c r="I93" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -11111,19 +11135,19 @@
         <v>31</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F94">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G94" s="1">
-        <v>64.52</v>
+        <v>70.97</v>
       </c>
       <c r="H94" s="1">
-        <v>35.48</v>
+        <v>29.03</v>
       </c>
       <c r="I94" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -11146,19 +11170,19 @@
         <v>36</v>
       </c>
       <c r="E95">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F95">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G95" s="1">
-        <v>80.56</v>
+        <v>86.11</v>
       </c>
       <c r="H95" s="1">
-        <v>19.44</v>
+        <v>13.89</v>
       </c>
       <c r="I95" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -11181,19 +11205,19 @@
         <v>43</v>
       </c>
       <c r="E96">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F96">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G96" s="1">
-        <v>81.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H96" s="1">
-        <v>18.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I96" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -11216,19 +11240,19 @@
         <v>43</v>
       </c>
       <c r="E97">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F97">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G97" s="1">
-        <v>83.72</v>
+        <v>93.02</v>
       </c>
       <c r="H97" s="1">
-        <v>16.28</v>
+        <v>6.98</v>
       </c>
       <c r="I97" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -11251,19 +11275,19 @@
         <v>24</v>
       </c>
       <c r="E98">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H98" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="I98" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -11531,25 +11555,25 @@
         <v>36</v>
       </c>
       <c r="E106">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G106" s="1">
-        <v>63.89</v>
+        <v>83.33</v>
       </c>
       <c r="H106" s="1">
-        <v>11.11</v>
+        <v>16.67</v>
       </c>
       <c r="I106" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J106">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11566,19 +11590,19 @@
         <v>23</v>
       </c>
       <c r="E107">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G107" s="1">
-        <v>82.61</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H107" s="1">
-        <v>17.39</v>
+        <v>13.04</v>
       </c>
       <c r="I107" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -11601,25 +11625,25 @@
         <v>23</v>
       </c>
       <c r="E108">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F108">
         <v>2</v>
       </c>
       <c r="G108" s="1">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H108" s="1">
         <v>8.699999999999999</v>
       </c>
       <c r="I108" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -11814,22 +11838,22 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G114" s="1">
         <v>47.62</v>
       </c>
       <c r="H114" s="1">
-        <v>9.52</v>
+        <v>14.29</v>
       </c>
       <c r="I114" s="2">
         <v>9.5</v>
       </c>
       <c r="J114">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K114" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -11916,25 +11940,25 @@
         <v>32</v>
       </c>
       <c r="E117">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F117">
+        <v>2</v>
+      </c>
+      <c r="G117" s="1">
+        <v>84.38</v>
+      </c>
+      <c r="H117" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="I117" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J117">
         <v>3</v>
       </c>
-      <c r="G117" s="1">
-        <v>75</v>
-      </c>
-      <c r="H117" s="1">
+      <c r="K117" s="1">
         <v>9.380000000000001</v>
-      </c>
-      <c r="I117" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J117">
-        <v>5</v>
-      </c>
-      <c r="K117" s="1">
-        <v>15.63</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -11986,25 +12010,25 @@
         <v>35</v>
       </c>
       <c r="E119">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F119">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G119" s="1">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="H119" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I119" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K119" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -12231,25 +12255,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G126" s="1">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H126" s="1">
-        <v>6.45</v>
+        <v>19.35</v>
       </c>
       <c r="I126" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J126">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -12266,25 +12290,25 @@
         <v>21</v>
       </c>
       <c r="E127">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G127" s="1">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="H127" s="1">
-        <v>4.76</v>
+        <v>33.33</v>
       </c>
       <c r="I127" s="2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -12301,19 +12325,19 @@
         <v>35</v>
       </c>
       <c r="E128">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F128">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G128" s="1">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>14.29</v>
+        <v>5.71</v>
       </c>
       <c r="I128" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -12336,25 +12360,25 @@
         <v>21</v>
       </c>
       <c r="E129">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G129" s="1">
-        <v>61.9</v>
+        <v>80.95</v>
       </c>
       <c r="H129" s="1">
-        <v>14.29</v>
+        <v>19.05</v>
       </c>
       <c r="I129" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -13036,22 +13060,25 @@
         <v>35</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F149">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H149" s="1">
-        <v>80</v>
+        <v>11.43</v>
+      </c>
+      <c r="I149" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J149">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K149" s="1">
-        <v>20</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -13348,19 +13375,19 @@
         <v>33</v>
       </c>
       <c r="E158">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F158">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G158" s="1">
-        <v>33.33</v>
+        <v>51.52</v>
       </c>
       <c r="H158" s="1">
-        <v>66.67</v>
+        <v>48.48</v>
       </c>
       <c r="I158" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -13593,16 +13620,16 @@
         <v>39</v>
       </c>
       <c r="E165">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F165">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G165" s="1">
-        <v>58.97</v>
+        <v>61.54</v>
       </c>
       <c r="H165" s="1">
-        <v>41.03</v>
+        <v>38.46</v>
       </c>
       <c r="I165" s="2">
         <v>6.8</v>
@@ -13628,19 +13655,19 @@
         <v>36</v>
       </c>
       <c r="E166">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F166">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G166" s="1">
-        <v>38.89</v>
+        <v>44.44</v>
       </c>
       <c r="H166" s="1">
-        <v>61.11</v>
+        <v>55.56</v>
       </c>
       <c r="I166" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -14118,22 +14145,25 @@
         <v>36</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F180">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H180" s="1">
-        <v>97.22</v>
+        <v>0</v>
+      </c>
+      <c r="I180" s="2">
+        <v>9.1</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -14150,22 +14180,25 @@
         <v>36</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F181">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H181" s="1">
-        <v>97.22</v>
+        <v>30.56</v>
+      </c>
+      <c r="I181" s="2">
+        <v>7.8</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -16019,19 +16052,19 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H32" s="1">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I32" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -16824,25 +16857,25 @@
         <v>38</v>
       </c>
       <c r="E55">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F55">
         <v>6</v>
       </c>
       <c r="G55" s="1">
-        <v>63.16</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H55" s="1">
         <v>15.79</v>
       </c>
       <c r="I55" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="1">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -17781,7 +17814,7 @@
         <v>3.23</v>
       </c>
       <c r="I82" s="2">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -17839,25 +17872,25 @@
         <v>26</v>
       </c>
       <c r="E84">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F84">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G84" s="1">
-        <v>69.23</v>
+        <v>53.85</v>
       </c>
       <c r="H84" s="1">
-        <v>26.92</v>
+        <v>46.15</v>
       </c>
       <c r="I84" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -17874,19 +17907,19 @@
         <v>23</v>
       </c>
       <c r="E85">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G85" s="1">
-        <v>100</v>
+        <v>82.61</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>17.39</v>
       </c>
       <c r="I85" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -17909,25 +17942,25 @@
         <v>32</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F86">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G86" s="1">
-        <v>62.5</v>
+        <v>56.25</v>
       </c>
       <c r="H86" s="1">
-        <v>25</v>
+        <v>43.75</v>
       </c>
       <c r="I86" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J86">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -17944,16 +17977,16 @@
         <v>34</v>
       </c>
       <c r="E87">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G87" s="1">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H87" s="1">
-        <v>5.88</v>
+        <v>11.76</v>
       </c>
       <c r="I87" s="2">
         <v>7.6</v>
@@ -17979,25 +18012,25 @@
         <v>36</v>
       </c>
       <c r="E88">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F88">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G88" s="1">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H88" s="1">
-        <v>16.67</v>
+        <v>30.56</v>
       </c>
       <c r="I88" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J88">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -18189,19 +18222,19 @@
         <v>31</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F94">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G94" s="1">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H94" s="1">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="I94" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -18236,7 +18269,7 @@
         <v>8.33</v>
       </c>
       <c r="I95" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -18609,25 +18642,25 @@
         <v>36</v>
       </c>
       <c r="E106">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G106" s="1">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="H106" s="1">
-        <v>2.78</v>
+        <v>16.67</v>
       </c>
       <c r="I106" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J106">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18679,25 +18712,25 @@
         <v>23</v>
       </c>
       <c r="E108">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F108">
         <v>2</v>
       </c>
       <c r="G108" s="1">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H108" s="1">
         <v>8.699999999999999</v>
       </c>
       <c r="I108" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -18889,25 +18922,25 @@
         <v>21</v>
       </c>
       <c r="E114">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F114">
         <v>0</v>
       </c>
       <c r="G114" s="1">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
       </c>
       <c r="I114" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J114">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K114" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -18994,25 +19027,25 @@
         <v>32</v>
       </c>
       <c r="E117">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F117">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
       </c>
       <c r="I117" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J117">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K117" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -19064,13 +19097,13 @@
         <v>35</v>
       </c>
       <c r="E119">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F119">
         <v>0</v>
       </c>
       <c r="G119" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -19079,10 +19112,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K119" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -19309,25 +19342,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G126" s="1">
-        <v>83.87</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="I126" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J126">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -19347,22 +19380,22 @@
         <v>14</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G127" s="1">
         <v>66.67</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="I127" s="2">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -19391,7 +19424,7 @@
         <v>5.71</v>
       </c>
       <c r="I128" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -19414,25 +19447,25 @@
         <v>21</v>
       </c>
       <c r="E129">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G129" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H129" s="1">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="I129" s="2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -20114,25 +20147,25 @@
         <v>35</v>
       </c>
       <c r="E149">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1">
-        <v>80</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>11.43</v>
       </c>
       <c r="I149" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J149">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K149" s="1">
-        <v>20</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -20429,19 +20462,19 @@
         <v>33</v>
       </c>
       <c r="E158">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F158">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G158" s="1">
-        <v>63.64</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H158" s="1">
-        <v>36.36</v>
+        <v>24.24</v>
       </c>
       <c r="I158" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -21199,25 +21232,25 @@
         <v>36</v>
       </c>
       <c r="E180">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F180">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H180" s="1">
-        <v>47.22</v>
+        <v>0</v>
       </c>
       <c r="I180" s="2">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -21234,25 +21267,25 @@
         <v>36</v>
       </c>
       <c r="E181">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F181">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G181" s="1">
-        <v>50</v>
+        <v>69.44</v>
       </c>
       <c r="H181" s="1">
-        <v>47.22</v>
+        <v>30.56</v>
       </c>
       <c r="I181" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -2438,13 +2438,13 @@
         <v>38</v>
       </c>
       <c r="E48">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F48">
         <v>6</v>
       </c>
       <c r="G48" s="1">
-        <v>60.53</v>
+        <v>63.16</v>
       </c>
       <c r="H48" s="1">
         <v>15.79</v>
@@ -2453,10 +2453,10 @@
         <v>7.8</v>
       </c>
       <c r="J48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K48" s="1">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2721,22 +2721,22 @@
         <v>27</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G56" s="1">
         <v>75</v>
       </c>
       <c r="H56" s="1">
+        <v>13.89</v>
+      </c>
+      <c r="I56" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="J56">
+        <v>4</v>
+      </c>
+      <c r="K56" s="1">
         <v>11.11</v>
-      </c>
-      <c r="I56" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J56">
-        <v>5</v>
-      </c>
-      <c r="K56" s="1">
-        <v>13.89</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4678,13 +4678,13 @@
         <v>44</v>
       </c>
       <c r="E112">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F112">
         <v>2</v>
       </c>
       <c r="G112" s="1">
-        <v>54.55</v>
+        <v>56.82</v>
       </c>
       <c r="H112" s="1">
         <v>4.55</v>
@@ -4693,10 +4693,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J112">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K112" s="1">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -9525,13 +9525,13 @@
         <v>38</v>
       </c>
       <c r="E48">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F48">
         <v>13</v>
       </c>
       <c r="G48" s="1">
-        <v>42.11</v>
+        <v>44.74</v>
       </c>
       <c r="H48" s="1">
         <v>34.21</v>
@@ -9540,10 +9540,10 @@
         <v>6.9</v>
       </c>
       <c r="J48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K48" s="1">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -9808,22 +9808,22 @@
         <v>28</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="1">
         <v>77.78</v>
       </c>
       <c r="H56" s="1">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="I56" s="2">
         <v>7.8</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56" s="1">
-        <v>13.89</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -11765,13 +11765,13 @@
         <v>44</v>
       </c>
       <c r="E112">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F112">
         <v>11</v>
       </c>
       <c r="G112" s="1">
-        <v>34.09</v>
+        <v>36.36</v>
       </c>
       <c r="H112" s="1">
         <v>25</v>
@@ -11780,10 +11780,10 @@
         <v>8.9</v>
       </c>
       <c r="J112">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K112" s="1">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -11800,16 +11800,16 @@
         <v>43</v>
       </c>
       <c r="E113">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F113">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G113" s="1">
-        <v>37.21</v>
+        <v>44.19</v>
       </c>
       <c r="H113" s="1">
-        <v>25.58</v>
+        <v>18.6</v>
       </c>
       <c r="I113" s="2">
         <v>9.1</v>
@@ -11835,16 +11835,16 @@
         <v>21</v>
       </c>
       <c r="E114">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G114" s="1">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H114" s="1">
-        <v>14.29</v>
+        <v>9.52</v>
       </c>
       <c r="I114" s="2">
         <v>9.5</v>
@@ -13270,19 +13270,19 @@
         <v>36</v>
       </c>
       <c r="E155">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F155">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G155" s="1">
-        <v>38.89</v>
+        <v>50</v>
       </c>
       <c r="H155" s="1">
-        <v>61.11</v>
+        <v>50</v>
       </c>
       <c r="I155" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -13305,19 +13305,19 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F156">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G156" s="1">
-        <v>64.09999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="H156" s="1">
-        <v>35.9</v>
+        <v>30.77</v>
       </c>
       <c r="I156" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -13340,19 +13340,19 @@
         <v>36</v>
       </c>
       <c r="E157">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F157">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G157" s="1">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H157" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="I157" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -13375,16 +13375,16 @@
         <v>33</v>
       </c>
       <c r="E158">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F158">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G158" s="1">
-        <v>51.52</v>
+        <v>54.55</v>
       </c>
       <c r="H158" s="1">
-        <v>48.48</v>
+        <v>45.45</v>
       </c>
       <c r="I158" s="2">
         <v>7.5</v>
@@ -16612,13 +16612,13 @@
         <v>38</v>
       </c>
       <c r="E48">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48">
         <v>10</v>
       </c>
       <c r="G48" s="1">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="H48" s="1">
         <v>26.32</v>
@@ -16627,10 +16627,10 @@
         <v>7.6</v>
       </c>
       <c r="J48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K48" s="1">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -16895,22 +16895,22 @@
         <v>28</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="1">
         <v>77.78</v>
       </c>
       <c r="H56" s="1">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="I56" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56" s="1">
-        <v>13.89</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -18852,25 +18852,25 @@
         <v>44</v>
       </c>
       <c r="E112">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>59.09</v>
+        <v>61.36</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
       </c>
       <c r="I112" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J112">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K112" s="1">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -18899,7 +18899,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J113">
         <v>16</v>
@@ -18934,7 +18934,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J114">
         <v>8</v>
@@ -20357,19 +20357,19 @@
         <v>36</v>
       </c>
       <c r="E155">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F155">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G155" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H155" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I155" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -20392,19 +20392,19 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F156">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>89.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="H156" s="1">
-        <v>10.26</v>
+        <v>5.13</v>
       </c>
       <c r="I156" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J156">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -9805,16 +9805,16 @@
         <v>36</v>
       </c>
       <c r="E56">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G56" s="1">
-        <v>80.56</v>
+        <v>83.33</v>
       </c>
       <c r="H56" s="1">
-        <v>19.44</v>
+        <v>16.67</v>
       </c>
       <c r="I56" s="2">
         <v>7.5</v>
@@ -10797,7 +10797,7 @@
         <v>46.15</v>
       </c>
       <c r="I84" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -10902,7 +10902,7 @@
         <v>11.76</v>
       </c>
       <c r="I87" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -10925,19 +10925,19 @@
         <v>36</v>
       </c>
       <c r="E88">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F88">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G88" s="1">
-        <v>63.89</v>
+        <v>72.22</v>
       </c>
       <c r="H88" s="1">
-        <v>36.11</v>
+        <v>27.78</v>
       </c>
       <c r="I88" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -17697,19 +17697,19 @@
         <v>21</v>
       </c>
       <c r="E79">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="1">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H79" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I79" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -17872,19 +17872,19 @@
         <v>26</v>
       </c>
       <c r="E84">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F84">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G84" s="1">
-        <v>53.85</v>
+        <v>76.92</v>
       </c>
       <c r="H84" s="1">
-        <v>46.15</v>
+        <v>23.08</v>
       </c>
       <c r="I84" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -17977,19 +17977,19 @@
         <v>34</v>
       </c>
       <c r="E87">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G87" s="1">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H87" s="1">
-        <v>11.76</v>
+        <v>8.82</v>
       </c>
       <c r="I87" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -18012,16 +18012,16 @@
         <v>36</v>
       </c>
       <c r="E88">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F88">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G88" s="1">
-        <v>69.44</v>
+        <v>86.11</v>
       </c>
       <c r="H88" s="1">
-        <v>30.56</v>
+        <v>13.89</v>
       </c>
       <c r="I88" s="2">
         <v>6.9</v>
@@ -18642,19 +18642,19 @@
         <v>36</v>
       </c>
       <c r="E106">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G106" s="1">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H106" s="1">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="I106" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -19062,16 +19062,16 @@
         <v>35</v>
       </c>
       <c r="E118">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G118" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H118" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="I118" s="2">
         <v>8</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -873,22 +873,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
+      <c r="I2" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -905,22 +908,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
+      <c r="I3" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -937,22 +943,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
+      <c r="I4" s="2">
+        <v>9.199999999999999</v>
+      </c>
       <c r="J4">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -969,22 +978,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
+      <c r="I5" s="2">
+        <v>9.6</v>
+      </c>
       <c r="J5">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1001,25 +1013,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1036,13 +1048,13 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>87.5</v>
+        <v>90.63</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1051,10 +1063,10 @@
         <v>9.4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>12.5</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1106,13 +1118,13 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1121,10 +1133,10 @@
         <v>9.6</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1141,22 +1153,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>34.38</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1173,22 +1188,25 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>83.78</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>16.22</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1205,22 +1223,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1237,22 +1258,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1269,22 +1293,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>27.27</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.1</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1301,22 +1328,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>18.75</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1429,22 +1459,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>73.17</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>9.76</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1461,22 +1494,25 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.1</v>
       </c>
       <c r="J20">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1493,22 +1529,25 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>25.71</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1525,22 +1564,25 @@
         <v>37</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
+      <c r="I22" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J22">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1589,22 +1631,25 @@
         <v>22</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
+      <c r="I24" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1621,22 +1666,25 @@
         <v>35</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>17.14</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J25">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1653,22 +1701,25 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>94.59</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>5.41</v>
+      </c>
+      <c r="I26" s="2">
+        <v>8.1</v>
       </c>
       <c r="J26">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1685,22 +1736,25 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>3.57</v>
+      </c>
+      <c r="I27" s="2">
+        <v>8.4</v>
       </c>
       <c r="J27">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1717,22 +1771,25 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>12.2</v>
+      </c>
+      <c r="I28" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J28">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1749,22 +1806,25 @@
         <v>16</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
       </c>
+      <c r="I29" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J29">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1813,22 +1873,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>70.37</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
+      <c r="I31" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J31">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1845,22 +1908,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
       </c>
+      <c r="I32" s="2">
+        <v>8</v>
+      </c>
       <c r="J32">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1877,22 +1943,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>60.71</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
+      <c r="I33" s="2">
+        <v>6.9</v>
+      </c>
       <c r="J33">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1909,22 +1978,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>26.32</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
+      <c r="I34" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J34">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1941,22 +2013,25 @@
         <v>31</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>19.35</v>
+      </c>
+      <c r="I35" s="2">
+        <v>7.6</v>
       </c>
       <c r="J35">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2005,22 +2080,25 @@
         <v>32</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I37" s="2">
+        <v>7.4</v>
       </c>
       <c r="J37">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2037,22 +2115,25 @@
         <v>33</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>18.18</v>
+      </c>
+      <c r="I38" s="2">
+        <v>7.3</v>
       </c>
       <c r="J38">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2485,22 +2566,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
       </c>
+      <c r="I52" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J52">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2517,22 +2601,25 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
       </c>
+      <c r="I53" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J53">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2843,22 +2930,25 @@
         <v>24</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>95.83</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
       </c>
+      <c r="I63" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J63">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3204,22 +3294,25 @@
         <v>16</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H74" s="1">
-        <v>0</v>
+        <v>6.25</v>
+      </c>
+      <c r="I74" s="2">
+        <v>8.1</v>
       </c>
       <c r="J74">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3268,22 +3361,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
       </c>
+      <c r="I76" s="2">
+        <v>9</v>
+      </c>
       <c r="J76">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3332,22 +3428,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>38.24</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
       </c>
+      <c r="I78" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J78">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3364,22 +3463,25 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
       </c>
+      <c r="I79" s="2">
+        <v>6</v>
+      </c>
       <c r="J79">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3588,22 +3690,25 @@
         <v>28</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G86" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H86" s="1">
-        <v>0</v>
+        <v>28.57</v>
+      </c>
+      <c r="I86" s="2">
+        <v>6.4</v>
       </c>
       <c r="J86">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3620,22 +3725,25 @@
         <v>32</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>18.75</v>
+      </c>
+      <c r="I87" s="2">
+        <v>7.7</v>
       </c>
       <c r="J87">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3652,22 +3760,25 @@
         <v>32</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>18.75</v>
+      </c>
+      <c r="I88" s="2">
+        <v>7.5</v>
       </c>
       <c r="J88">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3684,22 +3795,25 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="I89" s="2">
+        <v>7.3</v>
       </c>
       <c r="J89">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3716,22 +3830,25 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>8.33</v>
+      </c>
+      <c r="I90" s="2">
+        <v>7.1</v>
       </c>
       <c r="J90">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3748,22 +3865,25 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="I91" s="2">
+        <v>6</v>
       </c>
       <c r="J91">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3975,22 +4095,25 @@
         <v>33</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F98">
         <v>0</v>
       </c>
       <c r="G98" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
       </c>
+      <c r="I98" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J98">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -4007,22 +4130,25 @@
         <v>31</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>83.87</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
       </c>
+      <c r="I99" s="2">
+        <v>6.9</v>
+      </c>
       <c r="J99">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4039,22 +4165,25 @@
         <v>29</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>89.66</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
       </c>
+      <c r="I100" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J100">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4071,22 +4200,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F101">
         <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
       </c>
+      <c r="I101" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J101">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4135,22 +4267,25 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
       </c>
+      <c r="I103" s="2">
+        <v>8</v>
+      </c>
       <c r="J103">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4167,22 +4302,25 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>51.52</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
+      <c r="I104" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J104">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4359,22 +4497,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
       </c>
+      <c r="I110" s="2">
+        <v>9</v>
+      </c>
       <c r="J110">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4391,22 +4532,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>45.95</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
+      <c r="I111" s="2">
+        <v>9.199999999999999</v>
+      </c>
       <c r="J111">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4423,22 +4567,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>29.27</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
       </c>
+      <c r="I112" s="2">
+        <v>9.699999999999999</v>
+      </c>
       <c r="J112">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4688,22 +4835,25 @@
         <v>44</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F120">
         <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
       </c>
+      <c r="I120" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="J120">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -4755,22 +4905,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F122">
         <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
       </c>
+      <c r="I122" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J122">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -4787,22 +4940,25 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
       </c>
+      <c r="I123" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J123">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -4819,25 +4975,25 @@
         <v>32</v>
       </c>
       <c r="E124">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
       <c r="G124" s="1">
-        <v>53.13</v>
+        <v>100</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J124">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>46.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -4854,25 +5010,25 @@
         <v>32</v>
       </c>
       <c r="E125">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F125">
         <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>43.75</v>
+        <v>84.38</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J125">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K125" s="1">
-        <v>56.25</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5017,22 +5173,25 @@
         <v>38</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H130" s="1">
-        <v>0</v>
+        <v>31.58</v>
+      </c>
+      <c r="I130" s="2">
+        <v>7.6</v>
       </c>
       <c r="J130">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -5081,22 +5240,25 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G132" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H132" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I132" s="2">
+        <v>7</v>
       </c>
       <c r="J132">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -5113,22 +5275,25 @@
         <v>22</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G133" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>0</v>
+        <v>18.18</v>
+      </c>
+      <c r="I133" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J133">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5145,22 +5310,25 @@
         <v>31</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G134" s="1">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="H134" s="1">
-        <v>0</v>
+        <v>22.58</v>
+      </c>
+      <c r="I134" s="2">
+        <v>7.4</v>
       </c>
       <c r="J134">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -5419,25 +5587,25 @@
         <v>36</v>
       </c>
       <c r="E142">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>50</v>
+        <v>91.67</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I142" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J142">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -5454,25 +5622,25 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F143">
         <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>41.67</v>
+        <v>88.89</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J143">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K143" s="1">
-        <v>58.33</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -5489,25 +5657,25 @@
         <v>28</v>
       </c>
       <c r="E144">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F144">
         <v>0</v>
       </c>
       <c r="G144" s="1">
-        <v>46.43</v>
+        <v>100</v>
       </c>
       <c r="H144" s="1">
         <v>0</v>
       </c>
       <c r="I144" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J144">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>53.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -5524,25 +5692,25 @@
         <v>28</v>
       </c>
       <c r="E145">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>46.43</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J145">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>53.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -5559,25 +5727,25 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F146">
         <v>0</v>
       </c>
       <c r="G146" s="1">
-        <v>36.59</v>
+        <v>87.8</v>
       </c>
       <c r="H146" s="1">
         <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J146">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K146" s="1">
-        <v>63.41</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -5594,25 +5762,25 @@
         <v>16</v>
       </c>
       <c r="E147">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -5664,22 +5832,25 @@
         <v>28</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F149">
         <v>0</v>
       </c>
       <c r="G149" s="1">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
       </c>
+      <c r="I149" s="2">
+        <v>6.8</v>
+      </c>
       <c r="J149">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -5696,22 +5867,25 @@
         <v>20</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F150">
         <v>0</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H150" s="1">
         <v>0</v>
       </c>
+      <c r="I150" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J150">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6016,22 +6190,25 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G160" s="1">
-        <v>0</v>
+        <v>85.19</v>
       </c>
       <c r="H160" s="1">
-        <v>0</v>
+        <v>14.81</v>
+      </c>
+      <c r="I160" s="2">
+        <v>7.1</v>
       </c>
       <c r="J160">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -6048,22 +6225,25 @@
         <v>19</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G161" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H161" s="1">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="I161" s="2">
+        <v>6.7</v>
       </c>
       <c r="J161">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6080,22 +6260,25 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G162" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H162" s="1">
-        <v>0</v>
+        <v>29.17</v>
+      </c>
+      <c r="I162" s="2">
+        <v>6.3</v>
       </c>
       <c r="J162">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -6112,22 +6295,25 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G163" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H163" s="1">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="I163" s="2">
+        <v>7.4</v>
       </c>
       <c r="J163">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -6432,22 +6618,25 @@
         <v>37</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G173" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>0</v>
+        <v>13.51</v>
+      </c>
+      <c r="I173" s="2">
+        <v>7.4</v>
       </c>
       <c r="J173">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -6560,22 +6749,25 @@
         <v>20</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
       </c>
+      <c r="I177" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J177">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -6592,22 +6784,25 @@
         <v>20</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
       </c>
+      <c r="I178" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J178">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -6624,22 +6819,25 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F179">
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
       </c>
+      <c r="I179" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J179">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7168,22 +7366,25 @@
         <v>32</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G196" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H196" s="1">
-        <v>0</v>
+        <v>34.38</v>
+      </c>
+      <c r="I196" s="2">
+        <v>6.6</v>
       </c>
       <c r="J196">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -7200,22 +7401,25 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H197" s="1">
-        <v>0</v>
+        <v>27.78</v>
+      </c>
+      <c r="I197" s="2">
+        <v>6.7</v>
       </c>
       <c r="J197">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -7232,22 +7436,25 @@
         <v>31</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H198" s="1">
-        <v>0</v>
+        <v>29.03</v>
+      </c>
+      <c r="I198" s="2">
+        <v>7</v>
       </c>
       <c r="J198">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -7264,22 +7471,25 @@
         <v>37</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I199" s="2">
+        <v>8.9</v>
       </c>
       <c r="J199">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -7366,22 +7576,25 @@
         <v>35</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F202">
         <v>0</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
       </c>
+      <c r="I202" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J202">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -7398,22 +7611,25 @@
         <v>33</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>3.03</v>
+      </c>
+      <c r="I203" s="2">
+        <v>9</v>
       </c>
       <c r="J203">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -7430,22 +7646,25 @@
         <v>33</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>3.03</v>
+      </c>
+      <c r="I204" s="2">
+        <v>9</v>
       </c>
       <c r="J204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -7462,22 +7681,25 @@
         <v>32</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G205" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H205" s="1">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="I205" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J205">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -7689,19 +7911,19 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -7721,19 +7943,19 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -7753,19 +7975,19 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -7785,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7817,19 +8039,19 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7849,19 +8071,19 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>87.5</v>
+        <v>90.63</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>12.5</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7913,19 +8135,19 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -7945,19 +8167,19 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -7977,19 +8199,19 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -8009,19 +8231,19 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -8041,19 +8263,19 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8073,19 +8295,19 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -8105,19 +8327,19 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8233,19 +8455,19 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -8265,19 +8487,19 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="J20">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8297,19 +8519,19 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8329,19 +8551,19 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="J22">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -8393,19 +8615,19 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -8425,19 +8647,19 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -8457,19 +8679,19 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -8489,19 +8711,19 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -8521,19 +8743,19 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -8553,19 +8775,19 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -8617,19 +8839,19 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>70.37</v>
       </c>
       <c r="J31">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -8649,19 +8871,19 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="J32">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -8681,19 +8903,19 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>60.71</v>
       </c>
       <c r="J33">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -8713,19 +8935,19 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>26.32</v>
       </c>
       <c r="J34">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -8745,19 +8967,19 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="J35">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -8809,19 +9031,19 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="J37">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -8841,19 +9063,19 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="J38">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -9289,19 +9511,19 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="J52">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -9321,19 +9543,19 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="J53">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -9641,19 +9863,19 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>95.83</v>
       </c>
       <c r="J63">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -9993,19 +10215,19 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
       </c>
       <c r="H74" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="J74">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -10057,19 +10279,19 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="J76">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -10121,19 +10343,19 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>0</v>
+        <v>38.24</v>
       </c>
       <c r="J78">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -10153,19 +10375,19 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="J79">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -10377,19 +10599,19 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
       </c>
       <c r="H86" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J86">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -10409,19 +10631,19 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J87">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -10441,19 +10663,19 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G88" s="1">
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J88">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -10473,19 +10695,19 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G89" s="1">
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>95.83</v>
       </c>
       <c r="J89">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -10505,19 +10727,19 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G90" s="1">
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>95.83</v>
       </c>
       <c r="J90">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -10537,19 +10759,19 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G91" s="1">
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J91">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -10761,19 +10983,19 @@
         <v>0</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G98" s="1">
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J98">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -10793,19 +11015,19 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>0</v>
+        <v>83.87</v>
       </c>
       <c r="J99">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -10825,19 +11047,19 @@
         <v>0</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G100" s="1">
         <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>0</v>
+        <v>89.66</v>
       </c>
       <c r="J100">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -10857,19 +11079,19 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G101" s="1">
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="J101">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -10921,19 +11143,19 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G103" s="1">
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="J103">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -10953,19 +11175,19 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G104" s="1">
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>51.52</v>
       </c>
       <c r="J104">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -11145,19 +11367,19 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G110" s="1">
         <v>0</v>
       </c>
       <c r="H110" s="1">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="J110">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -11177,19 +11399,19 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G111" s="1">
         <v>0</v>
       </c>
       <c r="H111" s="1">
-        <v>0</v>
+        <v>45.95</v>
       </c>
       <c r="J111">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -11209,19 +11431,19 @@
         <v>0</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G112" s="1">
         <v>0</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>29.27</v>
       </c>
       <c r="J112">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -11465,19 +11687,19 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G120" s="1">
         <v>0</v>
       </c>
       <c r="H120" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J120">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -11529,19 +11751,19 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="J122">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -11561,19 +11783,19 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G123" s="1">
         <v>0</v>
       </c>
       <c r="H123" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="J123">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -11593,19 +11815,19 @@
         <v>0</v>
       </c>
       <c r="F124">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G124" s="1">
         <v>0</v>
       </c>
       <c r="H124" s="1">
-        <v>53.13</v>
+        <v>100</v>
       </c>
       <c r="J124">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>46.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -11625,19 +11847,19 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G125" s="1">
         <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>43.75</v>
+        <v>84.38</v>
       </c>
       <c r="J125">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K125" s="1">
-        <v>56.25</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -11785,19 +12007,19 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G130" s="1">
         <v>0</v>
       </c>
       <c r="H130" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J130">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -11849,19 +12071,19 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G132" s="1">
         <v>0</v>
       </c>
       <c r="H132" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J132">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -11881,19 +12103,19 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G133" s="1">
         <v>0</v>
       </c>
       <c r="H133" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J133">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -11913,19 +12135,19 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G134" s="1">
         <v>0</v>
       </c>
       <c r="H134" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J134">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -12169,19 +12391,19 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G142" s="1">
         <v>0</v>
       </c>
       <c r="H142" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J142">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -12201,19 +12423,19 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G143" s="1">
         <v>0</v>
       </c>
       <c r="H143" s="1">
-        <v>41.67</v>
+        <v>88.89</v>
       </c>
       <c r="J143">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K143" s="1">
-        <v>58.33</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -12233,19 +12455,19 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G144" s="1">
         <v>0</v>
       </c>
       <c r="H144" s="1">
-        <v>46.43</v>
+        <v>100</v>
       </c>
       <c r="J144">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>53.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -12265,19 +12487,19 @@
         <v>0</v>
       </c>
       <c r="F145">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G145" s="1">
         <v>0</v>
       </c>
       <c r="H145" s="1">
-        <v>46.43</v>
+        <v>100</v>
       </c>
       <c r="J145">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>53.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -12297,19 +12519,19 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G146" s="1">
         <v>0</v>
       </c>
       <c r="H146" s="1">
-        <v>36.59</v>
+        <v>87.8</v>
       </c>
       <c r="J146">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K146" s="1">
-        <v>63.41</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -12329,19 +12551,19 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G147" s="1">
         <v>0</v>
       </c>
       <c r="H147" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -12393,19 +12615,19 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1">
         <v>0</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="J149">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -12425,19 +12647,19 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G150" s="1">
         <v>0</v>
       </c>
       <c r="H150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J150">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -12745,19 +12967,19 @@
         <v>0</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G160" s="1">
         <v>0</v>
       </c>
       <c r="H160" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J160">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -12777,19 +12999,19 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G161" s="1">
         <v>0</v>
       </c>
       <c r="H161" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J161">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -12809,19 +13031,19 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G162" s="1">
         <v>0</v>
       </c>
       <c r="H162" s="1">
-        <v>0</v>
+        <v>95.83</v>
       </c>
       <c r="J162">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -12841,19 +13063,19 @@
         <v>0</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G163" s="1">
         <v>0</v>
       </c>
       <c r="H163" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J163">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -13161,19 +13383,19 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
       </c>
       <c r="H173" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J173">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -13289,19 +13511,19 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G177" s="1">
         <v>0</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J177">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -13321,19 +13543,19 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G178" s="1">
         <v>0</v>
       </c>
       <c r="H178" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J178">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -13353,19 +13575,19 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G179" s="1">
         <v>0</v>
       </c>
       <c r="H179" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="J179">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -13897,19 +14119,19 @@
         <v>0</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G196" s="1">
         <v>0</v>
       </c>
       <c r="H196" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J196">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -13929,19 +14151,19 @@
         <v>0</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G197" s="1">
         <v>0</v>
       </c>
       <c r="H197" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="J197">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -13961,19 +14183,19 @@
         <v>0</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G198" s="1">
         <v>0</v>
       </c>
       <c r="H198" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="J198">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -13993,19 +14215,19 @@
         <v>0</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G199" s="1">
         <v>0</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J199">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -14089,19 +14311,19 @@
         <v>0</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G202" s="1">
         <v>0</v>
       </c>
       <c r="H202" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J202">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -14121,19 +14343,19 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G203" s="1">
         <v>0</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J203">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -14153,19 +14375,19 @@
         <v>0</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G204" s="1">
         <v>0</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -14185,19 +14407,19 @@
         <v>0</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G205" s="1">
         <v>0</v>
       </c>
       <c r="H205" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J205">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -14394,22 +14616,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
+      <c r="I2" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -14426,22 +14651,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
+      <c r="I3" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -14458,22 +14686,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
+      <c r="I4" s="2">
+        <v>9.199999999999999</v>
+      </c>
       <c r="J4">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -14490,22 +14721,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
+      <c r="I5" s="2">
+        <v>9.6</v>
+      </c>
       <c r="J5">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -14522,25 +14756,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -14557,13 +14791,13 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>87.5</v>
+        <v>90.63</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -14572,10 +14806,10 @@
         <v>9.4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>12.5</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -14627,13 +14861,13 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -14642,10 +14876,10 @@
         <v>9.6</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -14662,22 +14896,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>34.38</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -14694,22 +14931,25 @@
         <v>37</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>83.78</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>16.22</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -14726,22 +14966,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -14758,22 +15001,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -14790,22 +15036,25 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>27.27</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.1</v>
       </c>
       <c r="J14">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -14822,22 +15071,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>18.75</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -14950,22 +15202,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>73.17</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>9.76</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -14982,22 +15237,25 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.1</v>
       </c>
       <c r="J20">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -15014,22 +15272,25 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>25.71</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15046,22 +15307,25 @@
         <v>37</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
       </c>
+      <c r="I22" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J22">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -15110,22 +15374,25 @@
         <v>22</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
+      <c r="I24" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -15142,22 +15409,25 @@
         <v>35</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>17.14</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J25">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -15174,22 +15444,25 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>94.59</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>5.41</v>
+      </c>
+      <c r="I26" s="2">
+        <v>8.1</v>
       </c>
       <c r="J26">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -15206,22 +15479,25 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>3.57</v>
+      </c>
+      <c r="I27" s="2">
+        <v>8.4</v>
       </c>
       <c r="J27">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -15238,22 +15514,25 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>12.2</v>
+      </c>
+      <c r="I28" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J28">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -15270,22 +15549,25 @@
         <v>16</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
       </c>
+      <c r="I29" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J29">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -15334,22 +15616,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>70.37</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
+      <c r="I31" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J31">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -15366,22 +15651,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
       </c>
+      <c r="I32" s="2">
+        <v>8</v>
+      </c>
       <c r="J32">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -15398,22 +15686,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>60.71</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
+      <c r="I33" s="2">
+        <v>6.9</v>
+      </c>
       <c r="J33">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -15430,22 +15721,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>26.32</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
+      <c r="I34" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J34">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -15462,22 +15756,25 @@
         <v>31</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>19.35</v>
+      </c>
+      <c r="I35" s="2">
+        <v>7.6</v>
       </c>
       <c r="J35">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -15526,22 +15823,25 @@
         <v>32</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I37" s="2">
+        <v>7.4</v>
       </c>
       <c r="J37">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -15558,22 +15858,25 @@
         <v>33</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>18.18</v>
+      </c>
+      <c r="I38" s="2">
+        <v>7.3</v>
       </c>
       <c r="J38">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -16006,22 +16309,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
       </c>
+      <c r="I52" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J52">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -16038,22 +16344,25 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
       </c>
+      <c r="I53" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J53">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -16364,22 +16673,25 @@
         <v>24</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>95.83</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
       </c>
+      <c r="I63" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J63">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -16725,22 +17037,25 @@
         <v>16</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H74" s="1">
-        <v>0</v>
+        <v>6.25</v>
+      </c>
+      <c r="I74" s="2">
+        <v>8.1</v>
       </c>
       <c r="J74">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -16789,22 +17104,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
       </c>
+      <c r="I76" s="2">
+        <v>9</v>
+      </c>
       <c r="J76">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -16853,22 +17171,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F78">
         <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>38.24</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
       </c>
+      <c r="I78" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J78">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -16885,22 +17206,25 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
       </c>
+      <c r="I79" s="2">
+        <v>6</v>
+      </c>
       <c r="J79">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -17109,22 +17433,25 @@
         <v>28</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G86" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H86" s="1">
-        <v>0</v>
+        <v>28.57</v>
+      </c>
+      <c r="I86" s="2">
+        <v>6.4</v>
       </c>
       <c r="J86">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -17141,22 +17468,25 @@
         <v>32</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>18.75</v>
+      </c>
+      <c r="I87" s="2">
+        <v>7.7</v>
       </c>
       <c r="J87">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -17173,22 +17503,25 @@
         <v>32</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>18.75</v>
+      </c>
+      <c r="I88" s="2">
+        <v>7.5</v>
       </c>
       <c r="J88">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -17205,22 +17538,25 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="I89" s="2">
+        <v>7.3</v>
       </c>
       <c r="J89">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -17237,22 +17573,25 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>8.33</v>
+      </c>
+      <c r="I90" s="2">
+        <v>7.1</v>
       </c>
       <c r="J90">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -17269,22 +17608,25 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="I91" s="2">
+        <v>6</v>
       </c>
       <c r="J91">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -17496,22 +17838,25 @@
         <v>33</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F98">
         <v>0</v>
       </c>
       <c r="G98" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
       </c>
+      <c r="I98" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J98">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -17528,22 +17873,25 @@
         <v>31</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F99">
         <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>83.87</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
       </c>
+      <c r="I99" s="2">
+        <v>6.9</v>
+      </c>
       <c r="J99">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -17560,22 +17908,25 @@
         <v>29</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>89.66</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
       </c>
+      <c r="I100" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J100">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -17592,22 +17943,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F101">
         <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
       </c>
+      <c r="I101" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J101">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -17656,22 +18010,25 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
       </c>
+      <c r="I103" s="2">
+        <v>8</v>
+      </c>
       <c r="J103">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -17688,22 +18045,25 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>51.52</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
+      <c r="I104" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J104">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -17880,22 +18240,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F110">
         <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
       </c>
+      <c r="I110" s="2">
+        <v>9</v>
+      </c>
       <c r="J110">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -17912,22 +18275,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>45.95</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
+      <c r="I111" s="2">
+        <v>9.199999999999999</v>
+      </c>
       <c r="J111">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -17944,22 +18310,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>29.27</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
       </c>
+      <c r="I112" s="2">
+        <v>9.699999999999999</v>
+      </c>
       <c r="J112">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -18209,22 +18578,25 @@
         <v>44</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F120">
         <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
       </c>
+      <c r="I120" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="J120">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -18276,22 +18648,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F122">
         <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
       </c>
+      <c r="I122" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J122">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -18308,22 +18683,25 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
       </c>
+      <c r="I123" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J123">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -18340,25 +18718,25 @@
         <v>32</v>
       </c>
       <c r="E124">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
       <c r="G124" s="1">
-        <v>53.13</v>
+        <v>100</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J124">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>46.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -18375,25 +18753,25 @@
         <v>32</v>
       </c>
       <c r="E125">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F125">
         <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>43.75</v>
+        <v>84.38</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J125">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K125" s="1">
-        <v>56.25</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -18538,22 +18916,25 @@
         <v>38</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H130" s="1">
-        <v>0</v>
+        <v>31.58</v>
+      </c>
+      <c r="I130" s="2">
+        <v>7.6</v>
       </c>
       <c r="J130">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -18602,22 +18983,25 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G132" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H132" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I132" s="2">
+        <v>7</v>
       </c>
       <c r="J132">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -18634,22 +19018,25 @@
         <v>22</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G133" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>0</v>
+        <v>18.18</v>
+      </c>
+      <c r="I133" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J133">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -18666,22 +19053,25 @@
         <v>31</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G134" s="1">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="H134" s="1">
-        <v>0</v>
+        <v>22.58</v>
+      </c>
+      <c r="I134" s="2">
+        <v>7.4</v>
       </c>
       <c r="J134">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -18940,25 +19330,25 @@
         <v>36</v>
       </c>
       <c r="E142">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>50</v>
+        <v>91.67</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I142" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J142">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -18975,25 +19365,25 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F143">
         <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>41.67</v>
+        <v>88.89</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J143">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K143" s="1">
-        <v>58.33</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -19010,25 +19400,25 @@
         <v>28</v>
       </c>
       <c r="E144">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F144">
         <v>0</v>
       </c>
       <c r="G144" s="1">
-        <v>46.43</v>
+        <v>100</v>
       </c>
       <c r="H144" s="1">
         <v>0</v>
       </c>
       <c r="I144" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J144">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>53.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -19045,25 +19435,25 @@
         <v>28</v>
       </c>
       <c r="E145">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>46.43</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J145">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>53.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -19080,25 +19470,25 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F146">
         <v>0</v>
       </c>
       <c r="G146" s="1">
-        <v>36.59</v>
+        <v>87.8</v>
       </c>
       <c r="H146" s="1">
         <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J146">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K146" s="1">
-        <v>63.41</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -19115,25 +19505,25 @@
         <v>16</v>
       </c>
       <c r="E147">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -19185,22 +19575,25 @@
         <v>28</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F149">
         <v>0</v>
       </c>
       <c r="G149" s="1">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
       </c>
+      <c r="I149" s="2">
+        <v>6.8</v>
+      </c>
       <c r="J149">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -19217,22 +19610,25 @@
         <v>20</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F150">
         <v>0</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H150" s="1">
         <v>0</v>
       </c>
+      <c r="I150" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J150">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -19537,22 +19933,25 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G160" s="1">
-        <v>0</v>
+        <v>85.19</v>
       </c>
       <c r="H160" s="1">
-        <v>0</v>
+        <v>14.81</v>
+      </c>
+      <c r="I160" s="2">
+        <v>7.1</v>
       </c>
       <c r="J160">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -19569,22 +19968,25 @@
         <v>19</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G161" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H161" s="1">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="I161" s="2">
+        <v>6.7</v>
       </c>
       <c r="J161">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -19601,22 +20003,25 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G162" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H162" s="1">
-        <v>0</v>
+        <v>29.17</v>
+      </c>
+      <c r="I162" s="2">
+        <v>6.3</v>
       </c>
       <c r="J162">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -19633,22 +20038,25 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G163" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H163" s="1">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="I163" s="2">
+        <v>7.4</v>
       </c>
       <c r="J163">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -19953,22 +20361,25 @@
         <v>37</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G173" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>0</v>
+        <v>13.51</v>
+      </c>
+      <c r="I173" s="2">
+        <v>7.4</v>
       </c>
       <c r="J173">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -20081,22 +20492,25 @@
         <v>20</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
       </c>
+      <c r="I177" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J177">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -20113,22 +20527,25 @@
         <v>20</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
       </c>
+      <c r="I178" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J178">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -20145,22 +20562,25 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F179">
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
       </c>
+      <c r="I179" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J179">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -20689,22 +21109,25 @@
         <v>32</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G196" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H196" s="1">
-        <v>0</v>
+        <v>34.38</v>
+      </c>
+      <c r="I196" s="2">
+        <v>6.6</v>
       </c>
       <c r="J196">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -20721,22 +21144,25 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H197" s="1">
-        <v>0</v>
+        <v>27.78</v>
+      </c>
+      <c r="I197" s="2">
+        <v>6.7</v>
       </c>
       <c r="J197">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -20753,22 +21179,25 @@
         <v>31</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H198" s="1">
-        <v>0</v>
+        <v>29.03</v>
+      </c>
+      <c r="I198" s="2">
+        <v>7</v>
       </c>
       <c r="J198">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -20785,22 +21214,25 @@
         <v>37</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I199" s="2">
+        <v>8.9</v>
       </c>
       <c r="J199">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -20887,22 +21319,25 @@
         <v>35</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F202">
         <v>0</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
       </c>
+      <c r="I202" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J202">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -20919,22 +21354,25 @@
         <v>33</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>3.03</v>
+      </c>
+      <c r="I203" s="2">
+        <v>9</v>
       </c>
       <c r="J203">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -20951,22 +21389,25 @@
         <v>33</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>3.03</v>
+      </c>
+      <c r="I204" s="2">
+        <v>9</v>
       </c>
       <c r="J204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -20983,22 +21424,25 @@
         <v>32</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G205" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H205" s="1">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="I205" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J205">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -873,25 +873,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1363,22 +1363,25 @@
         <v>44</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
+      <c r="I16" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J16">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1395,22 +1398,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.6</v>
       </c>
       <c r="J17">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1427,22 +1433,25 @@
         <v>35</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>8.57</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1567,22 +1576,22 @@
         <v>34</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
         <v>91.89</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1599,22 +1608,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
+      <c r="I23" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J23">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2048,22 +2060,25 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>31.25</v>
+      </c>
+      <c r="I36" s="2">
+        <v>7.2</v>
       </c>
       <c r="J36">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2150,22 +2165,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>39.47</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
       </c>
+      <c r="I39" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J39">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2182,22 +2200,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
       </c>
+      <c r="I40" s="2">
+        <v>6.7</v>
+      </c>
       <c r="J40">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2214,22 +2235,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
       </c>
+      <c r="I41" s="2">
+        <v>7.2</v>
+      </c>
       <c r="J41">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2246,22 +2270,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
       </c>
+      <c r="I42" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J42">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2278,22 +2305,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
       </c>
+      <c r="I43" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J43">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2310,22 +2340,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
       </c>
+      <c r="I44" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J44">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2342,22 +2375,25 @@
         <v>44</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
       </c>
+      <c r="I45" s="2">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J45">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2374,22 +2410,25 @@
         <v>44</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
       </c>
+      <c r="I46" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J46">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2406,22 +2445,25 @@
         <v>35</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
       </c>
+      <c r="I47" s="2">
+        <v>9.5</v>
+      </c>
       <c r="J47">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2438,22 +2480,25 @@
         <v>33</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
       </c>
+      <c r="I48" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="J48">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2470,22 +2515,25 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
       </c>
+      <c r="I49" s="2">
+        <v>9</v>
+      </c>
       <c r="J49">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2502,22 +2550,25 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
       </c>
+      <c r="I50" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J50">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2534,22 +2585,25 @@
         <v>29</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
+      <c r="I51" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J51">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3070,22 +3124,25 @@
         <v>32</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
       </c>
+      <c r="I67" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J67">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3102,22 +3159,25 @@
         <v>44</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
       </c>
+      <c r="I68" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J68">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3134,22 +3194,25 @@
         <v>37</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
       </c>
+      <c r="I69" s="2">
+        <v>8</v>
+      </c>
       <c r="J69">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3166,22 +3229,25 @@
         <v>32</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
       </c>
+      <c r="I70" s="2">
+        <v>7.6</v>
+      </c>
       <c r="J70">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3198,22 +3264,25 @@
         <v>44</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
       </c>
+      <c r="I71" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J71">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3230,22 +3299,25 @@
         <v>36</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>27.78</v>
+      </c>
+      <c r="I72" s="2">
+        <v>6.2</v>
       </c>
       <c r="J72">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3262,22 +3334,25 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
       </c>
+      <c r="I73" s="2">
+        <v>7</v>
+      </c>
       <c r="J73">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3361,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
       </c>
       <c r="I76" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J76">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K76" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3900,22 +3975,25 @@
         <v>32</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F92">
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
       </c>
+      <c r="I92" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J92">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -3932,22 +4010,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
       </c>
+      <c r="I93" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J93">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -3999,22 +4080,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
       </c>
+      <c r="I95" s="2">
+        <v>9.5</v>
+      </c>
       <c r="J95">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -4031,22 +4115,25 @@
         <v>19</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96">
         <v>0</v>
       </c>
       <c r="G96" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
       </c>
+      <c r="I96" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J96">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K96" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4063,22 +4150,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
       </c>
+      <c r="I97" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J97">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -4235,22 +4325,25 @@
         <v>31</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
       </c>
+      <c r="I102" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J102">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4337,22 +4430,25 @@
         <v>32</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H105" s="1">
-        <v>0</v>
+        <v>3.13</v>
+      </c>
+      <c r="I105" s="2">
+        <v>6.3</v>
       </c>
       <c r="J105">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -4369,22 +4465,25 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H106" s="1">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="I106" s="2">
+        <v>6.3</v>
       </c>
       <c r="J106">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4401,22 +4500,25 @@
         <v>32</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>6.25</v>
+      </c>
+      <c r="I107" s="2">
+        <v>6.4</v>
       </c>
       <c r="J107">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4433,22 +4535,25 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>31.58</v>
+      </c>
+      <c r="I108" s="2">
+        <v>6.4</v>
       </c>
       <c r="J108">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4465,22 +4570,25 @@
         <v>32</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I109" s="2">
+        <v>6.6</v>
       </c>
       <c r="J109">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4707,22 +4815,25 @@
         <v>22</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H116" s="1">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="I116" s="2">
+        <v>9</v>
       </c>
       <c r="J116">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -4739,22 +4850,25 @@
         <v>22</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H117" s="1">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="I117" s="2">
+        <v>9</v>
       </c>
       <c r="J117">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -4771,22 +4885,25 @@
         <v>33</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>30.3</v>
+      </c>
+      <c r="I118" s="2">
+        <v>6.9</v>
       </c>
       <c r="J118">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -4803,22 +4920,25 @@
         <v>33</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G119" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
+        <v>30.3</v>
+      </c>
+      <c r="I119" s="2">
+        <v>6.9</v>
       </c>
       <c r="J119">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -5013,22 +5133,22 @@
         <v>27</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G125" s="1">
         <v>84.38</v>
       </c>
       <c r="H125" s="1">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="I125" s="2">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="J125">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5045,22 +5165,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F126">
         <v>0</v>
       </c>
       <c r="G126" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
       </c>
+      <c r="I126" s="2">
+        <v>7.1</v>
+      </c>
       <c r="J126">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5077,22 +5200,25 @@
         <v>28</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F127">
         <v>0</v>
       </c>
       <c r="G127" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
       </c>
+      <c r="I127" s="2">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J127">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5109,22 +5235,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F128">
         <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
       </c>
+      <c r="I128" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J128">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5141,22 +5270,25 @@
         <v>19</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F129">
         <v>0</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
       </c>
+      <c r="I129" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J129">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5208,22 +5340,25 @@
         <v>35</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H131" s="1">
-        <v>0</v>
+        <v>22.86</v>
+      </c>
+      <c r="I131" s="2">
+        <v>8.1</v>
       </c>
       <c r="J131">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5345,22 +5480,25 @@
         <v>33</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G135" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H135" s="1">
-        <v>0</v>
+        <v>12.12</v>
+      </c>
+      <c r="I135" s="2">
+        <v>8.6</v>
       </c>
       <c r="J135">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -5797,25 +5935,25 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F148">
         <v>0</v>
       </c>
       <c r="G148" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J148">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K148" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5902,22 +6040,25 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F151">
         <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
       </c>
+      <c r="I151" s="2">
+        <v>6.8</v>
+      </c>
       <c r="J151">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -5934,22 +6075,25 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F152">
         <v>0</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
       </c>
+      <c r="I152" s="2">
+        <v>7.2</v>
+      </c>
       <c r="J152">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -5966,22 +6110,25 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F153">
         <v>0</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="H153" s="1">
         <v>0</v>
       </c>
+      <c r="I153" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J153">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -5998,22 +6145,25 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F154">
         <v>0</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
       </c>
+      <c r="I154" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J154">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6030,22 +6180,25 @@
         <v>35</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F155">
         <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
       </c>
+      <c r="I155" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J155">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6062,22 +6215,25 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
       </c>
+      <c r="I156" s="2">
+        <v>8.1</v>
+      </c>
       <c r="J156">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -6094,22 +6250,25 @@
         <v>40</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F157">
         <v>0</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H157" s="1">
         <v>0</v>
       </c>
+      <c r="I157" s="2">
+        <v>8.300000000000001</v>
+      </c>
       <c r="J157">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6126,22 +6285,25 @@
         <v>29</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F158">
         <v>0</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
       </c>
+      <c r="I158" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J158">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6158,22 +6320,25 @@
         <v>32</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
       </c>
+      <c r="I159" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J159">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -6330,22 +6495,25 @@
         <v>32</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G164" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H164" s="1">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="I164" s="2">
+        <v>5.9</v>
       </c>
       <c r="J164">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -6362,22 +6530,25 @@
         <v>36</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G165" s="1">
-        <v>0</v>
+        <v>86.11</v>
       </c>
       <c r="H165" s="1">
-        <v>0</v>
+        <v>13.89</v>
+      </c>
+      <c r="I165" s="2">
+        <v>5.9</v>
       </c>
       <c r="J165">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -6394,22 +6565,25 @@
         <v>33</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G166" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H166" s="1">
-        <v>0</v>
+        <v>12.12</v>
+      </c>
+      <c r="I166" s="2">
+        <v>6</v>
       </c>
       <c r="J166">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -6653,22 +6827,25 @@
         <v>31</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G174" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H174" s="1">
-        <v>0</v>
+        <v>25.81</v>
+      </c>
+      <c r="I174" s="2">
+        <v>6.5</v>
       </c>
       <c r="J174">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -6685,22 +6862,25 @@
         <v>19</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G175" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H175" s="1">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="I175" s="2">
+        <v>6.9</v>
       </c>
       <c r="J175">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -6717,22 +6897,25 @@
         <v>19</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G176" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="I176" s="2">
+        <v>6.9</v>
       </c>
       <c r="J176">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6854,22 +7037,25 @@
         <v>32</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
+      <c r="I180" s="2">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J180">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -6886,22 +7072,25 @@
         <v>32</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>21.88</v>
+      </c>
+      <c r="I181" s="2">
+        <v>7.6</v>
       </c>
       <c r="J181">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -6918,22 +7107,25 @@
         <v>33</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G182" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H182" s="1">
-        <v>0</v>
+        <v>51.52</v>
+      </c>
+      <c r="I182" s="2">
+        <v>5.9</v>
       </c>
       <c r="J182">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7238,22 +7430,25 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F192">
         <v>0</v>
       </c>
       <c r="G192" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
       </c>
+      <c r="I192" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J192">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -7270,22 +7465,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
       <c r="G193" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
       </c>
+      <c r="I193" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J193">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -7302,22 +7500,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F194">
         <v>0</v>
       </c>
       <c r="G194" s="1">
-        <v>0</v>
+        <v>75.61</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
       </c>
+      <c r="I194" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J194">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -7334,22 +7535,25 @@
         <v>17</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G195" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H195" s="1">
-        <v>0</v>
+        <v>29.41</v>
+      </c>
+      <c r="I195" s="2">
+        <v>5.7</v>
       </c>
       <c r="J195">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -7911,19 +8115,19 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
       <c r="H2" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -8359,19 +8563,19 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="J16">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -8391,19 +8595,19 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="J17">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -8423,19 +8627,19 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>97.14</v>
       </c>
       <c r="J18">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -8551,19 +8755,19 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>91.89</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -8583,19 +8787,19 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="J23">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -8999,19 +9203,19 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="J36">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -9095,19 +9299,19 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>39.47</v>
       </c>
       <c r="J39">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -9127,19 +9331,19 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J40">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -9159,19 +9363,19 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="J41">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -9191,19 +9395,19 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="J42">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -9223,19 +9427,19 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="J43">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -9255,19 +9459,19 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="J44">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -9287,19 +9491,19 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -9319,19 +9523,19 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J46">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -9351,19 +9555,19 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="J47">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -9383,19 +9587,19 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -9415,19 +9619,19 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J49">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -9447,19 +9651,19 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J50">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -9479,19 +9683,19 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="J51">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -9991,19 +10195,19 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="J67">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -10023,19 +10227,19 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="J68">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -10055,19 +10259,19 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="J69">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10087,19 +10291,19 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="J70">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -10119,19 +10323,19 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="J71">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -10151,19 +10355,19 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J72">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -10183,19 +10387,19 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="J73">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -10279,19 +10483,19 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="J76">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K76" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -10791,19 +10995,19 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="J92">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -10823,19 +11027,19 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G93" s="1">
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="J93">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -10887,19 +11091,19 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G95" s="1">
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="J95">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -10919,19 +11123,19 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G96" s="1">
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="J96">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K96" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -10951,19 +11155,19 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G97" s="1">
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="J97">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -11111,19 +11315,19 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G102" s="1">
         <v>0</v>
       </c>
       <c r="H102" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J102">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -11207,19 +11411,19 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G105" s="1">
         <v>0</v>
       </c>
       <c r="H105" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J105">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -11239,19 +11443,19 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G106" s="1">
         <v>0</v>
       </c>
       <c r="H106" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J106">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11271,19 +11475,19 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G107" s="1">
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J107">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -11303,19 +11507,19 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G108" s="1">
         <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J108">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -11335,19 +11539,19 @@
         <v>0</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G109" s="1">
         <v>0</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J109">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -11559,19 +11763,19 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G116" s="1">
         <v>0</v>
       </c>
       <c r="H116" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J116">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -11591,19 +11795,19 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G117" s="1">
         <v>0</v>
       </c>
       <c r="H117" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J117">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -11623,19 +11827,19 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G118" s="1">
         <v>0</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J118">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -11655,19 +11859,19 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G119" s="1">
         <v>0</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J119">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -11847,19 +12051,19 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G125" s="1">
         <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="J125">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -11879,19 +12083,19 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G126" s="1">
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="J126">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -11911,19 +12115,19 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G127" s="1">
         <v>0</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="J127">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -11943,19 +12147,19 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G128" s="1">
         <v>0</v>
       </c>
       <c r="H128" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="J128">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -11975,19 +12179,19 @@
         <v>0</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G129" s="1">
         <v>0</v>
       </c>
       <c r="H129" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="J129">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -12039,19 +12243,19 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
       </c>
       <c r="H131" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J131">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -12167,19 +12371,19 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G135" s="1">
         <v>0</v>
       </c>
       <c r="H135" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J135">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -12583,19 +12787,19 @@
         <v>0</v>
       </c>
       <c r="F148">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G148" s="1">
         <v>0</v>
       </c>
       <c r="H148" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="J148">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K148" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -12679,19 +12883,19 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G151" s="1">
         <v>0</v>
       </c>
       <c r="H151" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="J151">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -12711,19 +12915,19 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G152" s="1">
         <v>0</v>
       </c>
       <c r="H152" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="J152">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -12743,19 +12947,19 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G153" s="1">
         <v>0</v>
       </c>
       <c r="H153" s="1">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="J153">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -12775,19 +12979,19 @@
         <v>0</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G154" s="1">
         <v>0</v>
       </c>
       <c r="H154" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="J154">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -12807,19 +13011,19 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G155" s="1">
         <v>0</v>
       </c>
       <c r="H155" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="J155">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -12839,19 +13043,19 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G156" s="1">
         <v>0</v>
       </c>
       <c r="H156" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="J156">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -12871,19 +13075,19 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G157" s="1">
         <v>0</v>
       </c>
       <c r="H157" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J157">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -12903,19 +13107,19 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G158" s="1">
         <v>0</v>
       </c>
       <c r="H158" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="J158">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -12935,19 +13139,19 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G159" s="1">
         <v>0</v>
       </c>
       <c r="H159" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="J159">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -13095,19 +13299,19 @@
         <v>0</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G164" s="1">
         <v>0</v>
       </c>
       <c r="H164" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J164">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -13127,19 +13331,19 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G165" s="1">
         <v>0</v>
       </c>
       <c r="H165" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J165">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -13159,19 +13363,19 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
       </c>
       <c r="H166" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J166">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -13415,19 +13619,19 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
       </c>
       <c r="H174" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="J174">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -13447,19 +13651,19 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
       </c>
       <c r="H175" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="J175">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -13479,19 +13683,19 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="J176">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -13607,19 +13811,19 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>
       </c>
       <c r="H180" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="J180">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -13639,19 +13843,19 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G181" s="1">
         <v>0</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="J181">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -13671,19 +13875,19 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G182" s="1">
         <v>0</v>
       </c>
       <c r="H182" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J182">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -13991,19 +14195,19 @@
         <v>0</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G192" s="1">
         <v>0</v>
       </c>
       <c r="H192" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="J192">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -14023,19 +14227,19 @@
         <v>0</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G193" s="1">
         <v>0</v>
       </c>
       <c r="H193" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="J193">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -14055,19 +14259,19 @@
         <v>0</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G194" s="1">
         <v>0</v>
       </c>
       <c r="H194" s="1">
-        <v>0</v>
+        <v>75.61</v>
       </c>
       <c r="J194">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -14087,19 +14291,19 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G195" s="1">
         <v>0</v>
       </c>
       <c r="H195" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J195">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -14616,25 +14820,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -15106,22 +15310,25 @@
         <v>44</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
+      <c r="I16" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J16">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -15138,22 +15345,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.7</v>
       </c>
       <c r="J17">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -15170,22 +15380,25 @@
         <v>35</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>8.57</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15310,22 +15523,22 @@
         <v>34</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
         <v>91.89</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -15342,22 +15555,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
+      <c r="I23" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J23">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -15791,22 +16007,25 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>31.25</v>
+      </c>
+      <c r="I36" s="2">
+        <v>7.2</v>
       </c>
       <c r="J36">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -15893,22 +16112,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>39.47</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
       </c>
+      <c r="I39" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J39">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -15925,22 +16147,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
       </c>
+      <c r="I40" s="2">
+        <v>6.7</v>
+      </c>
       <c r="J40">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -15957,22 +16182,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
       </c>
+      <c r="I41" s="2">
+        <v>7.2</v>
+      </c>
       <c r="J41">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -15989,22 +16217,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
       </c>
+      <c r="I42" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J42">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -16021,22 +16252,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
       </c>
+      <c r="I43" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J43">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -16053,22 +16287,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
       </c>
+      <c r="I44" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J44">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -16085,22 +16322,25 @@
         <v>44</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
       </c>
+      <c r="I45" s="2">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J45">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -16117,22 +16357,25 @@
         <v>44</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
       </c>
+      <c r="I46" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J46">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -16149,22 +16392,25 @@
         <v>35</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
       </c>
+      <c r="I47" s="2">
+        <v>9.5</v>
+      </c>
       <c r="J47">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -16181,22 +16427,25 @@
         <v>33</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
       </c>
+      <c r="I48" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="J48">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -16213,22 +16462,25 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
       </c>
+      <c r="I49" s="2">
+        <v>9</v>
+      </c>
       <c r="J49">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -16245,22 +16497,25 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
       </c>
+      <c r="I50" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J50">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -16277,22 +16532,25 @@
         <v>29</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
+      <c r="I51" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J51">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -16813,22 +17071,25 @@
         <v>32</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
       </c>
+      <c r="I67" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J67">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -16845,22 +17106,25 @@
         <v>44</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
       </c>
+      <c r="I68" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J68">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -16877,22 +17141,25 @@
         <v>37</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
       </c>
+      <c r="I69" s="2">
+        <v>8</v>
+      </c>
       <c r="J69">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -16909,22 +17176,25 @@
         <v>32</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
       </c>
+      <c r="I70" s="2">
+        <v>7.6</v>
+      </c>
       <c r="J70">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -16941,22 +17211,25 @@
         <v>44</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
       </c>
+      <c r="I71" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J71">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -16973,22 +17246,25 @@
         <v>36</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>27.78</v>
+      </c>
+      <c r="I72" s="2">
+        <v>6.2</v>
       </c>
       <c r="J72">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -17005,22 +17281,25 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
       </c>
+      <c r="I73" s="2">
+        <v>7</v>
+      </c>
       <c r="J73">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -17104,25 +17383,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
       </c>
       <c r="I76" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J76">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K76" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -17643,22 +17922,25 @@
         <v>32</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F92">
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
       </c>
+      <c r="I92" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J92">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -17675,22 +17957,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
       </c>
+      <c r="I93" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J93">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -17742,22 +18027,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
       </c>
+      <c r="I95" s="2">
+        <v>9.5</v>
+      </c>
       <c r="J95">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -17774,22 +18062,25 @@
         <v>19</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96">
         <v>0</v>
       </c>
       <c r="G96" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
       </c>
+      <c r="I96" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J96">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K96" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -17806,22 +18097,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
       </c>
+      <c r="I97" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J97">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -17978,22 +18272,25 @@
         <v>31</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
       </c>
+      <c r="I102" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J102">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -18080,22 +18377,25 @@
         <v>32</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H105" s="1">
-        <v>0</v>
+        <v>3.13</v>
+      </c>
+      <c r="I105" s="2">
+        <v>6.3</v>
       </c>
       <c r="J105">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -18112,22 +18412,25 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H106" s="1">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="I106" s="2">
+        <v>6.3</v>
       </c>
       <c r="J106">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18144,22 +18447,25 @@
         <v>32</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>6.25</v>
+      </c>
+      <c r="I107" s="2">
+        <v>6.4</v>
       </c>
       <c r="J107">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -18176,22 +18482,25 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>31.58</v>
+      </c>
+      <c r="I108" s="2">
+        <v>6.4</v>
       </c>
       <c r="J108">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -18208,22 +18517,25 @@
         <v>32</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="I109" s="2">
+        <v>6.6</v>
       </c>
       <c r="J109">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -18450,22 +18762,25 @@
         <v>22</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H116" s="1">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="I116" s="2">
+        <v>9</v>
       </c>
       <c r="J116">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -18482,22 +18797,25 @@
         <v>22</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H117" s="1">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="I117" s="2">
+        <v>9</v>
       </c>
       <c r="J117">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -18514,22 +18832,25 @@
         <v>33</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>30.3</v>
+      </c>
+      <c r="I118" s="2">
+        <v>6.9</v>
       </c>
       <c r="J118">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -18546,22 +18867,25 @@
         <v>33</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G119" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
+        <v>30.3</v>
+      </c>
+      <c r="I119" s="2">
+        <v>6.9</v>
       </c>
       <c r="J119">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -18756,22 +19080,22 @@
         <v>27</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G125" s="1">
         <v>84.38</v>
       </c>
       <c r="H125" s="1">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="I125" s="2">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="J125">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -18788,22 +19112,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F126">
         <v>0</v>
       </c>
       <c r="G126" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
       </c>
+      <c r="I126" s="2">
+        <v>7.1</v>
+      </c>
       <c r="J126">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -18820,22 +19147,25 @@
         <v>28</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F127">
         <v>0</v>
       </c>
       <c r="G127" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
       </c>
+      <c r="I127" s="2">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J127">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -18852,22 +19182,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F128">
         <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
       </c>
+      <c r="I128" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J128">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -18884,22 +19217,25 @@
         <v>19</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F129">
         <v>0</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
       </c>
+      <c r="I129" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J129">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -18951,22 +19287,25 @@
         <v>35</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H131" s="1">
-        <v>0</v>
+        <v>22.86</v>
+      </c>
+      <c r="I131" s="2">
+        <v>8.1</v>
       </c>
       <c r="J131">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -19088,22 +19427,25 @@
         <v>33</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G135" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H135" s="1">
-        <v>0</v>
+        <v>12.12</v>
+      </c>
+      <c r="I135" s="2">
+        <v>8.6</v>
       </c>
       <c r="J135">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -19540,25 +19882,25 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F148">
         <v>0</v>
       </c>
       <c r="G148" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J148">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K148" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -19645,22 +19987,25 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F151">
         <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
       </c>
+      <c r="I151" s="2">
+        <v>6.8</v>
+      </c>
       <c r="J151">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -19677,22 +20022,25 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F152">
         <v>0</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
       </c>
+      <c r="I152" s="2">
+        <v>7.2</v>
+      </c>
       <c r="J152">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -19709,22 +20057,25 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F153">
         <v>0</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="H153" s="1">
         <v>0</v>
       </c>
+      <c r="I153" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J153">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -19741,22 +20092,25 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F154">
         <v>0</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
       </c>
+      <c r="I154" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J154">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -19773,22 +20127,25 @@
         <v>35</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F155">
         <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
       </c>
+      <c r="I155" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J155">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -19805,22 +20162,25 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
       </c>
+      <c r="I156" s="2">
+        <v>8.1</v>
+      </c>
       <c r="J156">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -19837,22 +20197,25 @@
         <v>40</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F157">
         <v>0</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H157" s="1">
         <v>0</v>
       </c>
+      <c r="I157" s="2">
+        <v>8.300000000000001</v>
+      </c>
       <c r="J157">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -19869,22 +20232,25 @@
         <v>29</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F158">
         <v>0</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
       </c>
+      <c r="I158" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J158">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -19901,22 +20267,25 @@
         <v>32</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
       </c>
+      <c r="I159" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J159">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -20073,22 +20442,25 @@
         <v>32</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G164" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H164" s="1">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="I164" s="2">
+        <v>5.9</v>
       </c>
       <c r="J164">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -20105,22 +20477,25 @@
         <v>36</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G165" s="1">
-        <v>0</v>
+        <v>86.11</v>
       </c>
       <c r="H165" s="1">
-        <v>0</v>
+        <v>13.89</v>
+      </c>
+      <c r="I165" s="2">
+        <v>5.9</v>
       </c>
       <c r="J165">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -20137,22 +20512,25 @@
         <v>33</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G166" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H166" s="1">
-        <v>0</v>
+        <v>12.12</v>
+      </c>
+      <c r="I166" s="2">
+        <v>6</v>
       </c>
       <c r="J166">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -20396,22 +20774,25 @@
         <v>31</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G174" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H174" s="1">
-        <v>0</v>
+        <v>25.81</v>
+      </c>
+      <c r="I174" s="2">
+        <v>6.5</v>
       </c>
       <c r="J174">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -20428,22 +20809,25 @@
         <v>19</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G175" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H175" s="1">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="I175" s="2">
+        <v>6.9</v>
       </c>
       <c r="J175">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -20460,22 +20844,25 @@
         <v>19</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G176" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="I176" s="2">
+        <v>6.9</v>
       </c>
       <c r="J176">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -20597,22 +20984,25 @@
         <v>32</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
+      <c r="I180" s="2">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J180">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -20629,22 +21019,25 @@
         <v>32</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>21.88</v>
+      </c>
+      <c r="I181" s="2">
+        <v>7.6</v>
       </c>
       <c r="J181">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -20661,22 +21054,25 @@
         <v>33</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G182" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H182" s="1">
-        <v>0</v>
+        <v>51.52</v>
+      </c>
+      <c r="I182" s="2">
+        <v>5.9</v>
       </c>
       <c r="J182">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -20981,22 +21377,25 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F192">
         <v>0</v>
       </c>
       <c r="G192" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
       </c>
+      <c r="I192" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J192">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -21013,22 +21412,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
       <c r="G193" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
       </c>
+      <c r="I193" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J193">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -21045,22 +21447,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F194">
         <v>0</v>
       </c>
       <c r="G194" s="1">
-        <v>0</v>
+        <v>75.61</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
       </c>
+      <c r="I194" s="2">
+        <v>6.4</v>
+      </c>
       <c r="J194">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -21077,22 +21482,25 @@
         <v>17</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G195" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H195" s="1">
-        <v>0</v>
+        <v>29.41</v>
+      </c>
+      <c r="I195" s="2">
+        <v>5.7</v>
       </c>
       <c r="J195">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -978,25 +978,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8211,19 +8211,19 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -14925,25 +14925,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>31.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1853,22 +1853,25 @@
         <v>32</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
       </c>
+      <c r="I30" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J30">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2165,25 +2168,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>39.47</v>
+        <v>78.95</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J39">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K39" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2200,25 +2203,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J40">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K40" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2235,25 +2238,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>19.35</v>
+        <v>70.97</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J41">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K41" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2270,25 +2273,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J42">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K42" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2305,25 +2308,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>53.13</v>
+        <v>78.13</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J43">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K43" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2340,25 +2343,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>56.25</v>
+        <v>71.88</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J44">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K44" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2690,22 +2693,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
       </c>
+      <c r="I54" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J54">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2792,22 +2798,25 @@
         <v>32</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
       </c>
+      <c r="I57" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J57">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2824,22 +2833,25 @@
         <v>44</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
       </c>
+      <c r="I58" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J58">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2856,22 +2868,25 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
       </c>
+      <c r="I59" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J59">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2888,22 +2903,25 @@
         <v>37</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
       </c>
+      <c r="I60" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J60">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2920,22 +2938,25 @@
         <v>32</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
       </c>
+      <c r="I61" s="2">
+        <v>8</v>
+      </c>
       <c r="J61">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2952,22 +2973,25 @@
         <v>44</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
       </c>
+      <c r="I62" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J62">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3404,22 +3428,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>3.33</v>
+      </c>
+      <c r="I75" s="2">
+        <v>7.5</v>
       </c>
       <c r="J75">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3436,25 +3463,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="1">
-        <v>10.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H76" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I76" s="2">
         <v>8</v>
       </c>
       <c r="J76">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K76" s="1">
-        <v>89.29000000000001</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3471,22 +3498,25 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>36.84</v>
+      </c>
+      <c r="I77" s="2">
+        <v>7.1</v>
       </c>
       <c r="J77">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3573,22 +3603,25 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
       </c>
+      <c r="I80" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J80">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K80" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3605,22 +3638,25 @@
         <v>37</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
       </c>
+      <c r="I81" s="2">
+        <v>8.300000000000001</v>
+      </c>
       <c r="J81">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K81" s="1">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3637,22 +3673,25 @@
         <v>36</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
       </c>
+      <c r="I82" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J82">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3669,22 +3708,25 @@
         <v>33</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
       </c>
+      <c r="I83" s="2">
+        <v>7.6</v>
+      </c>
       <c r="J83">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3701,22 +3743,25 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
       </c>
+      <c r="I84" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J84">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3733,22 +3778,25 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
       </c>
+      <c r="I85" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J85">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -5865,25 +5913,25 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G146" s="1">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H146" s="1">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="I146" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J146">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K146" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -6110,25 +6158,25 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G153" s="1">
-        <v>40.63</v>
+        <v>87.5</v>
       </c>
       <c r="H153" s="1">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I153" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J153">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>59.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6145,25 +6193,25 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G154" s="1">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H154" s="1">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="I154" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6180,25 +6228,25 @@
         <v>35</v>
       </c>
       <c r="E155">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" s="1">
-        <v>71.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H155" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I155" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J155">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6215,25 +6263,25 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" s="1">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H156" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="I156" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J156">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -6600,22 +6648,25 @@
         <v>32</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F167">
         <v>0</v>
       </c>
       <c r="G167" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H167" s="1">
         <v>0</v>
       </c>
+      <c r="I167" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J167">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -6632,22 +6683,25 @@
         <v>44</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
       <c r="G168" s="1">
-        <v>0</v>
+        <v>97.73</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
       </c>
+      <c r="I168" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J168">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6664,22 +6718,25 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
       </c>
+      <c r="I169" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J169">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6696,22 +6753,25 @@
         <v>37</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
       </c>
+      <c r="I170" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J170">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6728,22 +6788,25 @@
         <v>32</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F171">
         <v>0</v>
       </c>
       <c r="G171" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
       </c>
+      <c r="I171" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J171">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -6760,22 +6823,25 @@
         <v>44</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F172">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
       </c>
+      <c r="I172" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J172">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -7142,22 +7208,25 @@
         <v>37</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
+      <c r="I183" s="2">
+        <v>9</v>
+      </c>
       <c r="J183">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7174,22 +7243,25 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
       </c>
+      <c r="I184" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J184">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7206,22 +7278,25 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F185">
         <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
       </c>
+      <c r="I185" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J185">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7238,22 +7313,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
       </c>
+      <c r="I186" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J186">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7270,22 +7348,25 @@
         <v>20</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F187">
         <v>0</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
       </c>
+      <c r="I187" s="2">
+        <v>7.2</v>
+      </c>
       <c r="J187">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7302,22 +7383,25 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F188">
         <v>0</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
       </c>
+      <c r="I188" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J188">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7334,22 +7418,25 @@
         <v>35</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F189">
         <v>0</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
       </c>
+      <c r="I189" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="J189">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7366,22 +7453,25 @@
         <v>24</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F190">
         <v>0</v>
       </c>
       <c r="G190" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
       </c>
+      <c r="I190" s="2">
+        <v>8.1</v>
+      </c>
       <c r="J190">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7398,22 +7488,25 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
       </c>
+      <c r="I191" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J191">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -9011,19 +9104,19 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -9299,19 +9392,19 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>39.47</v>
+        <v>78.95</v>
       </c>
       <c r="J39">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K39" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -9331,19 +9424,19 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="J40">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K40" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -9363,19 +9456,19 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>19.35</v>
+        <v>70.97</v>
       </c>
       <c r="J41">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K41" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -9395,19 +9488,19 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="J42">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K42" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -9427,19 +9520,19 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>53.13</v>
+        <v>78.13</v>
       </c>
       <c r="J43">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K43" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -9459,19 +9552,19 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>56.25</v>
+        <v>71.88</v>
       </c>
       <c r="J44">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K44" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -9779,19 +9872,19 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="J54">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -9875,19 +9968,19 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="J57">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -9907,19 +10000,19 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="J58">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -9939,19 +10032,19 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J59">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -9971,19 +10064,19 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="J60">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -10003,19 +10096,19 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="J61">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -10035,19 +10128,19 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="J62">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -10451,19 +10544,19 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>43.33</v>
       </c>
       <c r="J75">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -10483,19 +10576,19 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>10.71</v>
+        <v>67.86</v>
       </c>
       <c r="J76">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K76" s="1">
-        <v>89.29000000000001</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -10515,19 +10608,19 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J77">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -10611,19 +10704,19 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="J80">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K80" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -10643,19 +10736,19 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="J81">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K81" s="1">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -10675,19 +10768,19 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="J82">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -10707,19 +10800,19 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="J83">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -10739,19 +10832,19 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G84" s="1">
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="J84">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -10771,19 +10864,19 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G85" s="1">
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="J85">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -12723,19 +12816,19 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G146" s="1">
         <v>0</v>
       </c>
       <c r="H146" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="J146">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K146" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -12947,19 +13040,19 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G153" s="1">
         <v>0</v>
       </c>
       <c r="H153" s="1">
-        <v>40.63</v>
+        <v>100</v>
       </c>
       <c r="J153">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>59.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -12979,19 +13072,19 @@
         <v>0</v>
       </c>
       <c r="F154">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G154" s="1">
         <v>0</v>
       </c>
       <c r="H154" s="1">
-        <v>60.61</v>
+        <v>100</v>
       </c>
       <c r="J154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -13011,19 +13104,19 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G155" s="1">
         <v>0</v>
       </c>
       <c r="H155" s="1">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="J155">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -13043,19 +13136,19 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G156" s="1">
         <v>0</v>
       </c>
       <c r="H156" s="1">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="J156">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -13395,19 +13488,19 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
       </c>
       <c r="H167" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J167">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -13427,19 +13520,19 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G168" s="1">
         <v>0</v>
       </c>
       <c r="H168" s="1">
-        <v>0</v>
+        <v>97.73</v>
       </c>
       <c r="J168">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -13459,19 +13552,19 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G169" s="1">
         <v>0</v>
       </c>
       <c r="H169" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="J169">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -13491,19 +13584,19 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G170" s="1">
         <v>0</v>
       </c>
       <c r="H170" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="J170">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -13523,19 +13616,19 @@
         <v>0</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G171" s="1">
         <v>0</v>
       </c>
       <c r="H171" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="J171">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -13555,19 +13648,19 @@
         <v>0</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
       </c>
       <c r="H172" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="J172">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -13907,19 +14000,19 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G183" s="1">
         <v>0</v>
       </c>
       <c r="H183" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="J183">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -13939,19 +14032,19 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G184" s="1">
         <v>0</v>
       </c>
       <c r="H184" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="J184">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -13971,19 +14064,19 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G185" s="1">
         <v>0</v>
       </c>
       <c r="H185" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J185">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -14003,19 +14096,19 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G186" s="1">
         <v>0</v>
       </c>
       <c r="H186" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="J186">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -14035,19 +14128,19 @@
         <v>0</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G187" s="1">
         <v>0</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J187">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -14067,19 +14160,19 @@
         <v>0</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G188" s="1">
         <v>0</v>
       </c>
       <c r="H188" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="J188">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -14099,19 +14192,19 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G189" s="1">
         <v>0</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="J189">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -14131,19 +14224,19 @@
         <v>0</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G190" s="1">
         <v>0</v>
       </c>
       <c r="H190" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="J190">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -14163,19 +14256,19 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G191" s="1">
         <v>0</v>
       </c>
       <c r="H191" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="J191">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -15800,22 +15893,25 @@
         <v>32</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
       </c>
+      <c r="I30" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J30">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -16112,25 +16208,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>39.47</v>
+        <v>78.95</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J39">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K39" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -16147,25 +16243,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J40">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K40" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -16182,25 +16278,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>19.35</v>
+        <v>70.97</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J41">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K41" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -16217,25 +16313,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J42">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K42" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -16252,25 +16348,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>53.13</v>
+        <v>78.13</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J43">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K43" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -16287,25 +16383,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>56.25</v>
+        <v>71.88</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J44">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K44" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -16637,22 +16733,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
       </c>
+      <c r="I54" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J54">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -16739,22 +16838,25 @@
         <v>32</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
       </c>
+      <c r="I57" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J57">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -16771,22 +16873,25 @@
         <v>44</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
       </c>
+      <c r="I58" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J58">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -16803,22 +16908,25 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
       </c>
+      <c r="I59" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J59">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -16835,22 +16943,25 @@
         <v>37</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
       </c>
+      <c r="I60" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J60">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -16867,22 +16978,25 @@
         <v>32</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
       </c>
+      <c r="I61" s="2">
+        <v>8</v>
+      </c>
       <c r="J61">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -16899,22 +17013,25 @@
         <v>44</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
       </c>
+      <c r="I62" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J62">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -17351,22 +17468,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>3.33</v>
+      </c>
+      <c r="I75" s="2">
+        <v>7.5</v>
       </c>
       <c r="J75">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -17383,25 +17503,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="1">
-        <v>10.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H76" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I76" s="2">
         <v>8</v>
       </c>
       <c r="J76">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K76" s="1">
-        <v>89.29000000000001</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -17418,22 +17538,25 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>36.84</v>
+      </c>
+      <c r="I77" s="2">
+        <v>7.1</v>
       </c>
       <c r="J77">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -17520,22 +17643,25 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F80">
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
       </c>
+      <c r="I80" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J80">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K80" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -17552,22 +17678,25 @@
         <v>37</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F81">
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
       </c>
+      <c r="I81" s="2">
+        <v>8.300000000000001</v>
+      </c>
       <c r="J81">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K81" s="1">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -17584,22 +17713,25 @@
         <v>36</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F82">
         <v>0</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
       </c>
+      <c r="I82" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J82">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -17616,22 +17748,25 @@
         <v>33</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
       </c>
+      <c r="I83" s="2">
+        <v>7.6</v>
+      </c>
       <c r="J83">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -17648,22 +17783,25 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
       </c>
+      <c r="I84" s="2">
+        <v>7.3</v>
+      </c>
       <c r="J84">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -17680,22 +17818,25 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F85">
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
       </c>
+      <c r="I85" s="2">
+        <v>7.7</v>
+      </c>
       <c r="J85">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -19812,25 +19953,25 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G146" s="1">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H146" s="1">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="I146" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J146">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K146" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -20057,25 +20198,25 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G153" s="1">
-        <v>40.63</v>
+        <v>87.5</v>
       </c>
       <c r="H153" s="1">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I153" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J153">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>59.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -20092,25 +20233,25 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G154" s="1">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H154" s="1">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="I154" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J154">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -20127,25 +20268,25 @@
         <v>35</v>
       </c>
       <c r="E155">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" s="1">
-        <v>71.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H155" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I155" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J155">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -20162,25 +20303,25 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" s="1">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H156" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="I156" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J156">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -20547,22 +20688,25 @@
         <v>32</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F167">
         <v>0</v>
       </c>
       <c r="G167" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H167" s="1">
         <v>0</v>
       </c>
+      <c r="I167" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J167">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -20579,22 +20723,25 @@
         <v>44</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
       <c r="G168" s="1">
-        <v>0</v>
+        <v>97.73</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
       </c>
+      <c r="I168" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J168">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -20611,22 +20758,25 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
       </c>
+      <c r="I169" s="2">
+        <v>8.699999999999999</v>
+      </c>
       <c r="J169">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -20643,22 +20793,25 @@
         <v>37</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
       </c>
+      <c r="I170" s="2">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J170">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -20675,22 +20828,25 @@
         <v>32</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F171">
         <v>0</v>
       </c>
       <c r="G171" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
       </c>
+      <c r="I171" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J171">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -20707,22 +20863,25 @@
         <v>44</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F172">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
       </c>
+      <c r="I172" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J172">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -21089,22 +21248,25 @@
         <v>37</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
+      <c r="I183" s="2">
+        <v>9</v>
+      </c>
       <c r="J183">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -21121,22 +21283,25 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
       </c>
+      <c r="I184" s="2">
+        <v>8.9</v>
+      </c>
       <c r="J184">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -21153,22 +21318,25 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F185">
         <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
       </c>
+      <c r="I185" s="2">
+        <v>7.5</v>
+      </c>
       <c r="J185">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -21185,22 +21353,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
       </c>
+      <c r="I186" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J186">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -21217,22 +21388,25 @@
         <v>20</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F187">
         <v>0</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
       </c>
+      <c r="I187" s="2">
+        <v>7.2</v>
+      </c>
       <c r="J187">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -21249,22 +21423,25 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F188">
         <v>0</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
       </c>
+      <c r="I188" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J188">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -21281,22 +21458,25 @@
         <v>35</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F189">
         <v>0</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
       </c>
+      <c r="I189" s="2">
+        <v>9.300000000000001</v>
+      </c>
       <c r="J189">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -21313,22 +21493,25 @@
         <v>24</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F190">
         <v>0</v>
       </c>
       <c r="G190" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
       </c>
+      <c r="I190" s="2">
+        <v>8.1</v>
+      </c>
       <c r="J190">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -21345,22 +21528,25 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
       </c>
+      <c r="I191" s="2">
+        <v>8.5</v>
+      </c>
       <c r="J191">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="192" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -3568,25 +3568,25 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
       </c>
       <c r="I79" s="2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="J79">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K79" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -10672,19 +10672,19 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="J79">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K79" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -17608,25 +17608,25 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
       </c>
       <c r="I79" s="2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="J79">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K79" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -2658,13 +2658,13 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -2673,10 +2673,10 @@
         <v>7.9</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3463,25 +3463,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>64.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H76" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I76" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J76">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3533,25 +3533,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>38.24</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H78" s="1">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="I78" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J78">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K78" s="1">
-        <v>61.76</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3568,25 +3568,25 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="1">
-        <v>15.79</v>
+        <v>89.47</v>
       </c>
       <c r="H79" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I79" s="2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J79">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>84.20999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -9840,19 +9840,19 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -10576,19 +10576,19 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>67.86</v>
+        <v>100</v>
       </c>
       <c r="J76">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -10640,19 +10640,19 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>38.24</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="J78">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K78" s="1">
-        <v>61.76</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -10672,19 +10672,19 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>15.79</v>
+        <v>100</v>
       </c>
       <c r="J79">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>84.20999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -16698,13 +16698,13 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -16713,10 +16713,10 @@
         <v>7.9</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -17503,25 +17503,25 @@
         <v>28</v>
       </c>
       <c r="E76">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>64.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H76" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I76" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J76">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -17573,25 +17573,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>38.24</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H78" s="1">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="I78" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J78">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K78" s="1">
-        <v>61.76</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -17608,25 +17608,25 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="1">
-        <v>15.79</v>
+        <v>89.47</v>
       </c>
       <c r="H79" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I79" s="2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J79">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>84.20999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -908,25 +908,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -943,25 +943,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -978,25 +978,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1013,25 +1013,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1048,25 +1048,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1083,25 +1083,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1185,19 +1185,19 @@
         <v>101</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="H11" s="1">
-        <v>16.22</v>
+        <v>16.67</v>
       </c>
       <c r="I11" s="2">
         <v>8</v>
@@ -1366,22 +1366,22 @@
         <v>32</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
         <v>72.73</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>27.27</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1401,22 +1401,22 @@
         <v>28</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1">
         <v>63.64</v>
       </c>
       <c r="H17" s="1">
-        <v>4.55</v>
+        <v>36.36</v>
       </c>
       <c r="I17" s="2">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="J17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1430,7 +1430,7 @@
         <v>103</v>
       </c>
       <c r="D18">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>31</v>
@@ -1439,19 +1439,19 @@
         <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>88.56999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>8.57</v>
+        <v>8.82</v>
       </c>
       <c r="I18" s="2">
         <v>8.6</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1608,25 +1608,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1888,25 +1888,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1923,25 +1923,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1958,25 +1958,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K33" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1993,25 +1993,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2168,25 +2168,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="I39" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2203,25 +2203,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="1">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I40" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2238,25 +2238,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1">
-        <v>70.97</v>
+        <v>83.87</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>16.13</v>
       </c>
       <c r="I41" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J41">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2273,25 +2273,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" s="1">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>26.32</v>
       </c>
       <c r="I42" s="2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2308,25 +2308,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G43" s="1">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="I43" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2343,25 +2343,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I44" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2445,7 +2445,7 @@
         <v>116</v>
       </c>
       <c r="D47">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47">
         <v>33</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -2463,10 +2463,10 @@
         <v>9.5</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2585,28 +2585,28 @@
         <v>117</v>
       </c>
       <c r="D51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J51">
         <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3043,25 +3043,25 @@
         <v>19</v>
       </c>
       <c r="E64">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
       </c>
       <c r="I64" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J64">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3078,25 +3078,25 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
       </c>
       <c r="I65" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3113,25 +3113,25 @@
         <v>33</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
       </c>
       <c r="I66" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J66">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3428,25 +3428,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" s="1">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="H75" s="1">
         <v>3.33</v>
       </c>
       <c r="I75" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J75">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K75" s="1">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3460,22 +3460,22 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E76">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H76" s="1">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="I76" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -3533,13 +3533,13 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F78">
         <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H78" s="1">
         <v>5.88</v>
@@ -3548,10 +3548,10 @@
         <v>8.6</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3635,7 +3635,7 @@
         <v>124</v>
       </c>
       <c r="D81">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E81">
         <v>30</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K81" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4300,28 +4300,28 @@
         <v>120</v>
       </c>
       <c r="D100">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E100">
         <v>26</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="1">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H100" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="I100" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J100">
         <v>3</v>
       </c>
       <c r="K100" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4341,22 +4341,22 @@
         <v>31</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="1">
         <v>88.56999999999999</v>
       </c>
       <c r="H101" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I101" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K101" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4408,25 +4408,25 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G103" s="1">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="I103" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4443,25 +4443,25 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G104" s="1">
-        <v>51.52</v>
+        <v>69.7</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="I104" s="2">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="J104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>48.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4688,25 +4688,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
       <c r="I111" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J111">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K111" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4723,25 +4723,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
       </c>
       <c r="I112" s="2">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J112">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K112" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -5038,25 +5038,25 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F121">
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
       </c>
       <c r="I121" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5108,25 +5108,25 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
       </c>
       <c r="I123" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5245,28 +5245,28 @@
         <v>134</v>
       </c>
       <c r="D127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E127">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" s="1">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="I127" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K127" s="1">
-        <v>17.86</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5283,25 +5283,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F128">
         <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
       </c>
       <c r="I128" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K128" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5385,22 +5385,22 @@
         <v>121</v>
       </c>
       <c r="D131">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E131">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F131">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G131" s="1">
-        <v>77.14</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H131" s="1">
-        <v>22.86</v>
+        <v>17.65</v>
       </c>
       <c r="I131" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -5470,7 +5470,7 @@
         <v>18.18</v>
       </c>
       <c r="I133" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -5598,25 +5598,25 @@
         <v>33</v>
       </c>
       <c r="E137">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G137" s="1">
-        <v>78.79000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="H137" s="1">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="I137" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J137">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -5633,25 +5633,25 @@
         <v>38</v>
       </c>
       <c r="E138">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G138" s="1">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H138" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I138" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J138">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5668,25 +5668,25 @@
         <v>24</v>
       </c>
       <c r="E139">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K139" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5703,25 +5703,25 @@
         <v>31</v>
       </c>
       <c r="E140">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F140">
         <v>0</v>
       </c>
       <c r="G140" s="1">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="H140" s="1">
         <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J140">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -5738,25 +5738,25 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G141" s="1">
-        <v>56.25</v>
+        <v>81.25</v>
       </c>
       <c r="H141" s="1">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="I141" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J141">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>43.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -5811,22 +5811,22 @@
         <v>32</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G143" s="1">
         <v>88.89</v>
       </c>
       <c r="H143" s="1">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="I143" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -5916,22 +5916,22 @@
         <v>37</v>
       </c>
       <c r="F146">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G146" s="1">
         <v>90.23999999999999</v>
       </c>
       <c r="H146" s="1">
-        <v>4.88</v>
+        <v>9.76</v>
       </c>
       <c r="I146" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -5983,25 +5983,25 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" s="1">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H148" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I148" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -6015,28 +6015,28 @@
         <v>124</v>
       </c>
       <c r="D149">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E149">
+        <v>25</v>
+      </c>
+      <c r="F149">
         <v>4</v>
       </c>
-      <c r="F149">
-        <v>0</v>
-      </c>
       <c r="G149" s="1">
-        <v>14.29</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
       <c r="I149" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J149">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>85.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6053,25 +6053,25 @@
         <v>20</v>
       </c>
       <c r="E150">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G150" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H150" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I150" s="2">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J150">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K150" s="1">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6088,25 +6088,25 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G151" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="H151" s="1">
-        <v>0</v>
+        <v>26.32</v>
       </c>
       <c r="I151" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J151">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K151" s="1">
-        <v>78.95</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6123,25 +6123,25 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>48.48</v>
+        <v>69.7</v>
       </c>
       <c r="H152" s="1">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="I152" s="2">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="J152">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -6225,22 +6225,22 @@
         <v>127</v>
       </c>
       <c r="D155">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E155">
         <v>34</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -6330,28 +6330,28 @@
         <v>138</v>
       </c>
       <c r="D158">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E158">
         <v>28</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H158" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="I158" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J158">
         <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6683,13 +6683,13 @@
         <v>44</v>
       </c>
       <c r="E168">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
       <c r="G168" s="1">
-        <v>97.73</v>
+        <v>100</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
@@ -6698,10 +6698,10 @@
         <v>7.9</v>
       </c>
       <c r="J168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6718,25 +6718,25 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
       </c>
       <c r="I169" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6753,25 +6753,25 @@
         <v>37</v>
       </c>
       <c r="E170">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J170">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6788,25 +6788,25 @@
         <v>32</v>
       </c>
       <c r="E171">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F171">
         <v>0</v>
       </c>
       <c r="G171" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
       </c>
       <c r="I171" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J171">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -6823,13 +6823,13 @@
         <v>44</v>
       </c>
       <c r="E172">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F172">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -6838,10 +6838,10 @@
         <v>7.8</v>
       </c>
       <c r="J172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -6855,19 +6855,19 @@
         <v>134</v>
       </c>
       <c r="D173">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E173">
         <v>32</v>
       </c>
       <c r="F173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G173" s="1">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="H173" s="1">
-        <v>13.51</v>
+        <v>11.11</v>
       </c>
       <c r="I173" s="2">
         <v>7.4</v>
@@ -6998,25 +6998,25 @@
         <v>20</v>
       </c>
       <c r="E177">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
       </c>
       <c r="I177" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J177">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -7033,25 +7033,25 @@
         <v>20</v>
       </c>
       <c r="E178">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
       </c>
       <c r="I178" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -7068,25 +7068,25 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F179">
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7205,7 +7205,7 @@
         <v>120</v>
       </c>
       <c r="D183">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E183">
         <v>33</v>
@@ -7214,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -7223,10 +7223,10 @@
         <v>9</v>
       </c>
       <c r="J183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K183" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7243,25 +7243,25 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
       </c>
       <c r="I184" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7415,7 +7415,7 @@
         <v>113</v>
       </c>
       <c r="D189">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E189">
         <v>27</v>
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="G189" s="1">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -7433,10 +7433,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J189">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K189" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7765,22 +7765,22 @@
         <v>117</v>
       </c>
       <c r="D199">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E199">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F199">
         <v>3</v>
       </c>
       <c r="G199" s="1">
-        <v>91.89</v>
+        <v>91.67</v>
       </c>
       <c r="H199" s="1">
-        <v>8.109999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="I199" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -7870,10 +7870,10 @@
         <v>139</v>
       </c>
       <c r="D202">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E202">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -8010,22 +8010,22 @@
         <v>144</v>
       </c>
       <c r="D206">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E206">
         <v>34</v>
       </c>
       <c r="F206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G206" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H206" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I206" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -8045,22 +8045,22 @@
         <v>138</v>
       </c>
       <c r="D207">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E207">
         <v>34</v>
       </c>
       <c r="F207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G207" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H207" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I207" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -8115,28 +8115,28 @@
         <v>144</v>
       </c>
       <c r="D209">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E209">
         <v>24</v>
       </c>
       <c r="F209">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G209" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H209" s="1">
-        <v>13.79</v>
+        <v>20</v>
       </c>
       <c r="I209" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8205,16 +8205,19 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -8237,22 +8240,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8269,22 +8275,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>89.47</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8301,22 +8310,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H5" s="1">
-        <v>75</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8333,22 +8345,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>96.88</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9.5</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8365,22 +8380,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>90.63</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8397,22 +8415,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>84.20999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -8429,22 +8450,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>90.31999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -8461,16 +8485,19 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>21.88</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -8490,13 +8517,13 @@
         <v>101</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -8525,16 +8552,19 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>29.17</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -8557,16 +8587,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -8589,16 +8622,19 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -8653,22 +8689,25 @@
         <v>44</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F16">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H16" s="1">
-        <v>72.73</v>
+        <v>11.36</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.6</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -8685,22 +8724,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F17">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H17" s="1">
-        <v>68.18000000000001</v>
+        <v>4.55</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -8714,25 +8756,28 @@
         <v>103</v>
       </c>
       <c r="D18">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>97.06</v>
       </c>
       <c r="H18" s="1">
-        <v>97.14</v>
+        <v>2.94</v>
+      </c>
+      <c r="I18" s="2">
+        <v>9.1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -8880,19 +8925,19 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -9005,16 +9050,19 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F27">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>67.86</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>32.14</v>
+      </c>
+      <c r="I27" s="2">
+        <v>8.1</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -9069,16 +9117,19 @@
         <v>16</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F29">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I29" s="2">
+        <v>7.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -9133,22 +9184,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>81.48</v>
       </c>
       <c r="H31" s="1">
-        <v>70.37</v>
+        <v>7.41</v>
+      </c>
+      <c r="I31" s="2">
+        <v>8.4</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -9165,22 +9219,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>92.59</v>
       </c>
       <c r="H32" s="1">
-        <v>77.78</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -9197,22 +9254,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>60.71</v>
+        <v>10.71</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.7</v>
       </c>
       <c r="J33">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K33" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -9232,19 +9292,19 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -9389,22 +9449,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F39">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>52.63</v>
       </c>
       <c r="H39" s="1">
-        <v>78.95</v>
+        <v>47.37</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.3</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -9421,22 +9484,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>29.17</v>
       </c>
       <c r="H40" s="1">
-        <v>87.5</v>
+        <v>70.83</v>
+      </c>
+      <c r="I40" s="2">
+        <v>6.1</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -9453,22 +9519,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="H41" s="1">
-        <v>70.97</v>
+        <v>48.39</v>
+      </c>
+      <c r="I41" s="2">
+        <v>6.3</v>
       </c>
       <c r="J41">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -9485,22 +9554,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>52.63</v>
       </c>
       <c r="H42" s="1">
-        <v>63.16</v>
+        <v>47.37</v>
+      </c>
+      <c r="I42" s="2">
+        <v>6.4</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -9517,22 +9589,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H43" s="1">
-        <v>78.13</v>
+        <v>46.88</v>
+      </c>
+      <c r="I43" s="2">
+        <v>6.6</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -9549,22 +9624,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F44">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="H44" s="1">
-        <v>71.88</v>
+        <v>56.25</v>
+      </c>
+      <c r="I44" s="2">
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -9642,7 +9720,7 @@
         <v>116</v>
       </c>
       <c r="D47">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -9654,13 +9732,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -9770,25 +9848,25 @@
         <v>117</v>
       </c>
       <c r="D51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="J51">
         <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -9837,16 +9915,19 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F53">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H53" s="1">
-        <v>87.88</v>
+        <v>24.24</v>
+      </c>
+      <c r="I53" s="2">
+        <v>8</v>
       </c>
       <c r="J53">
         <v>4</v>
@@ -9901,16 +9982,19 @@
         <v>38</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F55">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H55" s="1">
-        <v>84.20999999999999</v>
+        <v>10.53</v>
+      </c>
+      <c r="I55" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J55">
         <v>6</v>
@@ -10189,22 +10273,25 @@
         <v>19</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F64">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H64" s="1">
-        <v>57.89</v>
+        <v>5.26</v>
+      </c>
+      <c r="I64" s="2">
+        <v>7.2</v>
       </c>
       <c r="J64">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -10221,22 +10308,25 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F65">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H65" s="1">
-        <v>90.31999999999999</v>
+        <v>6.45</v>
+      </c>
+      <c r="I65" s="2">
+        <v>8.4</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -10253,22 +10343,25 @@
         <v>33</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F66">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H66" s="1">
-        <v>75.76000000000001</v>
+        <v>9.09</v>
+      </c>
+      <c r="I66" s="2">
+        <v>8</v>
       </c>
       <c r="J66">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -10544,19 +10637,19 @@
         <v>0</v>
       </c>
       <c r="F75">
+        <v>17</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>56.67</v>
+      </c>
+      <c r="J75">
         <v>13</v>
       </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
+      <c r="K75" s="1">
         <v>43.33</v>
-      </c>
-      <c r="J75">
-        <v>17</v>
-      </c>
-      <c r="K75" s="1">
-        <v>56.67</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -10570,13 +10663,13 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -10640,19 +10733,19 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>91.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -10730,7 +10823,7 @@
         <v>124</v>
       </c>
       <c r="D81">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -10742,13 +10835,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K81" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -10893,16 +10986,19 @@
         <v>28</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F86">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G86" s="1">
-        <v>0</v>
+        <v>53.57</v>
       </c>
       <c r="H86" s="1">
-        <v>100</v>
+        <v>46.43</v>
+      </c>
+      <c r="I86" s="2">
+        <v>6.1</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -10925,16 +11021,19 @@
         <v>32</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F87">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H87" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I87" s="2">
+        <v>7.1</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -10957,16 +11056,19 @@
         <v>32</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F88">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H88" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I88" s="2">
+        <v>7.2</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -11053,16 +11155,19 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F91">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H91" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I91" s="2">
+        <v>7.3</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -11277,16 +11382,19 @@
         <v>33</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F98">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G98" s="1">
-        <v>0</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H98" s="1">
-        <v>100</v>
+        <v>24.24</v>
+      </c>
+      <c r="I98" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -11309,16 +11417,19 @@
         <v>31</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F99">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>29.03</v>
       </c>
       <c r="H99" s="1">
-        <v>83.87</v>
+        <v>54.84</v>
+      </c>
+      <c r="I99" s="2">
+        <v>7.4</v>
       </c>
       <c r="J99">
         <v>5</v>
@@ -11338,25 +11449,28 @@
         <v>120</v>
       </c>
       <c r="D100">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F100">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H100" s="1">
-        <v>89.66</v>
+        <v>10</v>
+      </c>
+      <c r="I100" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J100">
         <v>3</v>
       </c>
       <c r="K100" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -11373,22 +11487,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F101">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H101" s="1">
-        <v>88.56999999999999</v>
+        <v>11.43</v>
+      </c>
+      <c r="I101" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K101" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -11440,19 +11557,19 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G103" s="1">
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>72.73</v>
+        <v>100</v>
       </c>
       <c r="J103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -11472,19 +11589,19 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G104" s="1">
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>51.52</v>
+        <v>100</v>
       </c>
       <c r="J104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>48.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -11696,19 +11813,19 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G111" s="1">
         <v>0</v>
       </c>
       <c r="H111" s="1">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="J111">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K111" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -11728,19 +11845,19 @@
         <v>0</v>
       </c>
       <c r="F112">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G112" s="1">
         <v>0</v>
       </c>
       <c r="H112" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="J112">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K112" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -11757,16 +11874,19 @@
         <v>37</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F113">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G113" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H113" s="1">
-        <v>100</v>
+        <v>13.51</v>
+      </c>
+      <c r="I113" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -11789,16 +11909,19 @@
         <v>41</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F114">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G114" s="1">
-        <v>0</v>
+        <v>73.17</v>
       </c>
       <c r="H114" s="1">
-        <v>100</v>
+        <v>26.83</v>
+      </c>
+      <c r="I114" s="2">
+        <v>6.9</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -11821,16 +11944,19 @@
         <v>36</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F115">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G115" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H115" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I115" s="2">
+        <v>8.6</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -11981,16 +12107,19 @@
         <v>44</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F120">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="G120" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H120" s="1">
-        <v>100</v>
+        <v>6.82</v>
+      </c>
+      <c r="I120" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -12013,22 +12142,25 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F121">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H121" s="1">
-        <v>96.3</v>
+        <v>11.11</v>
+      </c>
+      <c r="I121" s="2">
+        <v>8.5</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -12077,22 +12209,25 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F123">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G123" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H123" s="1">
-        <v>95.45</v>
+        <v>11.36</v>
+      </c>
+      <c r="I123" s="2">
+        <v>8.1</v>
       </c>
       <c r="J123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -12109,16 +12244,19 @@
         <v>32</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F124">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>71.88</v>
       </c>
       <c r="H124" s="1">
-        <v>100</v>
+        <v>28.13</v>
+      </c>
+      <c r="I124" s="2">
+        <v>8.5</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -12141,16 +12279,19 @@
         <v>32</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F125">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G125" s="1">
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="H125" s="1">
-        <v>100</v>
+        <v>56.25</v>
+      </c>
+      <c r="I125" s="2">
+        <v>9.1</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -12202,25 +12343,25 @@
         <v>134</v>
       </c>
       <c r="D127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E127">
         <v>0</v>
       </c>
       <c r="F127">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G127" s="1">
         <v>0</v>
       </c>
       <c r="H127" s="1">
-        <v>82.14</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K127" s="1">
-        <v>17.86</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -12240,19 +12381,19 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G128" s="1">
         <v>0</v>
       </c>
       <c r="H128" s="1">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="J128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K128" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -12330,13 +12471,13 @@
         <v>121</v>
       </c>
       <c r="D131">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
@@ -12493,16 +12634,19 @@
         <v>24</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F136">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G136" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H136" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I136" s="2">
+        <v>6</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -12525,22 +12669,25 @@
         <v>33</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F137">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G137" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H137" s="1">
-        <v>78.79000000000001</v>
+        <v>30.3</v>
+      </c>
+      <c r="I137" s="2">
+        <v>6.1</v>
       </c>
       <c r="J137">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -12557,22 +12704,25 @@
         <v>38</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F138">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G138" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H138" s="1">
-        <v>81.58</v>
+        <v>34.21</v>
+      </c>
+      <c r="I138" s="2">
+        <v>6.5</v>
       </c>
       <c r="J138">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -12589,22 +12739,25 @@
         <v>24</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F139">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H139" s="1">
-        <v>83.33</v>
+        <v>20.83</v>
+      </c>
+      <c r="I139" s="2">
+        <v>6.8</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K139" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -12621,22 +12774,25 @@
         <v>31</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F140">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G140" s="1">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H140" s="1">
-        <v>83.87</v>
+        <v>19.35</v>
+      </c>
+      <c r="I140" s="2">
+        <v>6</v>
       </c>
       <c r="J140">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -12653,22 +12809,25 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F141">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G141" s="1">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="H141" s="1">
-        <v>56.25</v>
+        <v>37.5</v>
+      </c>
+      <c r="I141" s="2">
+        <v>6.2</v>
       </c>
       <c r="J141">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>43.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -12685,16 +12844,19 @@
         <v>36</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F142">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H142" s="1">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I142" s="2">
+        <v>7.2</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -12717,22 +12879,25 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F143">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G143" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="H143" s="1">
-        <v>88.89</v>
+        <v>41.67</v>
+      </c>
+      <c r="I143" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -12749,16 +12914,19 @@
         <v>28</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F144">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G144" s="1">
-        <v>0</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H144" s="1">
-        <v>100</v>
+        <v>3.57</v>
+      </c>
+      <c r="I144" s="2">
+        <v>7.1</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -12781,16 +12949,19 @@
         <v>28</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F145">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>0</v>
+        <v>92.86</v>
       </c>
       <c r="H145" s="1">
-        <v>100</v>
+        <v>7.14</v>
+      </c>
+      <c r="I145" s="2">
+        <v>6.9</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -12813,22 +12984,25 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F146">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G146" s="1">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="H146" s="1">
-        <v>95.12</v>
+        <v>90.23999999999999</v>
+      </c>
+      <c r="I146" s="2">
+        <v>7.5</v>
       </c>
       <c r="J146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -12845,16 +13019,19 @@
         <v>16</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F147">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H147" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I147" s="2">
+        <v>8.4</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -12877,22 +13054,25 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F148">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G148" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H148" s="1">
-        <v>93.75</v>
+        <v>3.13</v>
+      </c>
+      <c r="I148" s="2">
+        <v>8.9</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -12906,25 +13086,28 @@
         <v>124</v>
       </c>
       <c r="D149">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F149">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G149" s="1">
-        <v>0</v>
+        <v>79.31</v>
       </c>
       <c r="H149" s="1">
-        <v>14.29</v>
+        <v>20.69</v>
+      </c>
+      <c r="I149" s="2">
+        <v>7.4</v>
       </c>
       <c r="J149">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>85.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -12941,22 +13124,25 @@
         <v>20</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F150">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H150" s="1">
-        <v>15</v>
+        <v>55</v>
+      </c>
+      <c r="I150" s="2">
+        <v>5.7</v>
       </c>
       <c r="J150">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K150" s="1">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -12973,22 +13159,25 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F151">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H151" s="1">
-        <v>21.05</v>
+        <v>31.58</v>
+      </c>
+      <c r="I151" s="2">
+        <v>7</v>
       </c>
       <c r="J151">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K151" s="1">
-        <v>78.95</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -13005,22 +13194,25 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F152">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H152" s="1">
-        <v>48.48</v>
+        <v>33.33</v>
+      </c>
+      <c r="I152" s="2">
+        <v>7.1</v>
       </c>
       <c r="J152">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -13037,16 +13229,19 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F153">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H153" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I153" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -13069,16 +13264,19 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F154">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>100</v>
+        <v>24.24</v>
+      </c>
+      <c r="I154" s="2">
+        <v>7.9</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -13098,19 +13296,22 @@
         <v>127</v>
       </c>
       <c r="D155">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F155">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H155" s="1">
-        <v>100</v>
+        <v>14.71</v>
+      </c>
+      <c r="I155" s="2">
+        <v>9.5</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -13133,16 +13334,19 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F156">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H156" s="1">
-        <v>100</v>
+        <v>6.06</v>
+      </c>
+      <c r="I156" s="2">
+        <v>9.6</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -13194,25 +13398,25 @@
         <v>138</v>
       </c>
       <c r="D158">
+        <v>30</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
         <v>29</v>
       </c>
-      <c r="E158">
-        <v>0</v>
-      </c>
-      <c r="F158">
-        <v>28</v>
-      </c>
       <c r="G158" s="1">
         <v>0</v>
       </c>
       <c r="H158" s="1">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
       <c r="J158">
         <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -13261,16 +13465,19 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F160">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G160" s="1">
-        <v>0</v>
+        <v>62.96</v>
       </c>
       <c r="H160" s="1">
-        <v>100</v>
+        <v>37.04</v>
+      </c>
+      <c r="I160" s="2">
+        <v>7.5</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -13293,16 +13500,19 @@
         <v>19</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F161">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G161" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H161" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I161" s="2">
+        <v>8.6</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -13325,16 +13535,19 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F162">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G162" s="1">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="H162" s="1">
-        <v>95.83</v>
+        <v>33.33</v>
+      </c>
+      <c r="I162" s="2">
+        <v>7.7</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -13357,16 +13570,19 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F163">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G163" s="1">
-        <v>0</v>
+        <v>79.17</v>
       </c>
       <c r="H163" s="1">
-        <v>100</v>
+        <v>20.83</v>
+      </c>
+      <c r="I163" s="2">
+        <v>7.4</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -13485,16 +13701,19 @@
         <v>32</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F167">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G167" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H167" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I167" s="2">
+        <v>8.6</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -13517,22 +13736,25 @@
         <v>44</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F168">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G168" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H168" s="1">
-        <v>97.73</v>
+        <v>0</v>
+      </c>
+      <c r="I168" s="2">
+        <v>8.5</v>
       </c>
       <c r="J168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -13549,22 +13771,25 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F169">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G169" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H169" s="1">
-        <v>96.3</v>
+        <v>0</v>
+      </c>
+      <c r="I169" s="2">
+        <v>8.6</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -13581,22 +13806,25 @@
         <v>37</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F170">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H170" s="1">
-        <v>89.19</v>
+        <v>0</v>
+      </c>
+      <c r="I170" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J170">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -13613,22 +13841,25 @@
         <v>32</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F171">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G171" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H171" s="1">
-        <v>84.38</v>
+        <v>0</v>
+      </c>
+      <c r="I171" s="2">
+        <v>8.1</v>
       </c>
       <c r="J171">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -13645,22 +13876,25 @@
         <v>44</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F172">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H172" s="1">
-        <v>93.18000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="I172" s="2">
+        <v>7.8</v>
       </c>
       <c r="J172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -13674,13 +13908,13 @@
         <v>134</v>
       </c>
       <c r="D173">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G173" s="1">
         <v>0</v>
@@ -13805,22 +14039,25 @@
         <v>20</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F177">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H177" s="1">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="I177" s="2">
+        <v>7.9</v>
       </c>
       <c r="J177">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -13837,22 +14074,25 @@
         <v>20</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F178">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H178" s="1">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="I178" s="2">
+        <v>7.8</v>
       </c>
       <c r="J178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -13869,22 +14109,25 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F179">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
-        <v>93.75</v>
+        <v>0</v>
+      </c>
+      <c r="I179" s="2">
+        <v>8.4</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -13994,25 +14237,28 @@
         <v>120</v>
       </c>
       <c r="D183">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F183">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H183" s="1">
-        <v>89.19</v>
+        <v>0</v>
+      </c>
+      <c r="I183" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K183" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -14032,19 +14278,19 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G184" s="1">
         <v>0</v>
       </c>
       <c r="H184" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="J184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -14186,7 +14432,7 @@
         <v>113</v>
       </c>
       <c r="D189">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -14198,13 +14444,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="1">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="J189">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K189" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -14506,19 +14752,22 @@
         <v>117</v>
       </c>
       <c r="D199">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F199">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="H199" s="1">
-        <v>100</v>
+        <v>2.78</v>
+      </c>
+      <c r="I199" s="2">
+        <v>8.9</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -14541,16 +14790,19 @@
         <v>32</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F200">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G200" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H200" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I200" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -14573,16 +14825,19 @@
         <v>33</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F201">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G201" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H201" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I201" s="2">
+        <v>8.6</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -14602,19 +14857,22 @@
         <v>139</v>
       </c>
       <c r="D202">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F202">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H202" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I202" s="2">
+        <v>9.1</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -14637,16 +14895,19 @@
         <v>33</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F203">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H203" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I203" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -14669,16 +14930,19 @@
         <v>33</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H204" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I204" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -14701,16 +14965,19 @@
         <v>32</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F205">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G205" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H205" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I205" s="2">
+        <v>8.6</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -14730,19 +14997,22 @@
         <v>144</v>
       </c>
       <c r="D206">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F206">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G206" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H206" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I206" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -14762,19 +15032,22 @@
         <v>138</v>
       </c>
       <c r="D207">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F207">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G207" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H207" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I207" s="2">
+        <v>8.4</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -14797,16 +15070,19 @@
         <v>33</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F208">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G208" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H208" s="1">
-        <v>100</v>
+        <v>3.03</v>
+      </c>
+      <c r="I208" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J208">
         <v>0</v>
@@ -14826,25 +15102,28 @@
         <v>144</v>
       </c>
       <c r="D209">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F209">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G209" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H209" s="1">
-        <v>96.55</v>
+        <v>20</v>
+      </c>
+      <c r="I209" s="2">
+        <v>7.4</v>
       </c>
       <c r="J209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14925,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -14948,25 +15227,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -14983,25 +15262,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15018,25 +15297,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1">
-        <v>25</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -15053,13 +15332,13 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -15068,10 +15347,10 @@
         <v>9.5</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -15088,25 +15367,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -15123,25 +15402,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -15158,25 +15437,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -15193,19 +15472,19 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>65.63</v>
+        <v>78.13</v>
       </c>
       <c r="H10" s="1">
-        <v>34.38</v>
+        <v>21.88</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -15225,19 +15504,19 @@
         <v>101</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="H11" s="1">
-        <v>16.22</v>
+        <v>16.67</v>
       </c>
       <c r="I11" s="2">
         <v>8</v>
@@ -15263,16 +15542,16 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="H12" s="1">
-        <v>33.33</v>
+        <v>29.17</v>
       </c>
       <c r="I12" s="2">
         <v>6.8</v>
@@ -15298,19 +15577,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H13" s="1">
-        <v>25</v>
+        <v>30.56</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -15403,25 +15682,25 @@
         <v>44</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>72.73</v>
+        <v>88.64</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>11.36</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -15438,25 +15717,25 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>63.64</v>
+        <v>95.45</v>
       </c>
       <c r="H17" s="1">
         <v>4.55</v>
       </c>
       <c r="I17" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -15470,28 +15749,28 @@
         <v>103</v>
       </c>
       <c r="D18">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>88.56999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H18" s="1">
-        <v>8.57</v>
+        <v>2.94</v>
       </c>
       <c r="I18" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15648,25 +15927,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -15800,7 +16079,7 @@
         <v>3.57</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -15858,19 +16137,19 @@
         <v>16</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I29" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -15928,25 +16207,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1">
-        <v>29.63</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -15963,25 +16242,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -15998,25 +16277,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J33">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K33" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -16033,25 +16312,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -16208,25 +16487,25 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G39" s="1">
-        <v>78.95</v>
+        <v>52.63</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="I39" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -16243,25 +16522,25 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G40" s="1">
-        <v>87.5</v>
+        <v>41.67</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="I40" s="2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -16278,25 +16557,25 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G41" s="1">
-        <v>70.97</v>
+        <v>51.61</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>48.39</v>
       </c>
       <c r="I41" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J41">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -16313,25 +16592,25 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1">
-        <v>63.16</v>
+        <v>52.63</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="I42" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -16348,25 +16627,25 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G43" s="1">
-        <v>78.13</v>
+        <v>59.38</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>40.63</v>
       </c>
       <c r="I43" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -16383,25 +16662,25 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G44" s="1">
-        <v>71.88</v>
+        <v>53.13</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>46.88</v>
       </c>
       <c r="I44" s="2">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -16485,7 +16764,7 @@
         <v>116</v>
       </c>
       <c r="D47">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47">
         <v>33</v>
@@ -16494,7 +16773,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -16503,10 +16782,10 @@
         <v>9.5</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>5.71</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -16625,28 +16904,28 @@
         <v>117</v>
       </c>
       <c r="D51">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J51">
         <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -16698,16 +16977,16 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="I53" s="2">
         <v>7.9</v>
@@ -16780,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J55">
         <v>6</v>
@@ -17083,25 +17362,25 @@
         <v>19</v>
       </c>
       <c r="E64">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
       </c>
       <c r="I64" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J64">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1">
-        <v>42.11</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -17118,25 +17397,25 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
       </c>
       <c r="I65" s="2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -17153,25 +17432,25 @@
         <v>33</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
       </c>
       <c r="I66" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J66">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -17468,25 +17747,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" s="1">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="H75" s="1">
         <v>3.33</v>
       </c>
       <c r="I75" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J75">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K75" s="1">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -17500,22 +17779,22 @@
         <v>101</v>
       </c>
       <c r="D76">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E76">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F76">
         <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H76" s="1">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="I76" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -17573,13 +17852,13 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F78">
         <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H78" s="1">
         <v>5.88</v>
@@ -17588,10 +17867,10 @@
         <v>8.6</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -17675,7 +17954,7 @@
         <v>124</v>
       </c>
       <c r="D81">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E81">
         <v>30</v>
@@ -17684,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -17693,10 +17972,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K81" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -17853,19 +18132,19 @@
         <v>28</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F86">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G86" s="1">
-        <v>71.43000000000001</v>
+        <v>53.57</v>
       </c>
       <c r="H86" s="1">
-        <v>28.57</v>
+        <v>46.43</v>
       </c>
       <c r="I86" s="2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -17888,19 +18167,19 @@
         <v>32</v>
       </c>
       <c r="E87">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F87">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G87" s="1">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="H87" s="1">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="I87" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -17923,16 +18202,16 @@
         <v>32</v>
       </c>
       <c r="E88">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F88">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G88" s="1">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H88" s="1">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I88" s="2">
         <v>7.5</v>
@@ -18028,19 +18307,19 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F91">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G91" s="1">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H91" s="1">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="I91" s="2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -18285,7 +18564,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -18320,7 +18599,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J99">
         <v>5</v>
@@ -18340,16 +18619,16 @@
         <v>120</v>
       </c>
       <c r="D100">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E100">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -18361,7 +18640,7 @@
         <v>3</v>
       </c>
       <c r="K100" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -18378,25 +18657,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F101">
         <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
       </c>
       <c r="I101" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K101" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -18448,25 +18727,25 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G103" s="1">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="I103" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -18483,25 +18762,25 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G104" s="1">
-        <v>51.52</v>
+        <v>69.7</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="I104" s="2">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="J104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>48.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -18728,25 +19007,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
       <c r="I111" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J111">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K111" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -18763,25 +19042,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
       </c>
       <c r="I112" s="2">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J112">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K112" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -18798,16 +19077,16 @@
         <v>37</v>
       </c>
       <c r="E113">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F113">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G113" s="1">
-        <v>91.89</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H113" s="1">
-        <v>8.109999999999999</v>
+        <v>13.51</v>
       </c>
       <c r="I113" s="2">
         <v>8.5</v>
@@ -18833,19 +19112,19 @@
         <v>41</v>
       </c>
       <c r="E114">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F114">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G114" s="1">
-        <v>82.93000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="H114" s="1">
-        <v>17.07</v>
+        <v>26.83</v>
       </c>
       <c r="I114" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -18880,7 +19159,7 @@
         <v>5.56</v>
       </c>
       <c r="I115" s="2">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -19081,22 +19360,22 @@
         <v>26</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="1">
         <v>96.3</v>
       </c>
       <c r="H121" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I121" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -19148,25 +19427,25 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
       </c>
       <c r="I123" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -19195,7 +19474,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -19230,7 +19509,7 @@
         <v>15.63</v>
       </c>
       <c r="I125" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -19285,28 +19564,28 @@
         <v>134</v>
       </c>
       <c r="D127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E127">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" s="1">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="I127" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K127" s="1">
-        <v>17.86</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -19323,25 +19602,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F128">
         <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
       </c>
       <c r="I128" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K128" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -19425,22 +19704,22 @@
         <v>121</v>
       </c>
       <c r="D131">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E131">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F131">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G131" s="1">
-        <v>77.14</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H131" s="1">
-        <v>22.86</v>
+        <v>17.65</v>
       </c>
       <c r="I131" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -19510,7 +19789,7 @@
         <v>18.18</v>
       </c>
       <c r="I133" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -19603,16 +19882,16 @@
         <v>24</v>
       </c>
       <c r="E136">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F136">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G136" s="1">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="H136" s="1">
-        <v>29.17</v>
+        <v>25</v>
       </c>
       <c r="I136" s="2">
         <v>6.2</v>
@@ -19638,25 +19917,25 @@
         <v>33</v>
       </c>
       <c r="E137">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G137" s="1">
-        <v>78.79000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="H137" s="1">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="I137" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J137">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -19673,25 +19952,25 @@
         <v>38</v>
       </c>
       <c r="E138">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G138" s="1">
-        <v>81.58</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H138" s="1">
-        <v>0</v>
+        <v>34.21</v>
       </c>
       <c r="I138" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J138">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -19708,25 +19987,25 @@
         <v>24</v>
       </c>
       <c r="E139">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="H139" s="1">
-        <v>0</v>
+        <v>20.83</v>
       </c>
       <c r="I139" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K139" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -19743,25 +20022,25 @@
         <v>31</v>
       </c>
       <c r="E140">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G140" s="1">
-        <v>83.87</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H140" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="I140" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J140">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -19778,25 +20057,25 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G141" s="1">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="H141" s="1">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I141" s="2">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="J141">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>43.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -19825,7 +20104,7 @@
         <v>8.33</v>
       </c>
       <c r="I142" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -19851,22 +20130,22 @@
         <v>32</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G143" s="1">
         <v>88.89</v>
       </c>
       <c r="H143" s="1">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="I143" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -19883,19 +20162,19 @@
         <v>28</v>
       </c>
       <c r="E144">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" s="1">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H144" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I144" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -19918,19 +20197,19 @@
         <v>28</v>
       </c>
       <c r="E145">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="H145" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="I145" s="2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -19956,22 +20235,22 @@
         <v>37</v>
       </c>
       <c r="F146">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G146" s="1">
         <v>90.23999999999999</v>
       </c>
       <c r="H146" s="1">
-        <v>4.88</v>
+        <v>9.76</v>
       </c>
       <c r="I146" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -20000,7 +20279,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -20023,25 +20302,25 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" s="1">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H148" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I148" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -20055,28 +20334,28 @@
         <v>124</v>
       </c>
       <c r="D149">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E149">
+        <v>25</v>
+      </c>
+      <c r="F149">
         <v>4</v>
       </c>
-      <c r="F149">
-        <v>0</v>
-      </c>
       <c r="G149" s="1">
-        <v>14.29</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
       <c r="I149" s="2">
         <v>6.8</v>
       </c>
       <c r="J149">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>85.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -20093,25 +20372,25 @@
         <v>20</v>
       </c>
       <c r="E150">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G150" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H150" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I150" s="2">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J150">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K150" s="1">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -20128,25 +20407,25 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G151" s="1">
-        <v>21.05</v>
+        <v>57.89</v>
       </c>
       <c r="H151" s="1">
-        <v>0</v>
+        <v>31.58</v>
       </c>
       <c r="I151" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J151">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K151" s="1">
-        <v>78.95</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -20163,25 +20442,25 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>48.48</v>
+        <v>69.7</v>
       </c>
       <c r="H152" s="1">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="I152" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J152">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -20198,19 +20477,19 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F153">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G153" s="1">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="H153" s="1">
-        <v>12.5</v>
+        <v>3.13</v>
       </c>
       <c r="I153" s="2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -20233,19 +20512,19 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F154">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G154" s="1">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H154" s="1">
-        <v>18.18</v>
+        <v>15.15</v>
       </c>
       <c r="I154" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -20265,22 +20544,22 @@
         <v>127</v>
       </c>
       <c r="D155">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E155">
         <v>34</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -20303,19 +20582,19 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H156" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I156" s="2">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -20370,28 +20649,28 @@
         <v>138</v>
       </c>
       <c r="D158">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E158">
         <v>28</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H158" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="I158" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J158">
         <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -20443,19 +20722,19 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G160" s="1">
-        <v>85.19</v>
+        <v>88.89</v>
       </c>
       <c r="H160" s="1">
-        <v>14.81</v>
+        <v>11.11</v>
       </c>
       <c r="I160" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -20478,19 +20757,19 @@
         <v>19</v>
       </c>
       <c r="E161">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F161">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G161" s="1">
-        <v>78.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H161" s="1">
-        <v>21.05</v>
+        <v>5.26</v>
       </c>
       <c r="I161" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -20513,19 +20792,19 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F162">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G162" s="1">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H162" s="1">
-        <v>29.17</v>
+        <v>20.83</v>
       </c>
       <c r="I162" s="2">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -20548,16 +20827,16 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G163" s="1">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H163" s="1">
-        <v>16.67</v>
+        <v>12.5</v>
       </c>
       <c r="I163" s="2">
         <v>7.4</v>
@@ -20700,7 +20979,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -20723,25 +21002,25 @@
         <v>44</v>
       </c>
       <c r="E168">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
       <c r="G168" s="1">
-        <v>97.73</v>
+        <v>100</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -20758,25 +21037,25 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
       </c>
       <c r="I169" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -20793,25 +21072,25 @@
         <v>37</v>
       </c>
       <c r="E170">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J170">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -20828,25 +21107,25 @@
         <v>32</v>
       </c>
       <c r="E171">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F171">
         <v>0</v>
       </c>
       <c r="G171" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
       </c>
       <c r="I171" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J171">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -20863,25 +21142,25 @@
         <v>44</v>
       </c>
       <c r="E172">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F172">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
       </c>
       <c r="I172" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -20895,19 +21174,19 @@
         <v>134</v>
       </c>
       <c r="D173">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E173">
         <v>32</v>
       </c>
       <c r="F173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G173" s="1">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="H173" s="1">
-        <v>13.51</v>
+        <v>11.11</v>
       </c>
       <c r="I173" s="2">
         <v>7.4</v>
@@ -21038,25 +21317,25 @@
         <v>20</v>
       </c>
       <c r="E177">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F177">
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
       </c>
       <c r="I177" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J177">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -21073,25 +21352,25 @@
         <v>20</v>
       </c>
       <c r="E178">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
       </c>
       <c r="I178" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -21108,25 +21387,25 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F179">
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -21245,7 +21524,7 @@
         <v>120</v>
       </c>
       <c r="D183">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E183">
         <v>33</v>
@@ -21254,19 +21533,19 @@
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
       <c r="I183" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K183" s="1">
-        <v>10.81</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -21283,25 +21562,25 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
       </c>
       <c r="I184" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -21455,7 +21734,7 @@
         <v>113</v>
       </c>
       <c r="D189">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E189">
         <v>27</v>
@@ -21464,7 +21743,7 @@
         <v>0</v>
       </c>
       <c r="G189" s="1">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -21473,10 +21752,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="J189">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K189" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -21805,22 +22084,22 @@
         <v>117</v>
       </c>
       <c r="D199">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E199">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G199" s="1">
-        <v>91.89</v>
+        <v>97.22</v>
       </c>
       <c r="H199" s="1">
-        <v>8.109999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="I199" s="2">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -21843,19 +22122,19 @@
         <v>32</v>
       </c>
       <c r="E200">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F200">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G200" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H200" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I200" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -21878,19 +22157,19 @@
         <v>33</v>
       </c>
       <c r="E201">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F201">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G201" s="1">
-        <v>87.88</v>
+        <v>100</v>
       </c>
       <c r="H201" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
       <c r="I201" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -21910,10 +22189,10 @@
         <v>139</v>
       </c>
       <c r="D202">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E202">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -21925,7 +22204,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -21948,19 +22227,19 @@
         <v>33</v>
       </c>
       <c r="E203">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H203" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I203" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -21983,19 +22262,19 @@
         <v>33</v>
       </c>
       <c r="E204">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H204" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I204" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -22018,19 +22297,19 @@
         <v>32</v>
       </c>
       <c r="E205">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F205">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G205" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H205" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I205" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -22050,22 +22329,22 @@
         <v>144</v>
       </c>
       <c r="D206">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E206">
         <v>34</v>
       </c>
       <c r="F206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G206" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H206" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I206" s="2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -22085,22 +22364,22 @@
         <v>138</v>
       </c>
       <c r="D207">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E207">
         <v>34</v>
       </c>
       <c r="F207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G207" s="1">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H207" s="1">
-        <v>8.109999999999999</v>
+        <v>5.56</v>
       </c>
       <c r="I207" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -22123,19 +22402,19 @@
         <v>33</v>
       </c>
       <c r="E208">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G208" s="1">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H208" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
       <c r="I208" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J208">
         <v>0</v>
@@ -22155,28 +22434,28 @@
         <v>144</v>
       </c>
       <c r="D209">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E209">
         <v>24</v>
       </c>
       <c r="F209">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G209" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H209" s="1">
-        <v>13.79</v>
+        <v>20</v>
       </c>
       <c r="I209" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1471,22 +1471,22 @@
         <v>30</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
         <v>73.17</v>
       </c>
       <c r="H19" s="1">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="I19" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1506,22 +1506,22 @@
         <v>26</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
         <v>74.29000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>20</v>
+        <v>25.71</v>
       </c>
       <c r="I20" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1541,22 +1541,22 @@
         <v>24</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1">
         <v>68.56999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>25.71</v>
+        <v>31.43</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1888,25 +1888,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1958,25 +1958,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1996,22 +1996,22 @@
         <v>7</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G34" s="1">
         <v>36.84</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="I34" s="2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1">
-        <v>63.16</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2063,13 +2063,13 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36">
         <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H36" s="1">
         <v>31.25</v>
@@ -2078,10 +2078,10 @@
         <v>7.2</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2101,22 +2101,22 @@
         <v>22</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37" s="1">
         <v>68.75</v>
       </c>
       <c r="H37" s="1">
-        <v>25</v>
+        <v>28.13</v>
       </c>
       <c r="I37" s="2">
         <v>7.4</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2448,25 +2448,25 @@
         <v>34</v>
       </c>
       <c r="E47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
       </c>
       <c r="I47" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2553,25 +2553,25 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G50" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I50" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2588,25 +2588,25 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="I51" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2623,25 +2623,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
       </c>
       <c r="I52" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J52">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K52" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2763,25 +2763,25 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="1">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I56" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K56" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2801,22 +2801,22 @@
         <v>29</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1">
         <v>90.63</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I57" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2836,22 +2836,22 @@
         <v>42</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1">
         <v>95.45</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="I58" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2906,22 +2906,22 @@
         <v>33</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
         <v>89.19</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>10.81</v>
       </c>
       <c r="I60" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2941,22 +2941,22 @@
         <v>30</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="1">
         <v>93.75</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I61" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2976,22 +2976,22 @@
         <v>40</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G62" s="1">
         <v>90.91</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="I62" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3011,22 +3011,22 @@
         <v>23</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="1">
         <v>95.83</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="I63" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3151,22 +3151,22 @@
         <v>26</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G67" s="1">
         <v>81.25</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="I67" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3183,25 +3183,25 @@
         <v>44</v>
       </c>
       <c r="E68">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G68" s="1">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="I68" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3221,22 +3221,22 @@
         <v>33</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G69" s="1">
         <v>89.19</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>10.81</v>
       </c>
       <c r="I69" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3256,22 +3256,22 @@
         <v>21</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G70" s="1">
         <v>65.63</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>34.38</v>
       </c>
       <c r="I70" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3291,22 +3291,22 @@
         <v>37</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G71" s="1">
         <v>84.09</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>15.91</v>
       </c>
       <c r="I71" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>15.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3323,25 +3323,25 @@
         <v>36</v>
       </c>
       <c r="E72">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F72">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G72" s="1">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="H72" s="1">
-        <v>27.78</v>
+        <v>50</v>
       </c>
       <c r="I72" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J72">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3358,25 +3358,25 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G73" s="1">
-        <v>62.16</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>32.43</v>
       </c>
       <c r="I73" s="2">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="J73">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>37.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3603,25 +3603,25 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" s="1">
-        <v>66.67</v>
+        <v>85.19</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>14.81</v>
       </c>
       <c r="I80" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J80">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3638,25 +3638,25 @@
         <v>36</v>
       </c>
       <c r="E81">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="1">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="I81" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J81">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3673,25 +3673,25 @@
         <v>36</v>
       </c>
       <c r="E82">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G82" s="1">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I82" s="2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3708,25 +3708,25 @@
         <v>33</v>
       </c>
       <c r="E83">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G83" s="1">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>21.21</v>
       </c>
       <c r="I83" s="2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J83">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3743,25 +3743,25 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G84" s="1">
-        <v>9.68</v>
+        <v>35.48</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="I84" s="2">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="J84">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>90.31999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3778,25 +3778,25 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G85" s="1">
-        <v>67.65000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="I85" s="2">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="J85">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4023,25 +4023,25 @@
         <v>32</v>
       </c>
       <c r="E92">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F92">
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J92">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4058,25 +4058,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93" s="1">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K93" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -4128,25 +4128,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -4163,25 +4163,25 @@
         <v>19</v>
       </c>
       <c r="E96">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F96">
         <v>0</v>
       </c>
       <c r="G96" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
       </c>
       <c r="I96" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J96">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4198,13 +4198,13 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -4213,10 +4213,10 @@
         <v>8.4</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K97" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -4653,25 +4653,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G110" s="1">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H110" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I110" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J110">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K110" s="1">
-        <v>88.89</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4688,25 +4688,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>48.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
       <c r="I111" s="2">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J111">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K111" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4723,25 +4723,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I112" s="2">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J112">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K112" s="1">
-        <v>65.84999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -5073,25 +5073,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G122" s="1">
-        <v>89.19</v>
+        <v>91.89</v>
       </c>
       <c r="H122" s="1">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="I122" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K122" s="1">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5216,22 +5216,22 @@
         <v>29</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" s="1">
         <v>93.55</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="I126" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5248,25 +5248,25 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G127" s="1">
-        <v>82.76000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H127" s="1">
-        <v>3.45</v>
+        <v>6.9</v>
       </c>
       <c r="I127" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J127">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5283,25 +5283,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G128" s="1">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="I128" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J128">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5318,25 +5318,25 @@
         <v>19</v>
       </c>
       <c r="E129">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" s="1">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H129" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I129" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -6336,22 +6336,22 @@
         <v>28</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G158" s="1">
         <v>93.33</v>
       </c>
       <c r="H158" s="1">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="I158" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6371,22 +6371,22 @@
         <v>31</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" s="1">
         <v>96.88</v>
       </c>
       <c r="H159" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I159" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -6896,22 +6896,22 @@
         <v>20</v>
       </c>
       <c r="F174">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G174" s="1">
         <v>64.52</v>
       </c>
       <c r="H174" s="1">
-        <v>25.81</v>
+        <v>35.48</v>
       </c>
       <c r="I174" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -6931,22 +6931,22 @@
         <v>14</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G175" s="1">
         <v>73.68000000000001</v>
       </c>
       <c r="H175" s="1">
-        <v>21.05</v>
+        <v>26.32</v>
       </c>
       <c r="I175" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -6966,22 +6966,22 @@
         <v>14</v>
       </c>
       <c r="F176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G176" s="1">
         <v>73.68000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>21.05</v>
+        <v>26.32</v>
       </c>
       <c r="I176" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -7103,13 +7103,13 @@
         <v>32</v>
       </c>
       <c r="E180">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7138,25 +7138,25 @@
         <v>32</v>
       </c>
       <c r="E181">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F181">
         <v>7</v>
       </c>
       <c r="G181" s="1">
-        <v>75</v>
+        <v>78.13</v>
       </c>
       <c r="H181" s="1">
         <v>21.88</v>
       </c>
       <c r="I181" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7313,25 +7313,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
       </c>
       <c r="I186" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J186">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K186" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7383,25 +7383,25 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G188" s="1">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H188" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="I188" s="2">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="J188">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7418,25 +7418,25 @@
         <v>34</v>
       </c>
       <c r="E189">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G189" s="1">
-        <v>79.41</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>14.71</v>
       </c>
       <c r="I189" s="2">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J189">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7453,25 +7453,25 @@
         <v>24</v>
       </c>
       <c r="E190">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G190" s="1">
-        <v>70.83</v>
+        <v>79.17</v>
       </c>
       <c r="H190" s="1">
-        <v>0</v>
+        <v>20.83</v>
       </c>
       <c r="I190" s="2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J190">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>29.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7488,25 +7488,25 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G191" s="1">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H191" s="1">
-        <v>0</v>
+        <v>32.26</v>
       </c>
       <c r="I191" s="2">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="J191">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -7526,22 +7526,22 @@
         <v>24</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G192" s="1">
         <v>85.70999999999999</v>
       </c>
       <c r="H192" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="I192" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J192">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K192" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -7558,25 +7558,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" s="1">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H193" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I193" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J193">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K193" s="1">
-        <v>17.86</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -7593,25 +7593,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F194">
         <v>0</v>
       </c>
       <c r="G194" s="1">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
       </c>
       <c r="I194" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J194">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K194" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -7701,22 +7701,22 @@
         <v>25</v>
       </c>
       <c r="F197">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G197" s="1">
         <v>69.44</v>
       </c>
       <c r="H197" s="1">
-        <v>27.78</v>
+        <v>30.56</v>
       </c>
       <c r="I197" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -7733,25 +7733,25 @@
         <v>31</v>
       </c>
       <c r="E198">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F198">
         <v>9</v>
       </c>
       <c r="G198" s="1">
-        <v>64.52</v>
+        <v>70.97</v>
       </c>
       <c r="H198" s="1">
         <v>29.03</v>
       </c>
       <c r="I198" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -8520,16 +8520,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -8657,16 +8660,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>71.88</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>28.13</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -8794,22 +8800,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>82.93000000000001</v>
+        <v>7.32</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.1</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -8826,22 +8835,25 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>94.29000000000001</v>
+        <v>14.29</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8858,22 +8870,25 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>94.29000000000001</v>
+        <v>14.29</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.5</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8890,16 +8905,19 @@
         <v>37</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F22">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -8922,16 +8940,19 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>2.78</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8.4</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -8954,16 +8975,19 @@
         <v>22</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.5</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -8986,16 +9010,19 @@
         <v>35</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F25">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>51.43</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>48.57</v>
+      </c>
+      <c r="I25" s="2">
+        <v>9.9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -9018,16 +9045,19 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>48.65</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>51.35</v>
+      </c>
+      <c r="I26" s="2">
+        <v>8.1</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -9062,7 +9092,7 @@
         <v>32.14</v>
       </c>
       <c r="I27" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -9085,16 +9115,19 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F28">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>53.66</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>46.34</v>
+      </c>
+      <c r="I28" s="2">
+        <v>8.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -9152,16 +9185,19 @@
         <v>32</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F30">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>8.5</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -9184,25 +9220,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>92.59</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J31">
         <v>2</v>
       </c>
-      <c r="G31" s="1">
-        <v>81.48</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="K31" s="1">
         <v>7.41</v>
-      </c>
-      <c r="I31" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
-      <c r="K31" s="1">
-        <v>11.11</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -9254,25 +9290,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>10.71</v>
+        <v>7.14</v>
       </c>
       <c r="I33" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -9289,22 +9325,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>7</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="H34" s="1">
         <v>36.84</v>
       </c>
+      <c r="I34" s="2">
+        <v>6.5</v>
+      </c>
       <c r="J34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1">
-        <v>63.16</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -9321,16 +9360,19 @@
         <v>31</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F35">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H35" s="1">
-        <v>96.77</v>
+        <v>25.81</v>
+      </c>
+      <c r="I35" s="2">
+        <v>7.5</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -9353,22 +9395,25 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F36">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="H36" s="1">
-        <v>90.63</v>
+        <v>34.38</v>
+      </c>
+      <c r="I36" s="2">
+        <v>7.4</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -9385,22 +9430,25 @@
         <v>32</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H37" s="1">
-        <v>93.75</v>
+        <v>31.25</v>
+      </c>
+      <c r="I37" s="2">
+        <v>7.4</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -9417,16 +9465,19 @@
         <v>33</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H38" s="1">
-        <v>90.91</v>
+        <v>18.18</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6.8</v>
       </c>
       <c r="J38">
         <v>3</v>
@@ -9659,16 +9710,19 @@
         <v>44</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F45">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I45" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -9691,16 +9745,19 @@
         <v>44</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F46">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>9</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -9723,22 +9780,25 @@
         <v>34</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F47">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H47" s="1">
-        <v>97.06</v>
+        <v>0</v>
+      </c>
+      <c r="I47" s="2">
+        <v>9.6</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -9755,16 +9815,19 @@
         <v>33</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F48">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>9.5</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -9787,16 +9850,19 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="H49" s="1">
-        <v>100</v>
+        <v>3.23</v>
+      </c>
+      <c r="I49" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -9819,22 +9885,25 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F50">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="H50" s="1">
-        <v>80</v>
+        <v>27.5</v>
+      </c>
+      <c r="I50" s="2">
+        <v>7.8</v>
       </c>
       <c r="J50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -9851,22 +9920,25 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="H51" s="1">
-        <v>83.33</v>
+        <v>23.33</v>
+      </c>
+      <c r="I51" s="2">
+        <v>8</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -9883,22 +9955,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F52">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H52" s="1">
-        <v>66.67</v>
+        <v>8.33</v>
+      </c>
+      <c r="I52" s="2">
+        <v>8.6</v>
       </c>
       <c r="J52">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K52" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -9950,16 +10025,19 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F54">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="H54" s="1">
-        <v>64.52</v>
+        <v>25.81</v>
+      </c>
+      <c r="I54" s="2">
+        <v>7.4</v>
       </c>
       <c r="J54">
         <v>11</v>
@@ -10017,22 +10095,25 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F56">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="H56" s="1">
-        <v>83.87</v>
+        <v>51.61</v>
+      </c>
+      <c r="I56" s="2">
+        <v>8.4</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K56" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -10049,22 +10130,25 @@
         <v>32</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F57">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H57" s="1">
-        <v>90.63</v>
+        <v>12.5</v>
+      </c>
+      <c r="I57" s="2">
+        <v>7.8</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -10081,22 +10165,25 @@
         <v>44</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F58">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H58" s="1">
-        <v>95.45</v>
+        <v>9.09</v>
+      </c>
+      <c r="I58" s="2">
+        <v>8.1</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -10113,16 +10200,19 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F59">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H59" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I59" s="2">
+        <v>8.1</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -10145,22 +10235,25 @@
         <v>37</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F60">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H60" s="1">
-        <v>89.19</v>
+        <v>13.51</v>
+      </c>
+      <c r="I60" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -10177,22 +10270,25 @@
         <v>32</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F61">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H61" s="1">
-        <v>93.75</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I61" s="2">
+        <v>7.6</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -10209,22 +10305,25 @@
         <v>44</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F62">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H62" s="1">
-        <v>90.91</v>
+        <v>11.36</v>
+      </c>
+      <c r="I62" s="2">
+        <v>7.7</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -10241,22 +10340,25 @@
         <v>24</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F63">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H63" s="1">
-        <v>95.83</v>
+        <v>8.33</v>
+      </c>
+      <c r="I63" s="2">
+        <v>7.9</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -10308,16 +10410,16 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="1">
-        <v>90.31999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H65" s="1">
-        <v>6.45</v>
+        <v>3.23</v>
       </c>
       <c r="I65" s="2">
         <v>8.4</v>
@@ -10378,22 +10480,25 @@
         <v>32</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F67">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H67" s="1">
-        <v>81.25</v>
+        <v>21.88</v>
+      </c>
+      <c r="I67" s="2">
+        <v>6.1</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -10410,22 +10515,25 @@
         <v>44</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F68">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H68" s="1">
-        <v>77.27</v>
+        <v>22.73</v>
+      </c>
+      <c r="I68" s="2">
+        <v>6.9</v>
       </c>
       <c r="J68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -10442,22 +10550,25 @@
         <v>37</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F69">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>83.78</v>
       </c>
       <c r="H69" s="1">
-        <v>89.19</v>
+        <v>16.22</v>
+      </c>
+      <c r="I69" s="2">
+        <v>7.6</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10474,22 +10585,25 @@
         <v>32</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F70">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>71.88</v>
       </c>
       <c r="H70" s="1">
-        <v>65.63</v>
+        <v>28.13</v>
+      </c>
+      <c r="I70" s="2">
+        <v>6.4</v>
       </c>
       <c r="J70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -10506,22 +10620,25 @@
         <v>44</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F71">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>86.36</v>
       </c>
       <c r="H71" s="1">
-        <v>84.09</v>
+        <v>13.64</v>
+      </c>
+      <c r="I71" s="2">
+        <v>6.5</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>15.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -10538,22 +10655,25 @@
         <v>36</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F72">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H72" s="1">
-        <v>75</v>
+        <v>50</v>
+      </c>
+      <c r="I72" s="2">
+        <v>6.2</v>
       </c>
       <c r="J72">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -10570,22 +10690,25 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F73">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H73" s="1">
-        <v>62.16</v>
+        <v>32.43</v>
+      </c>
+      <c r="I73" s="2">
+        <v>6.5</v>
       </c>
       <c r="J73">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>37.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -10794,22 +10917,25 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F80">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H80" s="1">
-        <v>66.67</v>
+        <v>22.22</v>
+      </c>
+      <c r="I80" s="2">
+        <v>6.6</v>
       </c>
       <c r="J80">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -10826,22 +10952,25 @@
         <v>36</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F81">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H81" s="1">
-        <v>83.33</v>
+        <v>8.33</v>
+      </c>
+      <c r="I81" s="2">
+        <v>7.7</v>
       </c>
       <c r="J81">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -10858,22 +10987,25 @@
         <v>36</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F82">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H82" s="1">
-        <v>69.44</v>
+        <v>22.22</v>
+      </c>
+      <c r="I82" s="2">
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -10890,22 +11022,25 @@
         <v>33</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F83">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H83" s="1">
-        <v>69.7</v>
+        <v>27.27</v>
+      </c>
+      <c r="I83" s="2">
+        <v>6.2</v>
       </c>
       <c r="J83">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -10922,22 +11057,25 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F84">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>32.26</v>
       </c>
       <c r="H84" s="1">
-        <v>9.68</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="I84" s="2">
+        <v>5.9</v>
       </c>
       <c r="J84">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>90.31999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -10954,22 +11092,25 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F85">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H85" s="1">
-        <v>67.65000000000001</v>
+        <v>29.41</v>
+      </c>
+      <c r="I85" s="2">
+        <v>6.9</v>
       </c>
       <c r="J85">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -11091,16 +11232,19 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F89">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="H89" s="1">
-        <v>95.83</v>
+        <v>37.5</v>
+      </c>
+      <c r="I89" s="2">
+        <v>7.5</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -11123,16 +11267,19 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F90">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G90" s="1">
-        <v>0</v>
+        <v>54.17</v>
       </c>
       <c r="H90" s="1">
-        <v>95.83</v>
+        <v>41.67</v>
+      </c>
+      <c r="I90" s="2">
+        <v>7.6</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -11190,22 +11337,25 @@
         <v>32</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F92">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
-        <v>90.63</v>
+        <v>0</v>
+      </c>
+      <c r="I92" s="2">
+        <v>8.4</v>
       </c>
       <c r="J92">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -11222,22 +11372,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F93">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G93" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H93" s="1">
-        <v>84.84999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="I93" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K93" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -11254,16 +11407,19 @@
         <v>22</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F94">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H94" s="1">
-        <v>90.91</v>
+        <v>0</v>
+      </c>
+      <c r="I94" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -11286,22 +11442,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F95">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H95" s="1">
-        <v>93.94</v>
+        <v>6.06</v>
+      </c>
+      <c r="I95" s="2">
+        <v>9.5</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -11318,22 +11477,25 @@
         <v>19</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F96">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G96" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H96" s="1">
-        <v>78.95</v>
+        <v>0</v>
+      </c>
+      <c r="I96" s="2">
+        <v>7.4</v>
       </c>
       <c r="J96">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -11350,22 +11512,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F97">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H97" s="1">
-        <v>84.38</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I97" s="2">
+        <v>9.1</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K97" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -11522,16 +11687,19 @@
         <v>31</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F102">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>8.6</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -11554,16 +11722,19 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F103">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>59.09</v>
       </c>
       <c r="H103" s="1">
-        <v>100</v>
+        <v>40.91</v>
+      </c>
+      <c r="I103" s="2">
+        <v>8.4</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -11586,16 +11757,19 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F104">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="H104" s="1">
-        <v>100</v>
+        <v>54.55</v>
+      </c>
+      <c r="I104" s="2">
+        <v>7.4</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -11618,16 +11792,19 @@
         <v>32</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F105">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="H105" s="1">
-        <v>100</v>
+        <v>84.38</v>
+      </c>
+      <c r="I105" s="2">
+        <v>5.1</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -11650,16 +11827,19 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F106">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="H106" s="1">
-        <v>100</v>
+        <v>66.67</v>
+      </c>
+      <c r="I106" s="2">
+        <v>5</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -11682,16 +11862,19 @@
         <v>32</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F107">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>28.13</v>
       </c>
       <c r="H107" s="1">
-        <v>100</v>
+        <v>71.88</v>
+      </c>
+      <c r="I107" s="2">
+        <v>5.1</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -11714,16 +11897,19 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F108">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H108" s="1">
-        <v>100</v>
+        <v>42.11</v>
+      </c>
+      <c r="I108" s="2">
+        <v>5.8</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -11746,16 +11932,19 @@
         <v>32</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F109">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H109" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I109" s="2">
+        <v>5</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -11778,22 +11967,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G110" s="1">
-        <v>0</v>
+        <v>38.89</v>
       </c>
       <c r="H110" s="1">
-        <v>11.11</v>
+        <v>8.33</v>
+      </c>
+      <c r="I110" s="2">
+        <v>7.8</v>
       </c>
       <c r="J110">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K110" s="1">
-        <v>88.89</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -11810,22 +12002,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F111">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>64.86</v>
       </c>
       <c r="H111" s="1">
-        <v>48.65</v>
+        <v>10.81</v>
+      </c>
+      <c r="I111" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J111">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K111" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -11842,22 +12037,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F112">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>41.46</v>
       </c>
       <c r="H112" s="1">
-        <v>34.15</v>
+        <v>14.63</v>
+      </c>
+      <c r="I112" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J112">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K112" s="1">
-        <v>65.84999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -11979,16 +12177,19 @@
         <v>22</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F116">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G116" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H116" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I116" s="2">
+        <v>9.5</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -12011,16 +12212,19 @@
         <v>22</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F117">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H117" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I117" s="2">
+        <v>9.5</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -12043,16 +12247,19 @@
         <v>33</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F118">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H118" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I118" s="2">
+        <v>8</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -12075,16 +12282,19 @@
         <v>33</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F119">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G119" s="1">
-        <v>0</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H119" s="1">
-        <v>100</v>
+        <v>21.21</v>
+      </c>
+      <c r="I119" s="2">
+        <v>8</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -12177,22 +12387,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F122">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G122" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H122" s="1">
-        <v>89.19</v>
+        <v>10.81</v>
+      </c>
+      <c r="I122" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K122" s="1">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -12209,19 +12422,19 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G123" s="1">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H123" s="1">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
       <c r="I123" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -12244,19 +12457,19 @@
         <v>32</v>
       </c>
       <c r="E124">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F124">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G124" s="1">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H124" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -12279,19 +12492,19 @@
         <v>32</v>
       </c>
       <c r="E125">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F125">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G125" s="1">
-        <v>43.75</v>
+        <v>84.38</v>
       </c>
       <c r="H125" s="1">
-        <v>56.25</v>
+        <v>15.63</v>
       </c>
       <c r="I125" s="2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -12314,22 +12527,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F126">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G126" s="1">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H126" s="1">
-        <v>93.55</v>
+        <v>29.03</v>
+      </c>
+      <c r="I126" s="2">
+        <v>6.3</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -12346,22 +12562,25 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F127">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G127" s="1">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H127" s="1">
-        <v>86.20999999999999</v>
+        <v>6.9</v>
+      </c>
+      <c r="I127" s="2">
+        <v>7.8</v>
       </c>
       <c r="J127">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -12378,22 +12597,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F128">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>85.29000000000001</v>
+        <v>8.82</v>
+      </c>
+      <c r="I128" s="2">
+        <v>7.6</v>
       </c>
       <c r="J128">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -12410,22 +12632,25 @@
         <v>19</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F129">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H129" s="1">
-        <v>73.68000000000001</v>
+        <v>5.26</v>
+      </c>
+      <c r="I129" s="2">
+        <v>7.9</v>
       </c>
       <c r="J129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -12442,16 +12667,19 @@
         <v>38</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F130">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>71.05</v>
       </c>
       <c r="H130" s="1">
-        <v>100</v>
+        <v>28.95</v>
+      </c>
+      <c r="I130" s="2">
+        <v>7.8</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -12474,16 +12702,19 @@
         <v>34</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F131">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H131" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I131" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -12506,16 +12737,19 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F132">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G132" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H132" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I132" s="2">
+        <v>7.6</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -12538,16 +12772,19 @@
         <v>22</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F133">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G133" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H133" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I133" s="2">
+        <v>8</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -12570,16 +12807,19 @@
         <v>31</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F134">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G134" s="1">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H134" s="1">
-        <v>100</v>
+        <v>19.35</v>
+      </c>
+      <c r="I134" s="2">
+        <v>7.5</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -12602,16 +12842,19 @@
         <v>33</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F135">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G135" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H135" s="1">
-        <v>100</v>
+        <v>6.06</v>
+      </c>
+      <c r="I135" s="2">
+        <v>8.9</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -12879,19 +13122,19 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F143">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G143" s="1">
-        <v>58.33</v>
+        <v>77.78</v>
       </c>
       <c r="H143" s="1">
-        <v>41.67</v>
+        <v>22.22</v>
       </c>
       <c r="I143" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -12984,19 +13227,19 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F146">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G146" s="1">
-        <v>9.76</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H146" s="1">
-        <v>90.23999999999999</v>
+        <v>31.71</v>
       </c>
       <c r="I146" s="2">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -13054,16 +13297,16 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H148" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I148" s="2">
         <v>8.9</v>
@@ -13229,19 +13472,19 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F153">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G153" s="1">
-        <v>75</v>
+        <v>84.38</v>
       </c>
       <c r="H153" s="1">
-        <v>25</v>
+        <v>15.63</v>
       </c>
       <c r="I153" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -13276,7 +13519,7 @@
         <v>24.24</v>
       </c>
       <c r="I154" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -13299,19 +13542,19 @@
         <v>34</v>
       </c>
       <c r="E155">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F155">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>85.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -13334,19 +13577,19 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G156" s="1">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H156" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="I156" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -13369,16 +13612,19 @@
         <v>40</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F157">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H157" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I157" s="2">
+        <v>8.4</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -13401,22 +13647,25 @@
         <v>30</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F158">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H158" s="1">
-        <v>96.67</v>
+        <v>10</v>
+      </c>
+      <c r="I158" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -13433,22 +13682,25 @@
         <v>32</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F159">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G159" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H159" s="1">
-        <v>96.88</v>
+        <v>6.25</v>
+      </c>
+      <c r="I159" s="2">
+        <v>8.9</v>
       </c>
       <c r="J159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -13465,19 +13717,19 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F160">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G160" s="1">
-        <v>62.96</v>
+        <v>92.59</v>
       </c>
       <c r="H160" s="1">
-        <v>37.04</v>
+        <v>7.41</v>
       </c>
       <c r="I160" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -13535,19 +13787,19 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F162">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G162" s="1">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="H162" s="1">
-        <v>33.33</v>
+        <v>29.17</v>
       </c>
       <c r="I162" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -13605,16 +13857,19 @@
         <v>32</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F164">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G164" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H164" s="1">
-        <v>100</v>
+        <v>34.38</v>
+      </c>
+      <c r="I164" s="2">
+        <v>5.8</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -13637,16 +13892,19 @@
         <v>36</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F165">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G165" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="H165" s="1">
-        <v>100</v>
+        <v>41.67</v>
+      </c>
+      <c r="I165" s="2">
+        <v>6</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -13911,16 +14169,19 @@
         <v>36</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F173">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G173" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H173" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I173" s="2">
+        <v>6.5</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -13943,22 +14204,25 @@
         <v>31</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F174">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G174" s="1">
-        <v>0</v>
+        <v>61.29</v>
       </c>
       <c r="H174" s="1">
-        <v>90.31999999999999</v>
+        <v>38.71</v>
+      </c>
+      <c r="I174" s="2">
+        <v>6.1</v>
       </c>
       <c r="J174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -13975,22 +14239,25 @@
         <v>19</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F175">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G175" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H175" s="1">
-        <v>94.73999999999999</v>
+        <v>31.58</v>
+      </c>
+      <c r="I175" s="2">
+        <v>7.1</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -14007,22 +14274,25 @@
         <v>19</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F176">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G176" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H176" s="1">
-        <v>94.73999999999999</v>
+        <v>31.58</v>
+      </c>
+      <c r="I176" s="2">
+        <v>7.1</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -14144,22 +14414,25 @@
         <v>32</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F180">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H180" s="1">
-        <v>96.88</v>
+        <v>0</v>
+      </c>
+      <c r="I180" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -14176,22 +14449,25 @@
         <v>32</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F181">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H181" s="1">
-        <v>96.88</v>
+        <v>0</v>
+      </c>
+      <c r="I181" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -14208,16 +14484,19 @@
         <v>33</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F182">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G182" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H182" s="1">
-        <v>100</v>
+        <v>3.03</v>
+      </c>
+      <c r="I182" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -14275,16 +14554,19 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F184">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G184" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H184" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I184" s="2">
+        <v>8</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -14307,16 +14589,19 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F185">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H185" s="1">
-        <v>65</v>
+        <v>15</v>
+      </c>
+      <c r="I185" s="2">
+        <v>8</v>
       </c>
       <c r="J185">
         <v>7</v>
@@ -14339,22 +14624,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F186">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G186" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H186" s="1">
-        <v>73.68000000000001</v>
+        <v>15.79</v>
+      </c>
+      <c r="I186" s="2">
+        <v>7.7</v>
       </c>
       <c r="J186">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K186" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -14403,22 +14691,25 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F188">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H188" s="1">
-        <v>65.79000000000001</v>
+        <v>26.32</v>
+      </c>
+      <c r="I188" s="2">
+        <v>8.4</v>
       </c>
       <c r="J188">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -14435,22 +14726,25 @@
         <v>34</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F189">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H189" s="1">
-        <v>79.41</v>
+        <v>11.76</v>
+      </c>
+      <c r="I189" s="2">
+        <v>9.1</v>
       </c>
       <c r="J189">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -14467,22 +14761,25 @@
         <v>24</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F190">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G190" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H190" s="1">
-        <v>70.83</v>
+        <v>8.33</v>
+      </c>
+      <c r="I190" s="2">
+        <v>7.9</v>
       </c>
       <c r="J190">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>29.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -14499,22 +14796,25 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F191">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G191" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H191" s="1">
-        <v>51.61</v>
+        <v>35.48</v>
+      </c>
+      <c r="I191" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J191">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -14531,22 +14831,25 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F192">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G192" s="1">
-        <v>0</v>
+        <v>60.71</v>
       </c>
       <c r="H192" s="1">
-        <v>85.70999999999999</v>
+        <v>32.14</v>
+      </c>
+      <c r="I192" s="2">
+        <v>6.2</v>
       </c>
       <c r="J192">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K192" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -14563,22 +14866,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F193">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G193" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H193" s="1">
-        <v>82.14</v>
+        <v>14.29</v>
+      </c>
+      <c r="I193" s="2">
+        <v>5.8</v>
       </c>
       <c r="J193">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K193" s="1">
-        <v>17.86</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -14595,22 +14901,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F194">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G194" s="1">
-        <v>0</v>
+        <v>41.46</v>
       </c>
       <c r="H194" s="1">
-        <v>75.61</v>
+        <v>41.46</v>
+      </c>
+      <c r="I194" s="2">
+        <v>6.2</v>
       </c>
       <c r="J194">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K194" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -14627,16 +14936,19 @@
         <v>17</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F195">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G195" s="1">
-        <v>0</v>
+        <v>58.82</v>
       </c>
       <c r="H195" s="1">
-        <v>100</v>
+        <v>41.18</v>
+      </c>
+      <c r="I195" s="2">
+        <v>5.9</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -14659,16 +14971,19 @@
         <v>32</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F196">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G196" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H196" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I196" s="2">
+        <v>7.5</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -14691,22 +15006,25 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F197">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="H197" s="1">
-        <v>97.22</v>
+        <v>36.11</v>
+      </c>
+      <c r="I197" s="2">
+        <v>6.6</v>
       </c>
       <c r="J197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -14723,22 +15041,25 @@
         <v>31</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F198">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H198" s="1">
-        <v>93.55</v>
+        <v>32.26</v>
+      </c>
+      <c r="I198" s="2">
+        <v>6.4</v>
       </c>
       <c r="J198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -15507,19 +15828,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H11" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -15647,19 +15968,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G15" s="1">
-        <v>81.25</v>
+        <v>71.88</v>
       </c>
       <c r="H15" s="1">
-        <v>18.75</v>
+        <v>28.13</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -15787,25 +16108,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>9.76</v>
+        <v>7.32</v>
       </c>
       <c r="I19" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -15822,25 +16143,25 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>20</v>
+        <v>14.29</v>
       </c>
       <c r="I20" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -15857,25 +16178,25 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>68.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>25.71</v>
+        <v>14.29</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15904,7 +16225,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="I22" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -15927,19 +16248,19 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>97.22</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I23" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -15974,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -16009,7 +16330,7 @@
         <v>17.14</v>
       </c>
       <c r="I25" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -16044,7 +16365,7 @@
         <v>5.41</v>
       </c>
       <c r="I26" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -16114,7 +16435,7 @@
         <v>12.2</v>
       </c>
       <c r="I28" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -16184,7 +16505,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -16207,25 +16528,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -16277,13 +16598,13 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -16292,10 +16613,10 @@
         <v>7.3</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -16312,25 +16633,25 @@
         <v>19</v>
       </c>
       <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
         <v>7</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
       <c r="G34" s="1">
+        <v>47.37</v>
+      </c>
+      <c r="H34" s="1">
         <v>36.84</v>
       </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
       <c r="I34" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1">
-        <v>63.16</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -16347,19 +16668,19 @@
         <v>31</v>
       </c>
       <c r="E35">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G35" s="1">
-        <v>77.42</v>
+        <v>70.97</v>
       </c>
       <c r="H35" s="1">
-        <v>19.35</v>
+        <v>25.81</v>
       </c>
       <c r="I35" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -16382,25 +16703,25 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36">
         <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H36" s="1">
         <v>31.25</v>
       </c>
       <c r="I36" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -16417,25 +16738,25 @@
         <v>32</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1">
-        <v>68.75</v>
+        <v>65.63</v>
       </c>
       <c r="H37" s="1">
-        <v>25</v>
+        <v>31.25</v>
       </c>
       <c r="I37" s="2">
         <v>7.4</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -16464,7 +16785,7 @@
         <v>18.18</v>
       </c>
       <c r="I38" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J38">
         <v>3</v>
@@ -16709,7 +17030,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -16744,7 +17065,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -16767,25 +17088,25 @@
         <v>34</v>
       </c>
       <c r="E47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
       </c>
       <c r="I47" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -16814,7 +17135,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="2">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -16837,19 +17158,19 @@
         <v>31</v>
       </c>
       <c r="E49">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I49" s="2">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -16872,25 +17193,25 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>80</v>
+        <v>97.5</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I50" s="2">
         <v>7.5</v>
       </c>
       <c r="J50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -16907,25 +17228,25 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="I51" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -16942,25 +17263,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
       </c>
       <c r="I52" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J52">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K52" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -17024,7 +17345,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J54">
         <v>11</v>
@@ -17082,25 +17403,25 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
       </c>
       <c r="I56" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K56" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -17117,25 +17438,25 @@
         <v>32</v>
       </c>
       <c r="E57">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G57" s="1">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I57" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -17152,25 +17473,25 @@
         <v>44</v>
       </c>
       <c r="E58">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G58" s="1">
-        <v>95.45</v>
+        <v>90.91</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="I58" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -17187,19 +17508,19 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="1">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I59" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -17222,25 +17543,25 @@
         <v>37</v>
       </c>
       <c r="E60">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G60" s="1">
-        <v>89.19</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>13.51</v>
       </c>
       <c r="I60" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -17257,25 +17578,25 @@
         <v>32</v>
       </c>
       <c r="E61">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>93.75</v>
+        <v>90.63</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I61" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -17292,25 +17613,25 @@
         <v>44</v>
       </c>
       <c r="E62">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>90.91</v>
+        <v>88.64</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>11.36</v>
       </c>
       <c r="I62" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -17327,25 +17648,25 @@
         <v>24</v>
       </c>
       <c r="E63">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="1">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I63" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -17467,25 +17788,25 @@
         <v>32</v>
       </c>
       <c r="E67">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G67" s="1">
-        <v>81.25</v>
+        <v>78.13</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>21.88</v>
       </c>
       <c r="I67" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J67">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -17505,22 +17826,22 @@
         <v>34</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G68" s="1">
         <v>77.27</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="I68" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -17537,25 +17858,25 @@
         <v>37</v>
       </c>
       <c r="E69">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G69" s="1">
-        <v>89.19</v>
+        <v>83.78</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>16.22</v>
       </c>
       <c r="I69" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -17572,25 +17893,25 @@
         <v>32</v>
       </c>
       <c r="E70">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G70" s="1">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>28.13</v>
       </c>
       <c r="I70" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -17607,25 +17928,25 @@
         <v>44</v>
       </c>
       <c r="E71">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G71" s="1">
-        <v>84.09</v>
+        <v>86.36</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="I71" s="2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>15.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -17642,25 +17963,25 @@
         <v>36</v>
       </c>
       <c r="E72">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F72">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G72" s="1">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="H72" s="1">
-        <v>27.78</v>
+        <v>50</v>
       </c>
       <c r="I72" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J72">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -17677,25 +17998,25 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G73" s="1">
-        <v>62.16</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>32.43</v>
       </c>
       <c r="I73" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J73">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>37.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -17922,25 +18243,25 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G80" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="I80" s="2">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -17957,25 +18278,25 @@
         <v>36</v>
       </c>
       <c r="E81">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G81" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I81" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J81">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -17992,25 +18313,25 @@
         <v>36</v>
       </c>
       <c r="E82">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G82" s="1">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="I82" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J82">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -18027,25 +18348,25 @@
         <v>33</v>
       </c>
       <c r="E83">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G83" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>27.27</v>
       </c>
       <c r="I83" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J83">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -18062,25 +18383,25 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G84" s="1">
-        <v>9.68</v>
+        <v>32.26</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="I84" s="2">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="J84">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>90.31999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -18097,25 +18418,25 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G85" s="1">
-        <v>67.65000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>29.41</v>
       </c>
       <c r="I85" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J85">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -18342,25 +18663,25 @@
         <v>32</v>
       </c>
       <c r="E92">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F92">
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J92">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -18377,25 +18698,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93" s="1">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K93" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -18424,7 +18745,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J94">
         <v>2</v>
@@ -18447,25 +18768,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -18482,25 +18803,25 @@
         <v>19</v>
       </c>
       <c r="E96">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F96">
         <v>0</v>
       </c>
       <c r="G96" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
       </c>
       <c r="I96" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J96">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -18517,25 +18838,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F97">
         <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
       </c>
       <c r="I97" s="2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K97" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -18739,7 +19060,7 @@
         <v>18.18</v>
       </c>
       <c r="I103" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -18762,19 +19083,19 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F104">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G104" s="1">
-        <v>69.7</v>
+        <v>66.67</v>
       </c>
       <c r="H104" s="1">
-        <v>30.3</v>
+        <v>33.33</v>
       </c>
       <c r="I104" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -18797,19 +19118,19 @@
         <v>32</v>
       </c>
       <c r="E105">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G105" s="1">
-        <v>96.88</v>
+        <v>15.63</v>
       </c>
       <c r="H105" s="1">
-        <v>3.13</v>
+        <v>84.38</v>
       </c>
       <c r="I105" s="2">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -18832,19 +19153,19 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F106">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G106" s="1">
-        <v>83.33</v>
+        <v>33.33</v>
       </c>
       <c r="H106" s="1">
-        <v>16.67</v>
+        <v>66.67</v>
       </c>
       <c r="I106" s="2">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -18867,19 +19188,19 @@
         <v>32</v>
       </c>
       <c r="E107">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F107">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G107" s="1">
-        <v>93.75</v>
+        <v>28.13</v>
       </c>
       <c r="H107" s="1">
-        <v>6.25</v>
+        <v>71.88</v>
       </c>
       <c r="I107" s="2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -18902,19 +19223,19 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F108">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G108" s="1">
-        <v>68.42</v>
+        <v>57.89</v>
       </c>
       <c r="H108" s="1">
-        <v>31.58</v>
+        <v>42.11</v>
       </c>
       <c r="I108" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -18937,19 +19258,19 @@
         <v>32</v>
       </c>
       <c r="E109">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F109">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G109" s="1">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H109" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I109" s="2">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -18972,25 +19293,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G110" s="1">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H110" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I110" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J110">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K110" s="1">
-        <v>88.89</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -19007,25 +19328,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F111">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>48.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
       <c r="I111" s="2">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J111">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K111" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -19042,25 +19363,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I112" s="2">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J112">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K112" s="1">
-        <v>65.84999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -19194,7 +19515,7 @@
         <v>4.55</v>
       </c>
       <c r="I116" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -19229,7 +19550,7 @@
         <v>4.55</v>
       </c>
       <c r="I117" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -19252,19 +19573,19 @@
         <v>33</v>
       </c>
       <c r="E118">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F118">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G118" s="1">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H118" s="1">
-        <v>30.3</v>
+        <v>18.18</v>
       </c>
       <c r="I118" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -19287,19 +19608,19 @@
         <v>33</v>
       </c>
       <c r="E119">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F119">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G119" s="1">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H119" s="1">
-        <v>30.3</v>
+        <v>21.21</v>
       </c>
       <c r="I119" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -19395,22 +19716,22 @@
         <v>33</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G122" s="1">
         <v>89.19</v>
       </c>
       <c r="H122" s="1">
-        <v>0</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I122" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K122" s="1">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -19474,7 +19795,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -19509,7 +19830,7 @@
         <v>15.63</v>
       </c>
       <c r="I125" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -19532,25 +19853,25 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G126" s="1">
-        <v>93.55</v>
+        <v>70.97</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>29.03</v>
       </c>
       <c r="I126" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -19567,25 +19888,25 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G127" s="1">
-        <v>82.76000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H127" s="1">
-        <v>3.45</v>
+        <v>6.9</v>
       </c>
       <c r="I127" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J127">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -19602,25 +19923,25 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G128" s="1">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="I128" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J128">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -19637,25 +19958,25 @@
         <v>19</v>
       </c>
       <c r="E129">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" s="1">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H129" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I129" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J129">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -19672,19 +19993,19 @@
         <v>38</v>
       </c>
       <c r="E130">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F130">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G130" s="1">
-        <v>68.42</v>
+        <v>71.05</v>
       </c>
       <c r="H130" s="1">
-        <v>31.58</v>
+        <v>28.95</v>
       </c>
       <c r="I130" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -19707,19 +20028,19 @@
         <v>34</v>
       </c>
       <c r="E131">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F131">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G131" s="1">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H131" s="1">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
       <c r="I131" s="2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -19742,19 +20063,19 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F132">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G132" s="1">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H132" s="1">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="I132" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -19777,19 +20098,19 @@
         <v>22</v>
       </c>
       <c r="E133">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G133" s="1">
-        <v>81.81999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="H133" s="1">
-        <v>18.18</v>
+        <v>22.73</v>
       </c>
       <c r="I133" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -19812,19 +20133,19 @@
         <v>31</v>
       </c>
       <c r="E134">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G134" s="1">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H134" s="1">
-        <v>22.58</v>
+        <v>19.35</v>
       </c>
       <c r="I134" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -19847,19 +20168,19 @@
         <v>33</v>
       </c>
       <c r="E135">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G135" s="1">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="H135" s="1">
-        <v>12.12</v>
+        <v>6.06</v>
       </c>
       <c r="I135" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -20127,16 +20448,16 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F143">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G143" s="1">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H143" s="1">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="I143" s="2">
         <v>7.8</v>
@@ -20232,19 +20553,19 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F146">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G146" s="1">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H146" s="1">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="I146" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -20302,16 +20623,16 @@
         <v>32</v>
       </c>
       <c r="E148">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H148" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I148" s="2">
         <v>8.800000000000001</v>
@@ -20477,19 +20798,19 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G153" s="1">
-        <v>96.88</v>
+        <v>84.38</v>
       </c>
       <c r="H153" s="1">
-        <v>3.13</v>
+        <v>15.63</v>
       </c>
       <c r="I153" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -20512,19 +20833,19 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G154" s="1">
-        <v>84.84999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>15.15</v>
+        <v>24.24</v>
       </c>
       <c r="I154" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -20559,7 +20880,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -20594,7 +20915,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -20629,7 +20950,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -20652,25 +20973,25 @@
         <v>30</v>
       </c>
       <c r="E158">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F158">
         <v>1</v>
       </c>
       <c r="G158" s="1">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H158" s="1">
         <v>3.33</v>
       </c>
       <c r="I158" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -20687,25 +21008,25 @@
         <v>32</v>
       </c>
       <c r="E159">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G159" s="1">
-        <v>96.88</v>
+        <v>93.75</v>
       </c>
       <c r="H159" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I159" s="2">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -20722,16 +21043,16 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G160" s="1">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H160" s="1">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
       <c r="I160" s="2">
         <v>7.3</v>
@@ -20862,19 +21183,19 @@
         <v>32</v>
       </c>
       <c r="E164">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F164">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G164" s="1">
-        <v>87.5</v>
+        <v>65.63</v>
       </c>
       <c r="H164" s="1">
-        <v>12.5</v>
+        <v>34.38</v>
       </c>
       <c r="I164" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -20897,16 +21218,16 @@
         <v>36</v>
       </c>
       <c r="E165">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F165">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G165" s="1">
-        <v>86.11</v>
+        <v>58.33</v>
       </c>
       <c r="H165" s="1">
-        <v>13.89</v>
+        <v>41.67</v>
       </c>
       <c r="I165" s="2">
         <v>5.9</v>
@@ -21177,19 +21498,19 @@
         <v>36</v>
       </c>
       <c r="E173">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F173">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G173" s="1">
-        <v>88.89</v>
+        <v>77.78</v>
       </c>
       <c r="H173" s="1">
-        <v>11.11</v>
+        <v>22.22</v>
       </c>
       <c r="I173" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -21212,25 +21533,25 @@
         <v>31</v>
       </c>
       <c r="E174">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F174">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G174" s="1">
-        <v>64.52</v>
+        <v>61.29</v>
       </c>
       <c r="H174" s="1">
-        <v>25.81</v>
+        <v>38.71</v>
       </c>
       <c r="I174" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J174">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -21247,25 +21568,25 @@
         <v>19</v>
       </c>
       <c r="E175">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G175" s="1">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H175" s="1">
-        <v>21.05</v>
+        <v>31.58</v>
       </c>
       <c r="I175" s="2">
         <v>6.9</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -21282,25 +21603,25 @@
         <v>19</v>
       </c>
       <c r="E176">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F176">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G176" s="1">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H176" s="1">
-        <v>21.05</v>
+        <v>31.58</v>
       </c>
       <c r="I176" s="2">
         <v>6.9</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -21422,25 +21743,25 @@
         <v>32</v>
       </c>
       <c r="E180">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
       <c r="I180" s="2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -21457,25 +21778,25 @@
         <v>32</v>
       </c>
       <c r="E181">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F181">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G181" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H181" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I181" s="2">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -21492,19 +21813,19 @@
         <v>33</v>
       </c>
       <c r="E182">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F182">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G182" s="1">
-        <v>48.48</v>
+        <v>96.97</v>
       </c>
       <c r="H182" s="1">
-        <v>51.52</v>
+        <v>3.03</v>
       </c>
       <c r="I182" s="2">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -21574,7 +21895,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -21597,19 +21918,19 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G185" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H185" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I185" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J185">
         <v>7</v>
@@ -21632,25 +21953,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
       </c>
       <c r="I186" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J186">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K186" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -21702,25 +22023,25 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G188" s="1">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H188" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="I188" s="2">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="J188">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -21737,25 +22058,25 @@
         <v>34</v>
       </c>
       <c r="E189">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G189" s="1">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="I189" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J189">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -21772,25 +22093,25 @@
         <v>24</v>
       </c>
       <c r="E190">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G190" s="1">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="H190" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I190" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J190">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>29.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -21807,25 +22128,25 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G191" s="1">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H191" s="1">
-        <v>0</v>
+        <v>32.26</v>
       </c>
       <c r="I191" s="2">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="J191">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -21842,25 +22163,25 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G192" s="1">
-        <v>85.70999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H192" s="1">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="I192" s="2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J192">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K192" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -21877,25 +22198,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G193" s="1">
-        <v>82.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H193" s="1">
-        <v>0</v>
+        <v>10.71</v>
       </c>
       <c r="I193" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J193">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K193" s="1">
-        <v>17.86</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -21912,25 +22233,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F194">
         <v>0</v>
       </c>
       <c r="G194" s="1">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
       </c>
       <c r="I194" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J194">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K194" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -21982,19 +22303,19 @@
         <v>32</v>
       </c>
       <c r="E196">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F196">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G196" s="1">
-        <v>65.63</v>
+        <v>87.5</v>
       </c>
       <c r="H196" s="1">
-        <v>34.38</v>
+        <v>12.5</v>
       </c>
       <c r="I196" s="2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -22017,25 +22338,25 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F197">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G197" s="1">
-        <v>69.44</v>
+        <v>63.89</v>
       </c>
       <c r="H197" s="1">
-        <v>27.78</v>
+        <v>36.11</v>
       </c>
       <c r="I197" s="2">
         <v>6.7</v>
       </c>
       <c r="J197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -22052,25 +22373,25 @@
         <v>31</v>
       </c>
       <c r="E198">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F198">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G198" s="1">
-        <v>64.52</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H198" s="1">
-        <v>29.03</v>
+        <v>32.26</v>
       </c>
       <c r="I198" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -4723,25 +4723,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="H112" s="1">
         <v>2.44</v>
       </c>
       <c r="I112" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J112">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K112" s="1">
-        <v>43.9</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7351,22 +7351,22 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G187" s="1">
         <v>50</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I187" s="2">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="J187">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -12037,25 +12037,25 @@
         <v>41</v>
       </c>
       <c r="E112">
+        <v>19</v>
+      </c>
+      <c r="F112">
+        <v>5</v>
+      </c>
+      <c r="G112" s="1">
+        <v>46.34</v>
+      </c>
+      <c r="H112" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="I112" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J112">
         <v>17</v>
       </c>
-      <c r="F112">
-        <v>6</v>
-      </c>
-      <c r="G112" s="1">
+      <c r="K112" s="1">
         <v>41.46</v>
-      </c>
-      <c r="H112" s="1">
-        <v>14.63</v>
-      </c>
-      <c r="I112" s="2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J112">
-        <v>18</v>
-      </c>
-      <c r="K112" s="1">
-        <v>43.9</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -13122,19 +13122,19 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F143">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G143" s="1">
-        <v>77.78</v>
+        <v>94.44</v>
       </c>
       <c r="H143" s="1">
-        <v>22.22</v>
+        <v>5.56</v>
       </c>
       <c r="I143" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -13927,16 +13927,19 @@
         <v>33</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F166">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G166" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H166" s="1">
-        <v>100</v>
+        <v>36.36</v>
+      </c>
+      <c r="I166" s="2">
+        <v>5.7</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -14659,22 +14662,25 @@
         <v>20</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F187">
         <v>10</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H187" s="1">
         <v>50</v>
       </c>
+      <c r="I187" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J187">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -19363,13 +19369,13 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="H112" s="1">
         <v>2.44</v>
@@ -19378,10 +19384,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J112">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K112" s="1">
-        <v>43.9</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -21253,19 +21259,19 @@
         <v>33</v>
       </c>
       <c r="E166">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F166">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G166" s="1">
-        <v>87.88</v>
+        <v>63.64</v>
       </c>
       <c r="H166" s="1">
-        <v>12.12</v>
+        <v>36.36</v>
       </c>
       <c r="I166" s="2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -21988,25 +21994,25 @@
         <v>20</v>
       </c>
       <c r="E187">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I187" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J187">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -3428,25 +3428,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" s="1">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H75" s="1">
         <v>3.33</v>
       </c>
       <c r="I75" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J75">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K75" s="1">
-        <v>43.33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3533,25 +3533,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F78">
         <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H78" s="1">
         <v>5.88</v>
       </c>
       <c r="I78" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -9675,19 +9675,19 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G44" s="1">
-        <v>43.75</v>
+        <v>46.88</v>
       </c>
       <c r="H44" s="1">
-        <v>56.25</v>
+        <v>53.13</v>
       </c>
       <c r="I44" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -9990,16 +9990,16 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F53">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" s="1">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H53" s="1">
-        <v>24.24</v>
+        <v>21.21</v>
       </c>
       <c r="I53" s="2">
         <v>8</v>
@@ -10025,19 +10025,19 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" s="1">
-        <v>38.71</v>
+        <v>41.94</v>
       </c>
       <c r="H54" s="1">
-        <v>25.81</v>
+        <v>22.58</v>
       </c>
       <c r="I54" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J54">
         <v>11</v>
@@ -10095,16 +10095,16 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F56">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G56" s="1">
-        <v>38.71</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H56" s="1">
-        <v>51.61</v>
+        <v>3.23</v>
       </c>
       <c r="I56" s="2">
         <v>8.4</v>
@@ -10725,16 +10725,19 @@
         <v>16</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F74">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H74" s="1">
-        <v>93.75</v>
+        <v>12.5</v>
+      </c>
+      <c r="I74" s="2">
+        <v>8.1</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -10757,22 +10760,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F75">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>43.33</v>
       </c>
       <c r="H75" s="1">
-        <v>56.67</v>
+        <v>26.67</v>
+      </c>
+      <c r="I75" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J75">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K75" s="1">
-        <v>43.33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -10789,16 +10795,19 @@
         <v>29</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F76">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>79.31</v>
       </c>
       <c r="H76" s="1">
-        <v>100</v>
+        <v>20.69</v>
+      </c>
+      <c r="I76" s="2">
+        <v>8.6</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -10821,16 +10830,19 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F77">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H77" s="1">
-        <v>100</v>
+        <v>42.11</v>
+      </c>
+      <c r="I77" s="2">
+        <v>8.5</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -10853,22 +10865,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F78">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>79.41</v>
       </c>
       <c r="H78" s="1">
-        <v>94.12</v>
+        <v>17.65</v>
+      </c>
+      <c r="I78" s="2">
+        <v>8.9</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -10885,16 +10900,19 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H79" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I79" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -13227,19 +13245,19 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F146">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G146" s="1">
-        <v>68.29000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="H146" s="1">
-        <v>31.71</v>
+        <v>24.39</v>
       </c>
       <c r="I146" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -17421,7 +17439,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J56">
         <v>3</v>
@@ -18074,25 +18092,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>53.33</v>
+        <v>70</v>
       </c>
       <c r="H75" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="I75" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J75">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K75" s="1">
-        <v>43.33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -18121,7 +18139,7 @@
         <v>6.9</v>
       </c>
       <c r="I76" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -18144,19 +18162,19 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G77" s="1">
-        <v>63.16</v>
+        <v>68.42</v>
       </c>
       <c r="H77" s="1">
-        <v>36.84</v>
+        <v>31.58</v>
       </c>
       <c r="I77" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -18179,25 +18197,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H78" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I78" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -18214,19 +18232,19 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H79" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="I79" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -20571,7 +20589,7 @@
         <v>14.63</v>
       </c>
       <c r="I146" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J146">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1888,25 +1888,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I31" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1923,25 +1923,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I32" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1958,25 +1958,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1">
-        <v>85.70999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>10.71</v>
       </c>
       <c r="I33" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2623,25 +2623,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I52" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J52">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>22.22</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2658,25 +2658,25 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="I53" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2728,25 +2728,25 @@
         <v>38</v>
       </c>
       <c r="E55">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" s="1">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>13.16</v>
       </c>
       <c r="I55" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2763,25 +2763,25 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="1">
-        <v>87.09999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H56" s="1">
-        <v>3.23</v>
+        <v>6.45</v>
       </c>
       <c r="I56" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3043,25 +3043,25 @@
         <v>19</v>
       </c>
       <c r="E64">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I64" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3078,13 +3078,13 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3093,10 +3093,10 @@
         <v>7.5</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3116,22 +3116,22 @@
         <v>30</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G66" s="1">
         <v>90.91</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="I66" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3396,22 +3396,22 @@
         <v>14</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="1">
         <v>87.5</v>
       </c>
       <c r="H74" s="1">
-        <v>6.25</v>
+        <v>12.5</v>
       </c>
       <c r="I74" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3428,25 +3428,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H75" s="1">
-        <v>3.33</v>
+        <v>16.67</v>
       </c>
       <c r="I75" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J75">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3536,22 +3536,22 @@
         <v>31</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="1">
         <v>91.18000000000001</v>
       </c>
       <c r="H78" s="1">
-        <v>5.88</v>
+        <v>8.82</v>
       </c>
       <c r="I78" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3921,22 +3921,22 @@
         <v>20</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" s="1">
         <v>83.33</v>
       </c>
       <c r="H89" s="1">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="I89" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3956,22 +3956,22 @@
         <v>21</v>
       </c>
       <c r="F90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="1">
         <v>87.5</v>
       </c>
       <c r="H90" s="1">
-        <v>8.33</v>
+        <v>12.5</v>
       </c>
       <c r="I90" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -4128,13 +4128,13 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -4143,10 +4143,10 @@
         <v>9.4</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -4723,25 +4723,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="H112" s="1">
         <v>2.44</v>
       </c>
       <c r="I112" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J112">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K112" s="1">
-        <v>41.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -5671,22 +5671,22 @@
         <v>23</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" s="1">
         <v>95.83</v>
       </c>
       <c r="H139" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="I139" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -7523,13 +7523,13 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F192">
         <v>2</v>
       </c>
       <c r="G192" s="1">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H192" s="1">
         <v>7.14</v>
@@ -7538,10 +7538,10 @@
         <v>6.3</v>
       </c>
       <c r="J192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -7558,25 +7558,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F193">
         <v>1</v>
       </c>
       <c r="G193" s="1">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H193" s="1">
         <v>3.57</v>
       </c>
       <c r="I193" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K193" s="1">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -8917,7 +8917,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -9010,19 +9010,19 @@
         <v>35</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>51.43</v>
+        <v>82.86</v>
       </c>
       <c r="H25" s="1">
-        <v>48.57</v>
+        <v>17.14</v>
       </c>
       <c r="I25" s="2">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -9045,19 +9045,19 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G26" s="1">
-        <v>48.65</v>
+        <v>91.89</v>
       </c>
       <c r="H26" s="1">
-        <v>51.35</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I26" s="2">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -9080,19 +9080,19 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>67.86</v>
+        <v>92.86</v>
       </c>
       <c r="H27" s="1">
-        <v>32.14</v>
+        <v>7.14</v>
       </c>
       <c r="I27" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -9115,19 +9115,19 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>53.66</v>
+        <v>87.8</v>
       </c>
       <c r="H28" s="1">
-        <v>46.34</v>
+        <v>12.2</v>
       </c>
       <c r="I28" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -9150,19 +9150,19 @@
         <v>16</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H29" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I29" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -9220,25 +9220,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I31" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -9255,25 +9255,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I32" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -9290,25 +9290,25 @@
         <v>28</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>7.14</v>
+        <v>14.29</v>
       </c>
       <c r="I33" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -9547,7 +9547,7 @@
         <v>70.83</v>
       </c>
       <c r="I40" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -9955,25 +9955,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F52">
         <v>3</v>
       </c>
       <c r="G52" s="1">
-        <v>69.44</v>
+        <v>88.89</v>
       </c>
       <c r="H52" s="1">
         <v>8.33</v>
       </c>
       <c r="I52" s="2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J52">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>22.22</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -9990,25 +9990,25 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F53">
         <v>7</v>
       </c>
       <c r="G53" s="1">
-        <v>66.67</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H53" s="1">
         <v>21.21</v>
       </c>
       <c r="I53" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -10060,25 +10060,25 @@
         <v>38</v>
       </c>
       <c r="E55">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G55" s="1">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H55" s="1">
-        <v>10.53</v>
+        <v>15.79</v>
       </c>
       <c r="I55" s="2">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -10095,25 +10095,25 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56" s="1">
-        <v>87.09999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H56" s="1">
         <v>3.23</v>
       </c>
       <c r="I56" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -10375,25 +10375,25 @@
         <v>19</v>
       </c>
       <c r="E64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" s="1">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H64" s="1">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="I64" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -10410,25 +10410,25 @@
         <v>31</v>
       </c>
       <c r="E65">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65" s="1">
-        <v>93.55</v>
+        <v>96.77</v>
       </c>
       <c r="H65" s="1">
         <v>3.23</v>
       </c>
       <c r="I65" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -10445,25 +10445,25 @@
         <v>33</v>
       </c>
       <c r="E66">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F66">
         <v>3</v>
       </c>
       <c r="G66" s="1">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H66" s="1">
         <v>9.09</v>
       </c>
       <c r="I66" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -10725,25 +10725,25 @@
         <v>16</v>
       </c>
       <c r="E74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74">
         <v>2</v>
       </c>
       <c r="G74" s="1">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H74" s="1">
         <v>12.5</v>
       </c>
       <c r="I74" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -10760,25 +10760,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F75">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1">
-        <v>43.33</v>
+        <v>83.33</v>
       </c>
       <c r="H75" s="1">
-        <v>26.67</v>
+        <v>16.67</v>
       </c>
       <c r="I75" s="2">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J75">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -10795,19 +10795,19 @@
         <v>29</v>
       </c>
       <c r="E76">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G76" s="1">
-        <v>79.31</v>
+        <v>89.66</v>
       </c>
       <c r="H76" s="1">
-        <v>20.69</v>
+        <v>10.34</v>
       </c>
       <c r="I76" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -10830,19 +10830,19 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F77">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G77" s="1">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H77" s="1">
-        <v>42.11</v>
+        <v>31.58</v>
       </c>
       <c r="I77" s="2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -10865,25 +10865,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F78">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="H78" s="1">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
       <c r="I78" s="2">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -10900,19 +10900,19 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G79" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H79" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I79" s="2">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -11250,25 +11250,25 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F89">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G89" s="1">
-        <v>58.33</v>
+        <v>75</v>
       </c>
       <c r="H89" s="1">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="I89" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -11285,25 +11285,25 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F90">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G90" s="1">
-        <v>54.17</v>
+        <v>79.17</v>
       </c>
       <c r="H90" s="1">
-        <v>41.67</v>
+        <v>20.83</v>
       </c>
       <c r="I90" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -11332,7 +11332,7 @@
         <v>25</v>
       </c>
       <c r="I91" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -11367,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -11402,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J93">
         <v>3</v>
@@ -11460,25 +11460,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H95" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -11810,19 +11810,19 @@
         <v>32</v>
       </c>
       <c r="E105">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F105">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G105" s="1">
-        <v>15.63</v>
+        <v>100</v>
       </c>
       <c r="H105" s="1">
-        <v>84.38</v>
+        <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -11845,19 +11845,19 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F106">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -11880,19 +11880,19 @@
         <v>32</v>
       </c>
       <c r="E107">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F107">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>28.13</v>
+        <v>100</v>
       </c>
       <c r="H107" s="1">
-        <v>71.88</v>
+        <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -11915,19 +11915,19 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F108">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G108" s="1">
-        <v>57.89</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>42.11</v>
+        <v>5.26</v>
       </c>
       <c r="I108" s="2">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -11950,19 +11950,19 @@
         <v>32</v>
       </c>
       <c r="E109">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F109">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G109" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H109" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I109" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -12020,19 +12020,19 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G111" s="1">
-        <v>64.86</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H111" s="1">
-        <v>10.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I111" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J111">
         <v>9</v>
@@ -12055,25 +12055,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G112" s="1">
-        <v>46.34</v>
+        <v>56.1</v>
       </c>
       <c r="H112" s="1">
-        <v>12.2</v>
+        <v>7.32</v>
       </c>
       <c r="I112" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J112">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K112" s="1">
-        <v>41.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -12592,7 +12592,7 @@
         <v>6.9</v>
       </c>
       <c r="I127" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -13000,13 +13000,13 @@
         <v>24</v>
       </c>
       <c r="E139">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F139">
         <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="H139" s="1">
         <v>20.83</v>
@@ -13015,10 +13015,10 @@
         <v>6.8</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -13117,7 +13117,7 @@
         <v>8.33</v>
       </c>
       <c r="I142" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -13245,19 +13245,19 @@
         <v>41</v>
       </c>
       <c r="E146">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F146">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G146" s="1">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H146" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
       <c r="I146" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -13805,19 +13805,19 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F162">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G162" s="1">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="H162" s="1">
-        <v>29.17</v>
+        <v>20.83</v>
       </c>
       <c r="I162" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -14680,19 +14680,19 @@
         <v>20</v>
       </c>
       <c r="E187">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F187">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H187" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I187" s="2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -14715,19 +14715,19 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F188">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G188" s="1">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H188" s="1">
-        <v>26.32</v>
+        <v>21.05</v>
       </c>
       <c r="I188" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -14750,19 +14750,19 @@
         <v>34</v>
       </c>
       <c r="E189">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F189">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G189" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H189" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I189" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -14797,7 +14797,7 @@
         <v>8.33</v>
       </c>
       <c r="I190" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -14820,19 +14820,19 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F191">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G191" s="1">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H191" s="1">
-        <v>35.48</v>
+        <v>22.58</v>
       </c>
       <c r="I191" s="2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -14855,25 +14855,25 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F192">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G192" s="1">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H192" s="1">
-        <v>32.14</v>
+        <v>17.86</v>
       </c>
       <c r="I192" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -14890,25 +14890,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G193" s="1">
-        <v>75</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H193" s="1">
-        <v>14.29</v>
+        <v>10.71</v>
       </c>
       <c r="I193" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K193" s="1">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -14960,16 +14960,16 @@
         <v>17</v>
       </c>
       <c r="E195">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F195">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G195" s="1">
-        <v>58.82</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H195" s="1">
-        <v>41.18</v>
+        <v>35.29</v>
       </c>
       <c r="I195" s="2">
         <v>5.9</v>
@@ -15759,7 +15759,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -15794,7 +15794,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -15817,19 +15817,19 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -15852,19 +15852,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H11" s="1">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -15887,19 +15887,19 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="H12" s="1">
-        <v>29.17</v>
+        <v>8.33</v>
       </c>
       <c r="I12" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -15922,19 +15922,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="H13" s="1">
-        <v>30.56</v>
+        <v>16.67</v>
       </c>
       <c r="I13" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -15957,19 +15957,19 @@
         <v>33</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>72.73</v>
+        <v>93.94</v>
       </c>
       <c r="H14" s="1">
-        <v>27.27</v>
+        <v>6.06</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -15992,19 +15992,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -16027,19 +16027,19 @@
         <v>44</v>
       </c>
       <c r="E16">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -16062,19 +16062,19 @@
         <v>44</v>
       </c>
       <c r="E17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H17" s="1">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -16097,16 +16097,16 @@
         <v>34</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>9</v>
@@ -16237,19 +16237,19 @@
         <v>37</v>
       </c>
       <c r="E22">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H22" s="1">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -16284,7 +16284,7 @@
         <v>2.78</v>
       </c>
       <c r="I23" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -16342,19 +16342,19 @@
         <v>35</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>82.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>17.14</v>
+        <v>14.29</v>
       </c>
       <c r="I25" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -16377,19 +16377,19 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -16424,7 +16424,7 @@
         <v>3.57</v>
       </c>
       <c r="I27" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -16447,19 +16447,19 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>87.8</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>12.2</v>
+        <v>7.32</v>
       </c>
       <c r="I28" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -16482,19 +16482,19 @@
         <v>16</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -16529,7 +16529,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -16552,25 +16552,25 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I31" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -16587,25 +16587,25 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I32" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -16625,22 +16625,22 @@
         <v>24</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1">
         <v>85.70999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="I33" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -16879,7 +16879,7 @@
         <v>58.33</v>
       </c>
       <c r="I40" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -17054,7 +17054,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -17089,7 +17089,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -17287,25 +17287,25 @@
         <v>36</v>
       </c>
       <c r="E52">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I52" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J52">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>22.22</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -17322,25 +17322,25 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H53" s="1">
-        <v>3.03</v>
+        <v>9.09</v>
       </c>
       <c r="I53" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -17395,22 +17395,22 @@
         <v>32</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G55" s="1">
         <v>84.20999999999999</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="I55" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -17427,25 +17427,25 @@
         <v>31</v>
       </c>
       <c r="E56">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="1">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I56" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -17462,19 +17462,19 @@
         <v>32</v>
       </c>
       <c r="E57">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H57" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I57" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -17497,19 +17497,19 @@
         <v>44</v>
       </c>
       <c r="E58">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="1">
-        <v>90.91</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H58" s="1">
-        <v>9.09</v>
+        <v>6.82</v>
       </c>
       <c r="I58" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -17544,7 +17544,7 @@
         <v>3.7</v>
       </c>
       <c r="I59" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -17567,19 +17567,19 @@
         <v>37</v>
       </c>
       <c r="E60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H60" s="1">
-        <v>13.51</v>
+        <v>10.81</v>
       </c>
       <c r="I60" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -17602,19 +17602,19 @@
         <v>32</v>
       </c>
       <c r="E61">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H61" s="1">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="I61" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -17637,19 +17637,19 @@
         <v>44</v>
       </c>
       <c r="E62">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F62">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>88.64</v>
+        <v>100</v>
       </c>
       <c r="H62" s="1">
-        <v>11.36</v>
+        <v>0</v>
       </c>
       <c r="I62" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -17684,7 +17684,7 @@
         <v>8.33</v>
       </c>
       <c r="I63" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -17707,25 +17707,25 @@
         <v>19</v>
       </c>
       <c r="E64">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G64" s="1">
-        <v>84.20999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="I64" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -17745,22 +17745,22 @@
         <v>30</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="1">
         <v>96.77</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I65" s="2">
         <v>8.1</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -17780,22 +17780,22 @@
         <v>30</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G66" s="1">
         <v>90.91</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="I66" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -17812,19 +17812,19 @@
         <v>32</v>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F67">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H67" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I67" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -17847,19 +17847,19 @@
         <v>44</v>
       </c>
       <c r="E68">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F68">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G68" s="1">
-        <v>77.27</v>
+        <v>88.64</v>
       </c>
       <c r="H68" s="1">
-        <v>22.73</v>
+        <v>11.36</v>
       </c>
       <c r="I68" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -17882,19 +17882,19 @@
         <v>37</v>
       </c>
       <c r="E69">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G69" s="1">
-        <v>83.78</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H69" s="1">
-        <v>16.22</v>
+        <v>13.51</v>
       </c>
       <c r="I69" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -17917,19 +17917,19 @@
         <v>32</v>
       </c>
       <c r="E70">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F70">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H70" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
       <c r="I70" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -17952,19 +17952,19 @@
         <v>44</v>
       </c>
       <c r="E71">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G71" s="1">
-        <v>86.36</v>
+        <v>97.73</v>
       </c>
       <c r="H71" s="1">
-        <v>13.64</v>
+        <v>2.27</v>
       </c>
       <c r="I71" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -17987,19 +17987,19 @@
         <v>36</v>
       </c>
       <c r="E72">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F72">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G72" s="1">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="H72" s="1">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="I72" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -18022,16 +18022,16 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F73">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G73" s="1">
-        <v>67.56999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H73" s="1">
-        <v>32.43</v>
+        <v>10.81</v>
       </c>
       <c r="I73" s="2">
         <v>6.5</v>
@@ -18057,25 +18057,25 @@
         <v>16</v>
       </c>
       <c r="E74">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H74" s="1">
         <v>6.25</v>
       </c>
       <c r="I74" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -18092,25 +18092,25 @@
         <v>30</v>
       </c>
       <c r="E75">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1">
-        <v>70</v>
+        <v>83.33</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I75" s="2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J75">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -18127,19 +18127,19 @@
         <v>29</v>
       </c>
       <c r="E76">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="1">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H76" s="1">
-        <v>6.9</v>
+        <v>10.34</v>
       </c>
       <c r="I76" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -18162,19 +18162,19 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G77" s="1">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H77" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I77" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -18197,25 +18197,25 @@
         <v>34</v>
       </c>
       <c r="E78">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H78" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I78" s="2">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -18232,19 +18232,19 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="1">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H79" s="1">
-        <v>5.26</v>
+        <v>10.53</v>
       </c>
       <c r="I79" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -18267,19 +18267,19 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F80">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G80" s="1">
-        <v>77.78</v>
+        <v>96.3</v>
       </c>
       <c r="H80" s="1">
-        <v>22.22</v>
+        <v>3.7</v>
       </c>
       <c r="I80" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -18302,19 +18302,19 @@
         <v>36</v>
       </c>
       <c r="E81">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" s="1">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H81" s="1">
-        <v>8.33</v>
+        <v>2.78</v>
       </c>
       <c r="I81" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -18337,19 +18337,19 @@
         <v>36</v>
       </c>
       <c r="E82">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G82" s="1">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="H82" s="1">
-        <v>22.22</v>
+        <v>8.33</v>
       </c>
       <c r="I82" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -18372,16 +18372,16 @@
         <v>33</v>
       </c>
       <c r="E83">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F83">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G83" s="1">
-        <v>72.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H83" s="1">
-        <v>27.27</v>
+        <v>15.15</v>
       </c>
       <c r="I83" s="2">
         <v>6.7</v>
@@ -18407,19 +18407,19 @@
         <v>31</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F84">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G84" s="1">
-        <v>32.26</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H84" s="1">
-        <v>67.73999999999999</v>
+        <v>19.35</v>
       </c>
       <c r="I84" s="2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -18442,19 +18442,19 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F85">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G85" s="1">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H85" s="1">
-        <v>29.41</v>
+        <v>5.88</v>
       </c>
       <c r="I85" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -18477,19 +18477,19 @@
         <v>28</v>
       </c>
       <c r="E86">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F86">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G86" s="1">
-        <v>53.57</v>
+        <v>75</v>
       </c>
       <c r="H86" s="1">
-        <v>46.43</v>
+        <v>25</v>
       </c>
       <c r="I86" s="2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -18547,16 +18547,16 @@
         <v>32</v>
       </c>
       <c r="E88">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F88">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G88" s="1">
-        <v>87.5</v>
+        <v>81.25</v>
       </c>
       <c r="H88" s="1">
-        <v>12.5</v>
+        <v>18.75</v>
       </c>
       <c r="I88" s="2">
         <v>7.5</v>
@@ -18585,22 +18585,22 @@
         <v>20</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" s="1">
         <v>83.33</v>
       </c>
       <c r="H89" s="1">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="I89" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -18620,22 +18620,22 @@
         <v>21</v>
       </c>
       <c r="F90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="1">
         <v>87.5</v>
       </c>
       <c r="H90" s="1">
-        <v>8.33</v>
+        <v>12.5</v>
       </c>
       <c r="I90" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -18699,7 +18699,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -18734,7 +18734,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J93">
         <v>3</v>
@@ -18792,25 +18792,25 @@
         <v>33</v>
       </c>
       <c r="E95">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F95">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -19142,19 +19142,19 @@
         <v>32</v>
       </c>
       <c r="E105">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F105">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G105" s="1">
-        <v>15.63</v>
+        <v>100</v>
       </c>
       <c r="H105" s="1">
-        <v>84.38</v>
+        <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -19177,19 +19177,19 @@
         <v>24</v>
       </c>
       <c r="E106">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F106">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -19212,19 +19212,19 @@
         <v>32</v>
       </c>
       <c r="E107">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F107">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>28.13</v>
+        <v>100</v>
       </c>
       <c r="H107" s="1">
-        <v>71.88</v>
+        <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -19247,19 +19247,19 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F108">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G108" s="1">
-        <v>57.89</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>42.11</v>
+        <v>5.26</v>
       </c>
       <c r="I108" s="2">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -19282,19 +19282,19 @@
         <v>32</v>
       </c>
       <c r="E109">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F109">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G109" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H109" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I109" s="2">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J111">
         <v>9</v>
@@ -19387,25 +19387,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="H112" s="1">
         <v>2.44</v>
       </c>
       <c r="I112" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J112">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K112" s="1">
-        <v>41.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -19422,19 +19422,19 @@
         <v>37</v>
       </c>
       <c r="E113">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G113" s="1">
-        <v>86.48999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="H113" s="1">
-        <v>13.51</v>
+        <v>5.41</v>
       </c>
       <c r="I113" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -19457,19 +19457,19 @@
         <v>41</v>
       </c>
       <c r="E114">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F114">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G114" s="1">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H114" s="1">
-        <v>26.83</v>
+        <v>19.51</v>
       </c>
       <c r="I114" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -19492,19 +19492,19 @@
         <v>36</v>
       </c>
       <c r="E115">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G115" s="1">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H115" s="1">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="I115" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -19819,7 +19819,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -19842,19 +19842,19 @@
         <v>32</v>
       </c>
       <c r="E125">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F125">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H125" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -19877,16 +19877,16 @@
         <v>31</v>
       </c>
       <c r="E126">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F126">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G126" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H126" s="1">
-        <v>29.03</v>
+        <v>22.58</v>
       </c>
       <c r="I126" s="2">
         <v>6.6</v>
@@ -19912,19 +19912,19 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G127" s="1">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H127" s="1">
-        <v>6.9</v>
+        <v>10.34</v>
       </c>
       <c r="I127" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -19947,19 +19947,19 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G128" s="1">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H128" s="1">
-        <v>8.82</v>
+        <v>2.94</v>
       </c>
       <c r="I128" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -19994,7 +19994,7 @@
         <v>5.26</v>
       </c>
       <c r="I129" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -20017,19 +20017,19 @@
         <v>38</v>
       </c>
       <c r="E130">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F130">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G130" s="1">
-        <v>71.05</v>
+        <v>92.11</v>
       </c>
       <c r="H130" s="1">
-        <v>28.95</v>
+        <v>7.89</v>
       </c>
       <c r="I130" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -20052,19 +20052,19 @@
         <v>34</v>
       </c>
       <c r="E131">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H131" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I131" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -20087,16 +20087,16 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G132" s="1">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H132" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="I132" s="2">
         <v>7.5</v>
@@ -20122,19 +20122,19 @@
         <v>22</v>
       </c>
       <c r="E133">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F133">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G133" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H133" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I133" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -20157,19 +20157,19 @@
         <v>31</v>
       </c>
       <c r="E134">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F134">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G134" s="1">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H134" s="1">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="I134" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -20192,19 +20192,19 @@
         <v>33</v>
       </c>
       <c r="E135">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135" s="1">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H135" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="I135" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -20227,19 +20227,19 @@
         <v>24</v>
       </c>
       <c r="E136">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F136">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G136" s="1">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H136" s="1">
-        <v>25</v>
+        <v>8.33</v>
       </c>
       <c r="I136" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -20262,19 +20262,19 @@
         <v>33</v>
       </c>
       <c r="E137">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F137">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G137" s="1">
-        <v>69.7</v>
+        <v>87.88</v>
       </c>
       <c r="H137" s="1">
-        <v>30.3</v>
+        <v>12.12</v>
       </c>
       <c r="I137" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -20297,19 +20297,19 @@
         <v>38</v>
       </c>
       <c r="E138">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F138">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G138" s="1">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H138" s="1">
-        <v>34.21</v>
+        <v>13.16</v>
       </c>
       <c r="I138" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -20332,25 +20332,25 @@
         <v>24</v>
       </c>
       <c r="E139">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F139">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G139" s="1">
-        <v>75</v>
+        <v>95.83</v>
       </c>
       <c r="H139" s="1">
-        <v>20.83</v>
+        <v>4.17</v>
       </c>
       <c r="I139" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -20367,19 +20367,19 @@
         <v>31</v>
       </c>
       <c r="E140">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F140">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G140" s="1">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H140" s="1">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -20402,16 +20402,16 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F141">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G141" s="1">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H141" s="1">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
       <c r="I141" s="2">
         <v>6.3</v>
@@ -20437,19 +20437,19 @@
         <v>36</v>
       </c>
       <c r="E142">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" s="1">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H142" s="1">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="I142" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -20472,16 +20472,16 @@
         <v>36</v>
       </c>
       <c r="E143">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" s="1">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H143" s="1">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="I143" s="2">
         <v>7.8</v>
@@ -20507,19 +20507,19 @@
         <v>28</v>
       </c>
       <c r="E144">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G144" s="1">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H144" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I144" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -20554,7 +20554,7 @@
         <v>7.14</v>
       </c>
       <c r="I145" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -20589,7 +20589,7 @@
         <v>14.63</v>
       </c>
       <c r="I146" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -20624,7 +20624,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -20659,7 +20659,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -20822,19 +20822,19 @@
         <v>32</v>
       </c>
       <c r="E153">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F153">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G153" s="1">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="H153" s="1">
-        <v>15.63</v>
+        <v>3.13</v>
       </c>
       <c r="I153" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -20857,19 +20857,19 @@
         <v>33</v>
       </c>
       <c r="E154">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G154" s="1">
-        <v>75.76000000000001</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>24.24</v>
+        <v>21.21</v>
       </c>
       <c r="I154" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -20904,7 +20904,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -20939,7 +20939,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -21662,19 +21662,19 @@
         <v>20</v>
       </c>
       <c r="E177">
+        <v>16</v>
+      </c>
+      <c r="F177">
+        <v>4</v>
+      </c>
+      <c r="G177" s="1">
+        <v>80</v>
+      </c>
+      <c r="H177" s="1">
         <v>20</v>
       </c>
-      <c r="F177">
-        <v>0</v>
-      </c>
-      <c r="G177" s="1">
-        <v>100</v>
-      </c>
-      <c r="H177" s="1">
-        <v>0</v>
-      </c>
       <c r="I177" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J177">
         <v>0</v>
@@ -21697,19 +21697,19 @@
         <v>20</v>
       </c>
       <c r="E178">
+        <v>16</v>
+      </c>
+      <c r="F178">
+        <v>4</v>
+      </c>
+      <c r="G178" s="1">
+        <v>80</v>
+      </c>
+      <c r="H178" s="1">
         <v>20</v>
       </c>
-      <c r="F178">
-        <v>0</v>
-      </c>
-      <c r="G178" s="1">
-        <v>100</v>
-      </c>
-      <c r="H178" s="1">
-        <v>0</v>
-      </c>
       <c r="I178" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -21732,19 +21732,19 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G179" s="1">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="H179" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I179" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -22012,19 +22012,19 @@
         <v>20</v>
       </c>
       <c r="E187">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F187">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G187" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H187" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I187" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -22082,19 +22082,19 @@
         <v>34</v>
       </c>
       <c r="E189">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G189" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H189" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I189" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -22117,16 +22117,16 @@
         <v>24</v>
       </c>
       <c r="E190">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G190" s="1">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H190" s="1">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
       <c r="I190" s="2">
         <v>7.7</v>
@@ -22152,19 +22152,19 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F191">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>67.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H191" s="1">
-        <v>32.26</v>
+        <v>0</v>
       </c>
       <c r="I191" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -22187,13 +22187,13 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F192">
         <v>4</v>
       </c>
       <c r="G192" s="1">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H192" s="1">
         <v>14.29</v>
@@ -22202,10 +22202,10 @@
         <v>6.2</v>
       </c>
       <c r="J192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -22222,13 +22222,13 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F193">
         <v>3</v>
       </c>
       <c r="G193" s="1">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H193" s="1">
         <v>10.71</v>
@@ -22237,10 +22237,10 @@
         <v>6.7</v>
       </c>
       <c r="J193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K193" s="1">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -22327,19 +22327,19 @@
         <v>32</v>
       </c>
       <c r="E196">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F196">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G196" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H196" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I196" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -22362,19 +22362,19 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F197">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G197" s="1">
-        <v>63.89</v>
+        <v>86.11</v>
       </c>
       <c r="H197" s="1">
-        <v>36.11</v>
+        <v>13.89</v>
       </c>
       <c r="I197" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -22397,16 +22397,16 @@
         <v>31</v>
       </c>
       <c r="E198">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F198">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G198" s="1">
-        <v>67.73999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H198" s="1">
-        <v>32.26</v>
+        <v>12.9</v>
       </c>
       <c r="I198" s="2">
         <v>6.6</v>
@@ -22432,19 +22432,19 @@
         <v>36</v>
       </c>
       <c r="E199">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" s="1">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H199" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="I199" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -22479,7 +22479,7 @@
         <v>0</v>
       </c>
       <c r="I200" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -22514,7 +22514,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -22549,7 +22549,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -22584,7 +22584,7 @@
         <v>0</v>
       </c>
       <c r="I203" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -22619,7 +22619,7 @@
         <v>0</v>
       </c>
       <c r="I204" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -22654,7 +22654,7 @@
         <v>6.25</v>
       </c>
       <c r="I205" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -22689,7 +22689,7 @@
         <v>5.56</v>
       </c>
       <c r="I206" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -22724,7 +22724,7 @@
         <v>5.56</v>
       </c>
       <c r="I207" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -22747,19 +22747,19 @@
         <v>33</v>
       </c>
       <c r="E208">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G208" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H208" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I208" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J208">
         <v>0</v>
@@ -22794,7 +22794,7 @@
         <v>20</v>
       </c>
       <c r="I209" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J209">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -911,22 +911,22 @@
         <v>18</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
         <v>90</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -946,22 +946,22 @@
         <v>18</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
         <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -978,25 +978,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8243,22 +8243,22 @@
         <v>18</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
         <v>90</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8278,22 +8278,22 @@
         <v>18</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
         <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8310,25 +8310,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -15549,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -15572,25 +15572,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15610,22 +15610,22 @@
         <v>18</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
         <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15642,25 +15642,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -19049,7 +19049,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -21242,16 +21242,16 @@
         <v>36</v>
       </c>
       <c r="E165">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F165">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G165" s="1">
-        <v>58.33</v>
+        <v>72.22</v>
       </c>
       <c r="H165" s="1">
-        <v>41.67</v>
+        <v>27.78</v>
       </c>
       <c r="I165" s="2">
         <v>5.9</v>
@@ -21429,7 +21429,7 @@
         <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -21464,7 +21464,7 @@
         <v>0</v>
       </c>
       <c r="I171" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -21557,19 +21557,19 @@
         <v>31</v>
       </c>
       <c r="E174">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F174">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G174" s="1">
-        <v>61.29</v>
+        <v>74.19</v>
       </c>
       <c r="H174" s="1">
-        <v>38.71</v>
+        <v>25.81</v>
       </c>
       <c r="I174" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -22047,19 +22047,19 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F188">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G188" s="1">
-        <v>78.95</v>
+        <v>86.84</v>
       </c>
       <c r="H188" s="1">
-        <v>21.05</v>
+        <v>13.16</v>
       </c>
       <c r="I188" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J188">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1471,22 +1471,22 @@
         <v>30</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1">
         <v>73.17</v>
       </c>
       <c r="H19" s="1">
-        <v>14.63</v>
+        <v>26.83</v>
       </c>
       <c r="I19" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1993,25 +1993,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1">
-        <v>36.84</v>
+        <v>42.11</v>
       </c>
       <c r="H34" s="1">
-        <v>47.37</v>
+        <v>57.89</v>
       </c>
       <c r="I34" s="2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2031,22 +2031,22 @@
         <v>24</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
         <v>77.42</v>
       </c>
       <c r="H35" s="1">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="I35" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2066,22 +2066,22 @@
         <v>20</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1">
         <v>62.5</v>
       </c>
       <c r="H36" s="1">
-        <v>31.25</v>
+        <v>37.5</v>
       </c>
       <c r="I36" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2101,22 +2101,22 @@
         <v>22</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1">
         <v>68.75</v>
       </c>
       <c r="H37" s="1">
-        <v>28.13</v>
+        <v>31.25</v>
       </c>
       <c r="I37" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2136,22 +2136,22 @@
         <v>24</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G38" s="1">
         <v>72.73</v>
       </c>
       <c r="H38" s="1">
-        <v>18.18</v>
+        <v>27.27</v>
       </c>
       <c r="I38" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2626,22 +2626,22 @@
         <v>32</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" s="1">
         <v>88.89</v>
       </c>
       <c r="H52" s="1">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="I52" s="2">
         <v>7.7</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2693,25 +2693,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G54" s="1">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>22.58</v>
       </c>
       <c r="I54" s="2">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="J54">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4058,25 +4058,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="1">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H93" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="I93" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -4093,25 +4093,25 @@
         <v>22</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F94">
         <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -4166,22 +4166,22 @@
         <v>17</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="1">
         <v>89.47</v>
       </c>
       <c r="H96" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I96" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4198,25 +4198,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="H97" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I97" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J97">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -4268,25 +4268,25 @@
         <v>31</v>
       </c>
       <c r="E99">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G99" s="1">
-        <v>83.87</v>
+        <v>93.55</v>
       </c>
       <c r="H99" s="1">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="I99" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4303,25 +4303,25 @@
         <v>30</v>
       </c>
       <c r="E100">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G100" s="1">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H100" s="1">
-        <v>3.33</v>
+        <v>10</v>
       </c>
       <c r="I100" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4338,25 +4338,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="1">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H101" s="1">
-        <v>2.86</v>
+        <v>5.71</v>
       </c>
       <c r="I101" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4653,25 +4653,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G110" s="1">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H110" s="1">
-        <v>8.33</v>
+        <v>36.11</v>
       </c>
       <c r="I110" s="2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J110">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4688,25 +4688,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G111" s="1">
-        <v>75.68000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="H111" s="1">
-        <v>0</v>
+        <v>16.22</v>
       </c>
       <c r="I111" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J111">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>24.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4723,25 +4723,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G112" s="1">
-        <v>60.98</v>
+        <v>73.17</v>
       </c>
       <c r="H112" s="1">
-        <v>2.44</v>
+        <v>26.83</v>
       </c>
       <c r="I112" s="2">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="J112">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -5073,13 +5073,13 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F122">
         <v>2</v>
       </c>
       <c r="G122" s="1">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H122" s="1">
         <v>5.41</v>
@@ -5088,10 +5088,10 @@
         <v>8.4</v>
       </c>
       <c r="J122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -6056,22 +6056,22 @@
         <v>7</v>
       </c>
       <c r="F150">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G150" s="1">
         <v>35</v>
       </c>
       <c r="H150" s="1">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I150" s="2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6088,13 +6088,13 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F151">
         <v>5</v>
       </c>
       <c r="G151" s="1">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H151" s="1">
         <v>26.32</v>
@@ -6103,10 +6103,10 @@
         <v>6.4</v>
       </c>
       <c r="J151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6476,22 +6476,22 @@
         <v>16</v>
       </c>
       <c r="F162">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G162" s="1">
         <v>66.67</v>
       </c>
       <c r="H162" s="1">
-        <v>29.17</v>
+        <v>33.33</v>
       </c>
       <c r="I162" s="2">
         <v>6.3</v>
       </c>
       <c r="J162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -7208,13 +7208,13 @@
         <v>36</v>
       </c>
       <c r="E183">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -7223,10 +7223,10 @@
         <v>9</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7278,25 +7278,25 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G185" s="1">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H185" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I185" s="2">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J185">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7313,25 +7313,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H186" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I186" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J186">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7561,22 +7561,22 @@
         <v>26</v>
       </c>
       <c r="F193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G193" s="1">
         <v>92.86</v>
       </c>
       <c r="H193" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I193" s="2">
         <v>7</v>
       </c>
       <c r="J193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -7593,25 +7593,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G194" s="1">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H194" s="1">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I194" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J194">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -8803,22 +8803,22 @@
         <v>33</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1">
         <v>80.48999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>7.32</v>
+        <v>19.51</v>
       </c>
       <c r="I19" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -9325,25 +9325,25 @@
         <v>19</v>
       </c>
       <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
         <v>9</v>
       </c>
-      <c r="F34">
-        <v>7</v>
-      </c>
       <c r="G34" s="1">
+        <v>52.63</v>
+      </c>
+      <c r="H34" s="1">
         <v>47.37</v>
       </c>
-      <c r="H34" s="1">
-        <v>36.84</v>
-      </c>
       <c r="I34" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -9363,22 +9363,22 @@
         <v>22</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" s="1">
         <v>70.97</v>
       </c>
       <c r="H35" s="1">
-        <v>25.81</v>
+        <v>29.03</v>
       </c>
       <c r="I35" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -9395,25 +9395,25 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H36" s="1">
-        <v>34.38</v>
+        <v>37.5</v>
       </c>
       <c r="I36" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -9433,22 +9433,22 @@
         <v>21</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="1">
         <v>65.63</v>
       </c>
       <c r="H37" s="1">
-        <v>31.25</v>
+        <v>34.38</v>
       </c>
       <c r="I37" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -9468,22 +9468,22 @@
         <v>24</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G38" s="1">
         <v>72.73</v>
       </c>
       <c r="H38" s="1">
-        <v>18.18</v>
+        <v>27.27</v>
       </c>
       <c r="I38" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -9535,19 +9535,19 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G40" s="1">
-        <v>29.17</v>
+        <v>41.67</v>
       </c>
       <c r="H40" s="1">
-        <v>70.83</v>
+        <v>58.33</v>
       </c>
       <c r="I40" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -9640,19 +9640,19 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G43" s="1">
-        <v>53.13</v>
+        <v>59.38</v>
       </c>
       <c r="H43" s="1">
-        <v>46.88</v>
+        <v>40.63</v>
       </c>
       <c r="I43" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -9687,7 +9687,7 @@
         <v>53.13</v>
       </c>
       <c r="I44" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -9885,19 +9885,19 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F50">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>72.5</v>
+        <v>100</v>
       </c>
       <c r="H50" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -9920,19 +9920,19 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G51" s="1">
-        <v>76.67</v>
+        <v>90</v>
       </c>
       <c r="H51" s="1">
-        <v>23.33</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -9958,22 +9958,22 @@
         <v>32</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" s="1">
         <v>88.89</v>
       </c>
       <c r="H52" s="1">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="I52" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -9990,19 +9990,19 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G53" s="1">
-        <v>78.79000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H53" s="1">
-        <v>21.21</v>
+        <v>18.18</v>
       </c>
       <c r="I53" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -10025,25 +10025,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F54">
         <v>7</v>
       </c>
       <c r="G54" s="1">
-        <v>41.94</v>
+        <v>77.42</v>
       </c>
       <c r="H54" s="1">
         <v>22.58</v>
       </c>
       <c r="I54" s="2">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J54">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -10737,7 +10737,7 @@
         <v>12.5</v>
       </c>
       <c r="I74" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -11250,19 +11250,19 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G89" s="1">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="H89" s="1">
-        <v>25</v>
+        <v>20.83</v>
       </c>
       <c r="I89" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -11285,19 +11285,19 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G90" s="1">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H90" s="1">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
       <c r="I90" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -11390,25 +11390,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="1">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H93" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="I93" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -11425,25 +11425,25 @@
         <v>22</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F94">
         <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -11498,22 +11498,22 @@
         <v>17</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="1">
         <v>89.47</v>
       </c>
       <c r="H96" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I96" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -11530,25 +11530,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G97" s="1">
-        <v>78.13</v>
+        <v>93.75</v>
       </c>
       <c r="H97" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I97" s="2">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="J97">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -11565,19 +11565,19 @@
         <v>33</v>
       </c>
       <c r="E98">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F98">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>75.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="H98" s="1">
-        <v>24.24</v>
+        <v>6.06</v>
       </c>
       <c r="I98" s="2">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -11600,25 +11600,25 @@
         <v>31</v>
       </c>
       <c r="E99">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F99">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G99" s="1">
-        <v>29.03</v>
+        <v>77.42</v>
       </c>
       <c r="H99" s="1">
-        <v>54.84</v>
+        <v>22.58</v>
       </c>
       <c r="I99" s="2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -11635,25 +11635,25 @@
         <v>30</v>
       </c>
       <c r="E100">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F100">
         <v>3</v>
       </c>
       <c r="G100" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H100" s="1">
         <v>10</v>
       </c>
       <c r="I100" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -11670,25 +11670,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G101" s="1">
-        <v>80</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H101" s="1">
-        <v>11.43</v>
+        <v>5.71</v>
       </c>
       <c r="I101" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -11740,19 +11740,19 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F103">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G103" s="1">
-        <v>59.09</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H103" s="1">
-        <v>40.91</v>
+        <v>18.18</v>
       </c>
       <c r="I103" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -11775,19 +11775,19 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F104">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G104" s="1">
-        <v>45.45</v>
+        <v>69.7</v>
       </c>
       <c r="H104" s="1">
-        <v>54.55</v>
+        <v>30.3</v>
       </c>
       <c r="I104" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -11985,25 +11985,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G110" s="1">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H110" s="1">
-        <v>8.33</v>
+        <v>36.11</v>
       </c>
       <c r="I110" s="2">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="J110">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -12020,25 +12020,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F111">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G111" s="1">
-        <v>67.56999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="H111" s="1">
-        <v>8.109999999999999</v>
+        <v>16.22</v>
       </c>
       <c r="I111" s="2">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="J111">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>24.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -12055,25 +12055,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F112">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G112" s="1">
-        <v>56.1</v>
+        <v>73.17</v>
       </c>
       <c r="H112" s="1">
-        <v>7.32</v>
+        <v>26.83</v>
       </c>
       <c r="I112" s="2">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="J112">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -12335,16 +12335,16 @@
         <v>44</v>
       </c>
       <c r="E120">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="I120" s="2">
         <v>8.699999999999999</v>
@@ -12370,19 +12370,19 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121" s="1">
-        <v>88.89</v>
+        <v>96.3</v>
       </c>
       <c r="H121" s="1">
-        <v>11.11</v>
+        <v>3.7</v>
       </c>
       <c r="I121" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -12405,25 +12405,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>86.48999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H122" s="1">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
       <c r="I122" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -12440,16 +12440,16 @@
         <v>44</v>
       </c>
       <c r="E123">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F123">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G123" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H123" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="I123" s="2">
         <v>8</v>
@@ -13350,19 +13350,19 @@
         <v>29</v>
       </c>
       <c r="E149">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F149">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G149" s="1">
-        <v>79.31</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H149" s="1">
-        <v>20.69</v>
+        <v>13.79</v>
       </c>
       <c r="I149" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -13388,22 +13388,22 @@
         <v>7</v>
       </c>
       <c r="F150">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G150" s="1">
         <v>35</v>
       </c>
       <c r="H150" s="1">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I150" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -13420,13 +13420,13 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F151">
         <v>6</v>
       </c>
       <c r="G151" s="1">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H151" s="1">
         <v>31.58</v>
@@ -13435,10 +13435,10 @@
         <v>7</v>
       </c>
       <c r="J151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -13455,16 +13455,16 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F152">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G152" s="1">
-        <v>66.67</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H152" s="1">
-        <v>33.33</v>
+        <v>15.15</v>
       </c>
       <c r="I152" s="2">
         <v>7.1</v>
@@ -13630,19 +13630,19 @@
         <v>40</v>
       </c>
       <c r="E157">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F157">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G157" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H157" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -13665,19 +13665,19 @@
         <v>30</v>
       </c>
       <c r="E158">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G158" s="1">
-        <v>90</v>
+        <v>96.67</v>
       </c>
       <c r="H158" s="1">
-        <v>10</v>
+        <v>3.33</v>
       </c>
       <c r="I158" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -13712,7 +13712,7 @@
         <v>6.25</v>
       </c>
       <c r="I159" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -13747,7 +13747,7 @@
         <v>7.41</v>
       </c>
       <c r="I160" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -13782,7 +13782,7 @@
         <v>5.26</v>
       </c>
       <c r="I161" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -13808,22 +13808,22 @@
         <v>18</v>
       </c>
       <c r="F162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G162" s="1">
         <v>75</v>
       </c>
       <c r="H162" s="1">
-        <v>20.83</v>
+        <v>25</v>
       </c>
       <c r="I162" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -13840,19 +13840,19 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F163">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G163" s="1">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H163" s="1">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
       <c r="I163" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>25</v>
       </c>
       <c r="I173" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -14540,25 +14540,25 @@
         <v>36</v>
       </c>
       <c r="E183">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
       <c r="I183" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -14575,19 +14575,19 @@
         <v>36</v>
       </c>
       <c r="E184">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H184" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I184" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -14610,25 +14610,25 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F185">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G185" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H185" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I185" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J185">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -14645,25 +14645,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G186" s="1">
-        <v>68.42</v>
+        <v>89.47</v>
       </c>
       <c r="H186" s="1">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="I186" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J186">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -14893,22 +14893,22 @@
         <v>24</v>
       </c>
       <c r="F193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G193" s="1">
         <v>85.70999999999999</v>
       </c>
       <c r="H193" s="1">
-        <v>10.71</v>
+        <v>14.29</v>
       </c>
       <c r="I193" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -14925,25 +14925,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F194">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G194" s="1">
-        <v>41.46</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H194" s="1">
-        <v>41.46</v>
+        <v>19.51</v>
       </c>
       <c r="I194" s="2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J194">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -14960,16 +14960,16 @@
         <v>17</v>
       </c>
       <c r="E195">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F195">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G195" s="1">
-        <v>64.70999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="H195" s="1">
-        <v>35.29</v>
+        <v>29.41</v>
       </c>
       <c r="I195" s="2">
         <v>5.9</v>
@@ -16132,25 +16132,25 @@
         <v>41</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>80.48999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H19" s="1">
-        <v>7.32</v>
+        <v>12.2</v>
       </c>
       <c r="I19" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -16167,19 +16167,19 @@
         <v>35</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -16202,19 +16202,19 @@
         <v>35</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -16657,25 +16657,25 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="H34" s="1">
-        <v>36.84</v>
+        <v>21.05</v>
       </c>
       <c r="I34" s="2">
         <v>6.1</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -16692,25 +16692,25 @@
         <v>31</v>
       </c>
       <c r="E35">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>70.97</v>
+        <v>93.55</v>
       </c>
       <c r="H35" s="1">
-        <v>25.81</v>
+        <v>6.45</v>
       </c>
       <c r="I35" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -16727,25 +16727,25 @@
         <v>32</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="H36" s="1">
-        <v>31.25</v>
+        <v>12.5</v>
       </c>
       <c r="I36" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -16762,25 +16762,25 @@
         <v>32</v>
       </c>
       <c r="E37">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G37" s="1">
-        <v>65.63</v>
+        <v>90.63</v>
       </c>
       <c r="H37" s="1">
-        <v>31.25</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I37" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -16797,25 +16797,25 @@
         <v>33</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1">
-        <v>72.73</v>
+        <v>87.88</v>
       </c>
       <c r="H38" s="1">
-        <v>18.18</v>
+        <v>12.12</v>
       </c>
       <c r="I38" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -16832,19 +16832,19 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F39">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G39" s="1">
-        <v>52.63</v>
+        <v>89.47</v>
       </c>
       <c r="H39" s="1">
-        <v>47.37</v>
+        <v>10.53</v>
       </c>
       <c r="I39" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -16867,19 +16867,19 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F40">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>41.67</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
-        <v>58.33</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -16902,19 +16902,19 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>51.61</v>
+        <v>100</v>
       </c>
       <c r="H41" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -16937,19 +16937,19 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G42" s="1">
-        <v>52.63</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>47.37</v>
+        <v>15.79</v>
       </c>
       <c r="I42" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -16972,19 +16972,19 @@
         <v>32</v>
       </c>
       <c r="E43">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F43">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G43" s="1">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="H43" s="1">
-        <v>40.63</v>
+        <v>12.5</v>
       </c>
       <c r="I43" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -17007,19 +17007,19 @@
         <v>32</v>
       </c>
       <c r="E44">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F44">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1">
-        <v>53.13</v>
+        <v>90.63</v>
       </c>
       <c r="H44" s="1">
-        <v>46.88</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I44" s="2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -17217,19 +17217,19 @@
         <v>40</v>
       </c>
       <c r="E50">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H50" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -17252,19 +17252,19 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" s="1">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="H51" s="1">
-        <v>13.33</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -17290,22 +17290,22 @@
         <v>32</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" s="1">
         <v>88.89</v>
       </c>
       <c r="H52" s="1">
-        <v>8.33</v>
+        <v>11.11</v>
       </c>
       <c r="I52" s="2">
         <v>7.7</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -17322,19 +17322,19 @@
         <v>33</v>
       </c>
       <c r="E53">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53" s="1">
-        <v>90.91</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H53" s="1">
-        <v>9.09</v>
+        <v>15.15</v>
       </c>
       <c r="I53" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -17357,25 +17357,25 @@
         <v>31</v>
       </c>
       <c r="E54">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G54" s="1">
-        <v>64.52</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="I54" s="2">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J54">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -18104,7 +18104,7 @@
         <v>16.67</v>
       </c>
       <c r="I75" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -18582,19 +18582,19 @@
         <v>24</v>
       </c>
       <c r="E89">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F89">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G89" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H89" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="I89" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -18617,19 +18617,19 @@
         <v>24</v>
       </c>
       <c r="E90">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="1">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H90" s="1">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="I90" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -18652,19 +18652,19 @@
         <v>24</v>
       </c>
       <c r="E91">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F91">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H91" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I91" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -18699,7 +18699,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -18722,25 +18722,25 @@
         <v>33</v>
       </c>
       <c r="E93">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="1">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H93" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="I93" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -18757,25 +18757,25 @@
         <v>22</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F94">
         <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -18804,7 +18804,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -18830,22 +18830,22 @@
         <v>17</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="1">
         <v>89.47</v>
       </c>
       <c r="H96" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I96" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -18862,25 +18862,25 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H97" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I97" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J97">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -18909,7 +18909,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -18932,25 +18932,25 @@
         <v>31</v>
       </c>
       <c r="E99">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G99" s="1">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H99" s="1">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I99" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -18970,22 +18970,22 @@
         <v>27</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G100" s="1">
         <v>90</v>
       </c>
       <c r="H100" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I100" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -19002,25 +19002,25 @@
         <v>35</v>
       </c>
       <c r="E101">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="1">
-        <v>91.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H101" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I101" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -19072,19 +19072,19 @@
         <v>22</v>
       </c>
       <c r="E103">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H103" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -19107,19 +19107,19 @@
         <v>33</v>
       </c>
       <c r="E104">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F104">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G104" s="1">
-        <v>66.67</v>
+        <v>90.91</v>
       </c>
       <c r="H104" s="1">
-        <v>33.33</v>
+        <v>9.09</v>
       </c>
       <c r="I104" s="2">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -19189,7 +19189,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -19224,7 +19224,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -19247,19 +19247,19 @@
         <v>19</v>
       </c>
       <c r="E108">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H108" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I108" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -19294,7 +19294,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -19317,25 +19317,25 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G110" s="1">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H110" s="1">
-        <v>8.33</v>
+        <v>36.11</v>
       </c>
       <c r="I110" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J110">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -19352,25 +19352,25 @@
         <v>37</v>
       </c>
       <c r="E111">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G111" s="1">
-        <v>75.68000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="H111" s="1">
-        <v>0</v>
+        <v>18.92</v>
       </c>
       <c r="I111" s="2">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J111">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>24.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -19387,25 +19387,25 @@
         <v>41</v>
       </c>
       <c r="E112">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G112" s="1">
-        <v>60.98</v>
+        <v>70.73</v>
       </c>
       <c r="H112" s="1">
-        <v>2.44</v>
+        <v>29.27</v>
       </c>
       <c r="I112" s="2">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="J112">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -19527,19 +19527,19 @@
         <v>22</v>
       </c>
       <c r="E116">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H116" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I116" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -19562,19 +19562,19 @@
         <v>22</v>
       </c>
       <c r="E117">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H117" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I117" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -19597,19 +19597,19 @@
         <v>33</v>
       </c>
       <c r="E118">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F118">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G118" s="1">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H118" s="1">
-        <v>18.18</v>
+        <v>9.09</v>
       </c>
       <c r="I118" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -19632,19 +19632,19 @@
         <v>33</v>
       </c>
       <c r="E119">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F119">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G119" s="1">
-        <v>78.79000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H119" s="1">
-        <v>21.21</v>
+        <v>9.09</v>
       </c>
       <c r="I119" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -19702,19 +19702,19 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H121" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I121" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -19737,25 +19737,25 @@
         <v>37</v>
       </c>
       <c r="E122">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F122">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H122" s="1">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
       <c r="I122" s="2">
         <v>8.4</v>
       </c>
       <c r="J122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -20682,16 +20682,16 @@
         <v>29</v>
       </c>
       <c r="E149">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F149">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G149" s="1">
-        <v>86.20999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H149" s="1">
-        <v>13.79</v>
+        <v>17.24</v>
       </c>
       <c r="I149" s="2">
         <v>6.8</v>
@@ -20717,25 +20717,25 @@
         <v>20</v>
       </c>
       <c r="E150">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F150">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G150" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H150" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I150" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -20752,25 +20752,25 @@
         <v>19</v>
       </c>
       <c r="E151">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F151">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G151" s="1">
-        <v>57.89</v>
+        <v>78.95</v>
       </c>
       <c r="H151" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I151" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -20787,19 +20787,19 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F152">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G152" s="1">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H152" s="1">
-        <v>30.3</v>
+        <v>18.18</v>
       </c>
       <c r="I152" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J152">
         <v>0</v>
@@ -20974,7 +20974,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -21009,7 +21009,7 @@
         <v>3.33</v>
       </c>
       <c r="I158" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -21044,7 +21044,7 @@
         <v>6.25</v>
       </c>
       <c r="I159" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -21067,16 +21067,16 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G160" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H160" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I160" s="2">
         <v>7.3</v>
@@ -21102,19 +21102,19 @@
         <v>19</v>
       </c>
       <c r="E161">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H161" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I161" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -21137,25 +21137,25 @@
         <v>24</v>
       </c>
       <c r="E162">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F162">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G162" s="1">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H162" s="1">
-        <v>20.83</v>
+        <v>8.33</v>
       </c>
       <c r="I162" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -21172,19 +21172,19 @@
         <v>24</v>
       </c>
       <c r="E163">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F163">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G163" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H163" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -21207,19 +21207,19 @@
         <v>32</v>
       </c>
       <c r="E164">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F164">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G164" s="1">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="H164" s="1">
-        <v>34.38</v>
+        <v>28.13</v>
       </c>
       <c r="I164" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -21277,16 +21277,16 @@
         <v>33</v>
       </c>
       <c r="E166">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F166">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G166" s="1">
-        <v>63.64</v>
+        <v>72.73</v>
       </c>
       <c r="H166" s="1">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="I166" s="2">
         <v>5.8</v>
@@ -21324,7 +21324,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -21359,7 +21359,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>0</v>
       </c>
       <c r="I169" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -21499,7 +21499,7 @@
         <v>0</v>
       </c>
       <c r="I172" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -21522,19 +21522,19 @@
         <v>36</v>
       </c>
       <c r="E173">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F173">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G173" s="1">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="H173" s="1">
-        <v>22.22</v>
+        <v>8.33</v>
       </c>
       <c r="I173" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -21592,19 +21592,19 @@
         <v>19</v>
       </c>
       <c r="E175">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F175">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G175" s="1">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H175" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I175" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -21627,19 +21627,19 @@
         <v>19</v>
       </c>
       <c r="E176">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F176">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G176" s="1">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H176" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I176" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -21779,7 +21779,7 @@
         <v>0</v>
       </c>
       <c r="I180" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -21814,7 +21814,7 @@
         <v>0</v>
       </c>
       <c r="I181" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -21837,19 +21837,19 @@
         <v>33</v>
       </c>
       <c r="E182">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G182" s="1">
-        <v>96.97</v>
+        <v>90.91</v>
       </c>
       <c r="H182" s="1">
-        <v>3.03</v>
+        <v>9.09</v>
       </c>
       <c r="I182" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -21872,25 +21872,25 @@
         <v>36</v>
       </c>
       <c r="E183">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
       <c r="I183" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -21919,7 +21919,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -21942,25 +21942,25 @@
         <v>20</v>
       </c>
       <c r="E185">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F185">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G185" s="1">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H185" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I185" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J185">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -21977,25 +21977,25 @@
         <v>19</v>
       </c>
       <c r="E186">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H186" s="1">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="I186" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J186">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -22047,16 +22047,16 @@
         <v>38</v>
       </c>
       <c r="E188">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F188">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G188" s="1">
-        <v>86.84</v>
+        <v>92.11</v>
       </c>
       <c r="H188" s="1">
-        <v>13.16</v>
+        <v>7.89</v>
       </c>
       <c r="I188" s="2">
         <v>8.1</v>
@@ -22187,19 +22187,19 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F192">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G192" s="1">
-        <v>85.70999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H192" s="1">
-        <v>14.29</v>
+        <v>3.57</v>
       </c>
       <c r="I192" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -22222,25 +22222,25 @@
         <v>28</v>
       </c>
       <c r="E193">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G193" s="1">
-        <v>85.70999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H193" s="1">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
       <c r="I193" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -22257,25 +22257,25 @@
         <v>41</v>
       </c>
       <c r="E194">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G194" s="1">
-        <v>82.93000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H194" s="1">
-        <v>0</v>
+        <v>19.51</v>
       </c>
       <c r="I194" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J194">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -22292,19 +22292,19 @@
         <v>17</v>
       </c>
       <c r="E195">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F195">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G195" s="1">
-        <v>70.59</v>
+        <v>100</v>
       </c>
       <c r="H195" s="1">
-        <v>29.41</v>
+        <v>0</v>
       </c>
       <c r="I195" s="2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J195">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -4421,25 +4421,25 @@
         <v>40</v>
       </c>
       <c r="E105">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F105">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G105" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H105" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I105" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J105">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K105" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7428,25 +7428,25 @@
         <v>26</v>
       </c>
       <c r="E191">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
       </c>
       <c r="I191" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J191">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K191" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -11199,19 +11199,19 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G105" s="1">
         <v>0</v>
       </c>
       <c r="H105" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J105">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K105" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -13951,19 +13951,19 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G191" s="1">
         <v>0</v>
       </c>
       <c r="H191" s="1">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="J191">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K191" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -17971,25 +17971,25 @@
         <v>40</v>
       </c>
       <c r="E105">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F105">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G105" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H105" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I105" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J105">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K105" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -20978,25 +20978,25 @@
         <v>26</v>
       </c>
       <c r="E191">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F191">
         <v>0</v>
       </c>
       <c r="G191" s="1">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
       </c>
       <c r="I191" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J191">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K191" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="192" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1712,22 +1712,22 @@
         <v>21</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
         <v>61.76</v>
       </c>
       <c r="H27" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3182,22 +3182,22 @@
         <v>24</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69" s="1">
         <v>70.59</v>
       </c>
       <c r="H69" s="1">
-        <v>29.41</v>
+        <v>26.47</v>
       </c>
       <c r="I69" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3214,22 +3214,25 @@
         <v>33</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
       </c>
+      <c r="I70" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J70">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3246,22 +3249,25 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
       </c>
+      <c r="I71" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J71">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3278,22 +3284,25 @@
         <v>32</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>3.13</v>
+      </c>
+      <c r="I72" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J72">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3310,22 +3319,25 @@
         <v>26</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
       </c>
+      <c r="I73" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J73">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3342,22 +3354,25 @@
         <v>33</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
       </c>
+      <c r="I74" s="2">
+        <v>9</v>
+      </c>
       <c r="J74">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4456,22 +4471,25 @@
         <v>18</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
       </c>
+      <c r="I106" s="2">
+        <v>9</v>
+      </c>
       <c r="J106">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4768,25 +4786,25 @@
         <v>26</v>
       </c>
       <c r="E115">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" s="1">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H115" s="1">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I115" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J115">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -5363,25 +5381,25 @@
         <v>43</v>
       </c>
       <c r="E132">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G132" s="1">
-        <v>34.88</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H132" s="1">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="I132" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J132">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K132" s="1">
-        <v>65.12</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -8703,19 +8721,19 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>67.65000000000001</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="J27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -10047,19 +10065,19 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10079,19 +10097,19 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="J70">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -10111,19 +10129,19 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="J71">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -10143,19 +10161,19 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="J72">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -10175,19 +10193,19 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="J73">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -10207,19 +10225,19 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
       </c>
       <c r="H74" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="J74">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -11231,19 +11249,19 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G106" s="1">
         <v>0</v>
       </c>
       <c r="H106" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="J106">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11519,19 +11537,19 @@
         <v>0</v>
       </c>
       <c r="F115">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G115" s="1">
         <v>0</v>
       </c>
       <c r="H115" s="1">
-        <v>84.62</v>
+        <v>100</v>
       </c>
       <c r="J115">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -12063,19 +12081,19 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G132" s="1">
         <v>0</v>
       </c>
       <c r="H132" s="1">
-        <v>34.88</v>
+        <v>86.05</v>
       </c>
       <c r="J132">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K132" s="1">
-        <v>65.12</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -15262,22 +15280,22 @@
         <v>21</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
         <v>61.76</v>
       </c>
       <c r="H27" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -16732,22 +16750,22 @@
         <v>24</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69" s="1">
         <v>70.59</v>
       </c>
       <c r="H69" s="1">
-        <v>29.41</v>
+        <v>26.47</v>
       </c>
       <c r="I69" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -16764,22 +16782,25 @@
         <v>33</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
       </c>
+      <c r="I70" s="2">
+        <v>7.8</v>
+      </c>
       <c r="J70">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -16796,22 +16817,25 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
       </c>
+      <c r="I71" s="2">
+        <v>8.4</v>
+      </c>
       <c r="J71">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -16828,22 +16852,25 @@
         <v>32</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>3.13</v>
+      </c>
+      <c r="I72" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J72">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -16860,22 +16887,25 @@
         <v>26</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
       </c>
+      <c r="I73" s="2">
+        <v>7.9</v>
+      </c>
       <c r="J73">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -16892,22 +16922,25 @@
         <v>33</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
       </c>
+      <c r="I74" s="2">
+        <v>9</v>
+      </c>
       <c r="J74">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -18006,22 +18039,25 @@
         <v>18</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
       </c>
+      <c r="I106" s="2">
+        <v>9</v>
+      </c>
       <c r="J106">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18318,25 +18354,25 @@
         <v>26</v>
       </c>
       <c r="E115">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" s="1">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H115" s="1">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I115" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J115">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -18913,25 +18949,25 @@
         <v>43</v>
       </c>
       <c r="E132">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G132" s="1">
-        <v>34.88</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H132" s="1">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="I132" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J132">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K132" s="1">
-        <v>65.12</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="133" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -834,25 +834,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>50</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -869,25 +869,25 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -907,22 +907,22 @@
         <v>16</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
         <v>84.20999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -936,10 +936,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1181,19 +1181,19 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>23</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>71.88</v>
+        <v>74.19</v>
       </c>
       <c r="H12" s="1">
-        <v>28.13</v>
+        <v>25.81</v>
       </c>
       <c r="I12" s="2">
         <v>7.6</v>
@@ -1356,19 +1356,19 @@
         <v>105</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17">
         <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>82.34999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H17" s="1">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="I17" s="2">
         <v>6.9</v>
@@ -1499,25 +1499,25 @@
         <v>18</v>
       </c>
       <c r="E21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1607,22 +1607,22 @@
         <v>38</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
         <v>97.44</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I24" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1636,19 +1636,19 @@
         <v>105</v>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I25" s="2">
         <v>8.6</v>
@@ -1674,25 +1674,25 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1">
-        <v>58.97</v>
+        <v>82.05</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>17.95</v>
       </c>
       <c r="I26" s="2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1709,25 +1709,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>61.76</v>
+        <v>97.06</v>
       </c>
       <c r="H27" s="1">
         <v>2.94</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1744,25 +1744,25 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>75.61</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>4.88</v>
+        <v>9.76</v>
       </c>
       <c r="I28" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1776,28 +1776,28 @@
         <v>107</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>78.05</v>
+        <v>90</v>
       </c>
       <c r="H29" s="1">
-        <v>4.88</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1814,25 +1814,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I30" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1846,19 +1846,19 @@
         <v>108</v>
       </c>
       <c r="D31">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="H31" s="1">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="I31" s="2">
         <v>8</v>
@@ -2412,22 +2412,22 @@
         <v>42</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1">
         <v>95.45</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="I47" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2441,16 +2441,16 @@
         <v>113</v>
       </c>
       <c r="D48">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E48">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2549,25 +2549,25 @@
         <v>31</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2587,22 +2587,22 @@
         <v>27</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
         <v>90</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I52" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2619,25 +2619,25 @@
         <v>26</v>
       </c>
       <c r="E53">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1">
-        <v>69.23</v>
+        <v>92.31</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="I53" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J53">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2686,19 +2686,19 @@
         <v>107</v>
       </c>
       <c r="D55">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E55">
         <v>26</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H55" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I55" s="2">
         <v>6.9</v>
@@ -2826,22 +2826,22 @@
         <v>107</v>
       </c>
       <c r="D59">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E59">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59">
         <v>7</v>
       </c>
       <c r="G59" s="1">
-        <v>83.33</v>
+        <v>83.72</v>
       </c>
       <c r="H59" s="1">
-        <v>16.67</v>
+        <v>16.28</v>
       </c>
       <c r="I59" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -2864,25 +2864,25 @@
         <v>39</v>
       </c>
       <c r="E60">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G60" s="1">
-        <v>58.97</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>28.21</v>
       </c>
       <c r="I60" s="2">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="J60">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2899,25 +2899,25 @@
         <v>34</v>
       </c>
       <c r="E61">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="1">
-        <v>85.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I61" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2934,25 +2934,25 @@
         <v>41</v>
       </c>
       <c r="E62">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I62" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J62">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>21.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2966,28 +2966,28 @@
         <v>116</v>
       </c>
       <c r="D63">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E63">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G63" s="1">
-        <v>60.98</v>
+        <v>85</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I63" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J63">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>39.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3007,22 +3007,22 @@
         <v>35</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="1">
         <v>97.22</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I64" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3141,19 +3141,19 @@
         <v>117</v>
       </c>
       <c r="D68">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E68">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F68">
         <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>73.81</v>
+        <v>74.42</v>
       </c>
       <c r="H68" s="1">
-        <v>23.81</v>
+        <v>23.26</v>
       </c>
       <c r="I68" s="2">
         <v>7.2</v>
@@ -3162,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3211,28 +3211,28 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E70">
         <v>29</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="1">
-        <v>87.88</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I70" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J70">
         <v>4</v>
       </c>
       <c r="K70" s="1">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3389,22 +3389,25 @@
         <v>15</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="I75" s="2">
+        <v>6.2</v>
       </c>
       <c r="J75">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3704,22 +3707,22 @@
         <v>26</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G84" s="1">
         <v>76.47</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="I84" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J84">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3733,28 +3736,28 @@
         <v>121</v>
       </c>
       <c r="D85">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E85">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" s="1">
-        <v>83.87</v>
+        <v>90</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I85" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J85">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3771,25 +3774,25 @@
         <v>40</v>
       </c>
       <c r="E86">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G86" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H86" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I86" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3806,25 +3809,25 @@
         <v>44</v>
       </c>
       <c r="E87">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G87" s="1">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="I87" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J87">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3841,25 +3844,25 @@
         <v>43</v>
       </c>
       <c r="E88">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G88" s="1">
-        <v>60.47</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="I88" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J88">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3873,28 +3876,28 @@
         <v>121</v>
       </c>
       <c r="D89">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E89">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G89" s="1">
-        <v>66.67</v>
+        <v>90.7</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I89" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J89">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3908,7 +3911,7 @@
         <v>122</v>
       </c>
       <c r="D90">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E90">
         <v>23</v>
@@ -3917,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -3926,10 +3929,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K90" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -4366,25 +4369,25 @@
         <v>37</v>
       </c>
       <c r="E103">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4401,25 +4404,25 @@
         <v>37</v>
       </c>
       <c r="E104">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4439,22 +4442,22 @@
         <v>32</v>
       </c>
       <c r="F105">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G105" s="1">
         <v>80</v>
       </c>
       <c r="H105" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I105" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -4471,25 +4474,25 @@
         <v>18</v>
       </c>
       <c r="E106">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>22.22</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="J106">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4506,13 +4509,13 @@
         <v>41</v>
       </c>
       <c r="E107">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F107">
         <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>78.05</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -4521,10 +4524,10 @@
         <v>7.2</v>
       </c>
       <c r="J107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K107" s="1">
-        <v>21.95</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4538,19 +4541,19 @@
         <v>120</v>
       </c>
       <c r="D108">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E108">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108" s="1">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H108" s="1">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I108" s="2">
         <v>6.6</v>
@@ -4559,7 +4562,7 @@
         <v>7</v>
       </c>
       <c r="K108" s="1">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -5063,22 +5066,22 @@
         <v>120</v>
       </c>
       <c r="D123">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E123">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F123">
         <v>3</v>
       </c>
       <c r="G123" s="1">
-        <v>92.86</v>
+        <v>93.02</v>
       </c>
       <c r="H123" s="1">
-        <v>7.14</v>
+        <v>6.98</v>
       </c>
       <c r="I123" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -5098,28 +5101,28 @@
         <v>119</v>
       </c>
       <c r="D124">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E124">
         <v>28</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G124" s="1">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="H124" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I124" s="2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J124">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -5136,25 +5139,25 @@
         <v>38</v>
       </c>
       <c r="E125">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G125" s="1">
-        <v>71.05</v>
+        <v>78.95</v>
       </c>
       <c r="H125" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="I125" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J125">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5174,22 +5177,22 @@
         <v>17</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G126" s="1">
         <v>65.38</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>34.62</v>
       </c>
       <c r="I126" s="2">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="J126">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5206,25 +5209,25 @@
         <v>32</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G127" s="1">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="I127" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5273,28 +5276,28 @@
         <v>116</v>
       </c>
       <c r="D129">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E129">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F129">
         <v>8</v>
       </c>
       <c r="G129" s="1">
-        <v>67.73999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="H129" s="1">
-        <v>25.81</v>
+        <v>26.67</v>
       </c>
       <c r="I129" s="2">
         <v>7</v>
       </c>
       <c r="J129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5349,22 +5352,22 @@
         <v>40</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G131" s="1">
         <v>90.91</v>
       </c>
       <c r="H131" s="1">
-        <v>2.27</v>
+        <v>9.09</v>
       </c>
       <c r="I131" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5381,25 +5384,25 @@
         <v>43</v>
       </c>
       <c r="E132">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F132">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G132" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H132" s="1">
-        <v>6.98</v>
+        <v>18.6</v>
       </c>
       <c r="I132" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J132">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -5413,28 +5416,28 @@
         <v>116</v>
       </c>
       <c r="D133">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E133">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F133">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G133" s="1">
-        <v>80.95</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H133" s="1">
-        <v>14.29</v>
+        <v>18.6</v>
       </c>
       <c r="I133" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5489,22 +5492,22 @@
         <v>31</v>
       </c>
       <c r="F135">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G135" s="1">
         <v>70.45</v>
       </c>
       <c r="H135" s="1">
-        <v>27.27</v>
+        <v>29.55</v>
       </c>
       <c r="I135" s="2">
         <v>6.3</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -5568,7 +5571,7 @@
         <v>17.14</v>
       </c>
       <c r="I137" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -5731,25 +5734,25 @@
         <v>34</v>
       </c>
       <c r="E142">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I142" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -5763,28 +5766,28 @@
         <v>121</v>
       </c>
       <c r="D143">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E143">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G143" s="1">
-        <v>95.12</v>
+        <v>95</v>
       </c>
       <c r="H143" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I143" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -5804,22 +5807,22 @@
         <v>35</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" s="1">
         <v>97.22</v>
       </c>
       <c r="H144" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I144" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -5836,13 +5839,13 @@
         <v>35</v>
       </c>
       <c r="E145">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -5851,10 +5854,10 @@
         <v>7.8</v>
       </c>
       <c r="J145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K145" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -6011,25 +6014,25 @@
         <v>19</v>
       </c>
       <c r="E150">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F150">
         <v>6</v>
       </c>
       <c r="G150" s="1">
-        <v>47.37</v>
+        <v>68.42</v>
       </c>
       <c r="H150" s="1">
         <v>31.58</v>
       </c>
       <c r="I150" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J150">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6186,19 +6189,19 @@
         <v>41</v>
       </c>
       <c r="E155">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>97.56</v>
+        <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -6221,25 +6224,25 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>92.31</v>
+        <v>94.87</v>
       </c>
       <c r="H156" s="1">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="I156" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -6253,19 +6256,19 @@
         <v>113</v>
       </c>
       <c r="D157">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E157">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F157">
         <v>4</v>
       </c>
       <c r="G157" s="1">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H157" s="1">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I157" s="2">
         <v>8.300000000000001</v>
@@ -6568,28 +6571,28 @@
         <v>119</v>
       </c>
       <c r="D166">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E166">
+        <v>19</v>
+      </c>
+      <c r="F166">
         <v>12</v>
       </c>
-      <c r="F166">
-        <v>0</v>
-      </c>
       <c r="G166" s="1">
-        <v>37.5</v>
+        <v>61.29</v>
       </c>
       <c r="H166" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="I166" s="2">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="J166">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -6708,22 +6711,22 @@
         <v>122</v>
       </c>
       <c r="D170">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E170">
         <v>41</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G170" s="1">
-        <v>97.62</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>2.38</v>
+        <v>4.65</v>
       </c>
       <c r="I170" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -6848,19 +6851,19 @@
         <v>108</v>
       </c>
       <c r="D174">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E174">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F174">
         <v>5</v>
       </c>
       <c r="G174" s="1">
-        <v>87.18000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H174" s="1">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="I174" s="2">
         <v>7</v>
@@ -7058,7 +7061,7 @@
         <v>120</v>
       </c>
       <c r="D180">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E180">
         <v>23</v>
@@ -7067,19 +7070,19 @@
         <v>7</v>
       </c>
       <c r="G180" s="1">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H180" s="1">
-        <v>22.58</v>
+        <v>23.33</v>
       </c>
       <c r="I180" s="2">
         <v>7.8</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7128,22 +7131,22 @@
         <v>117</v>
       </c>
       <c r="D182">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E182">
         <v>26</v>
       </c>
       <c r="F182">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G182" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H182" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I182" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -7198,16 +7201,16 @@
         <v>117</v>
       </c>
       <c r="D184">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E184">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -7219,7 +7222,7 @@
         <v>9</v>
       </c>
       <c r="K184" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7373,28 +7376,28 @@
         <v>122</v>
       </c>
       <c r="D189">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E189">
         <v>27</v>
       </c>
       <c r="F189">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G189" s="1">
-        <v>65.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H189" s="1">
-        <v>21.95</v>
+        <v>20</v>
       </c>
       <c r="I189" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J189">
         <v>5</v>
       </c>
       <c r="K189" s="1">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7583,28 +7586,28 @@
         <v>100</v>
       </c>
       <c r="D195">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E195">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F195">
         <v>4</v>
       </c>
       <c r="G195" s="1">
-        <v>86.84</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H195" s="1">
-        <v>10.53</v>
+        <v>10.26</v>
       </c>
       <c r="I195" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J195">
         <v>1</v>
       </c>
       <c r="K195" s="1">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -7918,22 +7921,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>92.86</v>
       </c>
       <c r="H2" s="1">
-        <v>50</v>
+        <v>7.14</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -7950,22 +7956,25 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>93.33</v>
       </c>
       <c r="H3" s="1">
-        <v>80</v>
+        <v>6.67</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -7982,22 +7991,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>84.20999999999999</v>
+        <v>15.79</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8011,19 +8023,22 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -8046,16 +8061,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -8078,16 +8096,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -8110,16 +8131,19 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -8142,16 +8166,19 @@
         <v>41</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>95.12</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>4.88</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -8174,16 +8201,19 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -8206,16 +8236,19 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7.69</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -8235,19 +8268,22 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>19.35</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -8270,16 +8306,19 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>11.36</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -8302,16 +8341,19 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F14">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>7.32</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -8334,16 +8376,19 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F15">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>84.44</v>
       </c>
       <c r="H15" s="1">
-        <v>97.78</v>
+        <v>13.33</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -8366,16 +8411,19 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>12.82</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -8395,19 +8443,22 @@
         <v>105</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -8430,16 +8481,19 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H18" s="1">
-        <v>89.47</v>
+        <v>7.89</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.6</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -8526,22 +8580,25 @@
         <v>18</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>94.44</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>9.6</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -8625,19 +8682,19 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>97.44</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -8651,13 +8708,13 @@
         <v>105</v>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -8686,22 +8743,25 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F26">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>82.05</v>
       </c>
       <c r="H26" s="1">
-        <v>58.97</v>
+        <v>17.95</v>
+      </c>
+      <c r="I26" s="2">
+        <v>6.7</v>
       </c>
       <c r="J26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -8718,22 +8778,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H27" s="1">
-        <v>64.70999999999999</v>
+        <v>5.88</v>
+      </c>
+      <c r="I27" s="2">
+        <v>7.9</v>
       </c>
       <c r="J27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -8753,19 +8816,19 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>80.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -8779,25 +8842,28 @@
         <v>107</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H29" s="1">
-        <v>82.93000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="I29" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -8814,22 +8880,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F30">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="H30" s="1">
-        <v>91.67</v>
+        <v>2.78</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7.7</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -8843,19 +8912,22 @@
         <v>108</v>
       </c>
       <c r="D31">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>3.23</v>
+      </c>
+      <c r="I31" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -8878,16 +8950,19 @@
         <v>31</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F32">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>8.6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -8910,16 +8985,19 @@
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>93.33</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>6.67</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.8</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -9038,16 +9116,19 @@
         <v>26</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H37" s="1">
-        <v>96.15000000000001</v>
+        <v>30.77</v>
+      </c>
+      <c r="I37" s="2">
+        <v>7</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -9134,16 +9215,19 @@
         <v>18</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F40">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I40" s="2">
+        <v>7.3</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -9166,16 +9250,19 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H41" s="1">
-        <v>93.55</v>
+        <v>22.58</v>
+      </c>
+      <c r="I41" s="2">
+        <v>7.7</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -9198,16 +9285,19 @@
         <v>35</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F42">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>97.14</v>
+        <v>5.71</v>
+      </c>
+      <c r="I42" s="2">
+        <v>7.8</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -9230,16 +9320,19 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F43">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>52.38</v>
       </c>
       <c r="H43" s="1">
-        <v>52.38</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J43">
         <v>10</v>
@@ -9262,16 +9355,19 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>64.86</v>
       </c>
       <c r="H44" s="1">
-        <v>67.56999999999999</v>
+        <v>2.7</v>
+      </c>
+      <c r="I44" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J44">
         <v>12</v>
@@ -9294,16 +9390,19 @@
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F45">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>63.33</v>
       </c>
       <c r="H45" s="1">
-        <v>100</v>
+        <v>36.67</v>
+      </c>
+      <c r="I45" s="2">
+        <v>7</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -9326,16 +9425,19 @@
         <v>32</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H46" s="1">
-        <v>96.88</v>
+        <v>12.5</v>
+      </c>
+      <c r="I46" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -9361,19 +9463,19 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -9387,25 +9489,25 @@
         <v>113</v>
       </c>
       <c r="D48">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="J48">
         <v>3</v>
       </c>
       <c r="K48" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -9422,16 +9524,19 @@
         <v>39</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F49">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>97.44</v>
       </c>
       <c r="H49" s="1">
-        <v>97.44</v>
+        <v>0</v>
+      </c>
+      <c r="I49" s="2">
+        <v>6.5</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -9454,16 +9559,19 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F50">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H50" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I50" s="2">
+        <v>7</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -9486,22 +9594,25 @@
         <v>31</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F51">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H51" s="1">
-        <v>93.55</v>
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -9518,22 +9629,25 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F52">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H52" s="1">
-        <v>90</v>
+        <v>16.67</v>
+      </c>
+      <c r="I52" s="2">
+        <v>7.7</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -9550,22 +9664,25 @@
         <v>26</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F53">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H53" s="1">
-        <v>69.23</v>
+        <v>34.62</v>
+      </c>
+      <c r="I53" s="2">
+        <v>6.9</v>
       </c>
       <c r="J53">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -9611,13 +9728,13 @@
         <v>107</v>
       </c>
       <c r="D55">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -9739,13 +9856,13 @@
         <v>107</v>
       </c>
       <c r="D59">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -9774,22 +9891,25 @@
         <v>39</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F60">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>56.41</v>
       </c>
       <c r="H60" s="1">
-        <v>58.97</v>
+        <v>43.59</v>
+      </c>
+      <c r="I60" s="2">
+        <v>6.4</v>
       </c>
       <c r="J60">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -9806,22 +9926,25 @@
         <v>34</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F61">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H61" s="1">
-        <v>85.29000000000001</v>
+        <v>11.76</v>
+      </c>
+      <c r="I61" s="2">
+        <v>7.1</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -9838,22 +9961,25 @@
         <v>41</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F62">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H62" s="1">
-        <v>78.05</v>
+        <v>12.2</v>
+      </c>
+      <c r="I62" s="2">
+        <v>7.1</v>
       </c>
       <c r="J62">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>21.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -9867,25 +9993,28 @@
         <v>116</v>
       </c>
       <c r="D63">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F63">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H63" s="1">
-        <v>60.98</v>
+        <v>20</v>
+      </c>
+      <c r="I63" s="2">
+        <v>6.5</v>
       </c>
       <c r="J63">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>39.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -9902,22 +10031,25 @@
         <v>36</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F64">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H64" s="1">
-        <v>97.22</v>
+        <v>25</v>
+      </c>
+      <c r="I64" s="2">
+        <v>6.3</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -10027,25 +10159,25 @@
         <v>117</v>
       </c>
       <c r="D68">
+        <v>43</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
         <v>42</v>
       </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>41</v>
-      </c>
       <c r="G68" s="1">
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>97.62</v>
+        <v>97.67</v>
       </c>
       <c r="J68">
         <v>1</v>
       </c>
       <c r="K68" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -10091,25 +10223,25 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>87.88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="J70">
         <v>4</v>
       </c>
       <c r="K70" s="1">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -10257,19 +10389,19 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J75">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -10414,16 +10546,19 @@
         <v>34</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F80">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H80" s="1">
-        <v>67.65000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="I80" s="2">
+        <v>8.6</v>
       </c>
       <c r="J80">
         <v>11</v>
@@ -10446,16 +10581,19 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F81">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H81" s="1">
-        <v>64.70999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="I81" s="2">
+        <v>8.9</v>
       </c>
       <c r="J81">
         <v>12</v>
@@ -10478,16 +10616,19 @@
         <v>26</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F82">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="H82" s="1">
-        <v>53.85</v>
+        <v>0</v>
+      </c>
+      <c r="I82" s="2">
+        <v>9.1</v>
       </c>
       <c r="J82">
         <v>12</v>
@@ -10510,16 +10651,19 @@
         <v>15</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F83">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H83" s="1">
-        <v>60</v>
+        <v>0</v>
+      </c>
+      <c r="I83" s="2">
+        <v>9.1</v>
       </c>
       <c r="J83">
         <v>6</v>
@@ -10542,22 +10686,25 @@
         <v>34</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F84">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H84" s="1">
-        <v>76.47</v>
+        <v>29.41</v>
+      </c>
+      <c r="I84" s="2">
+        <v>7.2</v>
       </c>
       <c r="J84">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -10571,25 +10718,28 @@
         <v>121</v>
       </c>
       <c r="D85">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F85">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H85" s="1">
-        <v>83.87</v>
+        <v>16.67</v>
+      </c>
+      <c r="I85" s="2">
+        <v>6.7</v>
       </c>
       <c r="J85">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -10606,22 +10756,25 @@
         <v>40</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F86">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G86" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H86" s="1">
-        <v>85</v>
+        <v>15</v>
+      </c>
+      <c r="I86" s="2">
+        <v>6.9</v>
       </c>
       <c r="J86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -10638,22 +10791,25 @@
         <v>44</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F87">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H87" s="1">
-        <v>86.36</v>
+        <v>4.55</v>
+      </c>
+      <c r="I87" s="2">
+        <v>7.3</v>
       </c>
       <c r="J87">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -10670,22 +10826,25 @@
         <v>43</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F88">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="H88" s="1">
-        <v>60.47</v>
+        <v>32.56</v>
+      </c>
+      <c r="I88" s="2">
+        <v>6.4</v>
       </c>
       <c r="J88">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -10699,25 +10858,28 @@
         <v>121</v>
       </c>
       <c r="D89">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F89">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="H89" s="1">
-        <v>66.67</v>
+        <v>13.95</v>
+      </c>
+      <c r="I89" s="2">
+        <v>6.7</v>
       </c>
       <c r="J89">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -10731,25 +10893,28 @@
         <v>122</v>
       </c>
       <c r="D90">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F90">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G90" s="1">
-        <v>0</v>
+        <v>63.33</v>
       </c>
       <c r="H90" s="1">
-        <v>74.19</v>
+        <v>13.33</v>
+      </c>
+      <c r="I90" s="2">
+        <v>7.2</v>
       </c>
       <c r="J90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K90" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -10798,16 +10963,19 @@
         <v>31</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F92">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I92" s="2">
+        <v>8.5</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -10894,16 +11062,19 @@
         <v>26</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F95">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>80.77</v>
       </c>
       <c r="H95" s="1">
-        <v>100</v>
+        <v>19.23</v>
+      </c>
+      <c r="I95" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -10990,16 +11161,19 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F98">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G98" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H98" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I98" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -11022,16 +11196,19 @@
         <v>38</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F99">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H99" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I99" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -11054,16 +11231,19 @@
         <v>26</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F100">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H100" s="1">
-        <v>100</v>
+        <v>3.85</v>
+      </c>
+      <c r="I100" s="2">
+        <v>8.1</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -11086,16 +11266,19 @@
         <v>32</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F101">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H101" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I101" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -11118,16 +11301,19 @@
         <v>15</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F102">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -11150,22 +11336,25 @@
         <v>37</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F103">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H103" s="1">
-        <v>97.3</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I103" s="2">
+        <v>9.4</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -11182,22 +11371,25 @@
         <v>37</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F104">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H104" s="1">
-        <v>97.3</v>
+        <v>18.92</v>
+      </c>
+      <c r="I104" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -11214,22 +11406,25 @@
         <v>40</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F105">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H105" s="1">
-        <v>90</v>
+        <v>40</v>
+      </c>
+      <c r="I105" s="2">
+        <v>7.8</v>
       </c>
       <c r="J105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -11246,22 +11441,25 @@
         <v>18</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F106">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
-        <v>22.22</v>
+        <v>0</v>
+      </c>
+      <c r="I106" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J106">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11278,22 +11476,25 @@
         <v>41</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F107">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>70.73</v>
       </c>
       <c r="H107" s="1">
-        <v>78.05</v>
+        <v>9.76</v>
+      </c>
+      <c r="I107" s="2">
+        <v>7</v>
       </c>
       <c r="J107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K107" s="1">
-        <v>21.95</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -11307,25 +11508,28 @@
         <v>120</v>
       </c>
       <c r="D108">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F108">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H108" s="1">
-        <v>82.93000000000001</v>
+        <v>2.5</v>
+      </c>
+      <c r="I108" s="2">
+        <v>6.2</v>
       </c>
       <c r="J108">
         <v>7</v>
       </c>
       <c r="K108" s="1">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -11342,16 +11546,19 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F109">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H109" s="1">
-        <v>63.89</v>
+        <v>16.67</v>
+      </c>
+      <c r="I109" s="2">
+        <v>6.7</v>
       </c>
       <c r="J109">
         <v>13</v>
@@ -11374,16 +11581,19 @@
         <v>39</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F110">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G110" s="1">
-        <v>0</v>
+        <v>94.87</v>
       </c>
       <c r="H110" s="1">
-        <v>100</v>
+        <v>5.13</v>
+      </c>
+      <c r="I110" s="2">
+        <v>9</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -11406,16 +11616,19 @@
         <v>32</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F111">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H111" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I111" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -11470,16 +11683,19 @@
         <v>31</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F113">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G113" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H113" s="1">
-        <v>100</v>
+        <v>6.45</v>
+      </c>
+      <c r="I113" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -11502,16 +11718,19 @@
         <v>30</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F114">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G114" s="1">
-        <v>0</v>
+        <v>96.67</v>
       </c>
       <c r="H114" s="1">
-        <v>100</v>
+        <v>3.33</v>
+      </c>
+      <c r="I114" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -11534,16 +11753,19 @@
         <v>26</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F115">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G115" s="1">
-        <v>0</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H115" s="1">
-        <v>100</v>
+        <v>3.85</v>
+      </c>
+      <c r="I115" s="2">
+        <v>7.5</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -11566,16 +11788,19 @@
         <v>26</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F116">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G116" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H116" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I116" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -11598,16 +11823,19 @@
         <v>19</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F117">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H117" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I117" s="2">
+        <v>8.4</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -11630,16 +11858,19 @@
         <v>34</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F118">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H118" s="1">
-        <v>97.06</v>
+        <v>2.94</v>
+      </c>
+      <c r="I118" s="2">
+        <v>9.1</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -11662,16 +11893,19 @@
         <v>18</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F119">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G119" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H119" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I119" s="2">
+        <v>9.1</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -11694,16 +11928,19 @@
         <v>40</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F120">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I120" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -11726,16 +11963,19 @@
         <v>44</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F121">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H121" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I121" s="2">
+        <v>8.9</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -11758,16 +11998,19 @@
         <v>43</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F122">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H122" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I122" s="2">
+        <v>8.9</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -11787,19 +12030,22 @@
         <v>120</v>
       </c>
       <c r="D123">
+        <v>43</v>
+      </c>
+      <c r="E123">
         <v>42</v>
       </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
       <c r="F123">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G123" s="1">
-        <v>0</v>
+        <v>97.67</v>
       </c>
       <c r="H123" s="1">
-        <v>100</v>
+        <v>2.33</v>
+      </c>
+      <c r="I123" s="2">
+        <v>8.9</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -11819,25 +12065,28 @@
         <v>119</v>
       </c>
       <c r="D124">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F124">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H124" s="1">
-        <v>82.34999999999999</v>
+        <v>25.71</v>
+      </c>
+      <c r="I124" s="2">
+        <v>7</v>
       </c>
       <c r="J124">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -11854,22 +12103,25 @@
         <v>38</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F125">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G125" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H125" s="1">
-        <v>71.05</v>
+        <v>18.42</v>
+      </c>
+      <c r="I125" s="2">
+        <v>7.4</v>
       </c>
       <c r="J125">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -11886,22 +12138,25 @@
         <v>26</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F126">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G126" s="1">
-        <v>0</v>
+        <v>69.23</v>
       </c>
       <c r="H126" s="1">
-        <v>65.38</v>
+        <v>30.77</v>
+      </c>
+      <c r="I126" s="2">
+        <v>6.5</v>
       </c>
       <c r="J126">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -11918,22 +12173,25 @@
         <v>32</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F127">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G127" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H127" s="1">
-        <v>78.13</v>
+        <v>21.88</v>
+      </c>
+      <c r="I127" s="2">
+        <v>8</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -11979,25 +12237,28 @@
         <v>116</v>
       </c>
       <c r="D129">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F129">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>56.67</v>
       </c>
       <c r="H129" s="1">
-        <v>93.55</v>
+        <v>43.33</v>
+      </c>
+      <c r="I129" s="2">
+        <v>6.8</v>
       </c>
       <c r="J129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -12014,16 +12275,19 @@
         <v>40</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F130">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H130" s="1">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="I130" s="2">
+        <v>6.9</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -12046,22 +12310,25 @@
         <v>44</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F131">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>86.36</v>
       </c>
       <c r="H131" s="1">
-        <v>93.18000000000001</v>
+        <v>13.64</v>
+      </c>
+      <c r="I131" s="2">
+        <v>7.5</v>
       </c>
       <c r="J131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -12081,19 +12348,19 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G132" s="1">
         <v>0</v>
       </c>
       <c r="H132" s="1">
-        <v>86.05</v>
+        <v>100</v>
       </c>
       <c r="J132">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -12107,25 +12374,25 @@
         <v>116</v>
       </c>
       <c r="D133">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G133" s="1">
         <v>0</v>
       </c>
       <c r="H133" s="1">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="J133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -12142,16 +12409,19 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F134">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G134" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H134" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I134" s="2">
+        <v>8</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -12177,19 +12447,19 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G135" s="1">
         <v>0</v>
       </c>
       <c r="H135" s="1">
-        <v>97.73</v>
+        <v>100</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -12206,16 +12476,19 @@
         <v>31</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F136">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G136" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H136" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I136" s="2">
+        <v>6.6</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -12238,16 +12511,19 @@
         <v>35</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F137">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G137" s="1">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H137" s="1">
-        <v>100</v>
+        <v>25.71</v>
+      </c>
+      <c r="I137" s="2">
+        <v>7.1</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -12270,16 +12546,19 @@
         <v>21</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F138">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G138" s="1">
-        <v>0</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H138" s="1">
-        <v>100</v>
+        <v>4.76</v>
+      </c>
+      <c r="I138" s="2">
+        <v>6.6</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -12302,16 +12581,19 @@
         <v>37</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F139">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>0</v>
+        <v>94.59</v>
       </c>
       <c r="H139" s="1">
-        <v>94.59</v>
+        <v>0</v>
+      </c>
+      <c r="I139" s="2">
+        <v>7.4</v>
       </c>
       <c r="J139">
         <v>2</v>
@@ -12334,16 +12616,19 @@
         <v>30</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F140">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G140" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H140" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I140" s="2">
+        <v>6.9</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -12366,16 +12651,19 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F141">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H141" s="1">
-        <v>68.75</v>
+        <v>0</v>
+      </c>
+      <c r="I141" s="2">
+        <v>7.4</v>
       </c>
       <c r="J141">
         <v>10</v>
@@ -12398,22 +12686,25 @@
         <v>34</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F142">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>0</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H142" s="1">
-        <v>94.12</v>
+        <v>8.82</v>
+      </c>
+      <c r="I142" s="2">
+        <v>7.8</v>
       </c>
       <c r="J142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -12427,25 +12718,28 @@
         <v>121</v>
       </c>
       <c r="D143">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F143">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G143" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H143" s="1">
-        <v>95.12</v>
+        <v>12.5</v>
+      </c>
+      <c r="I143" s="2">
+        <v>7.5</v>
       </c>
       <c r="J143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -12462,22 +12756,25 @@
         <v>36</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F144">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G144" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H144" s="1">
-        <v>97.22</v>
+        <v>16.67</v>
+      </c>
+      <c r="I144" s="2">
+        <v>7.6</v>
       </c>
       <c r="J144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -12494,22 +12791,25 @@
         <v>35</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F145">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H145" s="1">
-        <v>91.43000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="I145" s="2">
+        <v>9</v>
       </c>
       <c r="J145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K145" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -12526,16 +12826,19 @@
         <v>37</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F146">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G146" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H146" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I146" s="2">
+        <v>9</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -12558,16 +12861,19 @@
         <v>18</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F147">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H147" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I147" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -12654,22 +12960,25 @@
         <v>19</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F150">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H150" s="1">
-        <v>78.95</v>
+        <v>21.05</v>
+      </c>
+      <c r="I150" s="2">
+        <v>7.8</v>
       </c>
       <c r="J150">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -12782,16 +13091,19 @@
         <v>32</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F154">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H154" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I154" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -12814,16 +13126,19 @@
         <v>41</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F155">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>97.56</v>
       </c>
       <c r="H155" s="1">
-        <v>100</v>
+        <v>2.44</v>
+      </c>
+      <c r="I155" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -12846,22 +13161,25 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F156">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>97.44</v>
       </c>
       <c r="H156" s="1">
-        <v>94.87</v>
+        <v>2.56</v>
+      </c>
+      <c r="I156" s="2">
+        <v>9.4</v>
       </c>
       <c r="J156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -12875,19 +13193,22 @@
         <v>113</v>
       </c>
       <c r="D157">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F157">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H157" s="1">
-        <v>100</v>
+        <v>9.68</v>
+      </c>
+      <c r="I157" s="2">
+        <v>8.5</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -12910,16 +13231,19 @@
         <v>39</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F158">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H158" s="1">
-        <v>97.44</v>
+        <v>10.26</v>
+      </c>
+      <c r="I158" s="2">
+        <v>8.1</v>
       </c>
       <c r="J158">
         <v>1</v>
@@ -12942,16 +13266,19 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F159">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H159" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I159" s="2">
+        <v>8.6</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -12974,16 +13301,19 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F160">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G160" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H160" s="1">
-        <v>96.3</v>
+        <v>0</v>
+      </c>
+      <c r="I160" s="2">
+        <v>7.7</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -13006,16 +13336,19 @@
         <v>15</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F161">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G161" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H161" s="1">
-        <v>93.33</v>
+        <v>26.67</v>
+      </c>
+      <c r="I161" s="2">
+        <v>7.4</v>
       </c>
       <c r="J161">
         <v>1</v>
@@ -13038,16 +13371,19 @@
         <v>21</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F162">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G162" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H162" s="1">
-        <v>85.70999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="I162" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J162">
         <v>3</v>
@@ -13070,16 +13406,19 @@
         <v>32</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F163">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G163" s="1">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H163" s="1">
-        <v>100</v>
+        <v>31.25</v>
+      </c>
+      <c r="I163" s="2">
+        <v>6.4</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -13102,16 +13441,19 @@
         <v>41</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F164">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G164" s="1">
-        <v>0</v>
+        <v>51.22</v>
       </c>
       <c r="H164" s="1">
-        <v>100</v>
+        <v>48.78</v>
+      </c>
+      <c r="I164" s="2">
+        <v>5.7</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -13134,16 +13476,19 @@
         <v>39</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F165">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G165" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H165" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I165" s="2">
+        <v>6.1</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -13163,25 +13508,28 @@
         <v>119</v>
       </c>
       <c r="D166">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F166">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G166" s="1">
-        <v>0</v>
+        <v>58.06</v>
       </c>
       <c r="H166" s="1">
-        <v>37.5</v>
+        <v>41.94</v>
+      </c>
+      <c r="I166" s="2">
+        <v>6.2</v>
       </c>
       <c r="J166">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -13198,16 +13546,19 @@
         <v>40</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F167">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G167" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H167" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I167" s="2">
+        <v>7.7</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -13230,16 +13581,19 @@
         <v>44</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F168">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G168" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H168" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I168" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -13262,16 +13616,19 @@
         <v>43</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F169">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G169" s="1">
-        <v>0</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H169" s="1">
-        <v>100</v>
+        <v>4.65</v>
+      </c>
+      <c r="I169" s="2">
+        <v>7.8</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -13291,19 +13648,22 @@
         <v>122</v>
       </c>
       <c r="D170">
+        <v>43</v>
+      </c>
+      <c r="E170">
         <v>42</v>
       </c>
-      <c r="E170">
-        <v>0</v>
-      </c>
       <c r="F170">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>97.67</v>
       </c>
       <c r="H170" s="1">
-        <v>100</v>
+        <v>2.33</v>
+      </c>
+      <c r="I170" s="2">
+        <v>7.7</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -13390,16 +13750,19 @@
         <v>39</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F173">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G173" s="1">
-        <v>0</v>
+        <v>56.41</v>
       </c>
       <c r="H173" s="1">
-        <v>71.79000000000001</v>
+        <v>15.38</v>
+      </c>
+      <c r="I173" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J173">
         <v>11</v>
@@ -13419,19 +13782,22 @@
         <v>108</v>
       </c>
       <c r="D174">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F174">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G174" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H174" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I174" s="2">
+        <v>7.4</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -13454,16 +13820,19 @@
         <v>26</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F175">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G175" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H175" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I175" s="2">
+        <v>6.5</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -13486,16 +13855,19 @@
         <v>28</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F176">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G176" s="1">
-        <v>0</v>
+        <v>67.86</v>
       </c>
       <c r="H176" s="1">
-        <v>67.86</v>
+        <v>0</v>
+      </c>
+      <c r="I176" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J176">
         <v>9</v>
@@ -13518,16 +13890,19 @@
         <v>19</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F177">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H177" s="1">
-        <v>94.73999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="I177" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J177">
         <v>1</v>
@@ -13550,16 +13925,19 @@
         <v>32</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F178">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G178" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H178" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I178" s="2">
+        <v>7.5</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -13582,16 +13960,19 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F179">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G179" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H179" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I179" s="2">
+        <v>7.7</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -13611,7 +13992,7 @@
         <v>120</v>
       </c>
       <c r="D180">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -13623,13 +14004,13 @@
         <v>0</v>
       </c>
       <c r="H180" s="1">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -13675,13 +14056,13 @@
         <v>117</v>
       </c>
       <c r="D182">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G182" s="1">
         <v>0</v>
@@ -13739,25 +14120,25 @@
         <v>117</v>
       </c>
       <c r="D184">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E184">
         <v>0</v>
       </c>
       <c r="F184">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G184" s="1">
         <v>0</v>
       </c>
       <c r="H184" s="1">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="J184">
         <v>9</v>
       </c>
       <c r="K184" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -13899,25 +14280,25 @@
         <v>122</v>
       </c>
       <c r="D189">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E189">
         <v>0</v>
       </c>
       <c r="F189">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G189" s="1">
         <v>0</v>
       </c>
       <c r="H189" s="1">
-        <v>87.8</v>
+        <v>87.5</v>
       </c>
       <c r="J189">
         <v>5</v>
       </c>
       <c r="K189" s="1">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -14030,16 +14411,19 @@
         <v>34</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F193">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G193" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H193" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I193" s="2">
+        <v>8</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -14062,16 +14446,19 @@
         <v>39</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F194">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G194" s="1">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H194" s="1">
-        <v>84.62</v>
+        <v>0</v>
+      </c>
+      <c r="I194" s="2">
+        <v>7.5</v>
       </c>
       <c r="J194">
         <v>6</v>
@@ -14091,25 +14478,28 @@
         <v>100</v>
       </c>
       <c r="D195">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F195">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G195" s="1">
-        <v>0</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H195" s="1">
-        <v>97.37</v>
+        <v>7.69</v>
+      </c>
+      <c r="I195" s="2">
+        <v>7.4</v>
       </c>
       <c r="J195">
         <v>1</v>
       </c>
       <c r="K195" s="1">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -14126,16 +14516,19 @@
         <v>26</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F196">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G196" s="1">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H196" s="1">
-        <v>100</v>
+        <v>15.38</v>
+      </c>
+      <c r="I196" s="2">
+        <v>7.9</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -14158,16 +14551,19 @@
         <v>35</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F197">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H197" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I197" s="2">
+        <v>9</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -14190,16 +14586,19 @@
         <v>35</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F198">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H198" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I198" s="2">
+        <v>9.1</v>
       </c>
       <c r="J198">
         <v>0</v>
@@ -14222,16 +14621,19 @@
         <v>32</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F199">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H199" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I199" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -14254,16 +14656,19 @@
         <v>41</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F200">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G200" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H200" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I200" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -14286,16 +14691,19 @@
         <v>45</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F201">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G201" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H201" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I201" s="2">
+        <v>7.4</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -14318,16 +14726,19 @@
         <v>32</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F202">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H202" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I202" s="2">
+        <v>9</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -14402,25 +14813,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>50</v>
+        <v>92.86</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -14437,25 +14848,25 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>80</v>
+        <v>93.33</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I3" s="2">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -14475,22 +14886,22 @@
         <v>16</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
         <v>84.20999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -14504,10 +14915,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -14519,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -14554,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -14589,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -14612,19 +15023,19 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H8" s="1">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -14647,19 +15058,19 @@
         <v>41</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>90.23999999999999</v>
+        <v>95.12</v>
       </c>
       <c r="H9" s="1">
-        <v>9.76</v>
+        <v>4.88</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -14682,19 +15093,19 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -14729,7 +15140,7 @@
         <v>7.69</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -14749,19 +15160,19 @@
         <v>102</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>71.88</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>28.13</v>
+        <v>19.35</v>
       </c>
       <c r="I12" s="2">
         <v>7.6</v>
@@ -14787,19 +15198,19 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H13" s="1">
-        <v>18.18</v>
+        <v>11.36</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -14822,19 +15233,19 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="I14" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -14857,19 +15268,19 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>93.33</v>
+        <v>88.89</v>
       </c>
       <c r="H15" s="1">
-        <v>4.44</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -14892,19 +15303,19 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>15.38</v>
+        <v>12.82</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -14924,22 +15335,22 @@
         <v>105</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>28</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="H17" s="1">
-        <v>17.65</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -14962,19 +15373,19 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>89.47</v>
+        <v>81.58</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>7.89</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -15067,25 +15478,25 @@
         <v>18</v>
       </c>
       <c r="E21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15175,22 +15586,22 @@
         <v>38</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
         <v>97.44</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I24" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -15204,19 +15615,19 @@
         <v>105</v>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25">
         <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I25" s="2">
         <v>8.6</v>
@@ -15242,25 +15653,25 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1">
-        <v>58.97</v>
+        <v>82.05</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>17.95</v>
       </c>
       <c r="I26" s="2">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -15277,25 +15688,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>61.76</v>
+        <v>94.12</v>
       </c>
       <c r="H27" s="1">
-        <v>2.94</v>
+        <v>5.88</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -15312,25 +15723,25 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>75.61</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>4.88</v>
+        <v>9.76</v>
       </c>
       <c r="I28" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -15344,28 +15755,28 @@
         <v>107</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1">
-        <v>78.05</v>
+        <v>87.5</v>
       </c>
       <c r="H29" s="1">
-        <v>4.88</v>
+        <v>12.5</v>
       </c>
       <c r="I29" s="2">
         <v>8</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -15382,25 +15793,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I30" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -15414,22 +15825,22 @@
         <v>108</v>
       </c>
       <c r="D31">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="H31" s="1">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="I31" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -15452,19 +15863,19 @@
         <v>31</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -15499,7 +15910,7 @@
         <v>6.67</v>
       </c>
       <c r="I33" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -15627,19 +16038,19 @@
         <v>26</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="H37" s="1">
-        <v>46.15</v>
+        <v>30.77</v>
       </c>
       <c r="I37" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -15732,19 +16143,19 @@
         <v>18</v>
       </c>
       <c r="E40">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G40" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H40" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I40" s="2">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -15767,19 +16178,19 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1">
-        <v>35.48</v>
+        <v>70.97</v>
       </c>
       <c r="H41" s="1">
-        <v>58.06</v>
+        <v>22.58</v>
       </c>
       <c r="I41" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -15802,19 +16213,19 @@
         <v>35</v>
       </c>
       <c r="E42">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>97.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I42" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -15849,7 +16260,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J43">
         <v>10</v>
@@ -15884,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J44">
         <v>12</v>
@@ -15907,19 +16318,19 @@
         <v>30</v>
       </c>
       <c r="E45">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F45">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1">
-        <v>53.33</v>
+        <v>63.33</v>
       </c>
       <c r="H45" s="1">
-        <v>46.67</v>
+        <v>36.67</v>
       </c>
       <c r="I45" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -15954,7 +16365,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -15980,22 +16391,22 @@
         <v>42</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1">
         <v>95.45</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="I47" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -16009,16 +16420,16 @@
         <v>113</v>
       </c>
       <c r="D48">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E48">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -16030,7 +16441,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -16059,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -16094,7 +16505,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -16117,25 +16528,25 @@
         <v>31</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -16152,25 +16563,25 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G52" s="1">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I52" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -16187,25 +16598,25 @@
         <v>26</v>
       </c>
       <c r="E53">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G53" s="1">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>34.62</v>
       </c>
       <c r="I53" s="2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="J53">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -16254,19 +16665,19 @@
         <v>107</v>
       </c>
       <c r="D55">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E55">
         <v>26</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H55" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I55" s="2">
         <v>6.9</v>
@@ -16394,22 +16805,22 @@
         <v>107</v>
       </c>
       <c r="D59">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E59">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59">
         <v>7</v>
       </c>
       <c r="G59" s="1">
-        <v>83.33</v>
+        <v>83.72</v>
       </c>
       <c r="H59" s="1">
-        <v>16.67</v>
+        <v>16.28</v>
       </c>
       <c r="I59" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -16435,22 +16846,22 @@
         <v>23</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G60" s="1">
         <v>58.97</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>41.03</v>
       </c>
       <c r="I60" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J60">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -16467,25 +16878,25 @@
         <v>34</v>
       </c>
       <c r="E61">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>11.76</v>
       </c>
       <c r="I61" s="2">
         <v>7.2</v>
       </c>
       <c r="J61">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -16502,25 +16913,25 @@
         <v>41</v>
       </c>
       <c r="E62">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I62" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J62">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>21.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -16534,28 +16945,28 @@
         <v>116</v>
       </c>
       <c r="D63">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E63">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1">
-        <v>60.98</v>
+        <v>80</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I63" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J63">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>39.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -16572,25 +16983,25 @@
         <v>36</v>
       </c>
       <c r="E64">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G64" s="1">
-        <v>97.22</v>
+        <v>83.33</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I64" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -16709,19 +17120,19 @@
         <v>117</v>
       </c>
       <c r="D68">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E68">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F68">
         <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>73.81</v>
+        <v>74.42</v>
       </c>
       <c r="H68" s="1">
-        <v>23.81</v>
+        <v>23.26</v>
       </c>
       <c r="I68" s="2">
         <v>7.2</v>
@@ -16730,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -16779,28 +17190,28 @@
         <v>102</v>
       </c>
       <c r="D70">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E70">
         <v>29</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="1">
-        <v>87.88</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I70" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J70">
         <v>4</v>
       </c>
       <c r="K70" s="1">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -16957,22 +17368,25 @@
         <v>15</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H75" s="1">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="I75" s="2">
+        <v>6.4</v>
       </c>
       <c r="J75">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -17141,7 +17555,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J80">
         <v>11</v>
@@ -17176,7 +17590,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J81">
         <v>12</v>
@@ -17211,7 +17625,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J82">
         <v>12</v>
@@ -17246,7 +17660,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="2">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="J83">
         <v>6</v>
@@ -17272,22 +17686,22 @@
         <v>26</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G84" s="1">
         <v>76.47</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="I84" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J84">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -17301,28 +17715,28 @@
         <v>121</v>
       </c>
       <c r="D85">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E85">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G85" s="1">
-        <v>83.87</v>
+        <v>83.33</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I85" s="2">
         <v>6.8</v>
       </c>
       <c r="J85">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -17342,22 +17756,22 @@
         <v>34</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G86" s="1">
         <v>85</v>
       </c>
       <c r="H86" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I86" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -17374,25 +17788,25 @@
         <v>44</v>
       </c>
       <c r="E87">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="1">
-        <v>86.36</v>
+        <v>95.45</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="I87" s="2">
         <v>7.3</v>
       </c>
       <c r="J87">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -17409,25 +17823,25 @@
         <v>43</v>
       </c>
       <c r="E88">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G88" s="1">
-        <v>60.47</v>
+        <v>67.44</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>32.56</v>
       </c>
       <c r="I88" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J88">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -17441,28 +17855,28 @@
         <v>121</v>
       </c>
       <c r="D89">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E89">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G89" s="1">
-        <v>66.67</v>
+        <v>86.05</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>13.95</v>
       </c>
       <c r="I89" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J89">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -17476,28 +17890,28 @@
         <v>122</v>
       </c>
       <c r="D90">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E90">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G90" s="1">
-        <v>74.19</v>
+        <v>63.33</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="I90" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K90" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -17549,19 +17963,19 @@
         <v>31</v>
       </c>
       <c r="E92">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F92">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -17654,19 +18068,19 @@
         <v>26</v>
       </c>
       <c r="E95">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F95">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G95" s="1">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="H95" s="1">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
       <c r="I95" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -17794,19 +18208,19 @@
         <v>38</v>
       </c>
       <c r="E99">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F99">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G99" s="1">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H99" s="1">
-        <v>18.42</v>
+        <v>5.26</v>
       </c>
       <c r="I99" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -17829,19 +18243,19 @@
         <v>26</v>
       </c>
       <c r="E100">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G100" s="1">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H100" s="1">
-        <v>15.38</v>
+        <v>3.85</v>
       </c>
       <c r="I100" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -17864,19 +18278,19 @@
         <v>32</v>
       </c>
       <c r="E101">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F101">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G101" s="1">
-        <v>81.25</v>
+        <v>96.88</v>
       </c>
       <c r="H101" s="1">
-        <v>18.75</v>
+        <v>3.13</v>
       </c>
       <c r="I101" s="2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -17899,19 +18313,19 @@
         <v>15</v>
       </c>
       <c r="E102">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="H102" s="1">
-        <v>13.33</v>
+        <v>0</v>
       </c>
       <c r="I102" s="2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -17934,13 +18348,13 @@
         <v>37</v>
       </c>
       <c r="E103">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -17949,10 +18363,10 @@
         <v>9.4</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -17969,25 +18383,25 @@
         <v>37</v>
       </c>
       <c r="E104">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -18007,22 +18421,22 @@
         <v>32</v>
       </c>
       <c r="F105">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G105" s="1">
         <v>80</v>
       </c>
       <c r="H105" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I105" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -18039,25 +18453,25 @@
         <v>18</v>
       </c>
       <c r="E106">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>22.22</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J106">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18077,22 +18491,22 @@
         <v>32</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="1">
         <v>78.05</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I107" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K107" s="1">
-        <v>21.95</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -18106,28 +18520,28 @@
         <v>120</v>
       </c>
       <c r="D108">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E108">
         <v>33</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>80.48999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H108" s="1">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="I108" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J108">
         <v>7</v>
       </c>
       <c r="K108" s="1">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -18144,19 +18558,19 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G109" s="1">
-        <v>63.89</v>
+        <v>58.33</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="I109" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J109">
         <v>13</v>
@@ -18179,19 +18593,19 @@
         <v>39</v>
       </c>
       <c r="E110">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="1">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="H110" s="1">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="I110" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -18214,19 +18628,19 @@
         <v>32</v>
       </c>
       <c r="E111">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F111">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G111" s="1">
-        <v>90.63</v>
+        <v>84.38</v>
       </c>
       <c r="H111" s="1">
-        <v>9.380000000000001</v>
+        <v>15.63</v>
       </c>
       <c r="I111" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -18284,19 +18698,19 @@
         <v>31</v>
       </c>
       <c r="E113">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G113" s="1">
-        <v>100</v>
+        <v>93.55</v>
       </c>
       <c r="H113" s="1">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="I113" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -18319,19 +18733,19 @@
         <v>30</v>
       </c>
       <c r="E114">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" s="1">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H114" s="1">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="I114" s="2">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -18366,7 +18780,7 @@
         <v>3.85</v>
       </c>
       <c r="I115" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -18401,7 +18815,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="2">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -18424,19 +18838,19 @@
         <v>19</v>
       </c>
       <c r="E117">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G117" s="1">
-        <v>94.73999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H117" s="1">
-        <v>5.26</v>
+        <v>21.05</v>
       </c>
       <c r="I117" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -18459,19 +18873,19 @@
         <v>34</v>
       </c>
       <c r="E118">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="1">
-        <v>97.06</v>
+        <v>94.12</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I118" s="2">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -18506,7 +18920,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -18529,19 +18943,19 @@
         <v>40</v>
       </c>
       <c r="E120">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I120" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -18564,16 +18978,16 @@
         <v>44</v>
       </c>
       <c r="E121">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G121" s="1">
-        <v>93.18000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="H121" s="1">
-        <v>6.82</v>
+        <v>4.55</v>
       </c>
       <c r="I121" s="2">
         <v>9.1</v>
@@ -18599,19 +19013,19 @@
         <v>43</v>
       </c>
       <c r="E122">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>95.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H122" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="I122" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -18631,19 +19045,19 @@
         <v>120</v>
       </c>
       <c r="D123">
+        <v>43</v>
+      </c>
+      <c r="E123">
         <v>42</v>
       </c>
-      <c r="E123">
-        <v>39</v>
-      </c>
       <c r="F123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G123" s="1">
-        <v>92.86</v>
+        <v>97.67</v>
       </c>
       <c r="H123" s="1">
-        <v>7.14</v>
+        <v>2.33</v>
       </c>
       <c r="I123" s="2">
         <v>9.199999999999999</v>
@@ -18666,28 +19080,28 @@
         <v>119</v>
       </c>
       <c r="D124">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E124">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G124" s="1">
-        <v>82.34999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H124" s="1">
-        <v>0</v>
+        <v>25.71</v>
       </c>
       <c r="I124" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J124">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -18704,25 +19118,25 @@
         <v>38</v>
       </c>
       <c r="E125">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G125" s="1">
-        <v>71.05</v>
+        <v>81.58</v>
       </c>
       <c r="H125" s="1">
-        <v>0</v>
+        <v>18.42</v>
       </c>
       <c r="I125" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J125">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -18739,25 +19153,25 @@
         <v>26</v>
       </c>
       <c r="E126">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G126" s="1">
-        <v>65.38</v>
+        <v>69.23</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>30.77</v>
       </c>
       <c r="I126" s="2">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="J126">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -18777,22 +19191,22 @@
         <v>25</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G127" s="1">
         <v>78.13</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>21.88</v>
       </c>
       <c r="I127" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -18841,28 +19255,28 @@
         <v>116</v>
       </c>
       <c r="D129">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E129">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F129">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G129" s="1">
-        <v>67.73999999999999</v>
+        <v>60</v>
       </c>
       <c r="H129" s="1">
-        <v>25.81</v>
+        <v>40</v>
       </c>
       <c r="I129" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -18879,16 +19293,16 @@
         <v>40</v>
       </c>
       <c r="E130">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F130">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G130" s="1">
-        <v>72.5</v>
+        <v>67.5</v>
       </c>
       <c r="H130" s="1">
-        <v>27.5</v>
+        <v>32.5</v>
       </c>
       <c r="I130" s="2">
         <v>6.9</v>
@@ -18914,25 +19328,25 @@
         <v>44</v>
       </c>
       <c r="E131">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G131" s="1">
-        <v>90.91</v>
+        <v>86.36</v>
       </c>
       <c r="H131" s="1">
-        <v>2.27</v>
+        <v>13.64</v>
       </c>
       <c r="I131" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -18949,25 +19363,25 @@
         <v>43</v>
       </c>
       <c r="E132">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F132">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G132" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H132" s="1">
-        <v>6.98</v>
+        <v>18.6</v>
       </c>
       <c r="I132" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J132">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -18981,28 +19395,28 @@
         <v>116</v>
       </c>
       <c r="D133">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E133">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F133">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G133" s="1">
-        <v>80.95</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H133" s="1">
-        <v>14.29</v>
+        <v>18.6</v>
       </c>
       <c r="I133" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -19031,7 +19445,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -19057,22 +19471,22 @@
         <v>31</v>
       </c>
       <c r="F135">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G135" s="1">
         <v>70.45</v>
       </c>
       <c r="H135" s="1">
-        <v>27.27</v>
+        <v>29.55</v>
       </c>
       <c r="I135" s="2">
         <v>6.3</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -19101,7 +19515,7 @@
         <v>25.81</v>
       </c>
       <c r="I136" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -19124,19 +19538,19 @@
         <v>35</v>
       </c>
       <c r="E137">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F137">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G137" s="1">
-        <v>82.86</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H137" s="1">
-        <v>17.14</v>
+        <v>25.71</v>
       </c>
       <c r="I137" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -19159,16 +19573,16 @@
         <v>21</v>
       </c>
       <c r="E138">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="1">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H138" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I138" s="2">
         <v>6.7</v>
@@ -19206,7 +19620,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J139">
         <v>2</v>
@@ -19241,7 +19655,7 @@
         <v>16.67</v>
       </c>
       <c r="I140" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -19276,7 +19690,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J141">
         <v>10</v>
@@ -19302,22 +19716,22 @@
         <v>32</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G142" s="1">
         <v>94.12</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="I142" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -19331,28 +19745,28 @@
         <v>121</v>
       </c>
       <c r="D143">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E143">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>95.12</v>
+        <v>92.5</v>
       </c>
       <c r="H143" s="1">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I143" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -19369,25 +19783,25 @@
         <v>36</v>
       </c>
       <c r="E144">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G144" s="1">
-        <v>97.22</v>
+        <v>88.89</v>
       </c>
       <c r="H144" s="1">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="I144" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -19404,25 +19818,25 @@
         <v>35</v>
       </c>
       <c r="E145">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K145" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -19451,7 +19865,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -19486,7 +19900,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -19579,25 +19993,25 @@
         <v>19</v>
       </c>
       <c r="E150">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F150">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G150" s="1">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="H150" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I150" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J150">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -19719,19 +20133,19 @@
         <v>32</v>
       </c>
       <c r="E154">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H154" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I154" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -19766,7 +20180,7 @@
         <v>2.44</v>
       </c>
       <c r="I155" s="2">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -19789,25 +20203,25 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F156">
         <v>1</v>
       </c>
       <c r="G156" s="1">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H156" s="1">
         <v>2.56</v>
       </c>
       <c r="I156" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -19821,22 +20235,22 @@
         <v>113</v>
       </c>
       <c r="D157">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E157">
         <v>28</v>
       </c>
       <c r="F157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G157" s="1">
-        <v>87.5</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H157" s="1">
-        <v>12.5</v>
+        <v>9.68</v>
       </c>
       <c r="I157" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -19859,19 +20273,19 @@
         <v>39</v>
       </c>
       <c r="E158">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G158" s="1">
-        <v>94.87</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H158" s="1">
-        <v>2.56</v>
+        <v>10.26</v>
       </c>
       <c r="I158" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J158">
         <v>1</v>
@@ -19906,7 +20320,7 @@
         <v>0</v>
       </c>
       <c r="I159" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -19941,7 +20355,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -19964,19 +20378,19 @@
         <v>15</v>
       </c>
       <c r="E161">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G161" s="1">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H161" s="1">
-        <v>20</v>
+        <v>26.67</v>
       </c>
       <c r="I161" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J161">
         <v>1</v>
@@ -19999,19 +20413,19 @@
         <v>21</v>
       </c>
       <c r="E162">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G162" s="1">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H162" s="1">
-        <v>9.52</v>
+        <v>0</v>
       </c>
       <c r="I162" s="2">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="J162">
         <v>3</v>
@@ -20034,19 +20448,19 @@
         <v>32</v>
       </c>
       <c r="E163">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F163">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G163" s="1">
-        <v>78.13</v>
+        <v>68.75</v>
       </c>
       <c r="H163" s="1">
-        <v>21.88</v>
+        <v>31.25</v>
       </c>
       <c r="I163" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -20069,19 +20483,19 @@
         <v>41</v>
       </c>
       <c r="E164">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F164">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G164" s="1">
-        <v>70.73</v>
+        <v>51.22</v>
       </c>
       <c r="H164" s="1">
-        <v>29.27</v>
+        <v>48.78</v>
       </c>
       <c r="I164" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -20104,19 +20518,19 @@
         <v>39</v>
       </c>
       <c r="E165">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F165">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G165" s="1">
-        <v>74.36</v>
+        <v>61.54</v>
       </c>
       <c r="H165" s="1">
-        <v>25.64</v>
+        <v>38.46</v>
       </c>
       <c r="I165" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -20136,28 +20550,28 @@
         <v>119</v>
       </c>
       <c r="D166">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E166">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G166" s="1">
-        <v>37.5</v>
+        <v>58.06</v>
       </c>
       <c r="H166" s="1">
-        <v>0</v>
+        <v>41.94</v>
       </c>
       <c r="I166" s="2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="J166">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -20186,7 +20600,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -20221,7 +20635,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -20244,19 +20658,19 @@
         <v>43</v>
       </c>
       <c r="E169">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G169" s="1">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H169" s="1">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="I169" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -20276,22 +20690,22 @@
         <v>122</v>
       </c>
       <c r="D170">
+        <v>43</v>
+      </c>
+      <c r="E170">
         <v>42</v>
-      </c>
-      <c r="E170">
-        <v>41</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170" s="1">
-        <v>97.62</v>
+        <v>97.67</v>
       </c>
       <c r="H170" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="I170" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -20396,7 +20810,7 @@
         <v>0</v>
       </c>
       <c r="I173" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J173">
         <v>11</v>
@@ -20416,22 +20830,22 @@
         <v>108</v>
       </c>
       <c r="D174">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E174">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G174" s="1">
-        <v>87.18000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="H174" s="1">
-        <v>12.82</v>
+        <v>17.5</v>
       </c>
       <c r="I174" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -20454,16 +20868,16 @@
         <v>26</v>
       </c>
       <c r="E175">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F175">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G175" s="1">
-        <v>57.69</v>
+        <v>61.54</v>
       </c>
       <c r="H175" s="1">
-        <v>42.31</v>
+        <v>38.46</v>
       </c>
       <c r="I175" s="2">
         <v>6.7</v>
@@ -20501,7 +20915,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J176">
         <v>9</v>
@@ -20536,7 +20950,7 @@
         <v>0</v>
       </c>
       <c r="I177" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J177">
         <v>1</v>
@@ -20571,7 +20985,7 @@
         <v>18.75</v>
       </c>
       <c r="I178" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -20594,19 +21008,19 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F179">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G179" s="1">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H179" s="1">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="I179" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -20626,7 +21040,7 @@
         <v>120</v>
       </c>
       <c r="D180">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E180">
         <v>23</v>
@@ -20635,19 +21049,19 @@
         <v>7</v>
       </c>
       <c r="G180" s="1">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H180" s="1">
-        <v>22.58</v>
+        <v>23.33</v>
       </c>
       <c r="I180" s="2">
         <v>7.8</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -20696,22 +21110,22 @@
         <v>117</v>
       </c>
       <c r="D182">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E182">
         <v>26</v>
       </c>
       <c r="F182">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G182" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H182" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I182" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -20766,16 +21180,16 @@
         <v>117</v>
       </c>
       <c r="D184">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E184">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184" s="1">
-        <v>78.05</v>
+        <v>77.5</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -20787,7 +21201,7 @@
         <v>9</v>
       </c>
       <c r="K184" s="1">
-        <v>21.95</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -20941,28 +21355,28 @@
         <v>122</v>
       </c>
       <c r="D189">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E189">
         <v>27</v>
       </c>
       <c r="F189">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G189" s="1">
-        <v>65.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H189" s="1">
-        <v>21.95</v>
+        <v>20</v>
       </c>
       <c r="I189" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J189">
         <v>5</v>
       </c>
       <c r="K189" s="1">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -21096,7 +21510,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -21131,7 +21545,7 @@
         <v>0</v>
       </c>
       <c r="I194" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J194">
         <v>6</v>
@@ -21151,28 +21565,28 @@
         <v>100</v>
       </c>
       <c r="D195">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E195">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G195" s="1">
-        <v>86.84</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H195" s="1">
-        <v>10.53</v>
+        <v>7.69</v>
       </c>
       <c r="I195" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J195">
         <v>1</v>
       </c>
       <c r="K195" s="1">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -21189,19 +21603,19 @@
         <v>26</v>
       </c>
       <c r="E196">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F196">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G196" s="1">
-        <v>65.38</v>
+        <v>84.62</v>
       </c>
       <c r="H196" s="1">
-        <v>34.62</v>
+        <v>15.38</v>
       </c>
       <c r="I196" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -21236,7 +21650,7 @@
         <v>0</v>
       </c>
       <c r="I197" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -21271,7 +21685,7 @@
         <v>0</v>
       </c>
       <c r="I198" s="2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J198">
         <v>0</v>
@@ -21306,7 +21720,7 @@
         <v>0</v>
       </c>
       <c r="I199" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -21341,7 +21755,7 @@
         <v>0</v>
       </c>
       <c r="I200" s="2">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -21364,19 +21778,19 @@
         <v>45</v>
       </c>
       <c r="E201">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F201">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G201" s="1">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="H201" s="1">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="I201" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -21411,7 +21825,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J202">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -8003,7 +8003,7 @@
         <v>15.79</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -8376,16 +8376,16 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>84.44</v>
+        <v>86.67</v>
       </c>
       <c r="H15" s="1">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="I15" s="2">
         <v>6.8</v>
@@ -9020,16 +9020,19 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F34">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -9052,16 +9055,19 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I35" s="2">
+        <v>8.1</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -9084,16 +9090,19 @@
         <v>26</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I36" s="2">
+        <v>6.1</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -9151,16 +9160,19 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H38" s="1">
-        <v>73.68000000000001</v>
+        <v>15.79</v>
+      </c>
+      <c r="I38" s="2">
+        <v>7.7</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -9183,16 +9195,19 @@
         <v>34</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H39" s="1">
-        <v>82.34999999999999</v>
+        <v>17.65</v>
+      </c>
+      <c r="I39" s="2">
+        <v>7.4</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -9460,16 +9475,19 @@
         <v>44</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F47">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H47" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I47" s="2">
+        <v>8.5</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -9699,16 +9717,19 @@
         <v>34</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F54">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H54" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I54" s="2">
+        <v>8.1</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -9731,16 +9752,19 @@
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F55">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>86.67</v>
       </c>
       <c r="H55" s="1">
-        <v>100</v>
+        <v>13.33</v>
+      </c>
+      <c r="I55" s="2">
+        <v>7.6</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -9763,16 +9787,19 @@
         <v>40</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F56">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H56" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I56" s="2">
+        <v>7.9</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -9795,16 +9822,19 @@
         <v>44</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F57">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H57" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I57" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -9827,16 +9857,19 @@
         <v>43</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F58">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="H58" s="1">
-        <v>100</v>
+        <v>13.95</v>
+      </c>
+      <c r="I58" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -9859,16 +9892,19 @@
         <v>43</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F59">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H59" s="1">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I59" s="2">
+        <v>7.8</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -10066,16 +10102,19 @@
         <v>40</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F65">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H65" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I65" s="2">
+        <v>6.3</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -10098,16 +10137,19 @@
         <v>44</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F66">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="H66" s="1">
-        <v>100</v>
+        <v>15.91</v>
+      </c>
+      <c r="I66" s="2">
+        <v>7.2</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -10130,16 +10172,19 @@
         <v>43</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F67">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>100</v>
+        <v>23.26</v>
+      </c>
+      <c r="I67" s="2">
+        <v>6.7</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -10162,16 +10207,19 @@
         <v>43</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F68">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H68" s="1">
-        <v>97.67</v>
+        <v>23.26</v>
+      </c>
+      <c r="I68" s="2">
+        <v>6.4</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -10194,16 +10242,19 @@
         <v>34</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F69">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H69" s="1">
-        <v>97.06</v>
+        <v>32.35</v>
+      </c>
+      <c r="I69" s="2">
+        <v>6.7</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -10226,16 +10277,19 @@
         <v>34</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F70">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H70" s="1">
-        <v>88.23999999999999</v>
+        <v>38.24</v>
+      </c>
+      <c r="I70" s="2">
+        <v>8.5</v>
       </c>
       <c r="J70">
         <v>4</v>
@@ -10258,16 +10312,19 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F71">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H71" s="1">
-        <v>89.47</v>
+        <v>15.79</v>
+      </c>
+      <c r="I71" s="2">
+        <v>8.1</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -10290,16 +10347,19 @@
         <v>32</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F72">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H72" s="1">
-        <v>93.75</v>
+        <v>12.5</v>
+      </c>
+      <c r="I72" s="2">
+        <v>8.9</v>
       </c>
       <c r="J72">
         <v>2</v>
@@ -10322,16 +10382,19 @@
         <v>26</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F73">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H73" s="1">
-        <v>65.38</v>
+        <v>15.38</v>
+      </c>
+      <c r="I73" s="2">
+        <v>7.7</v>
       </c>
       <c r="J73">
         <v>9</v>
@@ -10354,16 +10417,19 @@
         <v>33</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F74">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H74" s="1">
-        <v>81.81999999999999</v>
+        <v>9.09</v>
+      </c>
+      <c r="I74" s="2">
+        <v>9.5</v>
       </c>
       <c r="J74">
         <v>6</v>
@@ -10931,16 +10997,19 @@
         <v>36</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F91">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H91" s="1">
-        <v>86.11</v>
+        <v>2.78</v>
+      </c>
+      <c r="I91" s="2">
+        <v>7.3</v>
       </c>
       <c r="J91">
         <v>5</v>
@@ -10998,16 +11067,19 @@
         <v>30</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F93">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G93" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H93" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I93" s="2">
+        <v>7</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -11030,16 +11102,19 @@
         <v>32</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F94">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I94" s="2">
+        <v>9.5</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -11097,16 +11172,19 @@
         <v>18</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F96">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G96" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H96" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I96" s="2">
+        <v>7.4</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -11129,16 +11207,19 @@
         <v>41</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F97">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H97" s="1">
-        <v>87.8</v>
+        <v>0</v>
+      </c>
+      <c r="I97" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J97">
         <v>5</v>
@@ -12208,16 +12289,19 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F128">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>100</v>
+        <v>32.35</v>
+      </c>
+      <c r="I128" s="2">
+        <v>6.4</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -12240,19 +12324,19 @@
         <v>30</v>
       </c>
       <c r="E129">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F129">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G129" s="1">
-        <v>56.67</v>
+        <v>60</v>
       </c>
       <c r="H129" s="1">
-        <v>43.33</v>
+        <v>40</v>
       </c>
       <c r="I129" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -12287,7 +12371,7 @@
         <v>35</v>
       </c>
       <c r="I130" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -12322,7 +12406,7 @@
         <v>13.64</v>
       </c>
       <c r="I131" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -12345,16 +12429,19 @@
         <v>43</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F132">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G132" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H132" s="1">
-        <v>100</v>
+        <v>25.58</v>
+      </c>
+      <c r="I132" s="2">
+        <v>7.1</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -12377,16 +12464,19 @@
         <v>43</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F133">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G133" s="1">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I133" s="2">
+        <v>7</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -12409,16 +12499,16 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F134">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G134" s="1">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H134" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I134" s="2">
         <v>8</v>
@@ -12444,16 +12534,19 @@
         <v>44</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F135">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="G135" s="1">
-        <v>0</v>
+        <v>79.55</v>
       </c>
       <c r="H135" s="1">
-        <v>100</v>
+        <v>20.45</v>
+      </c>
+      <c r="I135" s="2">
+        <v>7.1</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -13103,7 +13196,7 @@
         <v>3.13</v>
       </c>
       <c r="I154" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -13686,16 +13779,19 @@
         <v>21</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F171">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G171" s="1">
-        <v>0</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H171" s="1">
-        <v>100</v>
+        <v>4.76</v>
+      </c>
+      <c r="I171" s="2">
+        <v>8</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -13718,16 +13814,19 @@
         <v>39</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F172">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>51.28</v>
       </c>
       <c r="H172" s="1">
-        <v>56.41</v>
+        <v>5.13</v>
+      </c>
+      <c r="I172" s="2">
+        <v>7.8</v>
       </c>
       <c r="J172">
         <v>17</v>
@@ -13995,16 +14094,19 @@
         <v>30</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F180">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G180" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H180" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I180" s="2">
+        <v>7.9</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -14347,16 +14449,19 @@
         <v>26</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F191">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G191" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H191" s="1">
-        <v>84.62</v>
+        <v>23.08</v>
+      </c>
+      <c r="I191" s="2">
+        <v>6.8</v>
       </c>
       <c r="J191">
         <v>4</v>
@@ -14379,16 +14484,19 @@
         <v>15</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F192">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G192" s="1">
-        <v>0</v>
+        <v>46.67</v>
       </c>
       <c r="H192" s="1">
-        <v>100</v>
+        <v>53.33</v>
+      </c>
+      <c r="I192" s="2">
+        <v>6.1</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -14691,19 +14799,19 @@
         <v>45</v>
       </c>
       <c r="E201">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F201">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G201" s="1">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="H201" s="1">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="I201" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -15268,16 +15376,16 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="H15" s="1">
-        <v>8.890000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="I15" s="2">
         <v>7.4</v>
@@ -15933,16 +16041,16 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I34" s="2">
         <v>8.6</v>
@@ -15968,19 +16076,19 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>90.48</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>9.52</v>
+        <v>14.29</v>
       </c>
       <c r="I35" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -16003,19 +16111,19 @@
         <v>26</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
-        <v>80.77</v>
+        <v>61.54</v>
       </c>
       <c r="H36" s="1">
-        <v>19.23</v>
+        <v>38.46</v>
       </c>
       <c r="I36" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -16073,19 +16181,19 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" s="1">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="H38" s="1">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="I38" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -16108,19 +16216,19 @@
         <v>34</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1">
-        <v>50</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="I39" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -16633,19 +16741,19 @@
         <v>34</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H54" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I54" s="2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -16680,7 +16788,7 @@
         <v>13.33</v>
       </c>
       <c r="I55" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -16703,19 +16811,19 @@
         <v>40</v>
       </c>
       <c r="E56">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G56" s="1">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="H56" s="1">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="I56" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -16750,7 +16858,7 @@
         <v>4.55</v>
       </c>
       <c r="I57" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -16785,7 +16893,7 @@
         <v>13.95</v>
       </c>
       <c r="I58" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -16808,19 +16916,19 @@
         <v>43</v>
       </c>
       <c r="E59">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F59">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G59" s="1">
-        <v>83.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H59" s="1">
-        <v>16.28</v>
+        <v>20.93</v>
       </c>
       <c r="I59" s="2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -17018,19 +17126,19 @@
         <v>40</v>
       </c>
       <c r="E65">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G65" s="1">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="H65" s="1">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I65" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -17065,7 +17173,7 @@
         <v>15.91</v>
       </c>
       <c r="I66" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -17088,19 +17196,19 @@
         <v>43</v>
       </c>
       <c r="E67">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F67">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G67" s="1">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>20.93</v>
+        <v>23.26</v>
       </c>
       <c r="I67" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -17135,7 +17243,7 @@
         <v>23.26</v>
       </c>
       <c r="I68" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -17158,19 +17266,19 @@
         <v>34</v>
       </c>
       <c r="E69">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F69">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G69" s="1">
-        <v>70.59</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H69" s="1">
-        <v>26.47</v>
+        <v>32.35</v>
       </c>
       <c r="I69" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -17205,7 +17313,7 @@
         <v>2.94</v>
       </c>
       <c r="I70" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J70">
         <v>4</v>
@@ -17263,19 +17371,19 @@
         <v>32</v>
       </c>
       <c r="E72">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H72" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I72" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J72">
         <v>2</v>
@@ -17345,7 +17453,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J74">
         <v>6</v>
@@ -17928,19 +18036,19 @@
         <v>36</v>
       </c>
       <c r="E91">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" s="1">
-        <v>86.11</v>
+        <v>83.33</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I91" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J91">
         <v>5</v>
@@ -17998,19 +18106,19 @@
         <v>30</v>
       </c>
       <c r="E93">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93" s="1">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="H93" s="1">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="I93" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -18033,19 +18141,19 @@
         <v>32</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F94">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -18103,19 +18211,19 @@
         <v>18</v>
       </c>
       <c r="E96">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G96" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H96" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I96" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -18150,7 +18258,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J97">
         <v>5</v>
@@ -19223,19 +19331,19 @@
         <v>34</v>
       </c>
       <c r="E128">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F128">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G128" s="1">
-        <v>73.53</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H128" s="1">
-        <v>26.47</v>
+        <v>32.35</v>
       </c>
       <c r="I128" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -19293,19 +19401,19 @@
         <v>40</v>
       </c>
       <c r="E130">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F130">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G130" s="1">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="H130" s="1">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="I130" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -19363,19 +19471,19 @@
         <v>43</v>
       </c>
       <c r="E132">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F132">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G132" s="1">
-        <v>81.40000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="H132" s="1">
-        <v>18.6</v>
+        <v>25.58</v>
       </c>
       <c r="I132" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -19398,19 +19506,19 @@
         <v>43</v>
       </c>
       <c r="E133">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F133">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G133" s="1">
-        <v>81.40000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>18.6</v>
+        <v>20.93</v>
       </c>
       <c r="I133" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -19468,19 +19576,19 @@
         <v>44</v>
       </c>
       <c r="E135">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F135">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G135" s="1">
-        <v>70.45</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H135" s="1">
-        <v>29.55</v>
+        <v>18.18</v>
       </c>
       <c r="I135" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -20133,16 +20241,16 @@
         <v>32</v>
       </c>
       <c r="E154">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" s="1">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H154" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I154" s="2">
         <v>8.5</v>
@@ -20728,19 +20836,19 @@
         <v>21</v>
       </c>
       <c r="E171">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F171">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G171" s="1">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H171" s="1">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="I171" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -20763,19 +20871,19 @@
         <v>39</v>
       </c>
       <c r="E172">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G172" s="1">
-        <v>56.41</v>
+        <v>51.28</v>
       </c>
       <c r="H172" s="1">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="I172" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J172">
         <v>17</v>
@@ -21043,19 +21151,19 @@
         <v>30</v>
       </c>
       <c r="E180">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F180">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G180" s="1">
-        <v>76.67</v>
+        <v>86.67</v>
       </c>
       <c r="H180" s="1">
-        <v>23.33</v>
+        <v>13.33</v>
       </c>
       <c r="I180" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -21428,19 +21536,19 @@
         <v>26</v>
       </c>
       <c r="E191">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G191" s="1">
-        <v>84.62</v>
+        <v>61.54</v>
       </c>
       <c r="H191" s="1">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="I191" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J191">
         <v>4</v>
@@ -21475,7 +21583,7 @@
         <v>53.33</v>
       </c>
       <c r="I192" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -21778,16 +21886,16 @@
         <v>45</v>
       </c>
       <c r="E201">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G201" s="1">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="H201" s="1">
-        <v>11.11</v>
+        <v>13.33</v>
       </c>
       <c r="I201" s="2">
         <v>7.4</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -8615,16 +8615,19 @@
         <v>32</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -8647,16 +8650,19 @@
         <v>41</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F23">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>97.56</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>2.44</v>
+      </c>
+      <c r="I23" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -8679,16 +8685,19 @@
         <v>39</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F24">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>97.44</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>2.56</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -8813,16 +8822,19 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>85.37</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>14.63</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.4</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -8845,19 +8857,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G29" s="1">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H29" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I29" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -9440,19 +9452,19 @@
         <v>32</v>
       </c>
       <c r="E46">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46" s="1">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H46" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I46" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -11417,19 +11429,19 @@
         <v>37</v>
       </c>
       <c r="E103">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G103" s="1">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H103" s="1">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="I103" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -11452,19 +11464,19 @@
         <v>37</v>
       </c>
       <c r="E104">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F104">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>81.08</v>
+        <v>97.3</v>
       </c>
       <c r="H104" s="1">
-        <v>18.92</v>
+        <v>2.7</v>
       </c>
       <c r="I104" s="2">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -11487,19 +11499,19 @@
         <v>40</v>
       </c>
       <c r="E105">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F105">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G105" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H105" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I105" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -15633,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -15656,19 +15668,19 @@
         <v>41</v>
       </c>
       <c r="E23">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I23" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -15703,7 +15715,7 @@
         <v>2.56</v>
       </c>
       <c r="I24" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -15831,16 +15843,16 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="1">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H28" s="1">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="I28" s="2">
         <v>7.8</v>
@@ -15866,19 +15878,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" s="1">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="H29" s="1">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -16461,19 +16473,19 @@
         <v>32</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>96.88</v>
+        <v>93.75</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I46" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -18468,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -18503,7 +18515,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -18538,7 +18550,7 @@
         <v>20</v>
       </c>
       <c r="I105" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J105">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -8516,16 +8516,19 @@
         <v>32</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -8548,16 +8551,19 @@
         <v>32</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -8720,16 +8726,19 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>9.68</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -9312,16 +9321,16 @@
         <v>35</v>
       </c>
       <c r="E42">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>5.71</v>
+        <v>2.86</v>
       </c>
       <c r="I42" s="2">
         <v>7.8</v>
@@ -10464,16 +10473,19 @@
         <v>15</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F75">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="H75" s="1">
-        <v>100</v>
+        <v>46.67</v>
+      </c>
+      <c r="I75" s="2">
+        <v>6.3</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -11569,19 +11581,19 @@
         <v>41</v>
       </c>
       <c r="E107">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>70.73</v>
+        <v>75.61</v>
       </c>
       <c r="H107" s="1">
-        <v>9.76</v>
+        <v>4.88</v>
       </c>
       <c r="I107" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J107">
         <v>8</v>
@@ -11604,16 +11616,16 @@
         <v>40</v>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H108" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I108" s="2">
         <v>6.2</v>
@@ -11639,19 +11651,19 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G109" s="1">
-        <v>47.22</v>
+        <v>52.78</v>
       </c>
       <c r="H109" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I109" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J109">
         <v>13</v>
@@ -12546,16 +12558,16 @@
         <v>44</v>
       </c>
       <c r="E135">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F135">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G135" s="1">
-        <v>79.55</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H135" s="1">
-        <v>20.45</v>
+        <v>18.18</v>
       </c>
       <c r="I135" s="2">
         <v>7.1</v>
@@ -13861,19 +13873,19 @@
         <v>39</v>
       </c>
       <c r="E173">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F173">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G173" s="1">
-        <v>56.41</v>
+        <v>69.23</v>
       </c>
       <c r="H173" s="1">
-        <v>15.38</v>
+        <v>2.56</v>
       </c>
       <c r="I173" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J173">
         <v>11</v>
@@ -14141,16 +14153,19 @@
         <v>34</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F181">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H181" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I181" s="2">
+        <v>7.4</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -14237,16 +14252,19 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F184">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G184" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H184" s="1">
-        <v>77.5</v>
+        <v>72.5</v>
+      </c>
+      <c r="I184" s="2">
+        <v>6.5</v>
       </c>
       <c r="J184">
         <v>9</v>
@@ -14269,16 +14287,19 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F185">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H185" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I185" s="2">
+        <v>7.2</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -14301,16 +14322,19 @@
         <v>44</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F186">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G186" s="1">
-        <v>0</v>
+        <v>86.36</v>
       </c>
       <c r="H186" s="1">
-        <v>100</v>
+        <v>13.64</v>
+      </c>
+      <c r="I186" s="2">
+        <v>7</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -15540,7 +15564,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="I19" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -15563,19 +15587,19 @@
         <v>32</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="H20" s="1">
-        <v>21.88</v>
+        <v>15.63</v>
       </c>
       <c r="I20" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -15738,19 +15762,19 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>87.09999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>12.9</v>
+        <v>9.68</v>
       </c>
       <c r="I25" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -17488,16 +17512,16 @@
         <v>15</v>
       </c>
       <c r="E75">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G75" s="1">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="H75" s="1">
-        <v>40</v>
+        <v>46.67</v>
       </c>
       <c r="I75" s="2">
         <v>6.4</v>
@@ -18608,19 +18632,19 @@
         <v>41</v>
       </c>
       <c r="E107">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" s="1">
-        <v>78.05</v>
+        <v>75.61</v>
       </c>
       <c r="H107" s="1">
-        <v>2.44</v>
+        <v>4.88</v>
       </c>
       <c r="I107" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J107">
         <v>8</v>
@@ -18678,19 +18702,19 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F109">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G109" s="1">
-        <v>58.33</v>
+        <v>52.78</v>
       </c>
       <c r="H109" s="1">
-        <v>5.56</v>
+        <v>11.11</v>
       </c>
       <c r="I109" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J109">
         <v>13</v>
@@ -20930,7 +20954,7 @@
         <v>0</v>
       </c>
       <c r="I173" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J173">
         <v>11</v>
@@ -21198,19 +21222,19 @@
         <v>34</v>
       </c>
       <c r="E181">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G181" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H181" s="1">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="I181" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -21338,16 +21362,16 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G185" s="1">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H185" s="1">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="I185" s="2">
         <v>7.3</v>
@@ -21373,19 +21397,19 @@
         <v>44</v>
       </c>
       <c r="E186">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F186">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G186" s="1">
-        <v>93.18000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="H186" s="1">
-        <v>6.82</v>
+        <v>13.64</v>
       </c>
       <c r="I186" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J186">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -9960,7 +9960,7 @@
         <v>43.59</v>
       </c>
       <c r="I60" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -10065,7 +10065,7 @@
         <v>20</v>
       </c>
       <c r="I63" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -10088,16 +10088,16 @@
         <v>36</v>
       </c>
       <c r="E64">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F64">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G64" s="1">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H64" s="1">
-        <v>25</v>
+        <v>16.67</v>
       </c>
       <c r="I64" s="2">
         <v>6.3</v>
@@ -10788,7 +10788,7 @@
         <v>29.41</v>
       </c>
       <c r="I84" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -11441,19 +11441,19 @@
         <v>37</v>
       </c>
       <c r="E103">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F103">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H103" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -11476,19 +11476,19 @@
         <v>37</v>
       </c>
       <c r="E104">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H104" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -11756,16 +11756,19 @@
         <v>39</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F112">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H112" s="1">
-        <v>92.31</v>
+        <v>0</v>
+      </c>
+      <c r="I112" s="2">
+        <v>7.8</v>
       </c>
       <c r="J112">
         <v>3</v>
@@ -12803,19 +12806,19 @@
         <v>34</v>
       </c>
       <c r="E142">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" s="1">
-        <v>91.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H142" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
       <c r="I142" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -12838,19 +12841,19 @@
         <v>40</v>
       </c>
       <c r="E143">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F143">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="H143" s="1">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="I143" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -12873,19 +12876,19 @@
         <v>36</v>
       </c>
       <c r="E144">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F144">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G144" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H144" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I144" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -13885,7 +13888,7 @@
         <v>2.56</v>
       </c>
       <c r="I173" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J173">
         <v>11</v>
@@ -14188,16 +14191,19 @@
         <v>30</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F182">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G182" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H182" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I182" s="2">
+        <v>6.6</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -14220,16 +14226,19 @@
         <v>41</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F183">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G183" s="1">
-        <v>0</v>
+        <v>78.05</v>
       </c>
       <c r="H183" s="1">
-        <v>92.68000000000001</v>
+        <v>14.63</v>
+      </c>
+      <c r="I183" s="2">
+        <v>6.4</v>
       </c>
       <c r="J183">
         <v>3</v>
@@ -14252,19 +14261,19 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F184">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G184" s="1">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="H184" s="1">
-        <v>72.5</v>
+        <v>2.5</v>
       </c>
       <c r="I184" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J184">
         <v>9</v>
@@ -14357,16 +14366,19 @@
         <v>34</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F187">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H187" s="1">
-        <v>88.23999999999999</v>
+        <v>17.65</v>
+      </c>
+      <c r="I187" s="2">
+        <v>6.8</v>
       </c>
       <c r="J187">
         <v>4</v>
@@ -14389,16 +14401,19 @@
         <v>41</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F188">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>95.12</v>
+        <v>29.27</v>
+      </c>
+      <c r="I188" s="2">
+        <v>6.2</v>
       </c>
       <c r="J188">
         <v>2</v>
@@ -14453,16 +14468,19 @@
         <v>36</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F190">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G190" s="1">
-        <v>0</v>
+        <v>61.11</v>
       </c>
       <c r="H190" s="1">
-        <v>97.22</v>
+        <v>36.11</v>
+      </c>
+      <c r="I190" s="2">
+        <v>6.4</v>
       </c>
       <c r="J190">
         <v>1</v>
@@ -16987,16 +17005,16 @@
         <v>39</v>
       </c>
       <c r="E60">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F60">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G60" s="1">
-        <v>58.97</v>
+        <v>56.41</v>
       </c>
       <c r="H60" s="1">
-        <v>41.03</v>
+        <v>43.59</v>
       </c>
       <c r="I60" s="2">
         <v>6.2</v>
@@ -17827,16 +17845,16 @@
         <v>34</v>
       </c>
       <c r="E84">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F84">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G84" s="1">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="H84" s="1">
-        <v>23.53</v>
+        <v>29.41</v>
       </c>
       <c r="I84" s="2">
         <v>6.9</v>
@@ -18819,7 +18837,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J112">
         <v>3</v>
@@ -20942,16 +20960,16 @@
         <v>39</v>
       </c>
       <c r="E173">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" s="1">
-        <v>71.79000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="H173" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I173" s="2">
         <v>9.1</v>
@@ -21257,19 +21275,19 @@
         <v>30</v>
       </c>
       <c r="E182">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F182">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G182" s="1">
-        <v>86.67</v>
+        <v>83.33</v>
       </c>
       <c r="H182" s="1">
-        <v>13.33</v>
+        <v>16.67</v>
       </c>
       <c r="I182" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -21292,16 +21310,16 @@
         <v>41</v>
       </c>
       <c r="E183">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G183" s="1">
-        <v>80.48999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="H183" s="1">
-        <v>12.2</v>
+        <v>14.63</v>
       </c>
       <c r="I183" s="2">
         <v>6.6</v>
@@ -21327,19 +21345,19 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" s="1">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="H184" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I184" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J184">
         <v>9</v>
@@ -21432,19 +21450,19 @@
         <v>34</v>
       </c>
       <c r="E187">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F187">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="H187" s="1">
-        <v>11.76</v>
+        <v>17.65</v>
       </c>
       <c r="I187" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J187">
         <v>4</v>
@@ -21467,16 +21485,16 @@
         <v>41</v>
       </c>
       <c r="E188">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F188">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G188" s="1">
-        <v>75.61</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>19.51</v>
+        <v>29.27</v>
       </c>
       <c r="I188" s="2">
         <v>6.4</v>
@@ -21537,19 +21555,19 @@
         <v>36</v>
       </c>
       <c r="E190">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G190" s="1">
-        <v>75</v>
+        <v>61.11</v>
       </c>
       <c r="H190" s="1">
-        <v>22.22</v>
+        <v>36.11</v>
       </c>
       <c r="I190" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J190">
         <v>1</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -9531,16 +9531,19 @@
         <v>36</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F48">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H48" s="1">
-        <v>91.67</v>
+        <v>8.33</v>
+      </c>
+      <c r="I48" s="2">
+        <v>6.8</v>
       </c>
       <c r="J48">
         <v>3</v>
@@ -10508,16 +10511,19 @@
         <v>35</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F76">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H76" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I76" s="2">
+        <v>7.6</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -10540,16 +10546,19 @@
         <v>21</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F77">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H77" s="1">
-        <v>100</v>
+        <v>38.1</v>
+      </c>
+      <c r="I77" s="2">
+        <v>6.5</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -10572,16 +10581,19 @@
         <v>37</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F78">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>78.38</v>
       </c>
       <c r="H78" s="1">
-        <v>100</v>
+        <v>21.62</v>
+      </c>
+      <c r="I78" s="2">
+        <v>7.4</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -10604,16 +10616,19 @@
         <v>32</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F79">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H79" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I79" s="2">
+        <v>8.1</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -13016,16 +13031,19 @@
         <v>26</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F148">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>0</v>
+        <v>11.54</v>
       </c>
       <c r="H148" s="1">
-        <v>26.92</v>
+        <v>15.38</v>
+      </c>
+      <c r="I148" s="2">
+        <v>5.6</v>
       </c>
       <c r="J148">
         <v>19</v>
@@ -13048,16 +13066,19 @@
         <v>26</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F149">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G149" s="1">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="H149" s="1">
-        <v>23.08</v>
+        <v>0</v>
+      </c>
+      <c r="I149" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J149">
         <v>20</v>
@@ -13115,16 +13136,19 @@
         <v>36</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F151">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>27.78</v>
       </c>
       <c r="H151" s="1">
-        <v>30.56</v>
+        <v>2.78</v>
+      </c>
+      <c r="I151" s="2">
+        <v>8.5</v>
       </c>
       <c r="J151">
         <v>25</v>
@@ -13147,16 +13171,19 @@
         <v>40</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F152">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H152" s="1">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="I152" s="2">
+        <v>9.6</v>
       </c>
       <c r="J152">
         <v>30</v>
@@ -13179,16 +13206,19 @@
         <v>18</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F153">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>44.44</v>
       </c>
       <c r="H153" s="1">
-        <v>50</v>
+        <v>5.56</v>
+      </c>
+      <c r="I153" s="2">
+        <v>6.4</v>
       </c>
       <c r="J153">
         <v>9</v>
@@ -14436,16 +14466,19 @@
         <v>40</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F189">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H189" s="1">
-        <v>87.5</v>
+        <v>27.5</v>
+      </c>
+      <c r="I189" s="2">
+        <v>6.2</v>
       </c>
       <c r="J189">
         <v>5</v>
@@ -16585,19 +16618,19 @@
         <v>36</v>
       </c>
       <c r="E48">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I48" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J48">
         <v>3</v>
@@ -17565,19 +17598,19 @@
         <v>35</v>
       </c>
       <c r="E76">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G76" s="1">
-        <v>88.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H76" s="1">
-        <v>11.43</v>
+        <v>14.29</v>
       </c>
       <c r="I76" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -17600,19 +17633,19 @@
         <v>21</v>
       </c>
       <c r="E77">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G77" s="1">
-        <v>80.95</v>
+        <v>61.9</v>
       </c>
       <c r="H77" s="1">
-        <v>19.05</v>
+        <v>38.1</v>
       </c>
       <c r="I77" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -17647,7 +17680,7 @@
         <v>21.62</v>
       </c>
       <c r="I78" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -17682,7 +17715,7 @@
         <v>15.63</v>
       </c>
       <c r="I79" s="2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -20085,19 +20118,19 @@
         <v>26</v>
       </c>
       <c r="E148">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>26.92</v>
+        <v>11.54</v>
       </c>
       <c r="H148" s="1">
-        <v>0</v>
+        <v>15.38</v>
       </c>
       <c r="I148" s="2">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="J148">
         <v>19</v>
@@ -20132,7 +20165,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J149">
         <v>20</v>
@@ -20190,19 +20223,19 @@
         <v>36</v>
       </c>
       <c r="E151">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" s="1">
-        <v>30.56</v>
+        <v>27.78</v>
       </c>
       <c r="H151" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I151" s="2">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="J151">
         <v>25</v>
@@ -20237,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="I152" s="2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J152">
         <v>30</v>
@@ -20260,19 +20293,19 @@
         <v>18</v>
       </c>
       <c r="E153">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" s="1">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="H153" s="1">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="I153" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J153">
         <v>9</v>
@@ -21520,19 +21553,19 @@
         <v>40</v>
       </c>
       <c r="E189">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F189">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G189" s="1">
-        <v>67.5</v>
+        <v>60</v>
       </c>
       <c r="H189" s="1">
-        <v>20</v>
+        <v>27.5</v>
       </c>
       <c r="I189" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J189">
         <v>5</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1394,25 +1394,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>89.47</v>
+        <v>92.11</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>7.89</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2062,22 +2062,22 @@
         <v>13</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37" s="1">
         <v>50</v>
       </c>
       <c r="H37" s="1">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="I37" s="2">
         <v>6.2</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2094,25 +2094,25 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G38" s="1">
-        <v>52.63</v>
+        <v>57.89</v>
       </c>
       <c r="H38" s="1">
-        <v>21.05</v>
+        <v>42.11</v>
       </c>
       <c r="I38" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2132,22 +2132,22 @@
         <v>17</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G39" s="1">
         <v>50</v>
       </c>
       <c r="H39" s="1">
-        <v>32.35</v>
+        <v>50</v>
       </c>
       <c r="I39" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2237,22 +2237,22 @@
         <v>34</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="1">
         <v>97.14</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="I42" s="2">
         <v>7.9</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2269,25 +2269,25 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I43" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2304,25 +2304,25 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G44" s="1">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>16.22</v>
       </c>
       <c r="I44" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J44">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>32.43</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2377,22 +2377,22 @@
         <v>31</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="1">
         <v>96.88</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I46" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2482,22 +2482,22 @@
         <v>38</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
         <v>97.44</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I49" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3144,13 +3144,13 @@
         <v>43</v>
       </c>
       <c r="E68">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68">
         <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H68" s="1">
         <v>23.26</v>
@@ -3159,10 +3159,10 @@
         <v>7.2</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3179,13 +3179,13 @@
         <v>34</v>
       </c>
       <c r="E69">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F69">
         <v>9</v>
       </c>
       <c r="G69" s="1">
-        <v>70.59</v>
+        <v>73.53</v>
       </c>
       <c r="H69" s="1">
         <v>26.47</v>
@@ -3194,10 +3194,10 @@
         <v>6.6</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3214,25 +3214,25 @@
         <v>34</v>
       </c>
       <c r="E70">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G70" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H70" s="1">
-        <v>2.94</v>
+        <v>11.76</v>
       </c>
       <c r="I70" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3249,25 +3249,25 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I71" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3287,22 +3287,22 @@
         <v>29</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72" s="1">
         <v>90.63</v>
       </c>
       <c r="H72" s="1">
-        <v>3.13</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I72" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3319,25 +3319,25 @@
         <v>26</v>
       </c>
       <c r="E73">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G73" s="1">
-        <v>65.38</v>
+        <v>76.92</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="I73" s="2">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="J73">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3354,25 +3354,25 @@
         <v>33</v>
       </c>
       <c r="E74">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G74" s="1">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H74" s="1">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="I74" s="2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3917,22 +3917,22 @@
         <v>23</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G90" s="1">
         <v>76.67</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>23.33</v>
       </c>
       <c r="I90" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J90">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3952,22 +3952,22 @@
         <v>31</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G91" s="1">
         <v>86.11</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>13.89</v>
       </c>
       <c r="I91" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -4512,22 +4512,22 @@
         <v>33</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G107" s="1">
         <v>80.48999999999999</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>19.51</v>
       </c>
       <c r="I107" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J107">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4547,22 +4547,22 @@
         <v>32</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G108" s="1">
         <v>80</v>
       </c>
       <c r="H108" s="1">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="I108" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J108">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4582,22 +4582,22 @@
         <v>23</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G109" s="1">
         <v>63.89</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>36.11</v>
       </c>
       <c r="I109" s="2">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="J109">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4687,22 +4687,22 @@
         <v>36</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G112" s="1">
         <v>92.31</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="I112" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -5104,19 +5104,19 @@
         <v>35</v>
       </c>
       <c r="E124">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F124">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G124" s="1">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H124" s="1">
-        <v>20</v>
+        <v>17.14</v>
       </c>
       <c r="I124" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -5839,25 +5839,25 @@
         <v>35</v>
       </c>
       <c r="E145">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J145">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -5944,25 +5944,25 @@
         <v>26</v>
       </c>
       <c r="E148">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G148" s="1">
-        <v>26.92</v>
+        <v>46.15</v>
       </c>
       <c r="H148" s="1">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="I148" s="2">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="J148">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5979,25 +5979,25 @@
         <v>26</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G149" s="1">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>38.46</v>
       </c>
       <c r="I149" s="2">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J149">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6049,25 +6049,25 @@
         <v>36</v>
       </c>
       <c r="E151">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G151" s="1">
-        <v>30.56</v>
+        <v>80.56</v>
       </c>
       <c r="H151" s="1">
-        <v>0</v>
+        <v>19.44</v>
       </c>
       <c r="I151" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J151">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6084,25 +6084,25 @@
         <v>40</v>
       </c>
       <c r="E152">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>25</v>
+        <v>77.5</v>
       </c>
       <c r="H152" s="1">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="I152" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J152">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -6119,25 +6119,25 @@
         <v>18</v>
       </c>
       <c r="E153">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G153" s="1">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="H153" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="I153" s="2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="J153">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6367,22 +6367,22 @@
         <v>26</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" s="1">
         <v>96.3</v>
       </c>
       <c r="H160" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I160" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -6402,22 +6402,22 @@
         <v>11</v>
       </c>
       <c r="F161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G161" s="1">
         <v>73.33</v>
       </c>
       <c r="H161" s="1">
-        <v>20</v>
+        <v>26.67</v>
       </c>
       <c r="I161" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6437,22 +6437,22 @@
         <v>16</v>
       </c>
       <c r="F162">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G162" s="1">
         <v>76.19</v>
       </c>
       <c r="H162" s="1">
-        <v>9.52</v>
+        <v>23.81</v>
       </c>
       <c r="I162" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -7172,22 +7172,22 @@
         <v>33</v>
       </c>
       <c r="F183">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G183" s="1">
         <v>80.48999999999999</v>
       </c>
       <c r="H183" s="1">
-        <v>12.2</v>
+        <v>19.51</v>
       </c>
       <c r="I183" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7204,25 +7204,25 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G184" s="1">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="H184" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I184" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7309,25 +7309,25 @@
         <v>34</v>
       </c>
       <c r="E187">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F187">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G187" s="1">
-        <v>76.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H187" s="1">
-        <v>11.76</v>
+        <v>14.71</v>
       </c>
       <c r="I187" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K187" s="1">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7347,22 +7347,22 @@
         <v>31</v>
       </c>
       <c r="F188">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G188" s="1">
         <v>75.61</v>
       </c>
       <c r="H188" s="1">
-        <v>19.51</v>
+        <v>24.39</v>
       </c>
       <c r="I188" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7379,25 +7379,25 @@
         <v>40</v>
       </c>
       <c r="E189">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F189">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G189" s="1">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="H189" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I189" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J189">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7417,22 +7417,22 @@
         <v>27</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G190" s="1">
         <v>75</v>
       </c>
       <c r="H190" s="1">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="I190" s="2">
         <v>6.1</v>
       </c>
       <c r="J190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7452,22 +7452,22 @@
         <v>22</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G191" s="1">
         <v>84.62</v>
       </c>
       <c r="H191" s="1">
-        <v>0</v>
+        <v>15.38</v>
       </c>
       <c r="I191" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J191">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -7554,25 +7554,25 @@
         <v>39</v>
       </c>
       <c r="E194">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G194" s="1">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H194" s="1">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="I194" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J194">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -7589,13 +7589,13 @@
         <v>39</v>
       </c>
       <c r="E195">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F195">
         <v>4</v>
       </c>
       <c r="G195" s="1">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H195" s="1">
         <v>10.26</v>
@@ -7604,10 +7604,10 @@
         <v>7.2</v>
       </c>
       <c r="J195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -8481,25 +8481,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="H18" s="1">
-        <v>7.89</v>
+        <v>13.16</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -9149,22 +9149,22 @@
         <v>17</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37" s="1">
         <v>65.38</v>
       </c>
       <c r="H37" s="1">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="I37" s="2">
         <v>7</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -9181,25 +9181,25 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="H38" s="1">
-        <v>15.79</v>
+        <v>36.84</v>
       </c>
       <c r="I38" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -9216,25 +9216,25 @@
         <v>34</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G39" s="1">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>17.65</v>
+        <v>32.35</v>
       </c>
       <c r="I39" s="2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -9324,22 +9324,22 @@
         <v>33</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
         <v>94.29000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>2.86</v>
+        <v>5.71</v>
       </c>
       <c r="I42" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -9356,25 +9356,25 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="1">
-        <v>52.38</v>
+        <v>90.48</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>9.52</v>
       </c>
       <c r="I43" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -9391,25 +9391,25 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F44">
+        <v>6</v>
+      </c>
+      <c r="G44" s="1">
+        <v>81.08</v>
+      </c>
+      <c r="H44" s="1">
+        <v>16.22</v>
+      </c>
+      <c r="I44" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J44">
         <v>1</v>
       </c>
-      <c r="G44" s="1">
-        <v>64.86</v>
-      </c>
-      <c r="H44" s="1">
+      <c r="K44" s="1">
         <v>2.7</v>
-      </c>
-      <c r="I44" s="2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J44">
-        <v>12</v>
-      </c>
-      <c r="K44" s="1">
-        <v>32.43</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -9461,25 +9461,25 @@
         <v>32</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H46" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
       <c r="I46" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -9569,22 +9569,22 @@
         <v>38</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
         <v>97.44</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I49" s="2">
         <v>6.5</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -10231,13 +10231,13 @@
         <v>43</v>
       </c>
       <c r="E68">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68">
         <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H68" s="1">
         <v>23.26</v>
@@ -10246,10 +10246,10 @@
         <v>6.4</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -10266,13 +10266,13 @@
         <v>34</v>
       </c>
       <c r="E69">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F69">
         <v>11</v>
       </c>
       <c r="G69" s="1">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H69" s="1">
         <v>32.35</v>
@@ -10281,10 +10281,10 @@
         <v>6.7</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10301,25 +10301,25 @@
         <v>34</v>
       </c>
       <c r="E70">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F70">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G70" s="1">
-        <v>50</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H70" s="1">
-        <v>38.24</v>
+        <v>17.65</v>
       </c>
       <c r="I70" s="2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -10336,25 +10336,25 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71" s="1">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H71" s="1">
-        <v>15.79</v>
+        <v>13.16</v>
       </c>
       <c r="I71" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -10371,25 +10371,25 @@
         <v>32</v>
       </c>
       <c r="E72">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G72" s="1">
-        <v>81.25</v>
+        <v>93.75</v>
       </c>
       <c r="H72" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I72" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -10406,25 +10406,25 @@
         <v>26</v>
       </c>
       <c r="E73">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G73" s="1">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="H73" s="1">
-        <v>15.38</v>
+        <v>34.62</v>
       </c>
       <c r="I73" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J73">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -10441,25 +10441,25 @@
         <v>33</v>
       </c>
       <c r="E74">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" s="1">
-        <v>72.73</v>
+        <v>87.88</v>
       </c>
       <c r="H74" s="1">
-        <v>9.09</v>
+        <v>12.12</v>
       </c>
       <c r="I74" s="2">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -11001,25 +11001,25 @@
         <v>30</v>
       </c>
       <c r="E90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G90" s="1">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="H90" s="1">
-        <v>13.33</v>
+        <v>33.33</v>
       </c>
       <c r="I90" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J90">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -11036,25 +11036,25 @@
         <v>36</v>
       </c>
       <c r="E91">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G91" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H91" s="1">
-        <v>2.78</v>
+        <v>11.11</v>
       </c>
       <c r="I91" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -11596,25 +11596,25 @@
         <v>41</v>
       </c>
       <c r="E107">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F107">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G107" s="1">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="H107" s="1">
-        <v>4.88</v>
+        <v>21.95</v>
       </c>
       <c r="I107" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J107">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -11634,22 +11634,22 @@
         <v>33</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G108" s="1">
         <v>82.5</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I108" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J108">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -11666,25 +11666,25 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F109">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G109" s="1">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="H109" s="1">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="I109" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J109">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -11771,25 +11771,25 @@
         <v>39</v>
       </c>
       <c r="E112">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I112" s="2">
         <v>7.8</v>
       </c>
       <c r="J112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -12926,13 +12926,13 @@
         <v>35</v>
       </c>
       <c r="E145">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -12941,10 +12941,10 @@
         <v>9</v>
       </c>
       <c r="J145">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -13031,25 +13031,25 @@
         <v>26</v>
       </c>
       <c r="E148">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F148">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G148" s="1">
-        <v>11.54</v>
+        <v>30.77</v>
       </c>
       <c r="H148" s="1">
-        <v>15.38</v>
+        <v>69.23</v>
       </c>
       <c r="I148" s="2">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J148">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -13066,25 +13066,25 @@
         <v>26</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G149" s="1">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>38.46</v>
       </c>
       <c r="I149" s="2">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J149">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -13136,25 +13136,25 @@
         <v>36</v>
       </c>
       <c r="E151">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G151" s="1">
-        <v>27.78</v>
+        <v>77.78</v>
       </c>
       <c r="H151" s="1">
-        <v>2.78</v>
+        <v>22.22</v>
       </c>
       <c r="I151" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J151">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -13171,25 +13171,25 @@
         <v>40</v>
       </c>
       <c r="E152">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>25</v>
+        <v>77.5</v>
       </c>
       <c r="H152" s="1">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="I152" s="2">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J152">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -13206,25 +13206,25 @@
         <v>18</v>
       </c>
       <c r="E153">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G153" s="1">
-        <v>44.44</v>
+        <v>72.22</v>
       </c>
       <c r="H153" s="1">
-        <v>5.56</v>
+        <v>27.78</v>
       </c>
       <c r="I153" s="2">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J153">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -13454,22 +13454,22 @@
         <v>26</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" s="1">
         <v>96.3</v>
       </c>
       <c r="H160" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I160" s="2">
         <v>7.7</v>
       </c>
       <c r="J160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -13486,25 +13486,25 @@
         <v>15</v>
       </c>
       <c r="E161">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F161">
         <v>4</v>
       </c>
       <c r="G161" s="1">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H161" s="1">
         <v>26.67</v>
       </c>
       <c r="I161" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -13521,25 +13521,25 @@
         <v>21</v>
       </c>
       <c r="E162">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" s="1">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H162" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I162" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -13941,16 +13941,16 @@
         <v>40</v>
       </c>
       <c r="E174">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F174">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G174" s="1">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H174" s="1">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="I174" s="2">
         <v>7.4</v>
@@ -14256,25 +14256,25 @@
         <v>41</v>
       </c>
       <c r="E183">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F183">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G183" s="1">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H183" s="1">
-        <v>14.63</v>
+        <v>17.07</v>
       </c>
       <c r="I183" s="2">
         <v>6.4</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -14291,25 +14291,25 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F184">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G184" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H184" s="1">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="I184" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -14396,25 +14396,25 @@
         <v>34</v>
       </c>
       <c r="E187">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G187" s="1">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="H187" s="1">
-        <v>17.65</v>
+        <v>20.59</v>
       </c>
       <c r="I187" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K187" s="1">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -14434,22 +14434,22 @@
         <v>27</v>
       </c>
       <c r="F188">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G188" s="1">
         <v>65.84999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="I188" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -14466,25 +14466,25 @@
         <v>40</v>
       </c>
       <c r="E189">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F189">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G189" s="1">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="H189" s="1">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="I189" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J189">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -14504,22 +14504,22 @@
         <v>22</v>
       </c>
       <c r="F190">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G190" s="1">
         <v>61.11</v>
       </c>
       <c r="H190" s="1">
-        <v>36.11</v>
+        <v>38.89</v>
       </c>
       <c r="I190" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -14539,22 +14539,22 @@
         <v>16</v>
       </c>
       <c r="F191">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G191" s="1">
         <v>61.54</v>
       </c>
       <c r="H191" s="1">
-        <v>23.08</v>
+        <v>38.46</v>
       </c>
       <c r="I191" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J191">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -14641,25 +14641,25 @@
         <v>39</v>
       </c>
       <c r="E194">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G194" s="1">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H194" s="1">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="I194" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J194">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -14676,25 +14676,25 @@
         <v>39</v>
       </c>
       <c r="E195">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F195">
         <v>3</v>
       </c>
       <c r="G195" s="1">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H195" s="1">
         <v>7.69</v>
       </c>
       <c r="I195" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -15568,25 +15568,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="H18" s="1">
-        <v>7.89</v>
+        <v>13.16</v>
       </c>
       <c r="I18" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -16236,22 +16236,22 @@
         <v>17</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37" s="1">
         <v>65.38</v>
       </c>
       <c r="H37" s="1">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="I37" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -16268,25 +16268,25 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1">
-        <v>57.89</v>
+        <v>63.16</v>
       </c>
       <c r="H38" s="1">
-        <v>15.79</v>
+        <v>36.84</v>
       </c>
       <c r="I38" s="2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -16306,22 +16306,22 @@
         <v>23</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G39" s="1">
         <v>67.65000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>14.71</v>
+        <v>32.35</v>
       </c>
       <c r="I39" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>17.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -16411,22 +16411,22 @@
         <v>33</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
         <v>94.29000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>2.86</v>
+        <v>5.71</v>
       </c>
       <c r="I42" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -16443,25 +16443,25 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I43" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -16478,25 +16478,25 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G44" s="1">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>16.22</v>
       </c>
       <c r="I44" s="2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J44">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>32.43</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -16548,25 +16548,25 @@
         <v>32</v>
       </c>
       <c r="E46">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H46" s="1">
         <v>3.13</v>
       </c>
       <c r="I46" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -16656,22 +16656,22 @@
         <v>38</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
         <v>97.44</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I49" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -17318,13 +17318,13 @@
         <v>43</v>
       </c>
       <c r="E68">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F68">
         <v>10</v>
       </c>
       <c r="G68" s="1">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H68" s="1">
         <v>23.26</v>
@@ -17333,10 +17333,10 @@
         <v>7</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -17353,13 +17353,13 @@
         <v>34</v>
       </c>
       <c r="E69">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F69">
         <v>11</v>
       </c>
       <c r="G69" s="1">
-        <v>64.70999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H69" s="1">
         <v>32.35</v>
@@ -17368,10 +17368,10 @@
         <v>6.7</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -17388,25 +17388,25 @@
         <v>34</v>
       </c>
       <c r="E70">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G70" s="1">
-        <v>85.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H70" s="1">
-        <v>2.94</v>
+        <v>17.65</v>
       </c>
       <c r="I70" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -17423,25 +17423,25 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G71" s="1">
-        <v>89.47</v>
+        <v>86.84</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>13.16</v>
       </c>
       <c r="I71" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -17461,22 +17461,22 @@
         <v>30</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="1">
         <v>93.75</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I72" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -17496,22 +17496,22 @@
         <v>17</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G73" s="1">
         <v>65.38</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>34.62</v>
       </c>
       <c r="I73" s="2">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="J73">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -17528,25 +17528,25 @@
         <v>33</v>
       </c>
       <c r="E74">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G74" s="1">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H74" s="1">
-        <v>0</v>
+        <v>12.12</v>
       </c>
       <c r="I74" s="2">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J74">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -18088,25 +18088,25 @@
         <v>30</v>
       </c>
       <c r="E90">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G90" s="1">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="H90" s="1">
-        <v>13.33</v>
+        <v>33.33</v>
       </c>
       <c r="I90" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J90">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -18123,25 +18123,25 @@
         <v>36</v>
       </c>
       <c r="E91">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G91" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H91" s="1">
-        <v>2.78</v>
+        <v>11.11</v>
       </c>
       <c r="I91" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -18683,25 +18683,25 @@
         <v>41</v>
       </c>
       <c r="E107">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F107">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G107" s="1">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="H107" s="1">
-        <v>4.88</v>
+        <v>21.95</v>
       </c>
       <c r="I107" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J107">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -18721,22 +18721,22 @@
         <v>33</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G108" s="1">
         <v>82.5</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I108" s="2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J108">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -18753,25 +18753,25 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F109">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G109" s="1">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="H109" s="1">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="I109" s="2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J109">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -18858,25 +18858,25 @@
         <v>39</v>
       </c>
       <c r="E112">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="1">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="I112" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -20013,13 +20013,13 @@
         <v>35</v>
       </c>
       <c r="E145">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -20028,10 +20028,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J145">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -20118,25 +20118,25 @@
         <v>26</v>
       </c>
       <c r="E148">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F148">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G148" s="1">
-        <v>11.54</v>
+        <v>30.77</v>
       </c>
       <c r="H148" s="1">
-        <v>15.38</v>
+        <v>69.23</v>
       </c>
       <c r="I148" s="2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J148">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -20153,25 +20153,25 @@
         <v>26</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G149" s="1">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="H149" s="1">
-        <v>0</v>
+        <v>38.46</v>
       </c>
       <c r="I149" s="2">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="J149">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -20223,25 +20223,25 @@
         <v>36</v>
       </c>
       <c r="E151">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G151" s="1">
-        <v>27.78</v>
+        <v>77.78</v>
       </c>
       <c r="H151" s="1">
-        <v>2.78</v>
+        <v>22.22</v>
       </c>
       <c r="I151" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J151">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -20258,25 +20258,25 @@
         <v>40</v>
       </c>
       <c r="E152">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>25</v>
+        <v>77.5</v>
       </c>
       <c r="H152" s="1">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="I152" s="2">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J152">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -20293,25 +20293,25 @@
         <v>18</v>
       </c>
       <c r="E153">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G153" s="1">
-        <v>44.44</v>
+        <v>72.22</v>
       </c>
       <c r="H153" s="1">
-        <v>5.56</v>
+        <v>27.78</v>
       </c>
       <c r="I153" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J153">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -20541,22 +20541,22 @@
         <v>26</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" s="1">
         <v>96.3</v>
       </c>
       <c r="H160" s="1">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I160" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -20573,25 +20573,25 @@
         <v>15</v>
       </c>
       <c r="E161">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F161">
         <v>4</v>
       </c>
       <c r="G161" s="1">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H161" s="1">
         <v>26.67</v>
       </c>
       <c r="I161" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -20608,25 +20608,25 @@
         <v>21</v>
       </c>
       <c r="E162">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" s="1">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H162" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I162" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -21343,25 +21343,25 @@
         <v>41</v>
       </c>
       <c r="E183">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F183">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G183" s="1">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H183" s="1">
-        <v>14.63</v>
+        <v>17.07</v>
       </c>
       <c r="I183" s="2">
         <v>6.6</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -21378,25 +21378,25 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F184">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G184" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H184" s="1">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="I184" s="2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="J184">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -21483,25 +21483,25 @@
         <v>34</v>
       </c>
       <c r="E187">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G187" s="1">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="H187" s="1">
-        <v>17.65</v>
+        <v>20.59</v>
       </c>
       <c r="I187" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K187" s="1">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -21521,22 +21521,22 @@
         <v>27</v>
       </c>
       <c r="F188">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G188" s="1">
         <v>65.84999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="I188" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -21553,25 +21553,25 @@
         <v>40</v>
       </c>
       <c r="E189">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F189">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G189" s="1">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="H189" s="1">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="I189" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J189">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -21591,22 +21591,22 @@
         <v>22</v>
       </c>
       <c r="F190">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G190" s="1">
         <v>61.11</v>
       </c>
       <c r="H190" s="1">
-        <v>36.11</v>
+        <v>38.89</v>
       </c>
       <c r="I190" s="2">
         <v>6.3</v>
       </c>
       <c r="J190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -21626,22 +21626,22 @@
         <v>16</v>
       </c>
       <c r="F191">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G191" s="1">
         <v>61.54</v>
       </c>
       <c r="H191" s="1">
-        <v>23.08</v>
+        <v>38.46</v>
       </c>
       <c r="I191" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J191">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -21728,25 +21728,25 @@
         <v>39</v>
       </c>
       <c r="E194">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G194" s="1">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H194" s="1">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="I194" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J194">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -21763,25 +21763,25 @@
         <v>39</v>
       </c>
       <c r="E195">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F195">
         <v>3</v>
       </c>
       <c r="G195" s="1">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H195" s="1">
         <v>7.69</v>
       </c>
       <c r="I195" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -2447,22 +2447,22 @@
         <v>33</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
         <v>91.67</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="I48" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3564,25 +3564,25 @@
         <v>34</v>
       </c>
       <c r="E80">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G80" s="1">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>14.71</v>
       </c>
       <c r="I80" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J80">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3599,25 +3599,25 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G81" s="1">
-        <v>64.70999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>17.65</v>
       </c>
       <c r="I81" s="2">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J81">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3634,25 +3634,25 @@
         <v>26</v>
       </c>
       <c r="E82">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G82" s="1">
-        <v>53.85</v>
+        <v>80.77</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>19.23</v>
       </c>
       <c r="I82" s="2">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J82">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3672,22 +3672,22 @@
         <v>9</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G83" s="1">
         <v>60</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I83" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J83">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -5629,25 +5629,25 @@
         <v>37</v>
       </c>
       <c r="E139">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5699,25 +5699,25 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J141">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -6297,22 +6297,22 @@
         <v>37</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G158" s="1">
         <v>94.87</v>
       </c>
       <c r="H158" s="1">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="I158" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6924,25 +6924,25 @@
         <v>28</v>
       </c>
       <c r="E176">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I176" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6962,22 +6962,22 @@
         <v>18</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" s="1">
         <v>94.73999999999999</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I177" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9534,22 +9534,22 @@
         <v>30</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G48" s="1">
         <v>83.33</v>
       </c>
       <c r="H48" s="1">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="I48" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -10651,25 +10651,25 @@
         <v>34</v>
       </c>
       <c r="E80">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" s="1">
-        <v>67.65000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>11.76</v>
       </c>
       <c r="I80" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J80">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -10686,25 +10686,25 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81" s="1">
-        <v>64.70999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>14.71</v>
       </c>
       <c r="I81" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J81">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -10721,25 +10721,25 @@
         <v>26</v>
       </c>
       <c r="E82">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G82" s="1">
-        <v>53.85</v>
+        <v>69.23</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>30.77</v>
       </c>
       <c r="I82" s="2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="J82">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -10756,25 +10756,25 @@
         <v>15</v>
       </c>
       <c r="E83">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="1">
-        <v>60</v>
+        <v>93.33</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I83" s="2">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="J83">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -12716,13 +12716,13 @@
         <v>37</v>
       </c>
       <c r="E139">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
@@ -12731,10 +12731,10 @@
         <v>7.4</v>
       </c>
       <c r="J139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -12786,25 +12786,25 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J141">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -13384,22 +13384,22 @@
         <v>34</v>
       </c>
       <c r="F158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G158" s="1">
         <v>87.18000000000001</v>
       </c>
       <c r="H158" s="1">
-        <v>10.26</v>
+        <v>12.82</v>
       </c>
       <c r="I158" s="2">
         <v>8.1</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -14011,25 +14011,25 @@
         <v>28</v>
       </c>
       <c r="E176">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I176" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -14049,22 +14049,22 @@
         <v>18</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" s="1">
         <v>94.73999999999999</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I177" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -16621,22 +16621,22 @@
         <v>30</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G48" s="1">
         <v>83.33</v>
       </c>
       <c r="H48" s="1">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="I48" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -17738,25 +17738,25 @@
         <v>34</v>
       </c>
       <c r="E80">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" s="1">
-        <v>67.65000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>11.76</v>
       </c>
       <c r="I80" s="2">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J80">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -17773,25 +17773,25 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81" s="1">
-        <v>64.70999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>14.71</v>
       </c>
       <c r="I81" s="2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J81">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -17808,25 +17808,25 @@
         <v>26</v>
       </c>
       <c r="E82">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G82" s="1">
-        <v>53.85</v>
+        <v>69.23</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>30.77</v>
       </c>
       <c r="I82" s="2">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J82">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -17843,25 +17843,25 @@
         <v>15</v>
       </c>
       <c r="E83">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="1">
-        <v>60</v>
+        <v>93.33</v>
       </c>
       <c r="H83" s="1">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I83" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J83">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -19803,13 +19803,13 @@
         <v>37</v>
       </c>
       <c r="E139">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F139">
         <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
@@ -19818,10 +19818,10 @@
         <v>7.5</v>
       </c>
       <c r="J139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -19873,25 +19873,25 @@
         <v>32</v>
       </c>
       <c r="E141">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J141">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -20471,22 +20471,22 @@
         <v>34</v>
       </c>
       <c r="F158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G158" s="1">
         <v>87.18000000000001</v>
       </c>
       <c r="H158" s="1">
-        <v>10.26</v>
+        <v>12.82</v>
       </c>
       <c r="I158" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -21098,25 +21098,25 @@
         <v>28</v>
       </c>
       <c r="E176">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1">
-        <v>67.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="I176" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J176">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -21136,22 +21136,22 @@
         <v>18</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" s="1">
         <v>94.73999999999999</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="I177" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -4471,7 +4471,7 @@
         <v>124</v>
       </c>
       <c r="D106">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E106">
         <v>32</v>
@@ -4480,19 +4480,19 @@
         <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H106" s="1">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="I106" s="2">
         <v>7.6</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K106" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -6081,7 +6081,7 @@
         <v>123</v>
       </c>
       <c r="D152">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E152">
         <v>31</v>
@@ -6090,19 +6090,19 @@
         <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H152" s="1">
-        <v>22.5</v>
+        <v>21.43</v>
       </c>
       <c r="I152" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K152" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -11558,7 +11558,7 @@
         <v>124</v>
       </c>
       <c r="D106">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E106">
         <v>32</v>
@@ -11567,19 +11567,19 @@
         <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H106" s="1">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="I106" s="2">
         <v>7.1</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K106" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -11701,19 +11701,19 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F110">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G110" s="1">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H110" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="I110" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -12623,7 +12623,7 @@
         <v>18.18</v>
       </c>
       <c r="I136" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -13168,7 +13168,7 @@
         <v>123</v>
       </c>
       <c r="D152">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E152">
         <v>31</v>
@@ -13177,19 +13177,19 @@
         <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H152" s="1">
-        <v>22.5</v>
+        <v>21.43</v>
       </c>
       <c r="I152" s="2">
         <v>8.5</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K152" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -15125,7 +15125,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -15218,19 +15218,19 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H8" s="1">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -15253,19 +15253,19 @@
         <v>41</v>
       </c>
       <c r="E9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>95.12</v>
+        <v>97.56</v>
       </c>
       <c r="H9" s="1">
-        <v>4.88</v>
+        <v>2.44</v>
       </c>
       <c r="I9" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -15300,7 +15300,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -15323,19 +15323,19 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>92.31</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>7.69</v>
+        <v>10.26</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -15358,19 +15358,19 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H12" s="1">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -15393,19 +15393,19 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>88.64</v>
+        <v>95.45</v>
       </c>
       <c r="H13" s="1">
-        <v>11.36</v>
+        <v>4.55</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -15848,19 +15848,19 @@
         <v>39</v>
       </c>
       <c r="E26">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>82.05</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>17.95</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -15883,19 +15883,19 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H27" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I27" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -15953,19 +15953,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>85</v>
+        <v>97.5</v>
       </c>
       <c r="H29" s="1">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="I29" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -15988,16 +15988,16 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
         <v>8</v>
@@ -16128,19 +16128,19 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H34" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -16163,16 +16163,16 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>14.29</v>
+        <v>4.76</v>
       </c>
       <c r="I35" s="2">
         <v>7.9</v>
@@ -16770,7 +16770,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -16805,7 +16805,7 @@
         <v>16.67</v>
       </c>
       <c r="I53" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -16828,16 +16828,16 @@
         <v>26</v>
       </c>
       <c r="E54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F54">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G54" s="1">
-        <v>65.38</v>
+        <v>80.77</v>
       </c>
       <c r="H54" s="1">
-        <v>34.62</v>
+        <v>19.23</v>
       </c>
       <c r="I54" s="2">
         <v>7.2</v>
@@ -17073,19 +17073,19 @@
         <v>39</v>
       </c>
       <c r="E61">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F61">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G61" s="1">
-        <v>58.97</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H61" s="1">
-        <v>41.03</v>
+        <v>20.51</v>
       </c>
       <c r="I61" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -17108,19 +17108,19 @@
         <v>34</v>
       </c>
       <c r="E62">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>88.23999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H62" s="1">
-        <v>11.76</v>
+        <v>14.71</v>
       </c>
       <c r="I62" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -17143,19 +17143,19 @@
         <v>41</v>
       </c>
       <c r="E63">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G63" s="1">
-        <v>87.8</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H63" s="1">
-        <v>12.2</v>
+        <v>17.07</v>
       </c>
       <c r="I63" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -17190,7 +17190,7 @@
         <v>20</v>
       </c>
       <c r="I64" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -17213,19 +17213,19 @@
         <v>36</v>
       </c>
       <c r="E65">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65" s="1">
-        <v>83.33</v>
+        <v>80.56</v>
       </c>
       <c r="H65" s="1">
-        <v>16.67</v>
+        <v>19.44</v>
       </c>
       <c r="I65" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -18645,7 +18645,7 @@
         <v>124</v>
       </c>
       <c r="D106">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E106">
         <v>32</v>
@@ -18654,19 +18654,19 @@
         <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="H106" s="1">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="I106" s="2">
         <v>7.5</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K106" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -18788,19 +18788,19 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F110">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G110" s="1">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H110" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="I110" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -18858,19 +18858,19 @@
         <v>32</v>
       </c>
       <c r="E112">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G112" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H112" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I112" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -19710,7 +19710,7 @@
         <v>18.18</v>
       </c>
       <c r="I136" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -20255,7 +20255,7 @@
         <v>123</v>
       </c>
       <c r="D152">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E152">
         <v>31</v>
@@ -20264,19 +20264,19 @@
         <v>9</v>
       </c>
       <c r="G152" s="1">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H152" s="1">
-        <v>22.5</v>
+        <v>21.43</v>
       </c>
       <c r="I152" s="2">
         <v>8.4</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K152" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -20375,7 +20375,7 @@
         <v>2.44</v>
       </c>
       <c r="I155" s="2">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -20398,19 +20398,19 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="H156" s="1">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="I156" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -20538,19 +20538,19 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H160" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I160" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -20573,19 +20573,19 @@
         <v>15</v>
       </c>
       <c r="E161">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F161">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G161" s="1">
-        <v>73.33</v>
+        <v>93.33</v>
       </c>
       <c r="H161" s="1">
-        <v>26.67</v>
+        <v>6.67</v>
       </c>
       <c r="I161" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -20620,7 +20620,7 @@
         <v>4.76</v>
       </c>
       <c r="I162" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -21705,7 +21705,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J193">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -15020,7 +15020,7 @@
         <v>7.14</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -15043,19 +15043,19 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -15078,19 +15078,19 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H4" s="1">
-        <v>15.79</v>
+        <v>10.53</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -15918,19 +15918,19 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1">
-        <v>85.37</v>
+        <v>95.12</v>
       </c>
       <c r="H28" s="1">
-        <v>14.63</v>
+        <v>4.88</v>
       </c>
       <c r="I28" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -16653,19 +16653,19 @@
         <v>36</v>
       </c>
       <c r="E49">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G49" s="1">
-        <v>83.33</v>
+        <v>69.44</v>
       </c>
       <c r="H49" s="1">
-        <v>16.67</v>
+        <v>30.56</v>
       </c>
       <c r="I49" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -17435,7 +17435,7 @@
         <v>17.65</v>
       </c>
       <c r="I71" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -17505,7 +17505,7 @@
         <v>6.25</v>
       </c>
       <c r="I73" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -20153,19 +20153,19 @@
         <v>26</v>
       </c>
       <c r="E149">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F149">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G149" s="1">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="H149" s="1">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="I149" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -20188,19 +20188,19 @@
         <v>26</v>
       </c>
       <c r="E150">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F150">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G150" s="1">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
       <c r="H150" s="1">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
       <c r="I150" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -20235,7 +20235,7 @@
         <v>22.22</v>
       </c>
       <c r="I151" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -20258,19 +20258,19 @@
         <v>42</v>
       </c>
       <c r="E152">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F152">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>73.81</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H152" s="1">
-        <v>21.43</v>
+        <v>23.81</v>
       </c>
       <c r="I152" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J152">
         <v>2</v>
@@ -20293,19 +20293,19 @@
         <v>18</v>
       </c>
       <c r="E153">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F153">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G153" s="1">
-        <v>72.22</v>
+        <v>55.56</v>
       </c>
       <c r="H153" s="1">
-        <v>27.78</v>
+        <v>44.44</v>
       </c>
       <c r="I153" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -20328,19 +20328,19 @@
         <v>32</v>
       </c>
       <c r="E154">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F154">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G154" s="1">
-        <v>96.88</v>
+        <v>84.38</v>
       </c>
       <c r="H154" s="1">
-        <v>3.13</v>
+        <v>15.63</v>
       </c>
       <c r="I154" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -20433,19 +20433,19 @@
         <v>31</v>
       </c>
       <c r="E157">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G157" s="1">
-        <v>90.31999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H157" s="1">
-        <v>9.68</v>
+        <v>12.9</v>
       </c>
       <c r="I157" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -20620,7 +20620,7 @@
         <v>4.76</v>
       </c>
       <c r="I162" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -21845,7 +21845,7 @@
         <v>0</v>
       </c>
       <c r="I197" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -21880,7 +21880,7 @@
         <v>0</v>
       </c>
       <c r="I198" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J198">
         <v>0</v>
@@ -21915,7 +21915,7 @@
         <v>0</v>
       </c>
       <c r="I199" s="2">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -21938,19 +21938,19 @@
         <v>41</v>
       </c>
       <c r="E200">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" s="1">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="H200" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I200" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -22020,7 +22020,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J202">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -15113,16 +15113,16 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I5" s="2">
         <v>8.9</v>
@@ -15428,19 +15428,19 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>92.68000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H14" s="1">
-        <v>7.32</v>
+        <v>12.2</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -15463,19 +15463,19 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="H15" s="1">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -16408,19 +16408,19 @@
         <v>35</v>
       </c>
       <c r="E42">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H42" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -16443,19 +16443,19 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -16478,19 +16478,19 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>81.08</v>
+        <v>94.59</v>
       </c>
       <c r="H44" s="1">
-        <v>16.22</v>
+        <v>2.7</v>
       </c>
       <c r="I44" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -17773,16 +17773,16 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G81" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H81" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I81" s="2">
         <v>8.1</v>
@@ -17808,16 +17808,16 @@
         <v>34</v>
       </c>
       <c r="E82">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G82" s="1">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H82" s="1">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
       <c r="I82" s="2">
         <v>8.199999999999999</v>
@@ -17843,19 +17843,19 @@
         <v>26</v>
       </c>
       <c r="E83">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G83" s="1">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="H83" s="1">
-        <v>30.77</v>
+        <v>26.92</v>
       </c>
       <c r="I83" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -17878,19 +17878,19 @@
         <v>15</v>
       </c>
       <c r="E84">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="1">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H84" s="1">
-        <v>6.67</v>
+        <v>13.33</v>
       </c>
       <c r="I84" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -18905,7 +18905,7 @@
         <v>2.56</v>
       </c>
       <c r="I113" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -19733,19 +19733,19 @@
         <v>31</v>
       </c>
       <c r="E137">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F137">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G137" s="1">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H137" s="1">
-        <v>25.81</v>
+        <v>9.68</v>
       </c>
       <c r="I137" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -19768,19 +19768,19 @@
         <v>35</v>
       </c>
       <c r="E138">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F138">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G138" s="1">
-        <v>74.29000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H138" s="1">
-        <v>25.71</v>
+        <v>11.43</v>
       </c>
       <c r="I138" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -19803,16 +19803,16 @@
         <v>21</v>
       </c>
       <c r="E139">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G139" s="1">
-        <v>95.23999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H139" s="1">
-        <v>4.76</v>
+        <v>9.52</v>
       </c>
       <c r="I139" s="2">
         <v>6.7</v>
@@ -19850,7 +19850,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -19873,19 +19873,19 @@
         <v>30</v>
       </c>
       <c r="E141">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F141">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G141" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H141" s="1">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="I141" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J141">
         <v>0</v>
@@ -19920,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -19943,16 +19943,16 @@
         <v>34</v>
       </c>
       <c r="E143">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H143" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I143" s="2">
         <v>8.199999999999999</v>
@@ -19978,19 +19978,19 @@
         <v>40</v>
       </c>
       <c r="E144">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" s="1">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H144" s="1">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I144" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -20013,19 +20013,19 @@
         <v>36</v>
       </c>
       <c r="E145">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F145">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -20678,19 +20678,19 @@
         <v>41</v>
       </c>
       <c r="E164">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F164">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G164" s="1">
-        <v>51.22</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H164" s="1">
-        <v>48.78</v>
+        <v>7.32</v>
       </c>
       <c r="I164" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -20958,19 +20958,19 @@
         <v>39</v>
       </c>
       <c r="E172">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F172">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G172" s="1">
-        <v>64.09999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="H172" s="1">
-        <v>35.9</v>
+        <v>23.08</v>
       </c>
       <c r="I172" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -20993,16 +20993,16 @@
         <v>39</v>
       </c>
       <c r="E173">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F173">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G173" s="1">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H173" s="1">
-        <v>10.26</v>
+        <v>7.69</v>
       </c>
       <c r="I173" s="2">
         <v>8.300000000000001</v>
@@ -21098,19 +21098,19 @@
         <v>28</v>
       </c>
       <c r="E176">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G176" s="1">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H176" s="1">
-        <v>3.57</v>
+        <v>7.14</v>
       </c>
       <c r="I176" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -21133,19 +21133,19 @@
         <v>19</v>
       </c>
       <c r="E177">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177" s="1">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H177" s="1">
-        <v>5.26</v>
+        <v>10.53</v>
       </c>
       <c r="I177" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J177">
         <v>0</v>
@@ -21273,16 +21273,16 @@
         <v>34</v>
       </c>
       <c r="E181">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F181">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G181" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H181" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I181" s="2">
         <v>7.3</v>
@@ -21308,19 +21308,19 @@
         <v>30</v>
       </c>
       <c r="E182">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F182">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G182" s="1">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H182" s="1">
-        <v>16.67</v>
+        <v>10</v>
       </c>
       <c r="I182" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J182">
         <v>0</v>
@@ -21413,19 +21413,19 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H185" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I185" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -21973,19 +21973,19 @@
         <v>45</v>
       </c>
       <c r="E201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G201" s="1">
-        <v>86.67</v>
+        <v>84.44</v>
       </c>
       <c r="H201" s="1">
-        <v>13.33</v>
+        <v>15.56</v>
       </c>
       <c r="I201" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J201">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -15113,19 +15113,19 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>96.77</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>3.23</v>
+        <v>12.9</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -15160,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -15183,19 +15183,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="I7" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -15498,19 +15498,19 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>87.18000000000001</v>
+        <v>97.44</v>
       </c>
       <c r="H16" s="1">
-        <v>12.82</v>
+        <v>2.56</v>
       </c>
       <c r="I16" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -15533,19 +15533,19 @@
         <v>35</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H17" s="1">
-        <v>20</v>
+        <v>17.14</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -15568,19 +15568,19 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H18" s="1">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="I18" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -15603,19 +15603,19 @@
         <v>32</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="H19" s="1">
-        <v>9.380000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -15638,19 +15638,19 @@
         <v>32</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H20" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -16093,19 +16093,19 @@
         <v>30</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H33" s="1">
-        <v>6.67</v>
+        <v>13.33</v>
       </c>
       <c r="I33" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -16688,16 +16688,16 @@
         <v>39</v>
       </c>
       <c r="E50">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="1">
-        <v>97.44</v>
+        <v>92.31</v>
       </c>
       <c r="H50" s="1">
-        <v>2.56</v>
+        <v>7.69</v>
       </c>
       <c r="I50" s="2">
         <v>7.5</v>
@@ -16735,7 +16735,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -16793,19 +16793,19 @@
         <v>30</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H53" s="1">
-        <v>16.67</v>
+        <v>10</v>
       </c>
       <c r="I53" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -16828,19 +16828,19 @@
         <v>26</v>
       </c>
       <c r="E54">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G54" s="1">
-        <v>80.77</v>
+        <v>76.92</v>
       </c>
       <c r="H54" s="1">
-        <v>19.23</v>
+        <v>23.08</v>
       </c>
       <c r="I54" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -17423,19 +17423,19 @@
         <v>34</v>
       </c>
       <c r="E71">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G71" s="1">
-        <v>82.34999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H71" s="1">
-        <v>17.65</v>
+        <v>11.76</v>
       </c>
       <c r="I71" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -17458,16 +17458,16 @@
         <v>38</v>
       </c>
       <c r="E72">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G72" s="1">
-        <v>86.84</v>
+        <v>97.37</v>
       </c>
       <c r="H72" s="1">
-        <v>13.16</v>
+        <v>2.63</v>
       </c>
       <c r="I72" s="2">
         <v>8</v>
@@ -17528,19 +17528,19 @@
         <v>26</v>
       </c>
       <c r="E74">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F74">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G74" s="1">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H74" s="1">
-        <v>34.62</v>
+        <v>7.69</v>
       </c>
       <c r="I74" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -17563,19 +17563,19 @@
         <v>33</v>
       </c>
       <c r="E75">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H75" s="1">
-        <v>12.12</v>
+        <v>15.15</v>
       </c>
       <c r="I75" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -18415,7 +18415,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         <v>5.26</v>
       </c>
       <c r="I100" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -18520,7 +18520,7 @@
         <v>3.13</v>
       </c>
       <c r="I102" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -18555,7 +18555,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -18590,7 +18590,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -18625,7 +18625,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -18695,7 +18695,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -18718,19 +18718,19 @@
         <v>41</v>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F108">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G108" s="1">
-        <v>78.05</v>
+        <v>70.73</v>
       </c>
       <c r="H108" s="1">
-        <v>21.95</v>
+        <v>29.27</v>
       </c>
       <c r="I108" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -18753,19 +18753,19 @@
         <v>40</v>
       </c>
       <c r="E109">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F109">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G109" s="1">
-        <v>82.5</v>
+        <v>75</v>
       </c>
       <c r="H109" s="1">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="I109" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -18788,19 +18788,19 @@
         <v>36</v>
       </c>
       <c r="E110">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F110">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G110" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H110" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I110" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -19068,16 +19068,16 @@
         <v>19</v>
       </c>
       <c r="E118">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G118" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H118" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I118" s="2">
         <v>7.8</v>
@@ -19150,7 +19150,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -19173,19 +19173,19 @@
         <v>40</v>
       </c>
       <c r="E121">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H121" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I121" s="2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -19208,16 +19208,16 @@
         <v>44</v>
       </c>
       <c r="E122">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H122" s="1">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="I122" s="2">
         <v>9.1</v>
@@ -19243,19 +19243,19 @@
         <v>43</v>
       </c>
       <c r="E123">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G123" s="1">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H123" s="1">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="I123" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -19290,7 +19290,7 @@
         <v>2.33</v>
       </c>
       <c r="I124" s="2">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -19313,19 +19313,19 @@
         <v>35</v>
       </c>
       <c r="E125">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F125">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G125" s="1">
-        <v>74.29000000000001</v>
+        <v>80</v>
       </c>
       <c r="H125" s="1">
-        <v>25.71</v>
+        <v>20</v>
       </c>
       <c r="I125" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -19348,19 +19348,19 @@
         <v>38</v>
       </c>
       <c r="E126">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F126">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G126" s="1">
-        <v>81.58</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H126" s="1">
-        <v>18.42</v>
+        <v>15.79</v>
       </c>
       <c r="I126" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -19383,19 +19383,19 @@
         <v>26</v>
       </c>
       <c r="E127">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F127">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G127" s="1">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="H127" s="1">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
       <c r="I127" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -19418,19 +19418,19 @@
         <v>32</v>
       </c>
       <c r="E128">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G128" s="1">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H128" s="1">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="I128" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -20643,19 +20643,19 @@
         <v>32</v>
       </c>
       <c r="E163">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F163">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G163" s="1">
-        <v>68.75</v>
+        <v>62.5</v>
       </c>
       <c r="H163" s="1">
-        <v>31.25</v>
+        <v>37.5</v>
       </c>
       <c r="I163" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -20713,19 +20713,19 @@
         <v>39</v>
       </c>
       <c r="E165">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F165">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G165" s="1">
-        <v>61.54</v>
+        <v>74.36</v>
       </c>
       <c r="H165" s="1">
-        <v>38.46</v>
+        <v>25.64</v>
       </c>
       <c r="I165" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -20748,19 +20748,19 @@
         <v>31</v>
       </c>
       <c r="E166">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F166">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G166" s="1">
-        <v>58.06</v>
+        <v>70.97</v>
       </c>
       <c r="H166" s="1">
-        <v>41.94</v>
+        <v>29.03</v>
       </c>
       <c r="I166" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -21028,19 +21028,19 @@
         <v>40</v>
       </c>
       <c r="E174">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F174">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G174" s="1">
-        <v>82.5</v>
+        <v>75</v>
       </c>
       <c r="H174" s="1">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="I174" s="2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -21063,19 +21063,19 @@
         <v>26</v>
       </c>
       <c r="E175">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F175">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G175" s="1">
-        <v>61.54</v>
+        <v>42.31</v>
       </c>
       <c r="H175" s="1">
-        <v>38.46</v>
+        <v>57.69</v>
       </c>
       <c r="I175" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -21168,19 +21168,19 @@
         <v>32</v>
       </c>
       <c r="E178">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G178" s="1">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="H178" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="I178" s="2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -21203,19 +21203,19 @@
         <v>32</v>
       </c>
       <c r="E179">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F179">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -21343,16 +21343,16 @@
         <v>41</v>
       </c>
       <c r="E183">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F183">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G183" s="1">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H183" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
       <c r="I183" s="2">
         <v>6.6</v>
@@ -21378,19 +21378,19 @@
         <v>40</v>
       </c>
       <c r="E184">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F184">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G184" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H184" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I184" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -21740,7 +21740,7 @@
         <v>10.26</v>
       </c>
       <c r="I194" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -21763,19 +21763,19 @@
         <v>39</v>
       </c>
       <c r="E195">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F195">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G195" s="1">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H195" s="1">
-        <v>7.69</v>
+        <v>15.38</v>
       </c>
       <c r="I195" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -21798,19 +21798,19 @@
         <v>26</v>
       </c>
       <c r="E196">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F196">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G196" s="1">
-        <v>84.62</v>
+        <v>80.77</v>
       </c>
       <c r="H196" s="1">
-        <v>15.38</v>
+        <v>19.23</v>
       </c>
       <c r="I196" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J196">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -16198,19 +16198,19 @@
         <v>26</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="H36" s="1">
-        <v>38.46</v>
+        <v>30.77</v>
       </c>
       <c r="I36" s="2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -16233,19 +16233,19 @@
         <v>26</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>65.38</v>
+        <v>84.62</v>
       </c>
       <c r="H37" s="1">
-        <v>34.62</v>
+        <v>15.38</v>
       </c>
       <c r="I37" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -16268,16 +16268,16 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1">
-        <v>63.16</v>
+        <v>78.95</v>
       </c>
       <c r="H38" s="1">
-        <v>36.84</v>
+        <v>21.05</v>
       </c>
       <c r="I38" s="2">
         <v>6.8</v>
@@ -16303,16 +16303,16 @@
         <v>34</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="I39" s="2">
         <v>6.6</v>
@@ -16338,19 +16338,19 @@
         <v>18</v>
       </c>
       <c r="E40">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1">
-        <v>77.78</v>
+        <v>94.44</v>
       </c>
       <c r="H40" s="1">
-        <v>22.22</v>
+        <v>5.56</v>
       </c>
       <c r="I40" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -16373,19 +16373,19 @@
         <v>31</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G41" s="1">
-        <v>70.97</v>
+        <v>58.06</v>
       </c>
       <c r="H41" s="1">
-        <v>22.58</v>
+        <v>35.48</v>
       </c>
       <c r="I41" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -16513,16 +16513,16 @@
         <v>30</v>
       </c>
       <c r="E45">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1">
-        <v>63.33</v>
+        <v>76.67</v>
       </c>
       <c r="H45" s="1">
-        <v>36.67</v>
+        <v>23.33</v>
       </c>
       <c r="I45" s="2">
         <v>6.4</v>
@@ -16595,7 +16595,7 @@
         <v>21.05</v>
       </c>
       <c r="I47" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -17248,19 +17248,19 @@
         <v>40</v>
       </c>
       <c r="E66">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G66" s="1">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="H66" s="1">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="I66" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -17283,16 +17283,16 @@
         <v>44</v>
       </c>
       <c r="E67">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G67" s="1">
-        <v>84.09</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H67" s="1">
-        <v>15.91</v>
+        <v>6.82</v>
       </c>
       <c r="I67" s="2">
         <v>7.4</v>
@@ -17318,16 +17318,16 @@
         <v>43</v>
       </c>
       <c r="E68">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F68">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G68" s="1">
-        <v>76.73999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H68" s="1">
-        <v>23.26</v>
+        <v>13.95</v>
       </c>
       <c r="I68" s="2">
         <v>7</v>
@@ -17353,19 +17353,19 @@
         <v>43</v>
       </c>
       <c r="E69">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G69" s="1">
-        <v>76.73999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H69" s="1">
-        <v>23.26</v>
+        <v>18.6</v>
       </c>
       <c r="I69" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         <v>34</v>
       </c>
       <c r="E85">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F85">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G85" s="1">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H85" s="1">
-        <v>29.41</v>
+        <v>5.88</v>
       </c>
       <c r="I85" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -17948,19 +17948,19 @@
         <v>30</v>
       </c>
       <c r="E86">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F86">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G86" s="1">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="H86" s="1">
-        <v>16.67</v>
+        <v>6.67</v>
       </c>
       <c r="I86" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -17983,16 +17983,16 @@
         <v>40</v>
       </c>
       <c r="E87">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F87">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G87" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H87" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I87" s="2">
         <v>7</v>
@@ -18088,16 +18088,16 @@
         <v>43</v>
       </c>
       <c r="E90">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F90">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G90" s="1">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H90" s="1">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I90" s="2">
         <v>6.8</v>
@@ -18660,7 +18660,7 @@
         <v>19.05</v>
       </c>
       <c r="I106" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J106">
         <v>2</v>
@@ -18928,16 +18928,16 @@
         <v>31</v>
       </c>
       <c r="E114">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G114" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H114" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="I114" s="2">
         <v>8.6</v>
@@ -18963,19 +18963,19 @@
         <v>30</v>
       </c>
       <c r="E115">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G115" s="1">
-        <v>96.67</v>
+        <v>93.33</v>
       </c>
       <c r="H115" s="1">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="I115" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -18998,19 +18998,19 @@
         <v>26</v>
       </c>
       <c r="E116">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="1">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="H116" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="I116" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -19103,19 +19103,19 @@
         <v>34</v>
       </c>
       <c r="E119">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G119" s="1">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H119" s="1">
-        <v>2.94</v>
+        <v>8.82</v>
       </c>
       <c r="I119" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -19453,19 +19453,19 @@
         <v>34</v>
       </c>
       <c r="E129">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F129">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G129" s="1">
-        <v>67.65000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="H129" s="1">
-        <v>32.35</v>
+        <v>20.59</v>
       </c>
       <c r="I129" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -19488,16 +19488,16 @@
         <v>30</v>
       </c>
       <c r="E130">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F130">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G130" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H130" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I130" s="2">
         <v>6.9</v>
@@ -20795,7 +20795,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -20830,7 +20830,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -20853,19 +20853,19 @@
         <v>43</v>
       </c>
       <c r="E169">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G169" s="1">
-        <v>95.34999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="H169" s="1">
-        <v>4.65</v>
+        <v>2.33</v>
       </c>
       <c r="I169" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -20935,7 +20935,7 @@
         <v>4.76</v>
       </c>
       <c r="I171" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -21238,19 +21238,19 @@
         <v>30</v>
       </c>
       <c r="E180">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F180">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G180" s="1">
-        <v>86.67</v>
+        <v>80</v>
       </c>
       <c r="H180" s="1">
-        <v>13.33</v>
+        <v>20</v>
       </c>
       <c r="I180" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -21448,19 +21448,19 @@
         <v>44</v>
       </c>
       <c r="E186">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F186">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G186" s="1">
-        <v>86.36</v>
+        <v>88.64</v>
       </c>
       <c r="H186" s="1">
-        <v>13.64</v>
+        <v>11.36</v>
       </c>
       <c r="I186" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -21518,19 +21518,19 @@
         <v>41</v>
       </c>
       <c r="E188">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F188">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G188" s="1">
-        <v>65.84999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H188" s="1">
-        <v>34.15</v>
+        <v>7.32</v>
       </c>
       <c r="I188" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -21553,19 +21553,19 @@
         <v>40</v>
       </c>
       <c r="E189">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F189">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G189" s="1">
-        <v>62.5</v>
+        <v>90</v>
       </c>
       <c r="H189" s="1">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="I189" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -21588,19 +21588,19 @@
         <v>36</v>
       </c>
       <c r="E190">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F190">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G190" s="1">
-        <v>61.11</v>
+        <v>97.22</v>
       </c>
       <c r="H190" s="1">
-        <v>38.89</v>
+        <v>2.78</v>
       </c>
       <c r="I190" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J190">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -17388,16 +17388,16 @@
         <v>34</v>
       </c>
       <c r="E70">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F70">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G70" s="1">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H70" s="1">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="I70" s="2">
         <v>6.7</v>
@@ -19535,7 +19535,7 @@
         <v>35</v>
       </c>
       <c r="I131" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -19558,19 +19558,19 @@
         <v>44</v>
       </c>
       <c r="E132">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F132">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G132" s="1">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H132" s="1">
-        <v>13.64</v>
+        <v>9.09</v>
       </c>
       <c r="I132" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -19593,19 +19593,19 @@
         <v>43</v>
       </c>
       <c r="E133">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F133">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G133" s="1">
-        <v>74.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H133" s="1">
-        <v>25.58</v>
+        <v>18.6</v>
       </c>
       <c r="I133" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -19628,19 +19628,19 @@
         <v>43</v>
       </c>
       <c r="E134">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F134">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G134" s="1">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H134" s="1">
-        <v>20.93</v>
+        <v>23.26</v>
       </c>
       <c r="I134" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -19675,7 +19675,7 @@
         <v>0</v>
       </c>
       <c r="I135" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -19698,19 +19698,19 @@
         <v>44</v>
       </c>
       <c r="E136">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F136">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G136" s="1">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H136" s="1">
-        <v>18.18</v>
+        <v>11.36</v>
       </c>
       <c r="I136" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -21483,19 +21483,19 @@
         <v>34</v>
       </c>
       <c r="E187">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F187">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G187" s="1">
-        <v>76.47</v>
+        <v>97.06</v>
       </c>
       <c r="H187" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
       <c r="I187" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -21623,19 +21623,19 @@
         <v>26</v>
       </c>
       <c r="E191">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F191">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G191" s="1">
-        <v>61.54</v>
+        <v>92.31</v>
       </c>
       <c r="H191" s="1">
-        <v>38.46</v>
+        <v>7.69</v>
       </c>
       <c r="I191" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J191">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -15720,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -15755,7 +15755,7 @@
         <v>2.44</v>
       </c>
       <c r="I23" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -15790,7 +15790,7 @@
         <v>2.56</v>
       </c>
       <c r="I24" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>9.68</v>
       </c>
       <c r="I25" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -16630,7 +16630,7 @@
         <v>4.55</v>
       </c>
       <c r="I48" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -16910,7 +16910,7 @@
         <v>13.33</v>
       </c>
       <c r="I56" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -18018,16 +18018,16 @@
         <v>44</v>
       </c>
       <c r="E88">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="1">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H88" s="1">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="I88" s="2">
         <v>7.3</v>
@@ -18053,19 +18053,19 @@
         <v>43</v>
       </c>
       <c r="E89">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F89">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G89" s="1">
-        <v>67.44</v>
+        <v>90.7</v>
       </c>
       <c r="H89" s="1">
-        <v>32.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I89" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -20468,19 +20468,19 @@
         <v>39</v>
       </c>
       <c r="E158">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G158" s="1">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H158" s="1">
-        <v>12.82</v>
+        <v>10.26</v>
       </c>
       <c r="I158" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -20515,7 +20515,7 @@
         <v>0</v>
       </c>
       <c r="I159" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -21658,19 +21658,19 @@
         <v>15</v>
       </c>
       <c r="E192">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F192">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G192" s="1">
-        <v>46.67</v>
+        <v>73.33</v>
       </c>
       <c r="H192" s="1">
-        <v>53.33</v>
+        <v>26.67</v>
       </c>
       <c r="I192" s="2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J192">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -2202,22 +2202,22 @@
         <v>11</v>
       </c>
       <c r="F41">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1">
         <v>35.48</v>
       </c>
       <c r="H41" s="1">
-        <v>58.06</v>
+        <v>64.52</v>
       </c>
       <c r="I41" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2307,22 +2307,22 @@
         <v>30</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1">
         <v>81.08</v>
       </c>
       <c r="H44" s="1">
-        <v>16.22</v>
+        <v>18.92</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4194,25 +4194,25 @@
         <v>41</v>
       </c>
       <c r="E98">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="I98" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -4474,25 +4474,25 @@
         <v>42</v>
       </c>
       <c r="E106">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F106">
         <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H106" s="1">
         <v>19.05</v>
       </c>
       <c r="I106" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4932,22 +4932,22 @@
         <v>33</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="1">
         <v>97.06</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I119" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -6084,25 +6084,25 @@
         <v>42</v>
       </c>
       <c r="E152">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F152">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>73.81</v>
+        <v>76.19</v>
       </c>
       <c r="H152" s="1">
-        <v>21.43</v>
+        <v>23.81</v>
       </c>
       <c r="I152" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -9289,22 +9289,22 @@
         <v>22</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G41" s="1">
         <v>70.97</v>
       </c>
       <c r="H41" s="1">
-        <v>22.58</v>
+        <v>29.03</v>
       </c>
       <c r="I41" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -9356,19 +9356,19 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H43" s="1">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="I43" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -9394,22 +9394,22 @@
         <v>30</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1">
         <v>81.08</v>
       </c>
       <c r="H44" s="1">
-        <v>16.22</v>
+        <v>18.92</v>
       </c>
       <c r="I44" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -9508,7 +9508,7 @@
         <v>21.05</v>
       </c>
       <c r="I47" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -11281,25 +11281,25 @@
         <v>41</v>
       </c>
       <c r="E98">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="I98" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -11561,25 +11561,25 @@
         <v>42</v>
       </c>
       <c r="E106">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F106">
         <v>8</v>
       </c>
       <c r="G106" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H106" s="1">
         <v>19.05</v>
       </c>
       <c r="I106" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -12019,22 +12019,22 @@
         <v>32</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" s="1">
         <v>94.12</v>
       </c>
       <c r="H119" s="1">
-        <v>2.94</v>
+        <v>5.88</v>
       </c>
       <c r="I119" s="2">
         <v>9.1</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -13171,25 +13171,25 @@
         <v>42</v>
       </c>
       <c r="E152">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F152">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>73.81</v>
+        <v>76.19</v>
       </c>
       <c r="H152" s="1">
-        <v>21.43</v>
+        <v>23.81</v>
       </c>
       <c r="I152" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -14151,19 +14151,19 @@
         <v>30</v>
       </c>
       <c r="E180">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F180">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G180" s="1">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="H180" s="1">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="I180" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -16376,22 +16376,22 @@
         <v>18</v>
       </c>
       <c r="F41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G41" s="1">
         <v>58.06</v>
       </c>
       <c r="H41" s="1">
-        <v>35.48</v>
+        <v>41.94</v>
       </c>
       <c r="I41" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -16443,19 +16443,19 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I43" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -16481,22 +16481,22 @@
         <v>35</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="1">
         <v>94.59</v>
       </c>
       <c r="H44" s="1">
-        <v>2.7</v>
+        <v>5.41</v>
       </c>
       <c r="I44" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -16945,7 +16945,7 @@
         <v>12.5</v>
       </c>
       <c r="I57" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -17003,19 +17003,19 @@
         <v>43</v>
       </c>
       <c r="E59">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G59" s="1">
-        <v>86.05</v>
+        <v>88.37</v>
       </c>
       <c r="H59" s="1">
-        <v>13.95</v>
+        <v>11.63</v>
       </c>
       <c r="I59" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -17038,19 +17038,19 @@
         <v>43</v>
       </c>
       <c r="E60">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F60">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G60" s="1">
-        <v>79.06999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H60" s="1">
-        <v>20.93</v>
+        <v>13.95</v>
       </c>
       <c r="I60" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -17598,19 +17598,19 @@
         <v>15</v>
       </c>
       <c r="E76">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F76">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>53.33</v>
+        <v>100</v>
       </c>
       <c r="H76" s="1">
-        <v>46.67</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>35</v>
       </c>
       <c r="E77">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G77" s="1">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H77" s="1">
-        <v>14.29</v>
+        <v>5.71</v>
       </c>
       <c r="I77" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -17668,19 +17668,19 @@
         <v>21</v>
       </c>
       <c r="E78">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F78">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G78" s="1">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H78" s="1">
-        <v>38.1</v>
+        <v>4.76</v>
       </c>
       <c r="I78" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -17703,19 +17703,19 @@
         <v>37</v>
       </c>
       <c r="E79">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F79">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G79" s="1">
-        <v>78.38</v>
+        <v>97.3</v>
       </c>
       <c r="H79" s="1">
-        <v>21.62</v>
+        <v>2.7</v>
       </c>
       <c r="I79" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -17738,19 +17738,19 @@
         <v>32</v>
       </c>
       <c r="E80">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G80" s="1">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="H80" s="1">
-        <v>15.63</v>
+        <v>3.13</v>
       </c>
       <c r="I80" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -18123,19 +18123,19 @@
         <v>30</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F91">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G91" s="1">
-        <v>66.67</v>
+        <v>96.67</v>
       </c>
       <c r="H91" s="1">
-        <v>33.33</v>
+        <v>3.33</v>
       </c>
       <c r="I91" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -18158,19 +18158,19 @@
         <v>36</v>
       </c>
       <c r="E92">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G92" s="1">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H92" s="1">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="I92" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -18228,16 +18228,16 @@
         <v>30</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F94">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H94" s="1">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="I94" s="2">
         <v>7.8</v>
@@ -18263,19 +18263,19 @@
         <v>32</v>
       </c>
       <c r="E95">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="1">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H95" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I95" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -18298,19 +18298,19 @@
         <v>26</v>
       </c>
       <c r="E96">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G96" s="1">
-        <v>80.77</v>
+        <v>100</v>
       </c>
       <c r="H96" s="1">
-        <v>19.23</v>
+        <v>0</v>
       </c>
       <c r="I96" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -18333,19 +18333,19 @@
         <v>18</v>
       </c>
       <c r="E97">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H97" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I97" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -18368,25 +18368,25 @@
         <v>41</v>
       </c>
       <c r="E98">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="1">
-        <v>87.8</v>
+        <v>95.12</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="I98" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -18648,25 +18648,25 @@
         <v>42</v>
       </c>
       <c r="E106">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F106">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G106" s="1">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H106" s="1">
-        <v>19.05</v>
+        <v>14.29</v>
       </c>
       <c r="I106" s="2">
         <v>7.3</v>
       </c>
       <c r="J106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -19106,22 +19106,22 @@
         <v>30</v>
       </c>
       <c r="F119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G119" s="1">
         <v>88.23999999999999</v>
       </c>
       <c r="H119" s="1">
-        <v>8.82</v>
+        <v>11.76</v>
       </c>
       <c r="I119" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -20258,25 +20258,25 @@
         <v>42</v>
       </c>
       <c r="E152">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F152">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G152" s="1">
-        <v>71.43000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="H152" s="1">
-        <v>23.81</v>
+        <v>26.19</v>
       </c>
       <c r="I152" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -7312,22 +7312,22 @@
         <v>28</v>
       </c>
       <c r="F187">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
         <v>82.34999999999999</v>
       </c>
       <c r="H187" s="1">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="I187" s="2">
         <v>6.7</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -14399,22 +14399,22 @@
         <v>26</v>
       </c>
       <c r="F187">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G187" s="1">
         <v>76.47</v>
       </c>
       <c r="H187" s="1">
-        <v>20.59</v>
+        <v>23.53</v>
       </c>
       <c r="I187" s="2">
         <v>6.7</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -21486,22 +21486,22 @@
         <v>33</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" s="1">
         <v>97.06</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I187" s="2">
         <v>7.3</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1440,22 +1440,25 @@
         <v>34</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>11.76</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.3</v>
       </c>
       <c r="J20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1822,22 +1825,25 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>7.69</v>
+      </c>
+      <c r="I31" s="2">
+        <v>7.7</v>
       </c>
       <c r="J31">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2306,22 +2312,25 @@
         <v>41</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>7.32</v>
+      </c>
+      <c r="I45" s="2">
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2863,22 +2872,25 @@
         <v>41</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>9.76</v>
+      </c>
+      <c r="I61" s="2">
+        <v>6.7</v>
       </c>
       <c r="J61">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3277,22 +3289,25 @@
         <v>38</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>18.42</v>
+      </c>
+      <c r="I73" s="2">
+        <v>6.3</v>
       </c>
       <c r="J73">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3901,22 +3916,25 @@
         <v>32</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F91">
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
       </c>
+      <c r="I91" s="2">
+        <v>6.3</v>
+      </c>
       <c r="J91">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -4003,22 +4021,25 @@
         <v>29</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H94" s="1">
-        <v>0</v>
+        <v>3.45</v>
+      </c>
+      <c r="I94" s="2">
+        <v>6.1</v>
       </c>
       <c r="J94">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -4522,22 +4543,25 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="I109" s="2">
+        <v>8</v>
       </c>
       <c r="J109">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4799,25 +4823,25 @@
         <v>32</v>
       </c>
       <c r="E117">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F117">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
       </c>
       <c r="I117" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -4974,25 +4998,25 @@
         <v>31</v>
       </c>
       <c r="E122">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F122">
         <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
       </c>
       <c r="I122" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5254,22 +5278,25 @@
         <v>43</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H130" s="1">
-        <v>0</v>
+        <v>25.58</v>
+      </c>
+      <c r="I130" s="2">
+        <v>6.7</v>
       </c>
       <c r="J130">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -5286,22 +5313,25 @@
         <v>26</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>76.92</v>
       </c>
       <c r="H131" s="1">
-        <v>0</v>
+        <v>23.08</v>
+      </c>
+      <c r="I131" s="2">
+        <v>7.5</v>
       </c>
       <c r="J131">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5528,25 +5558,25 @@
         <v>30</v>
       </c>
       <c r="E138">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="1">
-        <v>63.33</v>
+        <v>93.33</v>
       </c>
       <c r="H138" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="I138" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J138">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5563,25 +5593,25 @@
         <v>31</v>
       </c>
       <c r="E139">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F139">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G139" s="1">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H139" s="1">
-        <v>22.58</v>
+        <v>25.81</v>
       </c>
       <c r="I139" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5613,10 +5643,10 @@
         <v>7.3</v>
       </c>
       <c r="J140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -5668,22 +5698,25 @@
         <v>28</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>0</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>10.71</v>
+      </c>
+      <c r="I142" s="2">
+        <v>7.7</v>
       </c>
       <c r="J142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -5700,25 +5733,25 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F143">
         <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J143">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -6155,25 +6188,25 @@
         <v>31</v>
       </c>
       <c r="E156">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F156">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G156" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H156" s="1">
-        <v>12.9</v>
+        <v>22.58</v>
       </c>
       <c r="I156" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J156">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -7030,22 +7063,25 @@
         <v>33</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>39.39</v>
+      </c>
+      <c r="I181" s="2">
+        <v>5.9</v>
       </c>
       <c r="J181">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7237,22 +7273,25 @@
         <v>43</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>69.77</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>30.23</v>
+      </c>
+      <c r="I187" s="2">
+        <v>6.9</v>
       </c>
       <c r="J187">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7584,22 +7623,25 @@
         <v>33</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H197" s="1">
-        <v>0</v>
+        <v>27.27</v>
+      </c>
+      <c r="I197" s="2">
+        <v>6.6</v>
       </c>
       <c r="J197">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -7616,22 +7658,25 @@
         <v>22</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H198" s="1">
-        <v>0</v>
+        <v>22.73</v>
+      </c>
+      <c r="I198" s="2">
+        <v>6.5</v>
       </c>
       <c r="J198">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -7648,22 +7693,25 @@
         <v>22</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>22.73</v>
+      </c>
+      <c r="I199" s="2">
+        <v>6.1</v>
       </c>
       <c r="J199">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -8646,19 +8694,19 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -8998,19 +9046,19 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -9446,19 +9494,19 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -9958,19 +10006,19 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -10342,19 +10390,19 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J73">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -10918,19 +10966,19 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G91" s="1">
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J91">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -11014,19 +11062,19 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G94" s="1">
         <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J94">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -11494,19 +11542,19 @@
         <v>0</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G109" s="1">
         <v>0</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J109">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -11750,19 +11798,19 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G117" s="1">
         <v>0</v>
       </c>
       <c r="H117" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -11910,19 +11958,19 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="J122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -12166,19 +12214,19 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G130" s="1">
         <v>0</v>
       </c>
       <c r="H130" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J130">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -12198,19 +12246,19 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
       </c>
       <c r="H131" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J131">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -12422,19 +12470,19 @@
         <v>0</v>
       </c>
       <c r="F138">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G138" s="1">
         <v>0</v>
       </c>
       <c r="H138" s="1">
-        <v>63.33</v>
+        <v>96.67</v>
       </c>
       <c r="J138">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -12454,19 +12502,19 @@
         <v>0</v>
       </c>
       <c r="F139">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G139" s="1">
         <v>0</v>
       </c>
       <c r="H139" s="1">
-        <v>80.65000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -12495,10 +12543,10 @@
         <v>96.97</v>
       </c>
       <c r="J140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -12550,19 +12598,19 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G142" s="1">
         <v>0</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -12582,19 +12630,19 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G143" s="1">
         <v>0</v>
       </c>
       <c r="H143" s="1">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="J143">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -12998,19 +13046,19 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G156" s="1">
         <v>0</v>
       </c>
       <c r="H156" s="1">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="J156">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -13798,19 +13846,19 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G181" s="1">
         <v>0</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J181">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -13990,19 +14038,19 @@
         <v>0</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G187" s="1">
         <v>0</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J187">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -14310,19 +14358,19 @@
         <v>0</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G197" s="1">
         <v>0</v>
       </c>
       <c r="H197" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J197">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -14342,19 +14390,19 @@
         <v>0</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G198" s="1">
         <v>0</v>
       </c>
       <c r="H198" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J198">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -14374,19 +14422,19 @@
         <v>0</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G199" s="1">
         <v>0</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J199">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -15405,22 +15453,25 @@
         <v>34</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>11.76</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.3</v>
       </c>
       <c r="J20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -15787,22 +15838,25 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>7.69</v>
+      </c>
+      <c r="I31" s="2">
+        <v>7.7</v>
       </c>
       <c r="J31">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -16271,22 +16325,25 @@
         <v>41</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>7.32</v>
+      </c>
+      <c r="I45" s="2">
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -16828,22 +16885,25 @@
         <v>41</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>9.76</v>
+      </c>
+      <c r="I61" s="2">
+        <v>6.8</v>
       </c>
       <c r="J61">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -17242,22 +17302,25 @@
         <v>38</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>18.42</v>
+      </c>
+      <c r="I73" s="2">
+        <v>6.7</v>
       </c>
       <c r="J73">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -17866,22 +17929,25 @@
         <v>32</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F91">
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
       </c>
+      <c r="I91" s="2">
+        <v>6.3</v>
+      </c>
       <c r="J91">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -17968,22 +18034,25 @@
         <v>29</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H94" s="1">
-        <v>0</v>
+        <v>3.45</v>
+      </c>
+      <c r="I94" s="2">
+        <v>6.1</v>
       </c>
       <c r="J94">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -18487,22 +18556,25 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H109" s="1">
-        <v>0</v>
+        <v>16.67</v>
+      </c>
+      <c r="I109" s="2">
+        <v>8</v>
       </c>
       <c r="J109">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -18764,25 +18836,25 @@
         <v>32</v>
       </c>
       <c r="E117">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F117">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
       </c>
       <c r="I117" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -18939,25 +19011,25 @@
         <v>31</v>
       </c>
       <c r="E122">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F122">
         <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
       </c>
       <c r="I122" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -19219,22 +19291,25 @@
         <v>43</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>74.42</v>
       </c>
       <c r="H130" s="1">
-        <v>0</v>
+        <v>25.58</v>
+      </c>
+      <c r="I130" s="2">
+        <v>6.7</v>
       </c>
       <c r="J130">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -19251,22 +19326,25 @@
         <v>26</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>76.92</v>
       </c>
       <c r="H131" s="1">
-        <v>0</v>
+        <v>23.08</v>
+      </c>
+      <c r="I131" s="2">
+        <v>7.5</v>
       </c>
       <c r="J131">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -19493,25 +19571,25 @@
         <v>30</v>
       </c>
       <c r="E138">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G138" s="1">
-        <v>63.33</v>
+        <v>93.33</v>
       </c>
       <c r="H138" s="1">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="I138" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J138">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -19528,25 +19606,25 @@
         <v>31</v>
       </c>
       <c r="E139">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F139">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G139" s="1">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H139" s="1">
-        <v>29.03</v>
+        <v>38.71</v>
       </c>
       <c r="I139" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -19566,22 +19644,22 @@
         <v>30</v>
       </c>
       <c r="F140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G140" s="1">
         <v>90.91</v>
       </c>
       <c r="H140" s="1">
-        <v>6.06</v>
+        <v>9.09</v>
       </c>
       <c r="I140" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -19633,22 +19711,25 @@
         <v>28</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>0</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>10.71</v>
+      </c>
+      <c r="I142" s="2">
+        <v>7.7</v>
       </c>
       <c r="J142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -19665,25 +19746,25 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F143">
         <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J143">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -20120,25 +20201,25 @@
         <v>31</v>
       </c>
       <c r="E156">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F156">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G156" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H156" s="1">
-        <v>12.9</v>
+        <v>22.58</v>
       </c>
       <c r="I156" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J156">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -20995,22 +21076,25 @@
         <v>33</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>39.39</v>
+      </c>
+      <c r="I181" s="2">
+        <v>5.9</v>
       </c>
       <c r="J181">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -21202,22 +21286,25 @@
         <v>43</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>69.77</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>30.23</v>
+      </c>
+      <c r="I187" s="2">
+        <v>6.9</v>
       </c>
       <c r="J187">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -21549,22 +21636,25 @@
         <v>33</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H197" s="1">
-        <v>0</v>
+        <v>27.27</v>
+      </c>
+      <c r="I197" s="2">
+        <v>6.6</v>
       </c>
       <c r="J197">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -21581,22 +21671,25 @@
         <v>22</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H198" s="1">
-        <v>0</v>
+        <v>22.73</v>
+      </c>
+      <c r="I198" s="2">
+        <v>6.5</v>
       </c>
       <c r="J198">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -21613,22 +21706,25 @@
         <v>22</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>22.73</v>
+      </c>
+      <c r="I199" s="2">
+        <v>6.1</v>
       </c>
       <c r="J199">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1965,22 +1965,25 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I35" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3152,22 +3155,25 @@
         <v>38</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>5.26</v>
+      </c>
+      <c r="I69" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J69">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3429,22 +3435,25 @@
         <v>28</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>21.43</v>
+      </c>
+      <c r="I77" s="2">
+        <v>6.1</v>
       </c>
       <c r="J77">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4511,22 +4520,25 @@
         <v>36</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F108">
         <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
       </c>
+      <c r="I108" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J108">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7798,22 +7810,25 @@
         <v>30</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H202" s="1">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="I202" s="2">
+        <v>4.8</v>
       </c>
       <c r="J202">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -7830,22 +7845,25 @@
         <v>30</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>36.67</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>63.33</v>
+      </c>
+      <c r="I203" s="2">
+        <v>5</v>
       </c>
       <c r="J203">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -7862,22 +7880,25 @@
         <v>33</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="I204" s="2">
+        <v>6.8</v>
       </c>
       <c r="J204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -7894,22 +7915,25 @@
         <v>33</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G205" s="1">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="H205" s="1">
-        <v>0</v>
+        <v>45.45</v>
+      </c>
+      <c r="I205" s="2">
+        <v>5.8</v>
       </c>
       <c r="J205">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -7926,22 +7950,25 @@
         <v>25</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G206" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H206" s="1">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="I206" s="2">
+        <v>5.7</v>
       </c>
       <c r="J206">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K206" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -9174,19 +9201,19 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -10262,19 +10289,19 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J69">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -10518,19 +10545,19 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J77">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -11510,19 +11537,19 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G108" s="1">
         <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J108">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -14518,19 +14545,19 @@
         <v>0</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G202" s="1">
         <v>0</v>
       </c>
       <c r="H202" s="1">
-        <v>0</v>
+        <v>96.67</v>
       </c>
       <c r="J202">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -14550,19 +14577,19 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G203" s="1">
         <v>0</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J203">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -14582,19 +14609,19 @@
         <v>0</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G204" s="1">
         <v>0</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -14614,19 +14641,19 @@
         <v>0</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G205" s="1">
         <v>0</v>
       </c>
       <c r="H205" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J205">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -14646,19 +14673,19 @@
         <v>0</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G206" s="1">
         <v>0</v>
       </c>
       <c r="H206" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J206">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K206" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -15978,22 +16005,25 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I35" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -17165,22 +17195,25 @@
         <v>38</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>5.26</v>
+      </c>
+      <c r="I69" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J69">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -17442,22 +17475,25 @@
         <v>28</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>21.43</v>
+      </c>
+      <c r="I77" s="2">
+        <v>6.2</v>
       </c>
       <c r="J77">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -18524,22 +18560,25 @@
         <v>36</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F108">
         <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
       </c>
+      <c r="I108" s="2">
+        <v>9.1</v>
+      </c>
       <c r="J108">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -21811,22 +21850,25 @@
         <v>30</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H202" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I202" s="2">
+        <v>5.5</v>
       </c>
       <c r="J202">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -21843,22 +21885,25 @@
         <v>30</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>36.67</v>
       </c>
       <c r="H203" s="1">
-        <v>0</v>
+        <v>63.33</v>
+      </c>
+      <c r="I203" s="2">
+        <v>5.6</v>
       </c>
       <c r="J203">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -21875,22 +21920,25 @@
         <v>33</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="I204" s="2">
+        <v>6.9</v>
       </c>
       <c r="J204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -21907,22 +21955,25 @@
         <v>33</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G205" s="1">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="H205" s="1">
-        <v>0</v>
+        <v>45.45</v>
+      </c>
+      <c r="I205" s="2">
+        <v>6.1</v>
       </c>
       <c r="J205">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -21939,22 +21990,25 @@
         <v>25</v>
       </c>
       <c r="E206">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G206" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H206" s="1">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="I206" s="2">
+        <v>6.1</v>
       </c>
       <c r="J206">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K206" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -982,7 +982,7 @@
         <v>79</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>26</v>
@@ -991,19 +991,19 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H7" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
         <v>8.1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3992,7 +3992,7 @@
         <v>101</v>
       </c>
       <c r="D93">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>24</v>
@@ -4001,19 +4001,19 @@
         <v>3</v>
       </c>
       <c r="G93" s="1">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H93" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="I93" s="2">
         <v>7.3</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -4027,7 +4027,7 @@
         <v>96</v>
       </c>
       <c r="D94">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E94">
         <v>28</v>
@@ -4036,19 +4036,19 @@
         <v>1</v>
       </c>
       <c r="G94" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H94" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="I94" s="2">
         <v>6.1</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -5077,7 +5077,7 @@
         <v>94</v>
       </c>
       <c r="D124">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E124">
         <v>12</v>
@@ -5086,19 +5086,19 @@
         <v>17</v>
       </c>
       <c r="G124" s="1">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="H124" s="1">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="I124" s="2">
         <v>6</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -5497,28 +5497,28 @@
         <v>95</v>
       </c>
       <c r="D136">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E136">
         <v>26</v>
       </c>
       <c r="F136">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G136" s="1">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H136" s="1">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
       <c r="I136" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J136">
         <v>1</v>
       </c>
       <c r="K136" s="1">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -5532,7 +5532,7 @@
         <v>95</v>
       </c>
       <c r="D137">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E137">
         <v>24</v>
@@ -5541,19 +5541,19 @@
         <v>5</v>
       </c>
       <c r="G137" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H137" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="I137" s="2">
         <v>7.1</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -5637,7 +5637,7 @@
         <v>97</v>
       </c>
       <c r="D140">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E140">
         <v>30</v>
@@ -5646,19 +5646,19 @@
         <v>2</v>
       </c>
       <c r="G140" s="1">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H140" s="1">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="I140" s="2">
         <v>7.3</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -5707,7 +5707,7 @@
         <v>97</v>
       </c>
       <c r="D142">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E142">
         <v>25</v>
@@ -5716,19 +5716,19 @@
         <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H142" s="1">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="I142" s="2">
         <v>7.7</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -6162,22 +6162,22 @@
         <v>104</v>
       </c>
       <c r="D155">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E155">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F155">
         <v>2</v>
       </c>
       <c r="G155" s="1">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H155" s="1">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="I155" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>94</v>
       </c>
       <c r="D165">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E165">
         <v>25</v>
@@ -6521,19 +6521,19 @@
         <v>7</v>
       </c>
       <c r="G165" s="1">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H165" s="1">
-        <v>21.21</v>
+        <v>20.59</v>
       </c>
       <c r="I165" s="2">
         <v>6.9</v>
       </c>
       <c r="J165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -7072,7 +7072,7 @@
         <v>96</v>
       </c>
       <c r="D181">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E181">
         <v>20</v>
@@ -7081,19 +7081,19 @@
         <v>13</v>
       </c>
       <c r="G181" s="1">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="H181" s="1">
-        <v>39.39</v>
+        <v>38.24</v>
       </c>
       <c r="I181" s="2">
         <v>5.9</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7317,7 +7317,7 @@
         <v>102</v>
       </c>
       <c r="D188">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E188">
         <v>29</v>
@@ -7326,19 +7326,19 @@
         <v>6</v>
       </c>
       <c r="G188" s="1">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="H188" s="1">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="I188" s="2">
         <v>8.1</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7352,7 +7352,7 @@
         <v>103</v>
       </c>
       <c r="D189">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E189">
         <v>30</v>
@@ -7361,19 +7361,19 @@
         <v>5</v>
       </c>
       <c r="G189" s="1">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H189" s="1">
-        <v>14.29</v>
+        <v>13.89</v>
       </c>
       <c r="I189" s="2">
         <v>7.6</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7953,22 +7953,22 @@
         <v>9</v>
       </c>
       <c r="F206">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G206" s="1">
         <v>36</v>
       </c>
       <c r="H206" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I206" s="2">
         <v>5.7</v>
       </c>
       <c r="J206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -8299,7 +8299,7 @@
         <v>79</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8311,13 +8311,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11051,7 +11051,7 @@
         <v>101</v>
       </c>
       <c r="D93">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -11063,13 +11063,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>77.14</v>
+        <v>75</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -11083,7 +11083,7 @@
         <v>96</v>
       </c>
       <c r="D94">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -11095,13 +11095,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -12043,7 +12043,7 @@
         <v>94</v>
       </c>
       <c r="D124">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -12055,13 +12055,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="1">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -12427,25 +12427,25 @@
         <v>95</v>
       </c>
       <c r="D136">
+        <v>34</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
         <v>33</v>
       </c>
-      <c r="E136">
-        <v>0</v>
-      </c>
-      <c r="F136">
-        <v>32</v>
-      </c>
       <c r="G136" s="1">
         <v>0</v>
       </c>
       <c r="H136" s="1">
-        <v>96.97</v>
+        <v>97.06</v>
       </c>
       <c r="J136">
         <v>1</v>
       </c>
       <c r="K136" s="1">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -12459,7 +12459,7 @@
         <v>95</v>
       </c>
       <c r="D137">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -12471,13 +12471,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="1">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -12555,7 +12555,7 @@
         <v>97</v>
       </c>
       <c r="D140">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -12567,13 +12567,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="1">
-        <v>96.97</v>
+        <v>94.12</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -12619,7 +12619,7 @@
         <v>97</v>
       </c>
       <c r="D142">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -12631,13 +12631,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="1">
-        <v>100</v>
+        <v>96.55</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -13035,13 +13035,13 @@
         <v>104</v>
       </c>
       <c r="D155">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E155">
         <v>0</v>
       </c>
       <c r="F155">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G155" s="1">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>94</v>
       </c>
       <c r="D165">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -13367,13 +13367,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="1">
-        <v>96.97</v>
+        <v>94.12</v>
       </c>
       <c r="J165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -13867,7 +13867,7 @@
         <v>96</v>
       </c>
       <c r="D181">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -13879,13 +13879,13 @@
         <v>0</v>
       </c>
       <c r="H181" s="1">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -14091,7 +14091,7 @@
         <v>102</v>
       </c>
       <c r="D188">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -14103,13 +14103,13 @@
         <v>0</v>
       </c>
       <c r="H188" s="1">
-        <v>100</v>
+        <v>97.22</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -14123,7 +14123,7 @@
         <v>103</v>
       </c>
       <c r="D189">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -14135,13 +14135,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="1">
-        <v>100</v>
+        <v>97.22</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -14673,19 +14673,19 @@
         <v>0</v>
       </c>
       <c r="F206">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G206" s="1">
         <v>0</v>
       </c>
       <c r="H206" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -15022,7 +15022,7 @@
         <v>79</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>26</v>
@@ -15031,19 +15031,19 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H7" s="1">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -18032,7 +18032,7 @@
         <v>101</v>
       </c>
       <c r="D93">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>24</v>
@@ -18041,19 +18041,19 @@
         <v>11</v>
       </c>
       <c r="G93" s="1">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H93" s="1">
-        <v>31.43</v>
+        <v>30.56</v>
       </c>
       <c r="I93" s="2">
         <v>6.8</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -18067,7 +18067,7 @@
         <v>96</v>
       </c>
       <c r="D94">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E94">
         <v>28</v>
@@ -18076,19 +18076,19 @@
         <v>1</v>
       </c>
       <c r="G94" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H94" s="1">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="I94" s="2">
         <v>6.1</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -19117,7 +19117,7 @@
         <v>94</v>
       </c>
       <c r="D124">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E124">
         <v>12</v>
@@ -19126,19 +19126,19 @@
         <v>17</v>
       </c>
       <c r="G124" s="1">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="H124" s="1">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="I124" s="2">
         <v>6.1</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -19537,28 +19537,28 @@
         <v>95</v>
       </c>
       <c r="D136">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E136">
         <v>26</v>
       </c>
       <c r="F136">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G136" s="1">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H136" s="1">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
       <c r="I136" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J136">
         <v>1</v>
       </c>
       <c r="K136" s="1">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -19572,7 +19572,7 @@
         <v>95</v>
       </c>
       <c r="D137">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E137">
         <v>24</v>
@@ -19581,19 +19581,19 @@
         <v>5</v>
       </c>
       <c r="G137" s="1">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H137" s="1">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
       <c r="I137" s="2">
         <v>7.1</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -19677,7 +19677,7 @@
         <v>97</v>
       </c>
       <c r="D140">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E140">
         <v>30</v>
@@ -19686,19 +19686,19 @@
         <v>3</v>
       </c>
       <c r="G140" s="1">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H140" s="1">
-        <v>9.09</v>
+        <v>8.82</v>
       </c>
       <c r="I140" s="2">
         <v>7.2</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -19747,7 +19747,7 @@
         <v>97</v>
       </c>
       <c r="D142">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E142">
         <v>25</v>
@@ -19756,19 +19756,19 @@
         <v>3</v>
       </c>
       <c r="G142" s="1">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H142" s="1">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="I142" s="2">
         <v>7.7</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -20202,22 +20202,22 @@
         <v>104</v>
       </c>
       <c r="D155">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E155">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F155">
         <v>2</v>
       </c>
       <c r="G155" s="1">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H155" s="1">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="I155" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -20552,7 +20552,7 @@
         <v>94</v>
       </c>
       <c r="D165">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E165">
         <v>25</v>
@@ -20561,19 +20561,19 @@
         <v>8</v>
       </c>
       <c r="G165" s="1">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H165" s="1">
-        <v>24.24</v>
+        <v>23.53</v>
       </c>
       <c r="I165" s="2">
         <v>6.8</v>
       </c>
       <c r="J165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -21112,7 +21112,7 @@
         <v>96</v>
       </c>
       <c r="D181">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E181">
         <v>20</v>
@@ -21121,19 +21121,19 @@
         <v>13</v>
       </c>
       <c r="G181" s="1">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="H181" s="1">
-        <v>39.39</v>
+        <v>38.24</v>
       </c>
       <c r="I181" s="2">
         <v>5.9</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -21357,7 +21357,7 @@
         <v>102</v>
       </c>
       <c r="D188">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E188">
         <v>29</v>
@@ -21366,19 +21366,19 @@
         <v>6</v>
       </c>
       <c r="G188" s="1">
-        <v>82.86</v>
+        <v>80.56</v>
       </c>
       <c r="H188" s="1">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="I188" s="2">
         <v>8.1</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -21392,7 +21392,7 @@
         <v>103</v>
       </c>
       <c r="D189">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E189">
         <v>30</v>
@@ -21401,19 +21401,19 @@
         <v>5</v>
       </c>
       <c r="G189" s="1">
-        <v>85.70999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H189" s="1">
-        <v>14.29</v>
+        <v>13.89</v>
       </c>
       <c r="I189" s="2">
         <v>7.6</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -21993,22 +21993,22 @@
         <v>9</v>
       </c>
       <c r="F206">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G206" s="1">
         <v>36</v>
       </c>
       <c r="H206" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I206" s="2">
         <v>6.1</v>
       </c>
       <c r="J206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11">

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1325,19 +1325,19 @@
         <v>101</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>11</v>
       </c>
       <c r="G15" s="1">
-        <v>73.17</v>
+        <v>73.81</v>
       </c>
       <c r="H15" s="1">
-        <v>26.83</v>
+        <v>26.19</v>
       </c>
       <c r="I15" s="2">
         <v>6.4</v>
@@ -1745,22 +1745,22 @@
         <v>108</v>
       </c>
       <c r="D27">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <v>19</v>
       </c>
       <c r="G27" s="1">
-        <v>54.76</v>
+        <v>53.66</v>
       </c>
       <c r="H27" s="1">
-        <v>45.24</v>
+        <v>46.34</v>
       </c>
       <c r="I27" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2445,19 +2445,19 @@
         <v>101</v>
       </c>
       <c r="D47">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E47">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47">
         <v>11</v>
       </c>
       <c r="G47" s="1">
-        <v>74.42</v>
+        <v>73.81</v>
       </c>
       <c r="H47" s="1">
-        <v>25.58</v>
+        <v>26.19</v>
       </c>
       <c r="I47" s="2">
         <v>6.7</v>
@@ -2900,22 +2900,22 @@
         <v>108</v>
       </c>
       <c r="D60">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E60">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F60">
         <v>7</v>
       </c>
       <c r="G60" s="1">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H60" s="1">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="I60" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3215,22 +3215,22 @@
         <v>121</v>
       </c>
       <c r="D69">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E69">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F69">
         <v>17</v>
       </c>
       <c r="G69" s="1">
-        <v>59.52</v>
+        <v>58.54</v>
       </c>
       <c r="H69" s="1">
-        <v>40.48</v>
+        <v>41.46</v>
       </c>
       <c r="I69" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -3915,19 +3915,19 @@
         <v>125</v>
       </c>
       <c r="D89">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E89">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F89">
         <v>14</v>
       </c>
       <c r="G89" s="1">
-        <v>65.84999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H89" s="1">
-        <v>34.15</v>
+        <v>33.33</v>
       </c>
       <c r="I89" s="2">
         <v>6.6</v>
@@ -4335,19 +4335,19 @@
         <v>119</v>
       </c>
       <c r="D101">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E101">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F101">
         <v>7</v>
       </c>
       <c r="G101" s="1">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H101" s="1">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="I101" s="2">
         <v>7.5</v>
@@ -4965,19 +4965,19 @@
         <v>125</v>
       </c>
       <c r="D119">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E119">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F119">
         <v>8</v>
       </c>
       <c r="G119" s="1">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H119" s="1">
-        <v>19.51</v>
+        <v>20</v>
       </c>
       <c r="I119" s="2">
         <v>7</v>
@@ -5805,22 +5805,22 @@
         <v>122</v>
       </c>
       <c r="D143">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E143">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F143">
         <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>92.86</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H143" s="1">
-        <v>7.14</v>
+        <v>7.32</v>
       </c>
       <c r="I143" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -6365,19 +6365,19 @@
         <v>119</v>
       </c>
       <c r="D159">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E159">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F159">
         <v>13</v>
       </c>
       <c r="G159" s="1">
-        <v>69.77</v>
+        <v>69.05</v>
       </c>
       <c r="H159" s="1">
-        <v>30.23</v>
+        <v>30.95</v>
       </c>
       <c r="I159" s="2">
         <v>6.9</v>
@@ -6750,22 +6750,22 @@
         <v>121</v>
       </c>
       <c r="D170">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E170">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F170">
         <v>9</v>
       </c>
       <c r="G170" s="1">
-        <v>78.05</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>21.95</v>
+        <v>21.43</v>
       </c>
       <c r="I170" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -6960,22 +6960,22 @@
         <v>122</v>
       </c>
       <c r="D176">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E176">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F176">
         <v>3</v>
       </c>
       <c r="G176" s="1">
-        <v>92.68000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H176" s="1">
-        <v>7.32</v>
+        <v>7.14</v>
       </c>
       <c r="I176" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -8618,13 +8618,13 @@
         <v>101</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -9002,13 +9002,13 @@
         <v>108</v>
       </c>
       <c r="D27">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -9642,13 +9642,13 @@
         <v>101</v>
       </c>
       <c r="D47">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
@@ -10058,13 +10058,13 @@
         <v>108</v>
       </c>
       <c r="D60">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
@@ -10346,13 +10346,13 @@
         <v>121</v>
       </c>
       <c r="D69">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -10986,13 +10986,13 @@
         <v>125</v>
       </c>
       <c r="D89">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G89" s="1">
         <v>0</v>
@@ -11370,13 +11370,13 @@
         <v>119</v>
       </c>
       <c r="D101">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G101" s="1">
         <v>0</v>
@@ -11946,13 +11946,13 @@
         <v>125</v>
       </c>
       <c r="D119">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G119" s="1">
         <v>0</v>
@@ -12714,13 +12714,13 @@
         <v>122</v>
       </c>
       <c r="D143">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G143" s="1">
         <v>0</v>
@@ -13226,13 +13226,13 @@
         <v>119</v>
       </c>
       <c r="D159">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E159">
         <v>0</v>
       </c>
       <c r="F159">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G159" s="1">
         <v>0</v>
@@ -13578,13 +13578,13 @@
         <v>121</v>
       </c>
       <c r="D170">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G170" s="1">
         <v>0</v>
@@ -13770,13 +13770,13 @@
         <v>122</v>
       </c>
       <c r="D176">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E176">
         <v>0</v>
       </c>
       <c r="F176">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G176" s="1">
         <v>0</v>
@@ -15365,19 +15365,19 @@
         <v>101</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>11</v>
       </c>
       <c r="G15" s="1">
-        <v>73.17</v>
+        <v>73.81</v>
       </c>
       <c r="H15" s="1">
-        <v>26.83</v>
+        <v>26.19</v>
       </c>
       <c r="I15" s="2">
         <v>6.7</v>
@@ -15785,22 +15785,22 @@
         <v>108</v>
       </c>
       <c r="D27">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <v>19</v>
       </c>
       <c r="G27" s="1">
-        <v>54.76</v>
+        <v>53.66</v>
       </c>
       <c r="H27" s="1">
-        <v>45.24</v>
+        <v>46.34</v>
       </c>
       <c r="I27" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -16485,19 +16485,19 @@
         <v>101</v>
       </c>
       <c r="D47">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E47">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47">
         <v>11</v>
       </c>
       <c r="G47" s="1">
-        <v>74.42</v>
+        <v>73.81</v>
       </c>
       <c r="H47" s="1">
-        <v>25.58</v>
+        <v>26.19</v>
       </c>
       <c r="I47" s="2">
         <v>6.7</v>
@@ -16940,22 +16940,22 @@
         <v>108</v>
       </c>
       <c r="D60">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E60">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F60">
         <v>7</v>
       </c>
       <c r="G60" s="1">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H60" s="1">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="I60" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -17255,22 +17255,22 @@
         <v>121</v>
       </c>
       <c r="D69">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E69">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F69">
         <v>17</v>
       </c>
       <c r="G69" s="1">
-        <v>59.52</v>
+        <v>58.54</v>
       </c>
       <c r="H69" s="1">
-        <v>40.48</v>
+        <v>41.46</v>
       </c>
       <c r="I69" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -17955,19 +17955,19 @@
         <v>125</v>
       </c>
       <c r="D89">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E89">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F89">
         <v>14</v>
       </c>
       <c r="G89" s="1">
-        <v>65.84999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H89" s="1">
-        <v>34.15</v>
+        <v>33.33</v>
       </c>
       <c r="I89" s="2">
         <v>6.6</v>
@@ -18375,19 +18375,19 @@
         <v>119</v>
       </c>
       <c r="D101">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E101">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F101">
         <v>7</v>
       </c>
       <c r="G101" s="1">
-        <v>82.93000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="H101" s="1">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="I101" s="2">
         <v>7.5</v>
@@ -19005,19 +19005,19 @@
         <v>125</v>
       </c>
       <c r="D119">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E119">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F119">
         <v>8</v>
       </c>
       <c r="G119" s="1">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H119" s="1">
-        <v>19.51</v>
+        <v>20</v>
       </c>
       <c r="I119" s="2">
         <v>7</v>
@@ -19845,22 +19845,22 @@
         <v>122</v>
       </c>
       <c r="D143">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E143">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F143">
         <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>92.86</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H143" s="1">
-        <v>7.14</v>
+        <v>7.32</v>
       </c>
       <c r="I143" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -20405,19 +20405,19 @@
         <v>119</v>
       </c>
       <c r="D159">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E159">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F159">
         <v>13</v>
       </c>
       <c r="G159" s="1">
-        <v>69.77</v>
+        <v>69.05</v>
       </c>
       <c r="H159" s="1">
-        <v>30.23</v>
+        <v>30.95</v>
       </c>
       <c r="I159" s="2">
         <v>6.9</v>
@@ -20790,22 +20790,22 @@
         <v>121</v>
       </c>
       <c r="D170">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E170">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F170">
         <v>9</v>
       </c>
       <c r="G170" s="1">
-        <v>78.05</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>21.95</v>
+        <v>21.43</v>
       </c>
       <c r="I170" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J170">
         <v>0</v>
@@ -21000,22 +21000,22 @@
         <v>122</v>
       </c>
       <c r="D176">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E176">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F176">
         <v>3</v>
       </c>
       <c r="G176" s="1">
-        <v>92.68000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H176" s="1">
-        <v>7.32</v>
+        <v>7.14</v>
       </c>
       <c r="I176" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J176">
         <v>0</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1561,7 +1561,7 @@
         <v>126</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>30</v>
@@ -1570,19 +1570,19 @@
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>90.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H22" s="1">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I22" s="2">
         <v>7.8</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1698,7 +1698,7 @@
         <v>116</v>
       </c>
       <c r="D26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>119</v>
@@ -1707,19 +1707,19 @@
         <v>10</v>
       </c>
       <c r="G26" s="1">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="H26" s="1">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I26" s="2">
         <v>7.4</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="1">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2042,7 +2042,7 @@
         <v>126</v>
       </c>
       <c r="D36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36">
         <v>28</v>
@@ -2051,19 +2051,19 @@
         <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H36" s="1">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="I36" s="2">
         <v>7.6</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2109,7 +2109,7 @@
         <v>116</v>
       </c>
       <c r="D38">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38">
         <v>125</v>
@@ -2118,19 +2118,19 @@
         <v>42</v>
       </c>
       <c r="G38" s="1">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="I38" s="2">
         <v>7.4</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5488,25 +5488,25 @@
         <v>36</v>
       </c>
       <c r="E136">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F136">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G136" s="1">
-        <v>66.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H136" s="1">
-        <v>8.300000000000001</v>
+        <v>27.8</v>
       </c>
       <c r="I136" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K136" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -5555,25 +5555,25 @@
         <v>186</v>
       </c>
       <c r="E138">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F138">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G138" s="1">
-        <v>87.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H138" s="1">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="I138" s="2">
         <v>7.4</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5899,7 +5899,7 @@
         <v>126</v>
       </c>
       <c r="D148">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E148">
         <v>28</v>
@@ -5908,19 +5908,19 @@
         <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H148" s="1">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="I148" s="2">
         <v>7.3</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5931,7 +5931,7 @@
         <v>116</v>
       </c>
       <c r="D149">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E149">
         <v>82</v>
@@ -5940,19 +5940,19 @@
         <v>21</v>
       </c>
       <c r="G149" s="1">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H149" s="1">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I149" s="2">
         <v>7.4</v>
       </c>
       <c r="J149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6001,19 +6001,19 @@
         <v>126</v>
       </c>
       <c r="D151">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E151">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F151">
         <v>4</v>
       </c>
       <c r="G151" s="1">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H151" s="1">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="I151" s="2">
         <v>8.699999999999999</v>
@@ -6068,19 +6068,19 @@
         <v>116</v>
       </c>
       <c r="D153">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E153">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F153">
         <v>15</v>
       </c>
       <c r="G153" s="1">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H153" s="1">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I153" s="2">
         <v>7.4</v>
@@ -6966,7 +6966,7 @@
         <v>126</v>
       </c>
       <c r="D179">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E179">
         <v>31</v>
@@ -6975,19 +6975,19 @@
         <v>1</v>
       </c>
       <c r="G179" s="1">
-        <v>96.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H179" s="1">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I179" s="2">
         <v>7.3</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K179" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7103,7 +7103,7 @@
         <v>116</v>
       </c>
       <c r="D183">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E183">
         <v>193</v>
@@ -7112,7 +7112,7 @@
         <v>32</v>
       </c>
       <c r="G183" s="1">
-        <v>85.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H183" s="1">
         <v>14.2</v>
@@ -7121,10 +7121,10 @@
         <v>7.4</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K183" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7141,13 +7141,13 @@
         <v>34</v>
       </c>
       <c r="E184">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F184">
         <v>13</v>
       </c>
       <c r="G184" s="1">
-        <v>58.8</v>
+        <v>61.8</v>
       </c>
       <c r="H184" s="1">
         <v>38.2</v>
@@ -7156,10 +7156,10 @@
         <v>5.9</v>
       </c>
       <c r="J184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7348,13 +7348,13 @@
         <v>138</v>
       </c>
       <c r="E190">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F190">
         <v>47</v>
       </c>
       <c r="G190" s="1">
-        <v>65.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H190" s="1">
         <v>34.1</v>
@@ -7363,10 +7363,10 @@
         <v>7.4</v>
       </c>
       <c r="J190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7418,19 +7418,19 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F192">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G192" s="1">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H192" s="1">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="I192" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -7520,16 +7520,16 @@
         <v>125</v>
       </c>
       <c r="E195">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F195">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G195" s="1">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="H195" s="1">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="I195" s="2">
         <v>7.4</v>
@@ -9304,7 +9304,7 @@
         <v>126</v>
       </c>
       <c r="D247">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E247">
         <v>22</v>
@@ -9313,19 +9313,19 @@
         <v>11</v>
       </c>
       <c r="G247" s="1">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="H247" s="1">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="I247" s="2">
         <v>6.8</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K247" s="1">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9406,7 +9406,7 @@
         <v>116</v>
       </c>
       <c r="D250">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E250">
         <v>69</v>
@@ -9415,19 +9415,19 @@
         <v>81</v>
       </c>
       <c r="G250" s="1">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="H250" s="1">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="I250" s="2">
         <v>7.4</v>
       </c>
       <c r="J250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K250" s="1">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -9840,25 +9840,25 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -9875,25 +9875,25 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -9910,25 +9910,25 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -9945,25 +9945,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -9977,25 +9977,25 @@
         <v>75</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -10012,25 +10012,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>22.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -10047,25 +10047,25 @@
         <v>41</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>17.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -10082,25 +10082,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -10117,25 +10117,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -10152,25 +10152,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -10187,25 +10187,25 @@
         <v>41</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>63.4</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>36.6</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -10219,25 +10219,25 @@
         <v>207</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="F13">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>76.8</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>23.2</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J13">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -10254,25 +10254,25 @@
         <v>38</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>18.4</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -10289,25 +10289,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -10321,25 +10321,25 @@
         <v>70</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F16">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>21.4</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -10356,25 +10356,25 @@
         <v>43</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -10391,25 +10391,25 @@
         <v>42</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J18">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -10426,25 +10426,25 @@
         <v>42</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -10461,25 +10461,25 @@
         <v>41</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F20">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J20">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -10493,25 +10493,25 @@
         <v>168</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F21">
-        <v>168</v>
+        <v>22</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>13.1</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J21">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -10525,7 +10525,7 @@
         <v>126</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -10537,13 +10537,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -10662,7 +10662,7 @@
         <v>116</v>
       </c>
       <c r="D26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -10674,13 +10674,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>99.2</v>
+        <v>98.5</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -10700,25 +10700,25 @@
         <v>19</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -10732,25 +10732,25 @@
         <v>19</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J28">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -10881,7 +10881,7 @@
         <v>100</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J32">
         <v>114</v>
@@ -11006,7 +11006,7 @@
         <v>126</v>
       </c>
       <c r="D36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -11018,13 +11018,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -11073,7 +11073,7 @@
         <v>116</v>
       </c>
       <c r="D38">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -11085,13 +11085,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J38">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -11190,7 +11190,7 @@
         <v>100</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J41">
         <v>60</v>
@@ -11213,25 +11213,25 @@
         <v>39</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J42">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -11248,25 +11248,25 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F43">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H43" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J43">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -11283,25 +11283,25 @@
         <v>25</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H44" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J44">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -11315,25 +11315,25 @@
         <v>94</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F45">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="H45" s="1">
-        <v>100</v>
+        <v>21.3</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J45">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -11534,7 +11534,7 @@
         <v>99.2</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J51">
         <v>119</v>
@@ -11557,25 +11557,25 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F52">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="H52" s="1">
-        <v>100</v>
+        <v>46.7</v>
       </c>
       <c r="I52" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J52">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -11592,25 +11592,25 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H53" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I53" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J53">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -11627,25 +11627,25 @@
         <v>28</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F54">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>53.6</v>
       </c>
       <c r="H54" s="1">
-        <v>100</v>
+        <v>46.4</v>
       </c>
       <c r="I54" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J54">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -11662,25 +11662,25 @@
         <v>21</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H55" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I55" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J55">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -11697,25 +11697,25 @@
         <v>17</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="H56" s="1">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="I56" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J56">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -11732,25 +11732,25 @@
         <v>19</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F57">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="H57" s="1">
-        <v>100</v>
+        <v>42.1</v>
       </c>
       <c r="I57" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J57">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -11764,25 +11764,25 @@
         <v>135</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F58">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="H58" s="1">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="I58" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J58">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -11878,7 +11878,7 @@
         <v>100</v>
       </c>
       <c r="I61" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J61">
         <v>68</v>
@@ -11901,25 +11901,25 @@
         <v>34</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F62">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="H62" s="1">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I62" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J62">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -11936,25 +11936,25 @@
         <v>37</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F63">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>70.3</v>
       </c>
       <c r="H63" s="1">
-        <v>100</v>
+        <v>29.7</v>
       </c>
       <c r="I63" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J63">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -12006,25 +12006,25 @@
         <v>29</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F65">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="H65" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
       <c r="I65" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J65">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -12073,25 +12073,25 @@
         <v>166</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F67">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>48.2</v>
       </c>
       <c r="H67" s="1">
-        <v>98.8</v>
+        <v>50.6</v>
       </c>
       <c r="I67" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J67">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -12362,7 +12362,7 @@
         <v>100</v>
       </c>
       <c r="I75" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J75">
         <v>278</v>
@@ -12385,25 +12385,25 @@
         <v>20</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F76">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H76" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I76" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J76">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -12420,25 +12420,25 @@
         <v>26</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F77">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="H77" s="1">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="I77" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J77">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -12455,25 +12455,25 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F78">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H78" s="1">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="I78" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J78">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -12490,25 +12490,25 @@
         <v>31</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F79">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H79" s="1">
-        <v>100</v>
+        <v>38.7</v>
       </c>
       <c r="I79" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J79">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -12522,25 +12522,25 @@
         <v>94</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F80">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>61.7</v>
       </c>
       <c r="H80" s="1">
-        <v>100</v>
+        <v>38.3</v>
       </c>
       <c r="I80" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J80">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -12636,7 +12636,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="I83" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J83">
         <v>64</v>
@@ -12729,25 +12729,25 @@
         <v>41</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F86">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G86" s="1">
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="H86" s="1">
-        <v>100</v>
+        <v>53.7</v>
       </c>
       <c r="I86" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J86">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -12764,25 +12764,25 @@
         <v>31</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F87">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="H87" s="1">
-        <v>100</v>
+        <v>45.2</v>
       </c>
       <c r="I87" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J87">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -12799,25 +12799,25 @@
         <v>38</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F88">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H88" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I88" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J88">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -12834,25 +12834,25 @@
         <v>28</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F89">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="H89" s="1">
-        <v>100</v>
+        <v>35.7</v>
       </c>
       <c r="I89" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J89">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -12869,25 +12869,25 @@
         <v>41</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F90">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G90" s="1">
-        <v>0</v>
+        <v>58.5</v>
       </c>
       <c r="H90" s="1">
-        <v>100</v>
+        <v>41.5</v>
       </c>
       <c r="I90" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J90">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -12901,25 +12901,25 @@
         <v>247</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="F91">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>44.9</v>
       </c>
       <c r="H91" s="1">
-        <v>100</v>
+        <v>55.1</v>
       </c>
       <c r="I91" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J91">
-        <v>247</v>
+        <v>68</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -13155,7 +13155,7 @@
         <v>94.5</v>
       </c>
       <c r="I98" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J98">
         <v>163</v>
@@ -13397,7 +13397,7 @@
         <v>99.5</v>
       </c>
       <c r="I105" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J105">
         <v>208</v>
@@ -13499,7 +13499,7 @@
         <v>100</v>
       </c>
       <c r="I108" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J108">
         <v>62</v>
@@ -13671,7 +13671,7 @@
         <v>100</v>
       </c>
       <c r="I113" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J113">
         <v>125</v>
@@ -13694,25 +13694,25 @@
         <v>39</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F114">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G114" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H114" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I114" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J114">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K114" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -13729,25 +13729,25 @@
         <v>28</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F115">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G115" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H115" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I115" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J115">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -13764,25 +13764,25 @@
         <v>20</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F116">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G116" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H116" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I116" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J116">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -13796,25 +13796,25 @@
         <v>87</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F117">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H117" s="1">
-        <v>100</v>
+        <v>24.1</v>
       </c>
       <c r="I117" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J117">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -13866,25 +13866,25 @@
         <v>29</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F119">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G119" s="1">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="H119" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
       <c r="I119" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J119">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -13901,25 +13901,25 @@
         <v>36</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F120">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G120" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H120" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I120" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J120">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -13936,25 +13936,25 @@
         <v>32</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F121">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H121" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I121" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J121">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -14038,25 +14038,25 @@
         <v>180</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F124">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H124" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I124" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J124">
-        <v>180</v>
+        <v>86</v>
       </c>
       <c r="K124" s="1">
-        <v>100</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -14222,7 +14222,7 @@
         <v>100</v>
       </c>
       <c r="I129" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J129">
         <v>134</v>
@@ -14245,25 +14245,25 @@
         <v>30</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F130">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G130" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H130" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I130" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J130">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -14280,25 +14280,25 @@
         <v>31</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F131">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G131" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H131" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I131" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J131">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -14312,25 +14312,25 @@
         <v>61</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F132">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G132" s="1">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H132" s="1">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I132" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J132">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -14347,25 +14347,25 @@
         <v>42</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F133">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G133" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I133" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J133">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -14382,25 +14382,25 @@
         <v>41</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F134">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G134" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H134" s="1">
-        <v>92.7</v>
+        <v>4.9</v>
       </c>
       <c r="I134" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J134">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -14417,25 +14417,25 @@
         <v>41</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F135">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G135" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H135" s="1">
-        <v>92.7</v>
+        <v>2.4</v>
       </c>
       <c r="I135" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J135">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -14452,25 +14452,25 @@
         <v>36</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F136">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G136" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H136" s="1">
-        <v>75</v>
+        <v>11.1</v>
       </c>
       <c r="I136" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J136">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K136" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -14487,25 +14487,25 @@
         <v>26</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F137">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G137" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H137" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I137" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J137">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -14519,25 +14519,25 @@
         <v>186</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="F138">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="G138" s="1">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="H138" s="1">
-        <v>91.90000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I138" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J138">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -14773,7 +14773,7 @@
         <v>100</v>
       </c>
       <c r="I145" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J145">
         <v>177</v>
@@ -14863,7 +14863,7 @@
         <v>126</v>
       </c>
       <c r="D148">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -14875,13 +14875,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
       </c>
       <c r="J148">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K148" s="1">
         <v>100</v>
@@ -14895,7 +14895,7 @@
         <v>116</v>
       </c>
       <c r="D149">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -14907,13 +14907,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I149" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J149">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K149" s="1">
         <v>100</v>
@@ -14933,25 +14933,25 @@
         <v>40</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F150">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="H150" s="1">
-        <v>100</v>
+        <v>7.5</v>
       </c>
       <c r="I150" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J150">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -14965,28 +14965,28 @@
         <v>126</v>
       </c>
       <c r="D151">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F151">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H151" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I151" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J151">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -15003,25 +15003,25 @@
         <v>38</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F152">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H152" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I152" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J152">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -15032,28 +15032,28 @@
         <v>116</v>
       </c>
       <c r="D153">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F153">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H153" s="1">
-        <v>100</v>
+        <v>13.4</v>
       </c>
       <c r="I153" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J153">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -15070,25 +15070,25 @@
         <v>36</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F154">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I154" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J154">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -15105,25 +15105,25 @@
         <v>36</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F155">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J155">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -15207,25 +15207,25 @@
         <v>132</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F158">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="H158" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="I158" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J158">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -15391,7 +15391,7 @@
         <v>100</v>
       </c>
       <c r="I163" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J163">
         <v>159</v>
@@ -15563,7 +15563,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="I168" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J168">
         <v>114</v>
@@ -15586,25 +15586,25 @@
         <v>30</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F169">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G169" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H169" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I169" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J169">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -15621,25 +15621,25 @@
         <v>34</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F170">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I170" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J170">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -15656,25 +15656,25 @@
         <v>20</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F171">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G171" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H171" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I171" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J171">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -15691,25 +15691,25 @@
         <v>36</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F172">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H172" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I172" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J172">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -15726,25 +15726,25 @@
         <v>28</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F173">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G173" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I173" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J173">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -15761,25 +15761,25 @@
         <v>32</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F174">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G174" s="1">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="H174" s="1">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="I174" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J174">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -15793,25 +15793,25 @@
         <v>180</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="F175">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="G175" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H175" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I175" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J175">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -15898,25 +15898,25 @@
         <v>30</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F178">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G178" s="1">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="H178" s="1">
-        <v>100</v>
+        <v>36.7</v>
       </c>
       <c r="I178" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J178">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -15930,7 +15930,7 @@
         <v>126</v>
       </c>
       <c r="D179">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -15942,13 +15942,13 @@
         <v>0</v>
       </c>
       <c r="H179" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I179" s="2">
         <v>0</v>
       </c>
       <c r="J179">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K179" s="1">
         <v>100</v>
@@ -15968,25 +15968,25 @@
         <v>33</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F180">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G180" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H180" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I180" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J180">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -16003,25 +16003,25 @@
         <v>33</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F181">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="H181" s="1">
-        <v>100</v>
+        <v>15.2</v>
       </c>
       <c r="I181" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J181">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -16038,25 +16038,25 @@
         <v>17</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F182">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G182" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I182" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J182">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -16067,28 +16067,28 @@
         <v>116</v>
       </c>
       <c r="D183">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F183">
-        <v>225</v>
+        <v>128</v>
       </c>
       <c r="G183" s="1">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H183" s="1">
-        <v>100</v>
+        <v>56.6</v>
       </c>
       <c r="I183" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J183">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -16105,25 +16105,25 @@
         <v>34</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F184">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G184" s="1">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="H184" s="1">
-        <v>97.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I184" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J184">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -16140,25 +16140,25 @@
         <v>24</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F185">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H185" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I185" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J185">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -16175,25 +16175,25 @@
         <v>14</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F186">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G186" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H186" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I186" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J186">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -16210,25 +16210,25 @@
         <v>21</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F187">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="H187" s="1">
-        <v>100</v>
+        <v>47.6</v>
       </c>
       <c r="I187" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J187">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -16245,25 +16245,25 @@
         <v>26</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F188">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="H188" s="1">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="I188" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J188">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -16280,25 +16280,25 @@
         <v>19</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F189">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="H189" s="1">
-        <v>100</v>
+        <v>42.1</v>
       </c>
       <c r="I189" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J189">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -16312,25 +16312,25 @@
         <v>138</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F190">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="G190" s="1">
-        <v>0</v>
+        <v>54.3</v>
       </c>
       <c r="H190" s="1">
-        <v>99.3</v>
+        <v>45.7</v>
       </c>
       <c r="I190" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J190">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -16347,25 +16347,25 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F191">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G191" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="H191" s="1">
-        <v>100</v>
+        <v>25.8</v>
       </c>
       <c r="I191" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J191">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -16382,25 +16382,25 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F192">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G192" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H192" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I192" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J192">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -16417,25 +16417,25 @@
         <v>34</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F193">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G193" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H193" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I193" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J193">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -16452,25 +16452,25 @@
         <v>32</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F194">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G194" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H194" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I194" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J194">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -16484,25 +16484,25 @@
         <v>125</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F195">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="G195" s="1">
-        <v>0</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H195" s="1">
-        <v>100</v>
+        <v>9.6</v>
       </c>
       <c r="I195" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J195">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -16633,7 +16633,7 @@
         <v>98.2</v>
       </c>
       <c r="I199" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J199">
         <v>114</v>
@@ -16656,25 +16656,25 @@
         <v>28</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F200">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G200" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H200" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I200" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J200">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K200" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -16691,25 +16691,25 @@
         <v>28</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F201">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G201" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H201" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I201" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J201">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K201" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -16726,25 +16726,25 @@
         <v>25</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F202">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H202" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I202" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J202">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -16761,25 +16761,25 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F203">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H203" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I203" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J203">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -16796,25 +16796,25 @@
         <v>20</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F204">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H204" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I204" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J204">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -16828,25 +16828,25 @@
         <v>115</v>
       </c>
       <c r="E205">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F205">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="G205" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H205" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I205" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J205">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -17012,7 +17012,7 @@
         <v>100</v>
       </c>
       <c r="I210" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J210">
         <v>159</v>
@@ -17254,7 +17254,7 @@
         <v>100</v>
       </c>
       <c r="I217" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J217">
         <v>235</v>
@@ -17277,25 +17277,25 @@
         <v>17</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F218">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G218" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H218" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I218" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J218">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K218" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -17309,25 +17309,25 @@
         <v>17</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F219">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G219" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H219" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I219" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J219">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K219" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -17388,7 +17388,7 @@
         <v>100</v>
       </c>
       <c r="I221" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J221">
         <v>33</v>
@@ -17411,25 +17411,25 @@
         <v>33</v>
       </c>
       <c r="E222">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F222">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G222" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H222" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I222" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J222">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K222" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -17446,25 +17446,25 @@
         <v>22</v>
       </c>
       <c r="E223">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F223">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G223" s="1">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="H223" s="1">
-        <v>100</v>
+        <v>31.8</v>
       </c>
       <c r="I223" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J223">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K223" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -17481,25 +17481,25 @@
         <v>22</v>
       </c>
       <c r="E224">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F224">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G224" s="1">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="H224" s="1">
-        <v>100</v>
+        <v>22.7</v>
       </c>
       <c r="I224" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J224">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K224" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -17513,25 +17513,25 @@
         <v>77</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F225">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="G225" s="1">
-        <v>0</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H225" s="1">
-        <v>100</v>
+        <v>29.9</v>
       </c>
       <c r="I225" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J225">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K225" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -17548,25 +17548,25 @@
         <v>30</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F226">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G226" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H226" s="1">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="I226" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J226">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K226" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -17583,25 +17583,25 @@
         <v>33</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F227">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G227" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H227" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I227" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J227">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K227" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -17615,25 +17615,25 @@
         <v>63</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F228">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="G228" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H228" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I228" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J228">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K228" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -17650,25 +17650,25 @@
         <v>31</v>
       </c>
       <c r="E229">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F229">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G229" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H229" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
       <c r="I229" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J229">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K229" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -17685,25 +17685,25 @@
         <v>31</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F230">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G230" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H230" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
       <c r="I230" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J230">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K230" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -17720,25 +17720,25 @@
         <v>29</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F231">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G231" s="1">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="H231" s="1">
-        <v>100</v>
+        <v>41.4</v>
       </c>
       <c r="I231" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J231">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -17752,25 +17752,25 @@
         <v>91</v>
       </c>
       <c r="E232">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F232">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="G232" s="1">
-        <v>0</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H232" s="1">
-        <v>100</v>
+        <v>17.6</v>
       </c>
       <c r="I232" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J232">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K232" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -17936,7 +17936,7 @@
         <v>100</v>
       </c>
       <c r="I237" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J237">
         <v>123</v>
@@ -18178,7 +18178,7 @@
         <v>100</v>
       </c>
       <c r="I244" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J244">
         <v>172</v>
@@ -18268,7 +18268,7 @@
         <v>126</v>
       </c>
       <c r="D247">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -18280,13 +18280,13 @@
         <v>0</v>
       </c>
       <c r="H247" s="1">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I247" s="2">
         <v>0</v>
       </c>
       <c r="J247">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K247" s="1">
         <v>100</v>
@@ -18370,7 +18370,7 @@
         <v>116</v>
       </c>
       <c r="D250">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -18382,13 +18382,13 @@
         <v>0</v>
       </c>
       <c r="H250" s="1">
-        <v>99.3</v>
+        <v>98.7</v>
       </c>
       <c r="I250" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J250">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K250" s="1">
         <v>100</v>
@@ -18408,25 +18408,25 @@
         <v>37</v>
       </c>
       <c r="E251">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F251">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G251" s="1">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="H251" s="1">
-        <v>100</v>
+        <v>10.8</v>
       </c>
       <c r="I251" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J251">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K251" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -18443,25 +18443,25 @@
         <v>33</v>
       </c>
       <c r="E252">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F252">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G252" s="1">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="H252" s="1">
-        <v>100</v>
+        <v>57.6</v>
       </c>
       <c r="I252" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J252">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K252" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -18510,25 +18510,25 @@
         <v>103</v>
       </c>
       <c r="E254">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F254">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="G254" s="1">
-        <v>0</v>
+        <v>45.6</v>
       </c>
       <c r="H254" s="1">
-        <v>100</v>
+        <v>54.4</v>
       </c>
       <c r="I254" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J254">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="K254" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -18545,25 +18545,25 @@
         <v>42</v>
       </c>
       <c r="E255">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F255">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G255" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H255" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I255" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J255">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K255" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -18580,25 +18580,25 @@
         <v>34</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F256">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G256" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H256" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I256" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J256">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K256" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -18615,25 +18615,25 @@
         <v>34</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F257">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G257" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H257" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I257" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J257">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K257" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -18650,25 +18650,25 @@
         <v>32</v>
       </c>
       <c r="E258">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F258">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G258" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H258" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I258" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J258">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K258" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -18685,25 +18685,25 @@
         <v>32</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F259">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G259" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H259" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I259" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J259">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K259" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -18717,25 +18717,25 @@
         <v>174</v>
       </c>
       <c r="E260">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="F260">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="G260" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H260" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J260">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="K260" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18804,19 +18804,19 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -18851,7 +18851,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>14</v>
@@ -18886,7 +18886,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J4">
         <v>17</v>
@@ -18909,19 +18909,19 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H5" s="1">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
         <v>19</v>
@@ -18941,16 +18941,16 @@
         <v>75</v>
       </c>
       <c r="E6">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>82.7</v>
+        <v>85.3</v>
       </c>
       <c r="H6" s="1">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="I6" s="2">
         <v>7.5</v>
@@ -18976,19 +18976,19 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>61.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>38.7</v>
+        <v>22.6</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>31</v>
@@ -19011,19 +19011,19 @@
         <v>41</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>78</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>41</v>
@@ -19058,7 +19058,7 @@
         <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>28</v>
@@ -19081,19 +19081,19 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>26.3</v>
+        <v>21.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
         <v>38</v>
@@ -19116,19 +19116,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>78.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>28</v>
@@ -19163,7 +19163,7 @@
         <v>36.6</v>
       </c>
       <c r="I12" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>41</v>
@@ -19183,16 +19183,16 @@
         <v>207</v>
       </c>
       <c r="E13">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F13">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G13" s="1">
-        <v>72.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H13" s="1">
-        <v>27.1</v>
+        <v>23.2</v>
       </c>
       <c r="I13" s="2">
         <v>7.5</v>
@@ -19218,19 +19218,19 @@
         <v>38</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>84.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>15.8</v>
+        <v>18.4</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
         <v>38</v>
@@ -19253,19 +19253,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>71.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="I15" s="2">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>32</v>
@@ -19332,7 +19332,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
         <v>43</v>
@@ -19355,19 +19355,19 @@
         <v>42</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1">
-        <v>73.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="I18" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J18">
         <v>42</v>
@@ -19390,19 +19390,19 @@
         <v>42</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I19" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J19">
         <v>42</v>
@@ -19437,7 +19437,7 @@
         <v>7.3</v>
       </c>
       <c r="I20" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J20">
         <v>41</v>
@@ -19489,7 +19489,7 @@
         <v>126</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>30</v>
@@ -19498,16 +19498,16 @@
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>90.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H22" s="1">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I22" s="2">
         <v>7.9</v>
       </c>
       <c r="J22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -19626,7 +19626,7 @@
         <v>116</v>
       </c>
       <c r="D26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>119</v>
@@ -19635,16 +19635,16 @@
         <v>10</v>
       </c>
       <c r="G26" s="1">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="H26" s="1">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I26" s="2">
         <v>7.5</v>
       </c>
       <c r="J26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -19676,7 +19676,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
         <v>19</v>
@@ -19970,7 +19970,7 @@
         <v>126</v>
       </c>
       <c r="D36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36">
         <v>28</v>
@@ -19979,16 +19979,16 @@
         <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H36" s="1">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="I36" s="2">
         <v>7.6</v>
       </c>
       <c r="J36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -20037,7 +20037,7 @@
         <v>116</v>
       </c>
       <c r="D38">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38">
         <v>125</v>
@@ -20046,16 +20046,16 @@
         <v>42</v>
       </c>
       <c r="G38" s="1">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="I38" s="2">
         <v>7.5</v>
       </c>
       <c r="J38">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K38" s="1">
         <v>100</v>
@@ -20177,19 +20177,19 @@
         <v>39</v>
       </c>
       <c r="E42">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="I42" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
         <v>39</v>
@@ -20224,7 +20224,7 @@
         <v>20</v>
       </c>
       <c r="I43" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J43">
         <v>30</v>
@@ -20247,19 +20247,19 @@
         <v>25</v>
       </c>
       <c r="E44">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G44" s="1">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H44" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I44" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J44">
         <v>25</v>
@@ -20279,16 +20279,16 @@
         <v>94</v>
       </c>
       <c r="E45">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F45">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G45" s="1">
-        <v>81.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="H45" s="1">
-        <v>18.1</v>
+        <v>21.3</v>
       </c>
       <c r="I45" s="2">
         <v>7.5</v>
@@ -20521,19 +20521,19 @@
         <v>30</v>
       </c>
       <c r="E52">
+        <v>16</v>
+      </c>
+      <c r="F52">
         <v>14</v>
       </c>
-      <c r="F52">
-        <v>16</v>
-      </c>
       <c r="G52" s="1">
+        <v>53.3</v>
+      </c>
+      <c r="H52" s="1">
         <v>46.7</v>
       </c>
-      <c r="H52" s="1">
-        <v>53.3</v>
-      </c>
       <c r="I52" s="2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="J52">
         <v>30</v>
@@ -20556,19 +20556,19 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G53" s="1">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H53" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I53" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J53">
         <v>20</v>
@@ -20591,19 +20591,19 @@
         <v>28</v>
       </c>
       <c r="E54">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F54">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1">
-        <v>32.1</v>
+        <v>53.6</v>
       </c>
       <c r="H54" s="1">
-        <v>67.90000000000001</v>
+        <v>46.4</v>
       </c>
       <c r="I54" s="2">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="J54">
         <v>28</v>
@@ -20626,19 +20626,19 @@
         <v>21</v>
       </c>
       <c r="E55">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F55">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="H55" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="I55" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J55">
         <v>21</v>
@@ -20661,19 +20661,19 @@
         <v>17</v>
       </c>
       <c r="E56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G56" s="1">
-        <v>41.2</v>
+        <v>35.3</v>
       </c>
       <c r="H56" s="1">
-        <v>58.8</v>
+        <v>64.7</v>
       </c>
       <c r="I56" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J56">
         <v>17</v>
@@ -20708,7 +20708,7 @@
         <v>42.1</v>
       </c>
       <c r="I57" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J57">
         <v>19</v>
@@ -20728,16 +20728,16 @@
         <v>135</v>
       </c>
       <c r="E58">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F58">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G58" s="1">
-        <v>42.2</v>
+        <v>47.4</v>
       </c>
       <c r="H58" s="1">
-        <v>57.8</v>
+        <v>52.6</v>
       </c>
       <c r="I58" s="2">
         <v>7.5</v>
@@ -20865,16 +20865,16 @@
         <v>34</v>
       </c>
       <c r="E62">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>91.2</v>
+        <v>85.3</v>
       </c>
       <c r="H62" s="1">
-        <v>8.800000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="I62" s="2">
         <v>8.699999999999999</v>
@@ -20900,19 +20900,19 @@
         <v>37</v>
       </c>
       <c r="E63">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G63" s="1">
-        <v>86.5</v>
+        <v>70.3</v>
       </c>
       <c r="H63" s="1">
-        <v>13.5</v>
+        <v>29.7</v>
       </c>
       <c r="I63" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J63">
         <v>37</v>
@@ -20970,19 +20970,19 @@
         <v>29</v>
       </c>
       <c r="E65">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65" s="1">
-        <v>93.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H65" s="1">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="I65" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J65">
         <v>29</v>
@@ -21037,16 +21037,16 @@
         <v>166</v>
       </c>
       <c r="E67">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F67">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G67" s="1">
-        <v>80.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>19.9</v>
+        <v>25.9</v>
       </c>
       <c r="I67" s="2">
         <v>7.5</v>
@@ -21349,19 +21349,19 @@
         <v>20</v>
       </c>
       <c r="E76">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F76">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G76" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H76" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I76" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J76">
         <v>20</v>
@@ -21384,19 +21384,19 @@
         <v>26</v>
       </c>
       <c r="E77">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G77" s="1">
-        <v>65.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H77" s="1">
-        <v>34.6</v>
+        <v>30.8</v>
       </c>
       <c r="I77" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J77">
         <v>26</v>
@@ -21419,19 +21419,19 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G78" s="1">
-        <v>58.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H78" s="1">
-        <v>41.2</v>
+        <v>29.4</v>
       </c>
       <c r="I78" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J78">
         <v>17</v>
@@ -21454,19 +21454,19 @@
         <v>31</v>
       </c>
       <c r="E79">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F79">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G79" s="1">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="H79" s="1">
-        <v>41.9</v>
+        <v>38.7</v>
       </c>
       <c r="I79" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J79">
         <v>31</v>
@@ -21486,16 +21486,16 @@
         <v>94</v>
       </c>
       <c r="E80">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F80">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G80" s="1">
-        <v>56.4</v>
+        <v>61.7</v>
       </c>
       <c r="H80" s="1">
-        <v>43.6</v>
+        <v>38.3</v>
       </c>
       <c r="I80" s="2">
         <v>7.5</v>
@@ -21693,19 +21693,19 @@
         <v>41</v>
       </c>
       <c r="E86">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F86">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G86" s="1">
-        <v>58.5</v>
+        <v>46.3</v>
       </c>
       <c r="H86" s="1">
-        <v>41.5</v>
+        <v>53.7</v>
       </c>
       <c r="I86" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J86">
         <v>41</v>
@@ -21728,19 +21728,19 @@
         <v>31</v>
       </c>
       <c r="E87">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F87">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G87" s="1">
-        <v>74.2</v>
+        <v>54.8</v>
       </c>
       <c r="H87" s="1">
-        <v>25.8</v>
+        <v>45.2</v>
       </c>
       <c r="I87" s="2">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J87">
         <v>31</v>
@@ -21763,16 +21763,16 @@
         <v>38</v>
       </c>
       <c r="E88">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G88" s="1">
-        <v>92.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H88" s="1">
-        <v>7.9</v>
+        <v>13.2</v>
       </c>
       <c r="I88" s="2">
         <v>7.3</v>
@@ -21810,7 +21810,7 @@
         <v>35.7</v>
       </c>
       <c r="I89" s="2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J89">
         <v>28</v>
@@ -21833,19 +21833,19 @@
         <v>41</v>
       </c>
       <c r="E90">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F90">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G90" s="1">
-        <v>68.3</v>
+        <v>58.5</v>
       </c>
       <c r="H90" s="1">
-        <v>31.7</v>
+        <v>41.5</v>
       </c>
       <c r="I90" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J90">
         <v>41</v>
@@ -21865,16 +21865,16 @@
         <v>247</v>
       </c>
       <c r="E91">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="F91">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G91" s="1">
-        <v>67.2</v>
+        <v>60.3</v>
       </c>
       <c r="H91" s="1">
-        <v>32.8</v>
+        <v>39.7</v>
       </c>
       <c r="I91" s="2">
         <v>7.5</v>
@@ -22670,7 +22670,7 @@
         <v>43.6</v>
       </c>
       <c r="I114" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J114">
         <v>39</v>
@@ -22705,7 +22705,7 @@
         <v>7.1</v>
       </c>
       <c r="I115" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J115">
         <v>28</v>
@@ -22728,19 +22728,19 @@
         <v>20</v>
       </c>
       <c r="E116">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G116" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H116" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I116" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J116">
         <v>20</v>
@@ -22760,16 +22760,16 @@
         <v>87</v>
       </c>
       <c r="E117">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F117">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G117" s="1">
-        <v>78.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H117" s="1">
-        <v>21.8</v>
+        <v>24.1</v>
       </c>
       <c r="I117" s="2">
         <v>7.5</v>
@@ -22830,19 +22830,19 @@
         <v>29</v>
       </c>
       <c r="E119">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F119">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G119" s="1">
-        <v>75.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H119" s="1">
-        <v>24.1</v>
+        <v>13.8</v>
       </c>
       <c r="I119" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J119">
         <v>29</v>
@@ -22865,19 +22865,19 @@
         <v>36</v>
       </c>
       <c r="E120">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F120">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G120" s="1">
-        <v>83.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H120" s="1">
-        <v>16.7</v>
+        <v>5.6</v>
       </c>
       <c r="I120" s="2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J120">
         <v>36</v>
@@ -22912,7 +22912,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J121">
         <v>32</v>
@@ -23002,16 +23002,16 @@
         <v>180</v>
       </c>
       <c r="E124">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F124">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G124" s="1">
-        <v>84.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="H124" s="1">
-        <v>15.6</v>
+        <v>11.7</v>
       </c>
       <c r="I124" s="2">
         <v>7.5</v>
@@ -23209,19 +23209,19 @@
         <v>30</v>
       </c>
       <c r="E130">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G130" s="1">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="H130" s="1">
-        <v>6.7</v>
+        <v>20</v>
       </c>
       <c r="I130" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J130">
         <v>30</v>
@@ -23244,19 +23244,19 @@
         <v>31</v>
       </c>
       <c r="E131">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G131" s="1">
-        <v>77.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H131" s="1">
-        <v>22.6</v>
+        <v>16.1</v>
       </c>
       <c r="I131" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J131">
         <v>31</v>
@@ -23276,16 +23276,16 @@
         <v>61</v>
       </c>
       <c r="E132">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F132">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G132" s="1">
-        <v>85.2</v>
+        <v>82</v>
       </c>
       <c r="H132" s="1">
-        <v>14.8</v>
+        <v>18</v>
       </c>
       <c r="I132" s="2">
         <v>7.5</v>
@@ -23311,19 +23311,19 @@
         <v>42</v>
       </c>
       <c r="E133">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G133" s="1">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H133" s="1">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="I133" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J133">
         <v>42</v>
@@ -23346,19 +23346,19 @@
         <v>41</v>
       </c>
       <c r="E134">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G134" s="1">
-        <v>92.7</v>
+        <v>90.2</v>
       </c>
       <c r="H134" s="1">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I134" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J134">
         <v>41</v>
@@ -23381,19 +23381,19 @@
         <v>41</v>
       </c>
       <c r="E135">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G135" s="1">
-        <v>90.2</v>
+        <v>92.7</v>
       </c>
       <c r="H135" s="1">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I135" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J135">
         <v>41</v>
@@ -23416,19 +23416,19 @@
         <v>36</v>
       </c>
       <c r="E136">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F136">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G136" s="1">
-        <v>66.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H136" s="1">
-        <v>30.6</v>
+        <v>13.9</v>
       </c>
       <c r="I136" s="2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J136">
         <v>36</v>
@@ -23463,7 +23463,7 @@
         <v>3.8</v>
       </c>
       <c r="I137" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J137">
         <v>26</v>
@@ -23483,16 +23483,16 @@
         <v>186</v>
       </c>
       <c r="E138">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F138">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G138" s="1">
-        <v>87.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="H138" s="1">
-        <v>11.8</v>
+        <v>7.5</v>
       </c>
       <c r="I138" s="2">
         <v>7.5</v>
@@ -23827,7 +23827,7 @@
         <v>126</v>
       </c>
       <c r="D148">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E148">
         <v>28</v>
@@ -23836,16 +23836,16 @@
         <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H148" s="1">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="I148" s="2">
         <v>7.3</v>
       </c>
       <c r="J148">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K148" s="1">
         <v>100</v>
@@ -23859,7 +23859,7 @@
         <v>116</v>
       </c>
       <c r="D149">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E149">
         <v>82</v>
@@ -23868,16 +23868,16 @@
         <v>21</v>
       </c>
       <c r="G149" s="1">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H149" s="1">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I149" s="2">
         <v>7.5</v>
       </c>
       <c r="J149">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K149" s="1">
         <v>100</v>
@@ -23909,7 +23909,7 @@
         <v>7.5</v>
       </c>
       <c r="I150" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J150">
         <v>40</v>
@@ -23929,25 +23929,25 @@
         <v>126</v>
       </c>
       <c r="D151">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E151">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F151">
         <v>4</v>
       </c>
       <c r="G151" s="1">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H151" s="1">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="I151" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J151">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K151" s="1">
         <v>100</v>
@@ -23979,7 +23979,7 @@
         <v>21.1</v>
       </c>
       <c r="I152" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J152">
         <v>38</v>
@@ -23996,25 +23996,25 @@
         <v>116</v>
       </c>
       <c r="D153">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E153">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F153">
         <v>15</v>
       </c>
       <c r="G153" s="1">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H153" s="1">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I153" s="2">
         <v>7.5</v>
       </c>
       <c r="J153">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K153" s="1">
         <v>100</v>
@@ -24046,7 +24046,7 @@
         <v>0</v>
       </c>
       <c r="I154" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J154">
         <v>36</v>
@@ -24081,7 +24081,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J155">
         <v>36</v>
@@ -24550,19 +24550,19 @@
         <v>30</v>
       </c>
       <c r="E169">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F169">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G169" s="1">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="H169" s="1">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="I169" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J169">
         <v>30</v>
@@ -24585,19 +24585,19 @@
         <v>34</v>
       </c>
       <c r="E170">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G170" s="1">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H170" s="1">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I170" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J170">
         <v>34</v>
@@ -24632,7 +24632,7 @@
         <v>10</v>
       </c>
       <c r="I171" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J171">
         <v>20</v>
@@ -24667,7 +24667,7 @@
         <v>5.6</v>
       </c>
       <c r="I172" s="2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J172">
         <v>36</v>
@@ -24690,16 +24690,16 @@
         <v>28</v>
       </c>
       <c r="E173">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G173" s="1">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H173" s="1">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I173" s="2">
         <v>7.4</v>
@@ -24725,19 +24725,19 @@
         <v>32</v>
       </c>
       <c r="E174">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G174" s="1">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H174" s="1">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="I174" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J174">
         <v>32</v>
@@ -24757,16 +24757,16 @@
         <v>180</v>
       </c>
       <c r="E175">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F175">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G175" s="1">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="H175" s="1">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I175" s="2">
         <v>7.5</v>
@@ -24862,19 +24862,19 @@
         <v>30</v>
       </c>
       <c r="E178">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F178">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G178" s="1">
-        <v>60</v>
+        <v>63.3</v>
       </c>
       <c r="H178" s="1">
-        <v>40</v>
+        <v>36.7</v>
       </c>
       <c r="I178" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J178">
         <v>30</v>
@@ -24894,7 +24894,7 @@
         <v>126</v>
       </c>
       <c r="D179">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E179">
         <v>31</v>
@@ -24903,16 +24903,16 @@
         <v>1</v>
       </c>
       <c r="G179" s="1">
-        <v>96.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H179" s="1">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I179" s="2">
         <v>7.3</v>
       </c>
       <c r="J179">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K179" s="1">
         <v>100</v>
@@ -24944,7 +24944,7 @@
         <v>0</v>
       </c>
       <c r="I180" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J180">
         <v>33</v>
@@ -24967,19 +24967,19 @@
         <v>33</v>
       </c>
       <c r="E181">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F181">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G181" s="1">
-        <v>57.6</v>
+        <v>84.8</v>
       </c>
       <c r="H181" s="1">
-        <v>42.4</v>
+        <v>15.2</v>
       </c>
       <c r="I181" s="2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J181">
         <v>33</v>
@@ -25014,7 +25014,7 @@
         <v>0</v>
       </c>
       <c r="I182" s="2">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="J182">
         <v>17</v>
@@ -25031,25 +25031,25 @@
         <v>116</v>
       </c>
       <c r="D183">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E183">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="F183">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G183" s="1">
-        <v>85.8</v>
+        <v>89.8</v>
       </c>
       <c r="H183" s="1">
-        <v>14.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I183" s="2">
         <v>7.5</v>
       </c>
       <c r="J183">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K183" s="1">
         <v>100</v>
@@ -25069,19 +25069,19 @@
         <v>34</v>
       </c>
       <c r="E184">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F184">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G184" s="1">
-        <v>58.8</v>
+        <v>32.4</v>
       </c>
       <c r="H184" s="1">
-        <v>38.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I184" s="2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J184">
         <v>34</v>
@@ -25104,19 +25104,19 @@
         <v>24</v>
       </c>
       <c r="E185">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F185">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G185" s="1">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="H185" s="1">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="I185" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J185">
         <v>24</v>
@@ -25151,7 +25151,7 @@
         <v>14.3</v>
       </c>
       <c r="I186" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J186">
         <v>14</v>
@@ -25174,16 +25174,16 @@
         <v>21</v>
       </c>
       <c r="E187">
+        <v>11</v>
+      </c>
+      <c r="F187">
         <v>10</v>
       </c>
-      <c r="F187">
-        <v>11</v>
-      </c>
       <c r="G187" s="1">
+        <v>52.4</v>
+      </c>
+      <c r="H187" s="1">
         <v>47.6</v>
-      </c>
-      <c r="H187" s="1">
-        <v>52.4</v>
       </c>
       <c r="I187" s="2">
         <v>5.9</v>
@@ -25209,16 +25209,16 @@
         <v>26</v>
       </c>
       <c r="E188">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F188">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G188" s="1">
-        <v>76.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H188" s="1">
-        <v>23.1</v>
+        <v>30.8</v>
       </c>
       <c r="I188" s="2">
         <v>6.4</v>
@@ -25244,19 +25244,19 @@
         <v>19</v>
       </c>
       <c r="E189">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F189">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G189" s="1">
-        <v>78.90000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="H189" s="1">
-        <v>21.1</v>
+        <v>42.1</v>
       </c>
       <c r="I189" s="2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J189">
         <v>19</v>
@@ -25276,16 +25276,16 @@
         <v>138</v>
       </c>
       <c r="E190">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F190">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G190" s="1">
-        <v>65.2</v>
+        <v>54.3</v>
       </c>
       <c r="H190" s="1">
-        <v>34.1</v>
+        <v>45.7</v>
       </c>
       <c r="I190" s="2">
         <v>7.5</v>
@@ -25311,19 +25311,19 @@
         <v>31</v>
       </c>
       <c r="E191">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F191">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G191" s="1">
-        <v>80.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="H191" s="1">
-        <v>19.4</v>
+        <v>25.8</v>
       </c>
       <c r="I191" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J191">
         <v>31</v>
@@ -25346,16 +25346,16 @@
         <v>28</v>
       </c>
       <c r="E192">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F192">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G192" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H192" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I192" s="2">
         <v>8.1</v>
@@ -25381,16 +25381,16 @@
         <v>34</v>
       </c>
       <c r="E193">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H193" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I193" s="2">
         <v>9</v>
@@ -25428,7 +25428,7 @@
         <v>0</v>
       </c>
       <c r="I194" s="2">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J194">
         <v>32</v>
@@ -25448,16 +25448,16 @@
         <v>125</v>
       </c>
       <c r="E195">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F195">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G195" s="1">
-        <v>88</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H195" s="1">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="I195" s="2">
         <v>7.5</v>
@@ -25632,7 +25632,7 @@
         <v>0</v>
       </c>
       <c r="I200" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J200">
         <v>28</v>
@@ -25655,19 +25655,19 @@
         <v>28</v>
       </c>
       <c r="E201">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G201" s="1">
-        <v>96.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H201" s="1">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="I201" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J201">
         <v>28</v>
@@ -25690,19 +25690,19 @@
         <v>25</v>
       </c>
       <c r="E202">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F202">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G202" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H202" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I202" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J202">
         <v>25</v>
@@ -25725,19 +25725,19 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F203">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G203" s="1">
-        <v>71.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H203" s="1">
-        <v>28.6</v>
+        <v>7.1</v>
       </c>
       <c r="I203" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J203">
         <v>14</v>
@@ -25760,19 +25760,19 @@
         <v>20</v>
       </c>
       <c r="E204">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G204" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H204" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I204" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J204">
         <v>20</v>
@@ -26253,7 +26253,7 @@
         <v>0</v>
       </c>
       <c r="I218" s="2">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J218">
         <v>17</v>
@@ -26375,19 +26375,19 @@
         <v>33</v>
       </c>
       <c r="E222">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F222">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G222" s="1">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="H222" s="1">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="I222" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J222">
         <v>33</v>
@@ -26410,16 +26410,16 @@
         <v>22</v>
       </c>
       <c r="E223">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F223">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G223" s="1">
-        <v>77.3</v>
+        <v>68.2</v>
       </c>
       <c r="H223" s="1">
-        <v>22.7</v>
+        <v>31.8</v>
       </c>
       <c r="I223" s="2">
         <v>6.5</v>
@@ -26457,7 +26457,7 @@
         <v>22.7</v>
       </c>
       <c r="I224" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J224">
         <v>22</v>
@@ -26477,16 +26477,16 @@
         <v>77</v>
       </c>
       <c r="E225">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F225">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G225" s="1">
-        <v>75.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H225" s="1">
-        <v>24.7</v>
+        <v>29.9</v>
       </c>
       <c r="I225" s="2">
         <v>7.5</v>
@@ -26512,16 +26512,16 @@
         <v>30</v>
       </c>
       <c r="E226">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F226">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G226" s="1">
-        <v>96.7</v>
+        <v>73.3</v>
       </c>
       <c r="H226" s="1">
-        <v>3.3</v>
+        <v>26.7</v>
       </c>
       <c r="I226" s="2">
         <v>7.5</v>
@@ -26547,19 +26547,19 @@
         <v>33</v>
       </c>
       <c r="E227">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G227" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H227" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I227" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J227">
         <v>33</v>
@@ -26579,16 +26579,16 @@
         <v>63</v>
       </c>
       <c r="E228">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G228" s="1">
-        <v>98.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H228" s="1">
-        <v>1.6</v>
+        <v>14.3</v>
       </c>
       <c r="I228" s="2">
         <v>7.5</v>
@@ -26614,19 +26614,19 @@
         <v>31</v>
       </c>
       <c r="E229">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G229" s="1">
-        <v>96.8</v>
+        <v>93.5</v>
       </c>
       <c r="H229" s="1">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="I229" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J229">
         <v>31</v>
@@ -26649,19 +26649,19 @@
         <v>31</v>
       </c>
       <c r="E230">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G230" s="1">
-        <v>96.8</v>
+        <v>93.5</v>
       </c>
       <c r="H230" s="1">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="I230" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J230">
         <v>31</v>
@@ -26684,19 +26684,19 @@
         <v>29</v>
       </c>
       <c r="E231">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F231">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G231" s="1">
-        <v>62.1</v>
+        <v>58.6</v>
       </c>
       <c r="H231" s="1">
-        <v>37.9</v>
+        <v>41.4</v>
       </c>
       <c r="I231" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J231">
         <v>29</v>
@@ -26716,16 +26716,16 @@
         <v>91</v>
       </c>
       <c r="E232">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F232">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G232" s="1">
-        <v>85.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H232" s="1">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="I232" s="2">
         <v>7.5</v>
@@ -27232,7 +27232,7 @@
         <v>126</v>
       </c>
       <c r="D247">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E247">
         <v>22</v>
@@ -27241,16 +27241,16 @@
         <v>11</v>
       </c>
       <c r="G247" s="1">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="H247" s="1">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="I247" s="2">
         <v>6.9</v>
       </c>
       <c r="J247">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K247" s="1">
         <v>100</v>
@@ -27334,7 +27334,7 @@
         <v>116</v>
       </c>
       <c r="D250">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E250">
         <v>69</v>
@@ -27343,16 +27343,16 @@
         <v>82</v>
       </c>
       <c r="G250" s="1">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="H250" s="1">
-        <v>54.3</v>
+        <v>53.9</v>
       </c>
       <c r="I250" s="2">
         <v>7.5</v>
       </c>
       <c r="J250">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K250" s="1">
         <v>100</v>
@@ -27372,19 +27372,19 @@
         <v>37</v>
       </c>
       <c r="E251">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F251">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G251" s="1">
-        <v>86.5</v>
+        <v>89.2</v>
       </c>
       <c r="H251" s="1">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="I251" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J251">
         <v>37</v>
@@ -27407,16 +27407,16 @@
         <v>33</v>
       </c>
       <c r="E252">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F252">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G252" s="1">
-        <v>45.5</v>
+        <v>42.4</v>
       </c>
       <c r="H252" s="1">
-        <v>54.5</v>
+        <v>57.6</v>
       </c>
       <c r="I252" s="2">
         <v>6.1</v>
@@ -27521,7 +27521,7 @@
         <v>0</v>
       </c>
       <c r="I255" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J255">
         <v>42</v>
@@ -27556,7 +27556,7 @@
         <v>0</v>
       </c>
       <c r="I256" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J256">
         <v>34</v>
@@ -27591,7 +27591,7 @@
         <v>0</v>
       </c>
       <c r="I257" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J257">
         <v>34</v>
@@ -27626,7 +27626,7 @@
         <v>0</v>
       </c>
       <c r="I258" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J258">
         <v>32</v>
@@ -27661,7 +27661,7 @@
         <v>0</v>
       </c>
       <c r="I259" s="2">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J259">
         <v>32</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -1025,7 +1025,7 @@
         <v>17.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>27.1</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>21.4</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>13.1</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F22">
         <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H22" s="1">
         <v>8.800000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1602,22 +1602,22 @@
         <v>26</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
         <v>86.7</v>
       </c>
       <c r="H23" s="1">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="I23" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1701,25 +1701,25 @@
         <v>131</v>
       </c>
       <c r="E26">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1">
-        <v>90.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I26" s="2">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1917,7 +1917,7 @@
         <v>3.5</v>
       </c>
       <c r="I32" s="2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>33</v>
       </c>
       <c r="E36">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F36">
         <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H36" s="1">
         <v>12.1</v>
@@ -2060,10 +2060,10 @@
         <v>7.6</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2112,25 +2112,25 @@
         <v>168</v>
       </c>
       <c r="E38">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F38">
         <v>42</v>
       </c>
       <c r="G38" s="1">
-        <v>74.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H38" s="1">
         <v>25</v>
       </c>
       <c r="I38" s="2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2424,22 +2424,22 @@
         <v>12</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G47" s="1">
         <v>40</v>
       </c>
       <c r="H47" s="1">
-        <v>56.7</v>
+        <v>60</v>
       </c>
       <c r="I47" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2561,22 +2561,22 @@
         <v>85</v>
       </c>
       <c r="F51">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G51" s="1">
         <v>71.40000000000001</v>
       </c>
       <c r="H51" s="1">
-        <v>27.7</v>
+        <v>28.6</v>
       </c>
       <c r="I51" s="2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2812,7 +2812,7 @@
         <v>57.8</v>
       </c>
       <c r="I58" s="2">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>25</v>
       </c>
       <c r="I61" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>18.7</v>
       </c>
       <c r="I67" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>10.8</v>
       </c>
       <c r="I75" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>43.6</v>
       </c>
       <c r="I80" s="2">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -3593,13 +3593,13 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F81">
         <v>7</v>
       </c>
       <c r="G81" s="1">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H81" s="1">
         <v>20.6</v>
@@ -3608,10 +3608,10 @@
         <v>7.1</v>
       </c>
       <c r="J81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3628,13 +3628,13 @@
         <v>30</v>
       </c>
       <c r="E82">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F82">
         <v>5</v>
       </c>
       <c r="G82" s="1">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="H82" s="1">
         <v>16.7</v>
@@ -3643,10 +3643,10 @@
         <v>7.1</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3660,25 +3660,25 @@
         <v>64</v>
       </c>
       <c r="E83">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F83">
         <v>12</v>
       </c>
       <c r="G83" s="1">
-        <v>78.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H83" s="1">
         <v>18.8</v>
       </c>
       <c r="I83" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3949,7 +3949,7 @@
         <v>32.8</v>
       </c>
       <c r="I91" s="2">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>14.1</v>
       </c>
       <c r="I98" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J98">
         <v>2</v>
@@ -4433,7 +4433,7 @@
         <v>13.5</v>
       </c>
       <c r="I105" s="2">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="J105">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         <v>4.8</v>
       </c>
       <c r="I108" s="2">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -4707,7 +4707,7 @@
         <v>36</v>
       </c>
       <c r="I113" s="2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>21.8</v>
       </c>
       <c r="I117" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>6</v>
       </c>
       <c r="I129" s="2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>14.8</v>
       </c>
       <c r="I132" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>8.1</v>
       </c>
       <c r="I138" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -5946,7 +5946,7 @@
         <v>20.2</v>
       </c>
       <c r="I149" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J149">
         <v>1</v>
@@ -6083,7 +6083,7 @@
         <v>13.4</v>
       </c>
       <c r="I153" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="I158" s="2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -6427,7 +6427,7 @@
         <v>11.9</v>
       </c>
       <c r="I163" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -6485,13 +6485,13 @@
         <v>34</v>
       </c>
       <c r="E165">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F165">
         <v>7</v>
       </c>
       <c r="G165" s="1">
-        <v>73.5</v>
+        <v>76.5</v>
       </c>
       <c r="H165" s="1">
         <v>20.6</v>
@@ -6500,10 +6500,10 @@
         <v>6.9</v>
       </c>
       <c r="J165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -6587,25 +6587,25 @@
         <v>114</v>
       </c>
       <c r="E168">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F168">
         <v>22</v>
       </c>
       <c r="G168" s="1">
-        <v>78.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H168" s="1">
         <v>19.3</v>
       </c>
       <c r="I168" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6841,7 +6841,7 @@
         <v>10</v>
       </c>
       <c r="I175" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -6969,25 +6969,25 @@
         <v>33</v>
       </c>
       <c r="E179">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F179">
         <v>1</v>
       </c>
       <c r="G179" s="1">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="H179" s="1">
         <v>3</v>
       </c>
       <c r="I179" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7106,25 +7106,25 @@
         <v>226</v>
       </c>
       <c r="E183">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F183">
         <v>32</v>
       </c>
       <c r="G183" s="1">
-        <v>85.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="H183" s="1">
         <v>14.2</v>
       </c>
       <c r="I183" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7360,7 +7360,7 @@
         <v>34.1</v>
       </c>
       <c r="I190" s="2">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>11.2</v>
       </c>
       <c r="I195" s="2">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>21.1</v>
       </c>
       <c r="I199" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J199">
         <v>2</v>
@@ -7876,7 +7876,7 @@
         <v>13</v>
       </c>
       <c r="I205" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -8048,7 +8048,7 @@
         <v>15.1</v>
       </c>
       <c r="I210" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J210">
         <v>0</v>
@@ -8290,7 +8290,7 @@
         <v>6</v>
       </c>
       <c r="I217" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="I219" s="2">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J219">
         <v>0</v>
@@ -8424,7 +8424,7 @@
         <v>6.1</v>
       </c>
       <c r="I221" s="2">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J221">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>24.7</v>
       </c>
       <c r="I225" s="2">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J225">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.6</v>
       </c>
       <c r="I228" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -8800,7 +8800,7 @@
         <v>14.3</v>
       </c>
       <c r="I232" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         <v>8.1</v>
       </c>
       <c r="I237" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J237">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>18</v>
       </c>
       <c r="I244" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -9421,7 +9421,7 @@
         <v>53.3</v>
       </c>
       <c r="I250" s="2">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="J250">
         <v>1</v>
@@ -9558,7 +9558,7 @@
         <v>35.9</v>
       </c>
       <c r="I254" s="2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -9989,7 +9989,7 @@
         <v>14.7</v>
       </c>
       <c r="I6" s="2">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -10231,7 +10231,7 @@
         <v>23.2</v>
       </c>
       <c r="I13" s="2">
-        <v>3.5</v>
+        <v>7.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -10333,7 +10333,7 @@
         <v>21.4</v>
       </c>
       <c r="I16" s="2">
-        <v>3.5</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -10505,7 +10505,7 @@
         <v>13.1</v>
       </c>
       <c r="I21" s="2">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -10528,25 +10528,25 @@
         <v>34</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H22" s="1">
-        <v>97.09999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -10563,25 +10563,25 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H23" s="1">
-        <v>96.7</v>
+        <v>16.7</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -10598,25 +10598,25 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -10633,25 +10633,25 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -10665,25 +10665,25 @@
         <v>131</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F26">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="H26" s="1">
-        <v>98.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26" s="2">
-        <v>3.5</v>
+        <v>7.9</v>
       </c>
       <c r="J26">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -10744,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -10881,7 +10881,7 @@
         <v>100</v>
       </c>
       <c r="I32" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>114</v>
@@ -10904,25 +10904,25 @@
         <v>31</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F33">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>38.7</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -10939,25 +10939,25 @@
         <v>41</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>73.2</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>26.8</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -10974,25 +10974,25 @@
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>23.3</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -11009,25 +11009,25 @@
         <v>33</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F36">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="H36" s="1">
-        <v>97</v>
+        <v>21.2</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J36">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -11044,25 +11044,25 @@
         <v>33</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>18.2</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J37">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -11076,25 +11076,25 @@
         <v>168</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F38">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>99.40000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="I38" s="2">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J38">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -11111,25 +11111,25 @@
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F39">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -11146,25 +11146,25 @@
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J40">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -11178,25 +11178,25 @@
         <v>60</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F41">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J41">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -11327,7 +11327,7 @@
         <v>21.3</v>
       </c>
       <c r="I45" s="2">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -11385,25 +11385,25 @@
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F47">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="H47" s="1">
-        <v>96.7</v>
+        <v>53.3</v>
       </c>
       <c r="I47" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J47">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -11455,25 +11455,25 @@
         <v>17</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H49" s="1">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J49">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -11490,25 +11490,25 @@
         <v>19</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H50" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J50">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -11522,25 +11522,25 @@
         <v>119</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F51">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="H51" s="1">
-        <v>99.2</v>
+        <v>65.5</v>
       </c>
       <c r="I51" s="2">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J51">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -11776,7 +11776,7 @@
         <v>52.6</v>
       </c>
       <c r="I58" s="2">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -11799,25 +11799,25 @@
         <v>42</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F59">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H59" s="1">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I59" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J59">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -11834,25 +11834,25 @@
         <v>26</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F60">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H60" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I60" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J60">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -11866,25 +11866,25 @@
         <v>68</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F61">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H61" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="J61">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -11971,25 +11971,25 @@
         <v>33</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F64">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="H64" s="1">
-        <v>97</v>
+        <v>54.5</v>
       </c>
       <c r="I64" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J64">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -12041,25 +12041,25 @@
         <v>33</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F66">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="H66" s="1">
-        <v>97</v>
+        <v>24.2</v>
       </c>
       <c r="I66" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J66">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -12073,25 +12073,25 @@
         <v>166</v>
       </c>
       <c r="E67">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="F67">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="G67" s="1">
-        <v>48.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>50.6</v>
+        <v>27.7</v>
       </c>
       <c r="I67" s="2">
-        <v>3.5</v>
+        <v>7.3</v>
       </c>
       <c r="J67">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>39.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -12108,25 +12108,25 @@
         <v>34</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F68">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H68" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I68" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J68">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -12178,25 +12178,25 @@
         <v>43</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F70">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H70" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I70" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J70">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -12213,25 +12213,25 @@
         <v>39</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F71">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H71" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I71" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J71">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -12248,25 +12248,25 @@
         <v>40</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F72">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H72" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I72" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J72">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -12283,25 +12283,25 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F73">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H73" s="1">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="I73" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J73">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -12318,25 +12318,25 @@
         <v>42</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F74">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H74" s="1">
-        <v>100</v>
+        <v>21.4</v>
       </c>
       <c r="I74" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J74">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -12350,25 +12350,25 @@
         <v>278</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="F75">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>72.3</v>
       </c>
       <c r="H75" s="1">
-        <v>100</v>
+        <v>27.7</v>
       </c>
       <c r="I75" s="2">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J75">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -12534,7 +12534,7 @@
         <v>38.3</v>
       </c>
       <c r="I80" s="2">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -12557,25 +12557,25 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F81">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H81" s="1">
-        <v>97.09999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="I81" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J81">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -12592,25 +12592,25 @@
         <v>30</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F82">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H82" s="1">
-        <v>96.7</v>
+        <v>20</v>
       </c>
       <c r="I82" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J82">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -12624,25 +12624,25 @@
         <v>64</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F83">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>79.7</v>
       </c>
       <c r="H83" s="1">
-        <v>96.90000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="I83" s="2">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J83">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -12659,25 +12659,25 @@
         <v>37</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F84">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="H84" s="1">
-        <v>100</v>
+        <v>40.5</v>
       </c>
       <c r="I84" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J84">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -12694,25 +12694,25 @@
         <v>31</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F85">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="H85" s="1">
-        <v>100</v>
+        <v>64.5</v>
       </c>
       <c r="I85" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J85">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -12901,25 +12901,25 @@
         <v>247</v>
       </c>
       <c r="E91">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F91">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="G91" s="1">
-        <v>44.9</v>
+        <v>58.3</v>
       </c>
       <c r="H91" s="1">
-        <v>55.1</v>
+        <v>41.7</v>
       </c>
       <c r="I91" s="2">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="J91">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -13155,7 +13155,7 @@
         <v>94.5</v>
       </c>
       <c r="I98" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J98">
         <v>163</v>
@@ -13178,25 +13178,25 @@
         <v>39</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F99">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H99" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I99" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J99">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -13213,25 +13213,25 @@
         <v>41</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F100">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H100" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="I100" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J100">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -13248,25 +13248,25 @@
         <v>38</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F101">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H101" s="1">
-        <v>100</v>
+        <v>18.4</v>
       </c>
       <c r="I101" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J101">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -13283,25 +13283,25 @@
         <v>28</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F102">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>60.7</v>
       </c>
       <c r="H102" s="1">
-        <v>100</v>
+        <v>39.3</v>
       </c>
       <c r="I102" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J102">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -13385,25 +13385,25 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F105">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H105" s="1">
-        <v>99.5</v>
+        <v>48.6</v>
       </c>
       <c r="I105" s="2">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J105">
-        <v>208</v>
+        <v>62</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -13499,7 +13499,7 @@
         <v>100</v>
       </c>
       <c r="I108" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J108">
         <v>62</v>
@@ -13522,25 +13522,25 @@
         <v>34</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F109">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H109" s="1">
-        <v>100</v>
+        <v>26.5</v>
       </c>
       <c r="I109" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J109">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -13557,25 +13557,25 @@
         <v>42</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F110">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G110" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H110" s="1">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I110" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J110">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -13592,25 +13592,25 @@
         <v>30</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F111">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H111" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I111" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J111">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -13627,25 +13627,25 @@
         <v>19</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F112">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H112" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I112" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J112">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -13659,25 +13659,25 @@
         <v>125</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F113">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="G113" s="1">
-        <v>0</v>
+        <v>68.8</v>
       </c>
       <c r="H113" s="1">
-        <v>100</v>
+        <v>31.2</v>
       </c>
       <c r="I113" s="2">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J113">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K113" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -13808,7 +13808,7 @@
         <v>24.1</v>
       </c>
       <c r="I117" s="2">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -13901,25 +13901,25 @@
         <v>36</v>
       </c>
       <c r="E120">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I120" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -13971,25 +13971,25 @@
         <v>21</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F122">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G122" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H122" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I122" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J122">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -14038,25 +14038,25 @@
         <v>180</v>
       </c>
       <c r="E124">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F124">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G124" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H124" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I124" s="2">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J124">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="K124" s="1">
-        <v>47.8</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -14073,25 +14073,25 @@
         <v>42</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F125">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G125" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H125" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I125" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J125">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -14108,25 +14108,25 @@
         <v>34</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F126">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G126" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H126" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I126" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J126">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -14143,25 +14143,25 @@
         <v>32</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F127">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G127" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H127" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I127" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J127">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -14178,25 +14178,25 @@
         <v>26</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F128">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H128" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I128" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J128">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -14210,25 +14210,25 @@
         <v>134</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F129">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H129" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I129" s="2">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J129">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -14324,7 +14324,7 @@
         <v>18</v>
       </c>
       <c r="I132" s="2">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -14531,7 +14531,7 @@
         <v>4.8</v>
       </c>
       <c r="I138" s="2">
-        <v>3.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -14773,7 +14773,7 @@
         <v>100</v>
       </c>
       <c r="I145" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J145">
         <v>177</v>
@@ -14910,7 +14910,7 @@
         <v>99</v>
       </c>
       <c r="I149" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J149">
         <v>104</v>
@@ -15047,7 +15047,7 @@
         <v>13.4</v>
       </c>
       <c r="I153" s="2">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -15140,25 +15140,25 @@
         <v>30</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F156">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I156" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J156">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -15175,25 +15175,25 @@
         <v>30</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F157">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J157">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -15207,25 +15207,25 @@
         <v>132</v>
       </c>
       <c r="E158">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F158">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G158" s="1">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="H158" s="1">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="I158" s="2">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J158">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -15242,25 +15242,25 @@
         <v>43</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F159">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G159" s="1">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="H159" s="1">
-        <v>100</v>
+        <v>2.3</v>
       </c>
       <c r="I159" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J159">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -15312,25 +15312,25 @@
         <v>40</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F161">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G161" s="1">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="H161" s="1">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="I161" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J161">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -15347,25 +15347,25 @@
         <v>37</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F162">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G162" s="1">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="H162" s="1">
-        <v>100</v>
+        <v>10.8</v>
       </c>
       <c r="I162" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J162">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -15379,25 +15379,25 @@
         <v>159</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F163">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="G163" s="1">
-        <v>0</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H163" s="1">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="I163" s="2">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J163">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -15414,25 +15414,25 @@
         <v>41</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F164">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G164" s="1">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H164" s="1">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="I164" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J164">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -15449,25 +15449,25 @@
         <v>34</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F165">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G165" s="1">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H165" s="1">
-        <v>94.09999999999999</v>
+        <v>29.4</v>
       </c>
       <c r="I165" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J165">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -15484,25 +15484,25 @@
         <v>25</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F166">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G166" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H166" s="1">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="I166" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J166">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -15519,25 +15519,25 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F167">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G167" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H167" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I167" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J167">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -15551,25 +15551,25 @@
         <v>114</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F168">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="G168" s="1">
-        <v>0</v>
+        <v>77.2</v>
       </c>
       <c r="H168" s="1">
-        <v>97.40000000000001</v>
+        <v>21.1</v>
       </c>
       <c r="I168" s="2">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J168">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -15805,7 +15805,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I175" s="2">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -15828,25 +15828,25 @@
         <v>39</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F176">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I176" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J176">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -15933,25 +15933,25 @@
         <v>33</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F179">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G179" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H179" s="1">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="I179" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J179">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -16070,25 +16070,25 @@
         <v>226</v>
       </c>
       <c r="E183">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="F183">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="G183" s="1">
-        <v>42.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H183" s="1">
-        <v>56.6</v>
+        <v>26.1</v>
       </c>
       <c r="I183" s="2">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J183">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="K183" s="1">
-        <v>50.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -16324,7 +16324,7 @@
         <v>45.7</v>
       </c>
       <c r="I190" s="2">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -16496,7 +16496,7 @@
         <v>9.6</v>
       </c>
       <c r="I195" s="2">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -16633,7 +16633,7 @@
         <v>98.2</v>
       </c>
       <c r="I199" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J199">
         <v>114</v>
@@ -16840,7 +16840,7 @@
         <v>13</v>
       </c>
       <c r="I205" s="2">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -17012,7 +17012,7 @@
         <v>100</v>
       </c>
       <c r="I210" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J210">
         <v>159</v>
@@ -17035,25 +17035,25 @@
         <v>34</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F211">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G211" s="1">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="H211" s="1">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I211" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J211">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K211" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -17070,25 +17070,25 @@
         <v>43</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F212">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G212" s="1">
-        <v>0</v>
+        <v>95.3</v>
       </c>
       <c r="H212" s="1">
-        <v>100</v>
+        <v>4.7</v>
       </c>
       <c r="I212" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J212">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K212" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -17105,25 +17105,25 @@
         <v>39</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F213">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G213" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H213" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I213" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J213">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K213" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -17140,25 +17140,25 @@
         <v>40</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F214">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G214" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H214" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I214" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J214">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K214" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -17175,25 +17175,25 @@
         <v>37</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F215">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G215" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H215" s="1">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="I215" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J215">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K215" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -17210,25 +17210,25 @@
         <v>42</v>
       </c>
       <c r="E216">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F216">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G216" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H216" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I216" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J216">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K216" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -17242,25 +17242,25 @@
         <v>235</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="F217">
-        <v>235</v>
+        <v>29</v>
       </c>
       <c r="G217" s="1">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="H217" s="1">
-        <v>100</v>
+        <v>12.3</v>
       </c>
       <c r="I217" s="2">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="J217">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="K217" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -17321,7 +17321,7 @@
         <v>0</v>
       </c>
       <c r="I219" s="2">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J219">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>100</v>
       </c>
       <c r="I221" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J221">
         <v>33</v>
@@ -17525,7 +17525,7 @@
         <v>29.9</v>
       </c>
       <c r="I225" s="2">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="J225">
         <v>0</v>
@@ -17627,7 +17627,7 @@
         <v>14.3</v>
       </c>
       <c r="I228" s="2">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -17764,7 +17764,7 @@
         <v>17.6</v>
       </c>
       <c r="I232" s="2">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -17787,25 +17787,25 @@
         <v>41</v>
       </c>
       <c r="E233">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F233">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G233" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H233" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I233" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J233">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K233" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -17822,25 +17822,25 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F234">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G234" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H234" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
       <c r="I234" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J234">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K234" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -17857,25 +17857,25 @@
         <v>41</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F235">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G235" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H235" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I235" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J235">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K235" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -17892,25 +17892,25 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F236">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G236" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H236" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I236" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J236">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K236" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -17924,25 +17924,25 @@
         <v>123</v>
       </c>
       <c r="E237">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F237">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="G237" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H237" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I237" s="2">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J237">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K237" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -18178,7 +18178,7 @@
         <v>100</v>
       </c>
       <c r="I244" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J244">
         <v>172</v>
@@ -18385,7 +18385,7 @@
         <v>98.7</v>
       </c>
       <c r="I250" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J250">
         <v>152</v>
@@ -18522,7 +18522,7 @@
         <v>54.4</v>
       </c>
       <c r="I254" s="2">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J254">
         <v>33</v>
@@ -18729,7 +18729,7 @@
         <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -18953,7 +18953,7 @@
         <v>14.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
         <v>75</v>
@@ -19195,7 +19195,7 @@
         <v>23.2</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>207</v>
@@ -19297,7 +19297,7 @@
         <v>21.4</v>
       </c>
       <c r="I16" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>70</v>
@@ -19469,7 +19469,7 @@
         <v>13.1</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
         <v>168</v>
@@ -19495,16 +19495,16 @@
         <v>30</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
         <v>88.2</v>
       </c>
       <c r="H22" s="1">
-        <v>8.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="I22" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
         <v>34</v>
@@ -19527,19 +19527,19 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="H23" s="1">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="I23" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
         <v>30</v>
@@ -19562,16 +19562,16 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
         <v>9.1</v>
@@ -19609,7 +19609,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I25" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J25">
         <v>31</v>
@@ -19632,16 +19632,16 @@
         <v>119</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="1">
         <v>90.8</v>
       </c>
       <c r="H26" s="1">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="J26">
         <v>131</v>
@@ -19708,7 +19708,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="J28">
         <v>19</v>
@@ -19845,7 +19845,7 @@
         <v>3.5</v>
       </c>
       <c r="I32" s="2">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J32">
         <v>114</v>
@@ -19868,19 +19868,19 @@
         <v>31</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1">
-        <v>64.5</v>
+        <v>61.3</v>
       </c>
       <c r="H33" s="1">
-        <v>35.5</v>
+        <v>38.7</v>
       </c>
       <c r="I33" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
         <v>31</v>
@@ -19903,19 +19903,19 @@
         <v>41</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1">
-        <v>53.7</v>
+        <v>73.2</v>
       </c>
       <c r="H34" s="1">
-        <v>46.3</v>
+        <v>26.8</v>
       </c>
       <c r="I34" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J34">
         <v>41</v>
@@ -19938,19 +19938,19 @@
         <v>30</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>83.3</v>
+        <v>76.7</v>
       </c>
       <c r="H35" s="1">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="I35" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <v>30</v>
@@ -19973,16 +19973,16 @@
         <v>33</v>
       </c>
       <c r="E36">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G36" s="1">
-        <v>84.8</v>
+        <v>78.8</v>
       </c>
       <c r="H36" s="1">
-        <v>12.1</v>
+        <v>21.2</v>
       </c>
       <c r="I36" s="2">
         <v>7.6</v>
@@ -20008,19 +20008,19 @@
         <v>33</v>
       </c>
       <c r="E37">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G37" s="1">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H37" s="1">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
       <c r="I37" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
         <v>33</v>
@@ -20043,16 +20043,16 @@
         <v>125</v>
       </c>
       <c r="F38">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G38" s="1">
         <v>74.40000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="I38" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J38">
         <v>168</v>
@@ -20087,7 +20087,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J39">
         <v>30</v>
@@ -20122,7 +20122,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J40">
         <v>30</v>
@@ -20154,7 +20154,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J41">
         <v>60</v>
@@ -20291,7 +20291,7 @@
         <v>21.3</v>
       </c>
       <c r="I45" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J45">
         <v>94</v>
@@ -20349,19 +20349,19 @@
         <v>30</v>
       </c>
       <c r="E47">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G47" s="1">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="H47" s="1">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="I47" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J47">
         <v>30</v>
@@ -20419,19 +20419,19 @@
         <v>17</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H49" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I49" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J49">
         <v>17</v>
@@ -20454,19 +20454,19 @@
         <v>19</v>
       </c>
       <c r="E50">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" s="1">
-        <v>89.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H50" s="1">
-        <v>10.5</v>
+        <v>21.1</v>
       </c>
       <c r="I50" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J50">
         <v>19</v>
@@ -20486,19 +20486,19 @@
         <v>119</v>
       </c>
       <c r="E51">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F51">
         <v>33</v>
       </c>
       <c r="G51" s="1">
-        <v>71.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="H51" s="1">
         <v>27.7</v>
       </c>
       <c r="I51" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J51">
         <v>119</v>
@@ -20740,7 +20740,7 @@
         <v>52.6</v>
       </c>
       <c r="I58" s="2">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="J58">
         <v>135</v>
@@ -20763,19 +20763,19 @@
         <v>42</v>
       </c>
       <c r="E59">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>13</v>
+      </c>
+      <c r="G59" s="1">
+        <v>69</v>
+      </c>
+      <c r="H59" s="1">
         <v>31</v>
       </c>
-      <c r="F59">
-        <v>11</v>
-      </c>
-      <c r="G59" s="1">
-        <v>73.8</v>
-      </c>
-      <c r="H59" s="1">
-        <v>26.2</v>
-      </c>
       <c r="I59" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J59">
         <v>42</v>
@@ -20798,19 +20798,19 @@
         <v>26</v>
       </c>
       <c r="E60">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G60" s="1">
-        <v>76.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H60" s="1">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="I60" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J60">
         <v>26</v>
@@ -20842,7 +20842,7 @@
         <v>25</v>
       </c>
       <c r="I61" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J61">
         <v>68</v>
@@ -20935,19 +20935,19 @@
         <v>33</v>
       </c>
       <c r="E64">
+        <v>14</v>
+      </c>
+      <c r="F64">
         <v>19</v>
       </c>
-      <c r="F64">
-        <v>14</v>
-      </c>
       <c r="G64" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="H64" s="1">
         <v>57.6</v>
       </c>
-      <c r="H64" s="1">
-        <v>42.4</v>
-      </c>
       <c r="I64" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J64">
         <v>33</v>
@@ -21037,19 +21037,19 @@
         <v>166</v>
       </c>
       <c r="E67">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F67">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G67" s="1">
-        <v>74.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H67" s="1">
-        <v>25.9</v>
+        <v>28.9</v>
       </c>
       <c r="I67" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J67">
         <v>166</v>
@@ -21084,7 +21084,7 @@
         <v>5.9</v>
       </c>
       <c r="I68" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J68">
         <v>34</v>
@@ -21142,19 +21142,19 @@
         <v>43</v>
       </c>
       <c r="E70">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" s="1">
-        <v>90.7</v>
+        <v>93</v>
       </c>
       <c r="H70" s="1">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I70" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J70">
         <v>43</v>
@@ -21177,19 +21177,19 @@
         <v>39</v>
       </c>
       <c r="E71">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G71" s="1">
-        <v>87.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H71" s="1">
-        <v>12.8</v>
+        <v>17.9</v>
       </c>
       <c r="I71" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J71">
         <v>39</v>
@@ -21212,19 +21212,19 @@
         <v>40</v>
       </c>
       <c r="E72">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G72" s="1">
-        <v>87.5</v>
+        <v>80</v>
       </c>
       <c r="H72" s="1">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I72" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J72">
         <v>40</v>
@@ -21247,19 +21247,19 @@
         <v>37</v>
       </c>
       <c r="E73">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G73" s="1">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="H73" s="1">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="I73" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J73">
         <v>37</v>
@@ -21282,19 +21282,19 @@
         <v>42</v>
       </c>
       <c r="E74">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F74">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G74" s="1">
-        <v>83.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H74" s="1">
-        <v>16.7</v>
+        <v>21.4</v>
       </c>
       <c r="I74" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J74">
         <v>42</v>
@@ -21314,19 +21314,19 @@
         <v>278</v>
       </c>
       <c r="E75">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F75">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G75" s="1">
-        <v>89.2</v>
+        <v>86.7</v>
       </c>
       <c r="H75" s="1">
-        <v>10.8</v>
+        <v>13.3</v>
       </c>
       <c r="I75" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J75">
         <v>278</v>
@@ -21498,7 +21498,7 @@
         <v>38.3</v>
       </c>
       <c r="I80" s="2">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="J80">
         <v>94</v>
@@ -21521,19 +21521,19 @@
         <v>34</v>
       </c>
       <c r="E81">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F81">
         <v>7</v>
       </c>
       <c r="G81" s="1">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H81" s="1">
         <v>20.6</v>
       </c>
       <c r="I81" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J81">
         <v>34</v>
@@ -21559,16 +21559,16 @@
         <v>24</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G82" s="1">
         <v>80</v>
       </c>
       <c r="H82" s="1">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="I82" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J82">
         <v>30</v>
@@ -21588,19 +21588,19 @@
         <v>64</v>
       </c>
       <c r="E83">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F83">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G83" s="1">
-        <v>78.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="H83" s="1">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
       <c r="I83" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J83">
         <v>64</v>
@@ -21623,19 +21623,19 @@
         <v>37</v>
       </c>
       <c r="E84">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F84">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G84" s="1">
-        <v>62.2</v>
+        <v>59.5</v>
       </c>
       <c r="H84" s="1">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
       <c r="I84" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J84">
         <v>37</v>
@@ -21658,19 +21658,19 @@
         <v>31</v>
       </c>
       <c r="E85">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F85">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G85" s="1">
-        <v>48.4</v>
+        <v>35.5</v>
       </c>
       <c r="H85" s="1">
-        <v>51.6</v>
+        <v>64.5</v>
       </c>
       <c r="I85" s="2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J85">
         <v>31</v>
@@ -21865,19 +21865,19 @@
         <v>247</v>
       </c>
       <c r="E91">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F91">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G91" s="1">
-        <v>60.3</v>
+        <v>58.3</v>
       </c>
       <c r="H91" s="1">
-        <v>39.7</v>
+        <v>41.7</v>
       </c>
       <c r="I91" s="2">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="J91">
         <v>247</v>
@@ -22119,7 +22119,7 @@
         <v>18.4</v>
       </c>
       <c r="I98" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J98">
         <v>163</v>
@@ -22142,16 +22142,16 @@
         <v>39</v>
       </c>
       <c r="E99">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F99">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G99" s="1">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="H99" s="1">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
       <c r="I99" s="2">
         <v>6.5</v>
@@ -22177,19 +22177,19 @@
         <v>41</v>
       </c>
       <c r="E100">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G100" s="1">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="H100" s="1">
-        <v>9.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="I100" s="2">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="J100">
         <v>41</v>
@@ -22224,7 +22224,7 @@
         <v>18.4</v>
       </c>
       <c r="I101" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J101">
         <v>38</v>
@@ -22247,19 +22247,19 @@
         <v>28</v>
       </c>
       <c r="E102">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F102">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G102" s="1">
-        <v>78.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="H102" s="1">
-        <v>21.4</v>
+        <v>39.3</v>
       </c>
       <c r="I102" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J102">
         <v>28</v>
@@ -22349,19 +22349,19 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F105">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G105" s="1">
-        <v>86.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="H105" s="1">
-        <v>13.5</v>
+        <v>19.7</v>
       </c>
       <c r="I105" s="2">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="J105">
         <v>208</v>
@@ -22463,7 +22463,7 @@
         <v>4.8</v>
       </c>
       <c r="I108" s="2">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J108">
         <v>62</v>
@@ -22521,19 +22521,19 @@
         <v>42</v>
       </c>
       <c r="E110">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F110">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G110" s="1">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="H110" s="1">
-        <v>33.3</v>
+        <v>31</v>
       </c>
       <c r="I110" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J110">
         <v>42</v>
@@ -22556,19 +22556,19 @@
         <v>30</v>
       </c>
       <c r="E111">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F111">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G111" s="1">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="H111" s="1">
-        <v>73.3</v>
+        <v>50</v>
       </c>
       <c r="I111" s="2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J111">
         <v>30</v>
@@ -22591,19 +22591,19 @@
         <v>19</v>
       </c>
       <c r="E112">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G112" s="1">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="H112" s="1">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I112" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J112">
         <v>19</v>
@@ -22623,19 +22623,19 @@
         <v>125</v>
       </c>
       <c r="E113">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F113">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G113" s="1">
-        <v>64</v>
+        <v>68.8</v>
       </c>
       <c r="H113" s="1">
-        <v>36</v>
+        <v>31.2</v>
       </c>
       <c r="I113" s="2">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J113">
         <v>125</v>
@@ -22772,7 +22772,7 @@
         <v>24.1</v>
       </c>
       <c r="I117" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J117">
         <v>87</v>
@@ -22865,16 +22865,16 @@
         <v>36</v>
       </c>
       <c r="E120">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G120" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H120" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I120" s="2">
         <v>8.6</v>
@@ -22935,16 +22935,16 @@
         <v>21</v>
       </c>
       <c r="E122">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G122" s="1">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H122" s="1">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="I122" s="2">
         <v>7</v>
@@ -23002,19 +23002,19 @@
         <v>180</v>
       </c>
       <c r="E124">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F124">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G124" s="1">
-        <v>88.3</v>
+        <v>90</v>
       </c>
       <c r="H124" s="1">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="I124" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J124">
         <v>180</v>
@@ -23049,7 +23049,7 @@
         <v>16.7</v>
       </c>
       <c r="I125" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J125">
         <v>42</v>
@@ -23084,7 +23084,7 @@
         <v>0</v>
       </c>
       <c r="I126" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J126">
         <v>34</v>
@@ -23119,7 +23119,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J127">
         <v>32</v>
@@ -23142,19 +23142,19 @@
         <v>26</v>
       </c>
       <c r="E128">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G128" s="1">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="H128" s="1">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="I128" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J128">
         <v>26</v>
@@ -23174,19 +23174,19 @@
         <v>134</v>
       </c>
       <c r="E129">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G129" s="1">
-        <v>94</v>
+        <v>93.3</v>
       </c>
       <c r="H129" s="1">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="I129" s="2">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J129">
         <v>134</v>
@@ -23288,7 +23288,7 @@
         <v>18</v>
       </c>
       <c r="I132" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J132">
         <v>61</v>
@@ -23495,7 +23495,7 @@
         <v>7.5</v>
       </c>
       <c r="I138" s="2">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="J138">
         <v>186</v>
@@ -23737,7 +23737,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J145">
         <v>177</v>
@@ -23874,7 +23874,7 @@
         <v>20.2</v>
       </c>
       <c r="I149" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J149">
         <v>104</v>
@@ -24011,7 +24011,7 @@
         <v>13.4</v>
       </c>
       <c r="I153" s="2">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J153">
         <v>112</v>
@@ -24116,7 +24116,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J156">
         <v>30</v>
@@ -24151,7 +24151,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J157">
         <v>30</v>
@@ -24183,7 +24183,7 @@
         <v>0</v>
       </c>
       <c r="I158" s="2">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J158">
         <v>132</v>
@@ -24206,19 +24206,19 @@
         <v>43</v>
       </c>
       <c r="E159">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F159">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G159" s="1">
-        <v>88.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="H159" s="1">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="I159" s="2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J159">
         <v>43</v>
@@ -24276,19 +24276,19 @@
         <v>40</v>
       </c>
       <c r="E161">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F161">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G161" s="1">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="H161" s="1">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="I161" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J161">
         <v>40</v>
@@ -24311,19 +24311,19 @@
         <v>37</v>
       </c>
       <c r="E162">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F162">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G162" s="1">
-        <v>83.8</v>
+        <v>89.2</v>
       </c>
       <c r="H162" s="1">
-        <v>16.2</v>
+        <v>10.8</v>
       </c>
       <c r="I162" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J162">
         <v>37</v>
@@ -24343,19 +24343,19 @@
         <v>159</v>
       </c>
       <c r="E163">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F163">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G163" s="1">
-        <v>88.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H163" s="1">
-        <v>11.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I163" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J163">
         <v>159</v>
@@ -24378,19 +24378,19 @@
         <v>41</v>
       </c>
       <c r="E164">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F164">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G164" s="1">
-        <v>90.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H164" s="1">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="I164" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J164">
         <v>41</v>
@@ -24413,19 +24413,19 @@
         <v>34</v>
       </c>
       <c r="E165">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F165">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G165" s="1">
-        <v>73.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H165" s="1">
-        <v>23.5</v>
+        <v>32.4</v>
       </c>
       <c r="I165" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J165">
         <v>34</v>
@@ -24448,19 +24448,19 @@
         <v>25</v>
       </c>
       <c r="E166">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F166">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G166" s="1">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H166" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I166" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J166">
         <v>25</v>
@@ -24495,7 +24495,7 @@
         <v>28.6</v>
       </c>
       <c r="I167" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J167">
         <v>14</v>
@@ -24515,19 +24515,19 @@
         <v>114</v>
       </c>
       <c r="E168">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F168">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G168" s="1">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="H168" s="1">
-        <v>21.1</v>
+        <v>22.8</v>
       </c>
       <c r="I168" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J168">
         <v>114</v>
@@ -24769,7 +24769,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I175" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J175">
         <v>180</v>
@@ -24792,19 +24792,19 @@
         <v>39</v>
       </c>
       <c r="E176">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H176" s="1">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="I176" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J176">
         <v>39</v>
@@ -24897,19 +24897,19 @@
         <v>33</v>
       </c>
       <c r="E179">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J179">
         <v>33</v>
@@ -25034,19 +25034,19 @@
         <v>226</v>
       </c>
       <c r="E183">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F183">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G183" s="1">
-        <v>89.8</v>
+        <v>91.2</v>
       </c>
       <c r="H183" s="1">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I183" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J183">
         <v>226</v>
@@ -25288,7 +25288,7 @@
         <v>45.7</v>
       </c>
       <c r="I190" s="2">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="J190">
         <v>138</v>
@@ -25460,7 +25460,7 @@
         <v>9.6</v>
       </c>
       <c r="I195" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J195">
         <v>125</v>
@@ -25804,7 +25804,7 @@
         <v>13</v>
       </c>
       <c r="I205" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J205">
         <v>115</v>
@@ -25976,7 +25976,7 @@
         <v>15.1</v>
       </c>
       <c r="I210" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J210">
         <v>159</v>
@@ -25999,19 +25999,19 @@
         <v>34</v>
       </c>
       <c r="E211">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F211">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G211" s="1">
-        <v>94.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="H211" s="1">
-        <v>5.9</v>
+        <v>14.7</v>
       </c>
       <c r="I211" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J211">
         <v>34</v>
@@ -26034,19 +26034,19 @@
         <v>43</v>
       </c>
       <c r="E212">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G212" s="1">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="H212" s="1">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="I212" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J212">
         <v>43</v>
@@ -26069,19 +26069,19 @@
         <v>39</v>
       </c>
       <c r="E213">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F213">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G213" s="1">
-        <v>92.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H213" s="1">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="I213" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J213">
         <v>39</v>
@@ -26104,19 +26104,19 @@
         <v>40</v>
       </c>
       <c r="E214">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F214">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G214" s="1">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="H214" s="1">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="I214" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J214">
         <v>40</v>
@@ -26139,19 +26139,19 @@
         <v>37</v>
       </c>
       <c r="E215">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F215">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G215" s="1">
-        <v>91.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="H215" s="1">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="I215" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J215">
         <v>37</v>
@@ -26174,16 +26174,16 @@
         <v>42</v>
       </c>
       <c r="E216">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F216">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G216" s="1">
-        <v>92.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H216" s="1">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="I216" s="2">
         <v>8.1</v>
@@ -26206,19 +26206,19 @@
         <v>235</v>
       </c>
       <c r="E217">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="F217">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G217" s="1">
-        <v>94</v>
+        <v>87.7</v>
       </c>
       <c r="H217" s="1">
-        <v>6</v>
+        <v>12.3</v>
       </c>
       <c r="I217" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J217">
         <v>235</v>
@@ -26285,7 +26285,7 @@
         <v>0</v>
       </c>
       <c r="I219" s="2">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J219">
         <v>17</v>
@@ -26352,7 +26352,7 @@
         <v>6.1</v>
       </c>
       <c r="I221" s="2">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="J221">
         <v>33</v>
@@ -26489,7 +26489,7 @@
         <v>29.9</v>
       </c>
       <c r="I225" s="2">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J225">
         <v>77</v>
@@ -26591,7 +26591,7 @@
         <v>14.3</v>
       </c>
       <c r="I228" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J228">
         <v>63</v>
@@ -26728,7 +26728,7 @@
         <v>17.6</v>
       </c>
       <c r="I232" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J232">
         <v>91</v>
@@ -26763,7 +26763,7 @@
         <v>0</v>
       </c>
       <c r="I233" s="2">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J233">
         <v>41</v>
@@ -26786,19 +26786,19 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G234" s="1">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H234" s="1">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="I234" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J234">
         <v>27</v>
@@ -26821,19 +26821,19 @@
         <v>41</v>
       </c>
       <c r="E235">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F235">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G235" s="1">
-        <v>95.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="H235" s="1">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I235" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J235">
         <v>41</v>
@@ -26856,19 +26856,19 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F236">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G236" s="1">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H236" s="1">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="I236" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J236">
         <v>14</v>
@@ -26888,19 +26888,19 @@
         <v>123</v>
       </c>
       <c r="E237">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F237">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G237" s="1">
-        <v>91.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H237" s="1">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I237" s="2">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J237">
         <v>123</v>
@@ -27142,7 +27142,7 @@
         <v>18</v>
       </c>
       <c r="I244" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J244">
         <v>172</v>
@@ -27349,7 +27349,7 @@
         <v>53.9</v>
       </c>
       <c r="I250" s="2">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="J250">
         <v>152</v>
@@ -27486,7 +27486,7 @@
         <v>35.9</v>
       </c>
       <c r="I254" s="2">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="J254">
         <v>103</v>
@@ -27693,7 +27693,7 @@
         <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
       <c r="J260">
         <v>174</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -4389,13 +4389,13 @@
         <v>30</v>
       </c>
       <c r="E104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="H104" s="1">
         <v>3.3</v>
@@ -4404,10 +4404,10 @@
         <v>6.1</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4421,13 +4421,13 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F105">
         <v>28</v>
       </c>
       <c r="G105" s="1">
-        <v>86.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="H105" s="1">
         <v>13.5</v>
@@ -4436,10 +4436,10 @@
         <v>6.3</v>
       </c>
       <c r="J105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -5902,13 +5902,13 @@
         <v>33</v>
       </c>
       <c r="E148">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F148">
         <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H148" s="1">
         <v>12.1</v>
@@ -5917,10 +5917,10 @@
         <v>7.3</v>
       </c>
       <c r="J148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5934,13 +5934,13 @@
         <v>104</v>
       </c>
       <c r="E149">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F149">
         <v>21</v>
       </c>
       <c r="G149" s="1">
-        <v>78.8</v>
+        <v>79.8</v>
       </c>
       <c r="H149" s="1">
         <v>20.2</v>
@@ -5949,10 +5949,10 @@
         <v>7.1</v>
       </c>
       <c r="J149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -7590,13 +7590,13 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F197">
         <v>6</v>
       </c>
       <c r="G197" s="1">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H197" s="1">
         <v>16.7</v>
@@ -7605,10 +7605,10 @@
         <v>8.1</v>
       </c>
       <c r="J197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -7625,13 +7625,13 @@
         <v>36</v>
       </c>
       <c r="E198">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F198">
         <v>5</v>
       </c>
       <c r="G198" s="1">
-        <v>83.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H198" s="1">
         <v>13.9</v>
@@ -7640,10 +7640,10 @@
         <v>7.6</v>
       </c>
       <c r="J198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -7657,13 +7657,13 @@
         <v>114</v>
       </c>
       <c r="E199">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F199">
         <v>24</v>
       </c>
       <c r="G199" s="1">
-        <v>77.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H199" s="1">
         <v>21.1</v>
@@ -7672,10 +7672,10 @@
         <v>7.5</v>
       </c>
       <c r="J199">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -9307,13 +9307,13 @@
         <v>34</v>
       </c>
       <c r="E247">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F247">
         <v>11</v>
       </c>
       <c r="G247" s="1">
-        <v>64.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H247" s="1">
         <v>32.4</v>
@@ -9322,10 +9322,10 @@
         <v>6.8</v>
       </c>
       <c r="J247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9409,13 +9409,13 @@
         <v>152</v>
       </c>
       <c r="E250">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F250">
         <v>81</v>
       </c>
       <c r="G250" s="1">
-        <v>45.4</v>
+        <v>46.1</v>
       </c>
       <c r="H250" s="1">
         <v>53.3</v>
@@ -9424,10 +9424,10 @@
         <v>5.6</v>
       </c>
       <c r="J250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -10767,25 +10767,25 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F29">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J29">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -10802,25 +10802,25 @@
         <v>38</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F30">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J30">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -10869,25 +10869,25 @@
         <v>114</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F32">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>62.3</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>37.7</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J32">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -12143,25 +12143,25 @@
         <v>43</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F69">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H69" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I69" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J69">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -12350,25 +12350,25 @@
         <v>278</v>
       </c>
       <c r="E75">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="F75">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G75" s="1">
-        <v>72.3</v>
+        <v>86.7</v>
       </c>
       <c r="H75" s="1">
-        <v>27.7</v>
+        <v>13.3</v>
       </c>
       <c r="I75" s="2">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="J75">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>15.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -13353,25 +13353,25 @@
         <v>30</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F104">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H104" s="1">
-        <v>96.7</v>
+        <v>33.3</v>
       </c>
       <c r="I104" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J104">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -13385,25 +13385,25 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F105">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="G105" s="1">
-        <v>51</v>
+        <v>60.6</v>
       </c>
       <c r="H105" s="1">
-        <v>48.6</v>
+        <v>39.4</v>
       </c>
       <c r="I105" s="2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="J105">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K105" s="1">
-        <v>29.8</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -13420,25 +13420,25 @@
         <v>34</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F106">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H106" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I106" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J106">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -13455,25 +13455,25 @@
         <v>28</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F107">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H107" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I107" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J107">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -13487,25 +13487,25 @@
         <v>62</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F108">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H108" s="1">
-        <v>100</v>
+        <v>8.1</v>
       </c>
       <c r="I108" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J108">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -13831,25 +13831,25 @@
         <v>31</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F118">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H118" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I118" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J118">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -14038,25 +14038,25 @@
         <v>180</v>
       </c>
       <c r="E124">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F124">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G124" s="1">
-        <v>60</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H124" s="1">
-        <v>40</v>
+        <v>26.1</v>
       </c>
       <c r="I124" s="2">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="J124">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K124" s="1">
-        <v>34.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -14796,25 +14796,25 @@
         <v>31</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F146">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G146" s="1">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="H146" s="1">
-        <v>100</v>
+        <v>41.9</v>
       </c>
       <c r="I146" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J146">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -14831,25 +14831,25 @@
         <v>40</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F147">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G147" s="1">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="H147" s="1">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="I147" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J147">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -14866,25 +14866,25 @@
         <v>33</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F148">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H148" s="1">
-        <v>97</v>
+        <v>12.1</v>
       </c>
       <c r="I148" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J148">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -14898,25 +14898,25 @@
         <v>104</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F149">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="G149" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H149" s="1">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="I149" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J149">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -15277,25 +15277,25 @@
         <v>39</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F160">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G160" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H160" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I160" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J160">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -15379,25 +15379,25 @@
         <v>159</v>
       </c>
       <c r="E163">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F163">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G163" s="1">
-        <v>67.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H163" s="1">
-        <v>32.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I163" s="2">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="J163">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>24.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -16519,25 +16519,25 @@
         <v>42</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F196">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G196" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H196" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I196" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J196">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -16554,25 +16554,25 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F197">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G197" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H197" s="1">
-        <v>97.2</v>
+        <v>11.1</v>
       </c>
       <c r="I197" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J197">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -16589,25 +16589,25 @@
         <v>36</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F198">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G198" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H198" s="1">
-        <v>97.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I198" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J198">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -16621,25 +16621,25 @@
         <v>114</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F199">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="G199" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H199" s="1">
-        <v>98.2</v>
+        <v>18.4</v>
       </c>
       <c r="I199" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J199">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -17994,25 +17994,25 @@
         <v>30</v>
       </c>
       <c r="E239">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F239">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G239" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H239" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I239" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J239">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K239" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -18029,25 +18029,25 @@
         <v>34</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F240">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G240" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H240" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I240" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J240">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K240" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -18099,25 +18099,25 @@
         <v>28</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F242">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G242" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H242" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I242" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J242">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K242" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -18134,25 +18134,25 @@
         <v>28</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F243">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G243" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H243" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I243" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J243">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K243" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -18166,25 +18166,25 @@
         <v>172</v>
       </c>
       <c r="E244">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F244">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G244" s="1">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="H244" s="1">
-        <v>100</v>
+        <v>39.5</v>
       </c>
       <c r="I244" s="2">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J244">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="K244" s="1">
-        <v>100</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -18201,25 +18201,25 @@
         <v>30</v>
       </c>
       <c r="E245">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F245">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G245" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H245" s="1">
-        <v>96.7</v>
+        <v>63.3</v>
       </c>
       <c r="I245" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J245">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K245" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -18236,25 +18236,25 @@
         <v>30</v>
       </c>
       <c r="E246">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F246">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G246" s="1">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="H246" s="1">
-        <v>100</v>
+        <v>63.3</v>
       </c>
       <c r="I246" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J246">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K246" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -18271,25 +18271,25 @@
         <v>34</v>
       </c>
       <c r="E247">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F247">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G247" s="1">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="H247" s="1">
-        <v>97.09999999999999</v>
+        <v>23.5</v>
       </c>
       <c r="I247" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J247">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -18306,25 +18306,25 @@
         <v>33</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F248">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G248" s="1">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="H248" s="1">
-        <v>100</v>
+        <v>36.4</v>
       </c>
       <c r="I248" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J248">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K248" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -18341,25 +18341,25 @@
         <v>25</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F249">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G249" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H249" s="1">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="I249" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J249">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K249" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -18373,25 +18373,25 @@
         <v>152</v>
       </c>
       <c r="E250">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F250">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G250" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H250" s="1">
-        <v>98.7</v>
+        <v>49.3</v>
       </c>
       <c r="I250" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J250">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="K250" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -19743,7 +19743,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J29">
         <v>40</v>
@@ -19766,16 +19766,16 @@
         <v>38</v>
       </c>
       <c r="E30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>94.7</v>
+        <v>89.5</v>
       </c>
       <c r="H30" s="1">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="I30" s="2">
         <v>9.199999999999999</v>
@@ -19833,19 +19833,19 @@
         <v>114</v>
       </c>
       <c r="E32">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32" s="1">
-        <v>96.5</v>
+        <v>94.7</v>
       </c>
       <c r="H32" s="1">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="I32" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J32">
         <v>114</v>
@@ -21119,7 +21119,7 @@
         <v>7</v>
       </c>
       <c r="I69" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J69">
         <v>43</v>
@@ -22317,19 +22317,19 @@
         <v>30</v>
       </c>
       <c r="E104">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G104" s="1">
-        <v>93.3</v>
+        <v>66.7</v>
       </c>
       <c r="H104" s="1">
-        <v>3.3</v>
+        <v>33.3</v>
       </c>
       <c r="I104" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J104">
         <v>30</v>
@@ -22349,19 +22349,19 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F105">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G105" s="1">
-        <v>79.8</v>
+        <v>76</v>
       </c>
       <c r="H105" s="1">
-        <v>19.7</v>
+        <v>24</v>
       </c>
       <c r="I105" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J105">
         <v>208</v>
@@ -22384,19 +22384,19 @@
         <v>34</v>
       </c>
       <c r="E106">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F106">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G106" s="1">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H106" s="1">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="I106" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J106">
         <v>34</v>
@@ -22431,7 +22431,7 @@
         <v>3.6</v>
       </c>
       <c r="I107" s="2">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J107">
         <v>28</v>
@@ -22451,19 +22451,19 @@
         <v>62</v>
       </c>
       <c r="E108">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G108" s="1">
-        <v>95.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H108" s="1">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="I108" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J108">
         <v>62</v>
@@ -22795,19 +22795,19 @@
         <v>31</v>
       </c>
       <c r="E118">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F118">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G118" s="1">
-        <v>74.2</v>
+        <v>93.5</v>
       </c>
       <c r="H118" s="1">
-        <v>25.8</v>
+        <v>6.5</v>
       </c>
       <c r="I118" s="2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J118">
         <v>31</v>
@@ -23002,19 +23002,19 @@
         <v>180</v>
       </c>
       <c r="E124">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F124">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G124" s="1">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="H124" s="1">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="I124" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J124">
         <v>180</v>
@@ -23760,19 +23760,19 @@
         <v>31</v>
       </c>
       <c r="E146">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F146">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G146" s="1">
-        <v>71</v>
+        <v>58.1</v>
       </c>
       <c r="H146" s="1">
-        <v>29</v>
+        <v>41.9</v>
       </c>
       <c r="I146" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J146">
         <v>31</v>
@@ -23795,19 +23795,19 @@
         <v>40</v>
       </c>
       <c r="E147">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F147">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G147" s="1">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="H147" s="1">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="I147" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J147">
         <v>40</v>
@@ -23830,19 +23830,19 @@
         <v>33</v>
       </c>
       <c r="E148">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F148">
         <v>4</v>
       </c>
       <c r="G148" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H148" s="1">
         <v>12.1</v>
       </c>
       <c r="I148" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J148">
         <v>33</v>
@@ -23862,19 +23862,19 @@
         <v>104</v>
       </c>
       <c r="E149">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F149">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G149" s="1">
-        <v>78.8</v>
+        <v>75</v>
       </c>
       <c r="H149" s="1">
-        <v>20.2</v>
+        <v>25</v>
       </c>
       <c r="I149" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J149">
         <v>104</v>
@@ -24253,7 +24253,7 @@
         <v>5.1</v>
       </c>
       <c r="I160" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J160">
         <v>39</v>
@@ -25483,16 +25483,16 @@
         <v>42</v>
       </c>
       <c r="E196">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F196">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G196" s="1">
-        <v>69</v>
+        <v>66.7</v>
       </c>
       <c r="H196" s="1">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="I196" s="2">
         <v>6.9</v>
@@ -25518,19 +25518,19 @@
         <v>36</v>
       </c>
       <c r="E197">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F197">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G197" s="1">
-        <v>80.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H197" s="1">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="I197" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J197">
         <v>36</v>
@@ -25553,19 +25553,19 @@
         <v>36</v>
       </c>
       <c r="E198">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F198">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G198" s="1">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="H198" s="1">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I198" s="2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J198">
         <v>36</v>
@@ -25585,19 +25585,19 @@
         <v>114</v>
       </c>
       <c r="E199">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F199">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G199" s="1">
-        <v>77.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H199" s="1">
-        <v>21.1</v>
+        <v>18.4</v>
       </c>
       <c r="I199" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J199">
         <v>114</v>
@@ -26958,19 +26958,19 @@
         <v>30</v>
       </c>
       <c r="E239">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F239">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G239" s="1">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="H239" s="1">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I239" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J239">
         <v>30</v>
@@ -26993,19 +26993,19 @@
         <v>34</v>
       </c>
       <c r="E240">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F240">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G240" s="1">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H240" s="1">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I240" s="2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J240">
         <v>34</v>
@@ -27098,19 +27098,19 @@
         <v>28</v>
       </c>
       <c r="E243">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F243">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G243" s="1">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H243" s="1">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I243" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J243">
         <v>28</v>
@@ -27130,19 +27130,19 @@
         <v>172</v>
       </c>
       <c r="E244">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F244">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G244" s="1">
-        <v>82</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H244" s="1">
-        <v>18</v>
+        <v>15.1</v>
       </c>
       <c r="I244" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J244">
         <v>172</v>
@@ -27165,19 +27165,19 @@
         <v>30</v>
       </c>
       <c r="E245">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F245">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G245" s="1">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="H245" s="1">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="I245" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J245">
         <v>30</v>
@@ -27212,7 +27212,7 @@
         <v>63.3</v>
       </c>
       <c r="I246" s="2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J246">
         <v>30</v>
@@ -27235,19 +27235,19 @@
         <v>34</v>
       </c>
       <c r="E247">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F247">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G247" s="1">
-        <v>64.7</v>
+        <v>76.5</v>
       </c>
       <c r="H247" s="1">
-        <v>32.4</v>
+        <v>23.5</v>
       </c>
       <c r="I247" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J247">
         <v>34</v>
@@ -27270,19 +27270,19 @@
         <v>33</v>
       </c>
       <c r="E248">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F248">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G248" s="1">
-        <v>54.5</v>
+        <v>63.6</v>
       </c>
       <c r="H248" s="1">
-        <v>45.5</v>
+        <v>36.4</v>
       </c>
       <c r="I248" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J248">
         <v>33</v>
@@ -27305,16 +27305,16 @@
         <v>25</v>
       </c>
       <c r="E249">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F249">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G249" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H249" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I249" s="2">
         <v>6.1</v>
@@ -27337,19 +27337,19 @@
         <v>152</v>
       </c>
       <c r="E250">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F250">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G250" s="1">
-        <v>45.4</v>
+        <v>50</v>
       </c>
       <c r="H250" s="1">
-        <v>53.9</v>
+        <v>50</v>
       </c>
       <c r="I250" s="2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J250">
         <v>152</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -11350,25 +11350,25 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F46">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="H46" s="1">
-        <v>100</v>
+        <v>40.7</v>
       </c>
       <c r="I46" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J46">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -11420,25 +11420,25 @@
         <v>26</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F48">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H48" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I48" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J48">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -11455,25 +11455,25 @@
         <v>17</v>
       </c>
       <c r="E49">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>70.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H49" s="1">
-        <v>29.4</v>
+        <v>5.9</v>
       </c>
       <c r="I49" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>23.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -11522,25 +11522,25 @@
         <v>119</v>
       </c>
       <c r="E51">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F51">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="G51" s="1">
-        <v>34.5</v>
+        <v>67.2</v>
       </c>
       <c r="H51" s="1">
-        <v>65.5</v>
+        <v>32.8</v>
       </c>
       <c r="I51" s="2">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J51">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>47.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -12936,25 +12936,25 @@
         <v>30</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F92">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G92" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H92" s="1">
-        <v>96.7</v>
+        <v>10</v>
       </c>
       <c r="I92" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J92">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -12971,25 +12971,25 @@
         <v>31</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F93">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G93" s="1">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="H93" s="1">
-        <v>87.09999999999999</v>
+        <v>38.7</v>
       </c>
       <c r="I93" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J93">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -13006,25 +13006,25 @@
         <v>34</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F94">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H94" s="1">
-        <v>94.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J94">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -13041,25 +13041,25 @@
         <v>25</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F95">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H95" s="1">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="I95" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J95">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -13076,25 +13076,25 @@
         <v>29</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F96">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G96" s="1">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="H96" s="1">
-        <v>96.59999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="I96" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J96">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K96" s="1">
-        <v>100</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -13111,25 +13111,25 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F97">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H97" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I97" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J97">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -13143,25 +13143,25 @@
         <v>163</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="F98">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="G98" s="1">
-        <v>0</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H98" s="1">
-        <v>94.5</v>
+        <v>20.2</v>
       </c>
       <c r="I98" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J98">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -13318,25 +13318,25 @@
         <v>32</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F103">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="H103" s="1">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="I103" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J103">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -13385,25 +13385,25 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F105">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G105" s="1">
-        <v>60.6</v>
+        <v>69.2</v>
       </c>
       <c r="H105" s="1">
-        <v>39.4</v>
+        <v>30.8</v>
       </c>
       <c r="I105" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J105">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -14554,25 +14554,25 @@
         <v>31</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F139">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H139" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J139">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -14589,25 +14589,25 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F140">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G140" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H140" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J140">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K140" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -14624,25 +14624,25 @@
         <v>41</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F141">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J141">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -14659,25 +14659,25 @@
         <v>30</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F142">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G142" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J142">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -14694,25 +14694,25 @@
         <v>20</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F143">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H143" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J143">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -14729,25 +14729,25 @@
         <v>28</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F144">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G144" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H144" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I144" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J144">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -14761,25 +14761,25 @@
         <v>177</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F145">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J145">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -15863,25 +15863,25 @@
         <v>41</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F177">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="H177" s="1">
-        <v>100</v>
+        <v>7.3</v>
       </c>
       <c r="I177" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J177">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -15910,13 +15910,13 @@
         <v>36.7</v>
       </c>
       <c r="I178" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -15933,25 +15933,25 @@
         <v>33</v>
       </c>
       <c r="E179">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
         <v>7.9</v>
       </c>
       <c r="J179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -16070,25 +16070,25 @@
         <v>226</v>
       </c>
       <c r="E183">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="F183">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G183" s="1">
-        <v>73.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H183" s="1">
-        <v>26.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I183" s="2">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="J183">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -17344,25 +17344,25 @@
         <v>33</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F220">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G220" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H220" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I220" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J220">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K220" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -17376,25 +17376,25 @@
         <v>33</v>
       </c>
       <c r="E221">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F221">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G221" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H221" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I221" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J221">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K221" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -18064,25 +18064,25 @@
         <v>20</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F241">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G241" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H241" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I241" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J241">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K241" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -18166,25 +18166,25 @@
         <v>172</v>
       </c>
       <c r="E244">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F244">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G244" s="1">
-        <v>60.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H244" s="1">
-        <v>39.5</v>
+        <v>29.1</v>
       </c>
       <c r="I244" s="2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="J244">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K244" s="1">
-        <v>30.2</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -20314,19 +20314,19 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F46">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1">
-        <v>66.7</v>
+        <v>59.3</v>
       </c>
       <c r="H46" s="1">
-        <v>33.3</v>
+        <v>40.7</v>
       </c>
       <c r="I46" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J46">
         <v>27</v>
@@ -20384,19 +20384,19 @@
         <v>26</v>
       </c>
       <c r="E48">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G48" s="1">
-        <v>88.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H48" s="1">
-        <v>11.5</v>
+        <v>26.9</v>
       </c>
       <c r="I48" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J48">
         <v>26</v>
@@ -20486,16 +20486,16 @@
         <v>119</v>
       </c>
       <c r="E51">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F51">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G51" s="1">
-        <v>72.3</v>
+        <v>67.2</v>
       </c>
       <c r="H51" s="1">
-        <v>27.7</v>
+        <v>32.8</v>
       </c>
       <c r="I51" s="2">
         <v>7</v>
@@ -21900,19 +21900,19 @@
         <v>30</v>
       </c>
       <c r="E92">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G92" s="1">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="H92" s="1">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="I92" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J92">
         <v>30</v>
@@ -21935,19 +21935,19 @@
         <v>31</v>
       </c>
       <c r="E93">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G93" s="1">
-        <v>61.3</v>
+        <v>58.1</v>
       </c>
       <c r="H93" s="1">
-        <v>38.7</v>
+        <v>41.9</v>
       </c>
       <c r="I93" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J93">
         <v>31</v>
@@ -21970,19 +21970,19 @@
         <v>34</v>
       </c>
       <c r="E94">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H94" s="1">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="I94" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J94">
         <v>34</v>
@@ -22017,7 +22017,7 @@
         <v>40</v>
       </c>
       <c r="I95" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J95">
         <v>25</v>
@@ -22040,19 +22040,19 @@
         <v>29</v>
       </c>
       <c r="E96">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" s="1">
-        <v>86.2</v>
+        <v>82.8</v>
       </c>
       <c r="H96" s="1">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="I96" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J96">
         <v>29</v>
@@ -22075,19 +22075,19 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H97" s="1">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I97" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J97">
         <v>14</v>
@@ -22107,19 +22107,19 @@
         <v>163</v>
       </c>
       <c r="E98">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F98">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G98" s="1">
-        <v>80.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="H98" s="1">
-        <v>18.4</v>
+        <v>20.2</v>
       </c>
       <c r="I98" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J98">
         <v>163</v>
@@ -22282,19 +22282,19 @@
         <v>32</v>
       </c>
       <c r="E103">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G103" s="1">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I103" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J103">
         <v>32</v>
@@ -22349,16 +22349,16 @@
         <v>208</v>
       </c>
       <c r="E105">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F105">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G105" s="1">
-        <v>76</v>
+        <v>69.2</v>
       </c>
       <c r="H105" s="1">
-        <v>24</v>
+        <v>30.8</v>
       </c>
       <c r="I105" s="2">
         <v>6.8</v>
@@ -23530,7 +23530,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J139">
         <v>31</v>
@@ -23565,7 +23565,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J140">
         <v>27</v>
@@ -23635,7 +23635,7 @@
         <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J142">
         <v>30</v>
@@ -23670,7 +23670,7 @@
         <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J143">
         <v>20</v>
@@ -23705,7 +23705,7 @@
         <v>0</v>
       </c>
       <c r="I144" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J144">
         <v>28</v>
@@ -23737,7 +23737,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J145">
         <v>177</v>
@@ -24839,7 +24839,7 @@
         <v>7.3</v>
       </c>
       <c r="I177" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J177">
         <v>41</v>
@@ -25046,7 +25046,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I183" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J183">
         <v>226</v>
@@ -26308,19 +26308,19 @@
         <v>33</v>
       </c>
       <c r="E220">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G220" s="1">
-        <v>93.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H220" s="1">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="I220" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J220">
         <v>33</v>
@@ -26340,19 +26340,19 @@
         <v>33</v>
       </c>
       <c r="E221">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F221">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G221" s="1">
-        <v>93.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H221" s="1">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="I221" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J221">
         <v>33</v>

--- a/DetalleXDocente.xlsx
+++ b/DetalleXDocente.xlsx
@@ -4042,13 +4042,13 @@
         <v>34</v>
       </c>
       <c r="E94">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F94">
         <v>2</v>
       </c>
       <c r="G94" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H94" s="1">
         <v>5.9</v>
@@ -4057,10 +4057,10 @@
         <v>7.3</v>
       </c>
       <c r="J94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -4112,13 +4112,13 @@
         <v>29</v>
       </c>
       <c r="E96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F96">
         <v>3</v>
       </c>
       <c r="G96" s="1">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="H96" s="1">
         <v>10.3</v>
@@ -4127,10 +4127,10 @@
         <v>7.7</v>
       </c>
       <c r="J96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4179,13 +4179,13 @@
         <v>163</v>
       </c>
       <c r="E98">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F98">
         <v>23</v>
       </c>
       <c r="G98" s="1">
-        <v>80.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H98" s="1">
         <v>14.1</v>
@@ -4194,10 +4194,10 @@
         <v>7.2</v>
       </c>
       <c r="J98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>1.2</v>
+        <v>0</v>
 